--- a/ensemble/eval_results/ensemble_eval_result.xlsx
+++ b/ensemble/eval_results/ensemble_eval_result.xlsx
@@ -556,31 +556,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.999</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9408</v>
+        <v>0.8421</v>
       </c>
       <c r="D4" t="n">
-        <v>0.576</v>
+        <v>0.472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9942</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.973</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6116</v>
+        <v>0.6545</v>
       </c>
       <c r="H4" t="n">
-        <v>0.759</v>
+        <v>0.7826</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8991</v>
+        <v>0.9142</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7337</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="5">
@@ -590,31 +590,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9902</v>
+        <v>0.9564</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9383</v>
+        <v>0.9258</v>
       </c>
       <c r="D5" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9956</v>
       </c>
       <c r="F5" t="n">
         <v>0.973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.766</v>
+        <v>0.7423</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8571</v>
+        <v>0.8421</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9485</v>
+        <v>0.9421</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8351</v>
+        <v>0.8185</v>
       </c>
     </row>
   </sheetData>
@@ -674,13 +674,13 @@
         <v>0.3840620868297284</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7640960812568665</v>
+        <v>0.6401544809341431</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5340186587576077</v>
+        <v>0.4927047919833665</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -694,10 +694,10 @@
         <v>0.5733754884752394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8802544474601746</v>
+        <v>0.8106477856636047</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328587358927393</v>
+        <v>0.7096565152938826</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -714,10 +714,10 @@
         <v>0.3362632856158089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8109527826309204</v>
+        <v>0.5343343019485474</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4927487596564029</v>
+        <v>0.4005425994289453</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -734,10 +734,10 @@
         <v>0.197416943404845</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006774462759494781</v>
+        <v>0.07995949685573578</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1468815421182348</v>
+        <v>0.1712765534836484</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -754,10 +754,10 @@
         <v>0.1304129038381526</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002893198048695922</v>
+        <v>0.082851842045784</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07958320084714854</v>
+        <v>0.1062360821795112</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>0.1749632749314859</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0005258172168396413</v>
+        <v>0.07148779183626175</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1003599808776636</v>
+        <v>0.1240139724174709</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -794,10 +794,10 @@
         <v>0.1620237434290886</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01377213560044765</v>
+        <v>0.1018553152680397</v>
       </c>
       <c r="E8" t="n">
-        <v>0.118635819888254</v>
+        <v>0.1479968797774513</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -814,10 +814,10 @@
         <v>0.2067114025008345</v>
       </c>
       <c r="D9" t="n">
-        <v>0.180578425526619</v>
+        <v>0.1624566614627838</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2133723871744476</v>
+        <v>0.2073317991531692</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -834,10 +834,10 @@
         <v>0.2094139514215262</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01162613462656736</v>
+        <v>0.09507719427347183</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1615994222360308</v>
+        <v>0.1894164421183323</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
         <v>0.3121416345283932</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1023872345685959</v>
+        <v>0.09311451762914658</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3315163767442385</v>
+        <v>0.3284254710977554</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -874,10 +874,10 @@
         <v>0.34482818316826</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3318856656551361</v>
+        <v>0.4074588716030121</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3814410389593247</v>
+        <v>0.4066321076086167</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -894,10 +894,10 @@
         <v>0.1363991400315087</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00314352591522038</v>
+        <v>0.07669267803430557</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09984158050578806</v>
+        <v>0.1243579645454831</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -914,10 +914,10 @@
         <v>0.1328238651082339</v>
       </c>
       <c r="D14" t="n">
-        <v>0.007772163953632116</v>
+        <v>0.08403961360454559</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08480291644856892</v>
+        <v>0.1102253996655401</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -934,10 +934,10 @@
         <v>0.1570568250298337</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002460514428094029</v>
+        <v>0.08036602288484573</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1084199503444532</v>
+        <v>0.1343884531633704</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -954,10 +954,10 @@
         <v>0.1738206865066103</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06969129294157028</v>
+        <v>0.1260222643613815</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1570215426394435</v>
+        <v>0.175798533112714</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -971,13 +971,13 @@
         <v>0.5319802357920328</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4454146041673417</v>
+        <v>0.4454146041673416</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9036062955856323</v>
+        <v>0.7301503419876099</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6270003785150023</v>
+        <v>0.5691817273156614</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -994,10 +994,10 @@
         <v>0.1063094770430837</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001144084730185568</v>
+        <v>0.07430438697338104</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0650240606499682</v>
+        <v>0.08941082806436668</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1014,10 +1014,10 @@
         <v>0.3300317782652731</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1115614771842957</v>
+        <v>0.1774915903806686</v>
       </c>
       <c r="E19" t="n">
-        <v>0.297236796597923</v>
+        <v>0.3192135009967139</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1034,10 +1034,10 @@
         <v>0.2254710742981195</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1004083156585693</v>
+        <v>0.1683749258518219</v>
       </c>
       <c r="E20" t="n">
-        <v>0.19477182348872</v>
+        <v>0.2174273602198042</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1054,10 +1054,10 @@
         <v>0.371430941548388</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5323368310928345</v>
+        <v>0.3201504349708557</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4194481960077829</v>
+        <v>0.3487193973004567</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>0.2076885775679576</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01321571506559849</v>
+        <v>0.08038441836833954</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1728727725624288</v>
+        <v>0.1952623403300092</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1094,10 +1094,10 @@
         <v>0.2466677054434032</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01177948899567127</v>
+        <v>0.08228681981563568</v>
       </c>
       <c r="E23" t="n">
-        <v>0.169118628855549</v>
+        <v>0.1926210724622038</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         <v>0.2037462076810409</v>
       </c>
       <c r="D24" t="n">
-        <v>0.003638957161456347</v>
+        <v>0.0772460550069809</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1519638535092651</v>
+        <v>0.1764995527911066</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1134,10 +1134,10 @@
         <v>0.1141275809874744</v>
       </c>
       <c r="D25" t="n">
-        <v>0.007823584601283073</v>
+        <v>0.1044724434614182</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08958607257277341</v>
+        <v>0.1218023588594851</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1151,13 +1151,13 @@
         <v>0.2503107923620951</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2108669414302068</v>
+        <v>0.2108669414302069</v>
       </c>
       <c r="D26" t="n">
-        <v>0.04197414964437485</v>
+        <v>0.09751566499471664</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1677172944788923</v>
+        <v>0.1862311329290062</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1171,13 +1171,13 @@
         <v>0.1350564249621374</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1522052698006218</v>
+        <v>0.1522052698006219</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01285972911864519</v>
+        <v>0.0811070054769516</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1000404746271348</v>
+        <v>0.1227895667465703</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1194,10 +1194,10 @@
         <v>0.434211807854486</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7813240885734558</v>
+        <v>0.6532812118530273</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5935685678042334</v>
+        <v>0.5508876088974239</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -1211,13 +1211,13 @@
         <v>0.6963319065420144</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4888966980041124</v>
+        <v>0.4888966980041123</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9840186238288879</v>
+        <v>0.8433486819267273</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7230824094583382</v>
+        <v>0.6761924288242845</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -1234,10 +1234,10 @@
         <v>0.2780810266264825</v>
       </c>
       <c r="D30" t="n">
-        <v>0.420736700296402</v>
+        <v>0.1993528604507446</v>
       </c>
       <c r="E30" t="n">
-        <v>0.422267573758011</v>
+        <v>0.3484729604761252</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1254,10 +1254,10 @@
         <v>0.2871319729310349</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3247651159763336</v>
+        <v>0.3110226988792419</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3215240768539973</v>
+        <v>0.3169432711549667</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1274,10 +1274,10 @@
         <v>0.257434799193592</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8382196426391602</v>
+        <v>0.3355513215065002</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4844387625092161</v>
+        <v>0.3168826554649961</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1294,13 +1294,13 @@
         <v>0.3253541959000909</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9380861520767212</v>
+        <v>0.4675439894199371</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5706654482145759</v>
+        <v>0.4138180606623145</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1314,10 +1314,10 @@
         <v>0.2684088577622227</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6514846682548523</v>
+        <v>0.4146960377693176</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4558502163260386</v>
+        <v>0.3769206728308603</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1331,13 +1331,13 @@
         <v>0.5733300892086813</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4028275028754816</v>
+        <v>0.4028275028754815</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9141210317611694</v>
+        <v>0.779198944568634</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6300928746151108</v>
+        <v>0.5851188455509323</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -1351,13 +1351,13 @@
         <v>0.1669542361053648</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1350934922589145</v>
+        <v>0.1350934922589146</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01555389352142811</v>
+        <v>0.09160153567790985</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1058672072952358</v>
+        <v>0.1312164213473964</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1374,10 +1374,10 @@
         <v>0.4501275090499132</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8811548352241516</v>
+        <v>0.7377341985702515</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6461294859592723</v>
+        <v>0.5983226070746389</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -1394,10 +1394,10 @@
         <v>0.3120200740474516</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08257676661014557</v>
+        <v>0.1271708011627197</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2546946220049689</v>
+        <v>0.2695593001891603</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1414,10 +1414,10 @@
         <v>0.1525936185354979</v>
       </c>
       <c r="D39" t="n">
-        <v>0.004447101149708033</v>
+        <v>0.07603143155574799</v>
       </c>
       <c r="E39" t="n">
-        <v>0.09522986285395725</v>
+        <v>0.1190913063226372</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1434,10 +1434,10 @@
         <v>0.3782246135494279</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07040233910083771</v>
+        <v>0.1030887216329575</v>
       </c>
       <c r="E40" t="n">
-        <v>0.328691001056273</v>
+        <v>0.3395864619003129</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1451,13 +1451,13 @@
         <v>0.2974227048719745</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2308411419120279</v>
+        <v>0.230841141912028</v>
       </c>
       <c r="D41" t="n">
-        <v>0.03389675170183182</v>
+        <v>0.124691866338253</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1873868661619447</v>
+        <v>0.2176519043740852</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1474,10 +1474,10 @@
         <v>0.1465028461098328</v>
       </c>
       <c r="D42" t="n">
-        <v>0.008187382481992245</v>
+        <v>0.09147782623767853</v>
       </c>
       <c r="E42" t="n">
-        <v>0.09982147837893864</v>
+        <v>0.1275849596308341</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0.1623377990685961</v>
       </c>
       <c r="D43" t="n">
-        <v>0.009114032611250877</v>
+        <v>0.08016782253980637</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1182003604718567</v>
+        <v>0.1418849571147085</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0.1315338020594521</v>
       </c>
       <c r="D44" t="n">
-        <v>0.006044634617865086</v>
+        <v>0.07677610963582993</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1223365457641972</v>
+        <v>0.1459137041035189</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1534,10 +1534,10 @@
         <v>0.2784166040675529</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3633109629154205</v>
+        <v>0.4199314117431641</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3332711356219146</v>
+        <v>0.3521446185644958</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1551,13 +1551,13 @@
         <v>0.1695897593892664</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2378057669481436</v>
+        <v>0.2378057669481435</v>
       </c>
       <c r="D46" t="n">
-        <v>0.04393613710999489</v>
+        <v>0.1347412019968033</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1504438878158016</v>
+        <v>0.1807122427780711</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1574,10 +1574,10 @@
         <v>0.2457921807875107</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0224878191947937</v>
+        <v>0.09939192235469818</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1973979085174852</v>
+        <v>0.2230326095707867</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1594,10 +1594,10 @@
         <v>0.209244585855142</v>
       </c>
       <c r="D48" t="n">
-        <v>0.001748386537656188</v>
+        <v>0.07859568297863007</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1787627323051263</v>
+        <v>0.2043784977854509</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1614,10 +1614,10 @@
         <v>0.1427439829623747</v>
       </c>
       <c r="D49" t="n">
-        <v>0.004057799465954304</v>
+        <v>0.07710108160972595</v>
       </c>
       <c r="E49" t="n">
-        <v>0.09251196876082089</v>
+        <v>0.1168597294754114</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0.1509608933820573</v>
       </c>
       <c r="D50" t="n">
-        <v>0.004881610162556171</v>
+        <v>0.08196831494569778</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1061879480775556</v>
+        <v>0.1318835163386028</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1654,10 +1654,10 @@
         <v>0.1139518175910539</v>
       </c>
       <c r="D51" t="n">
-        <v>0.007151809986680746</v>
+        <v>0.07833297550678253</v>
       </c>
       <c r="E51" t="n">
-        <v>0.085730172241961</v>
+        <v>0.1094572274153282</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1674,10 +1674,10 @@
         <v>0.3900875671990131</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4771513342857361</v>
+        <v>0.3464239239692688</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4918333224173459</v>
+        <v>0.4482575189785235</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1694,10 +1694,10 @@
         <v>0.2054801333693836</v>
       </c>
       <c r="D53" t="n">
-        <v>0.007350748870521784</v>
+        <v>0.09190525859594345</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1709866561684636</v>
+        <v>0.1991714927436041</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1714,10 +1714,10 @@
         <v>0.1484410092213372</v>
       </c>
       <c r="D54" t="n">
-        <v>0.00146501581184566</v>
+        <v>0.0754503458738327</v>
       </c>
       <c r="E54" t="n">
-        <v>0.08085988678937654</v>
+        <v>0.1055216634767056</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0.1625413550263328</v>
       </c>
       <c r="D55" t="n">
-        <v>0.01120107807219028</v>
+        <v>0.07501175254583359</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1190585271386927</v>
+        <v>0.1403287519632405</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1754,10 +1754,10 @@
         <v>0.1639039215304618</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0006005787290632725</v>
+        <v>0.07161860167980194</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1088294471002989</v>
+        <v>0.1325021214172118</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1774,10 +1774,10 @@
         <v>0.4164246332943039</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8579200506210327</v>
+        <v>0.603712260723114</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6096648286325769</v>
+        <v>0.524928898666604</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -1794,10 +1794,10 @@
         <v>0.2283001683073818</v>
       </c>
       <c r="D58" t="n">
-        <v>0.004553993232548237</v>
+        <v>0.08009590208530426</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1723573133239618</v>
+        <v>0.1975379496082138</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -1814,10 +1814,10 @@
         <v>0.1627608839275426</v>
       </c>
       <c r="D59" t="n">
-        <v>0.009782582521438599</v>
+        <v>0.09685248136520386</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1535531295203929</v>
+        <v>0.1825764291349813</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -1831,13 +1831,13 @@
         <v>0.3275477716064862</v>
       </c>
       <c r="C60" t="n">
-        <v>0.3481202592206567</v>
+        <v>0.3481202592206568</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1363774985074997</v>
+        <v>0.2289982289075851</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2706818431115475</v>
+        <v>0.301555419911576</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>0.218892973261877</v>
       </c>
       <c r="D61" t="n">
-        <v>0.09915418922901154</v>
+        <v>0.1315983235836029</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1693827619554692</v>
+        <v>0.1801974734069997</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -1874,10 +1874,10 @@
         <v>0.1169476007559232</v>
       </c>
       <c r="D62" t="n">
-        <v>0.003251437796279788</v>
+        <v>0.07247041910886765</v>
       </c>
       <c r="E62" t="n">
-        <v>0.08263000096898161</v>
+        <v>0.1057029947398442</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0.1779025379235713</v>
       </c>
       <c r="D63" t="n">
-        <v>0.04029678553342819</v>
+        <v>0.1133854761719704</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1340678832937847</v>
+        <v>0.1584307801732988</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -1914,10 +1914,10 @@
         <v>0.1582499449966986</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0005237373989075422</v>
+        <v>0.07683394104242325</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1088676338380776</v>
+        <v>0.1343043683859162</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -1934,10 +1934,10 @@
         <v>0.1125542101685188</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0005953896907158196</v>
+        <v>0.0715283527970314</v>
       </c>
       <c r="E65" t="n">
-        <v>0.07348267893056208</v>
+        <v>0.0971269999660006</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
         <v>0.1136698268734273</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0009417893597856164</v>
+        <v>0.07287000119686127</v>
       </c>
       <c r="E66" t="n">
-        <v>0.06977995846727476</v>
+        <v>0.09375602907963332</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -1974,10 +1974,10 @@
         <v>0.1649059773822238</v>
       </c>
       <c r="D67" t="n">
-        <v>0.01061465404927731</v>
+        <v>0.07812841236591339</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1265752343260632</v>
+        <v>0.1490798204316086</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -1991,13 +1991,13 @@
         <v>0.1913880645570693</v>
       </c>
       <c r="C68" t="n">
-        <v>0.192709948815574</v>
+        <v>0.1927099488155739</v>
       </c>
       <c r="D68" t="n">
-        <v>0.002247888594865799</v>
+        <v>0.07923229783773422</v>
       </c>
       <c r="E68" t="n">
-        <v>0.128781967322503</v>
+        <v>0.1544434370701258</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2014,10 +2014,10 @@
         <v>0.1937242343187526</v>
       </c>
       <c r="D69" t="n">
-        <v>0.001773500815033913</v>
+        <v>0.08510554581880569</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1580766289345469</v>
+        <v>0.1858539772691374</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0.2330012744726119</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0458260104060173</v>
+        <v>0.08363978564739227</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1598729827930194</v>
+        <v>0.1724775745401443</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0.1325738335290409</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0004237395187374204</v>
+        <v>0.07056868076324463</v>
       </c>
       <c r="E71" t="n">
-        <v>0.08612453740975523</v>
+        <v>0.1095061844912576</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2074,10 +2074,10 @@
         <v>0.1325738538236776</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0031516975723207</v>
+        <v>0.07237669080495834</v>
       </c>
       <c r="E72" t="n">
-        <v>0.09990655799196664</v>
+        <v>0.1229815557361792</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -2094,10 +2094,10 @@
         <v>0.1698225480092422</v>
       </c>
       <c r="D73" t="n">
-        <v>0.003110484685748816</v>
+        <v>0.07290973514318466</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1232117721068644</v>
+        <v>0.1464781889260097</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -2114,10 +2114,10 @@
         <v>0.11612651888992</v>
       </c>
       <c r="D74" t="n">
-        <v>0.005948095116764307</v>
+        <v>0.07825128734111786</v>
       </c>
       <c r="E74" t="n">
-        <v>0.07647048264208844</v>
+        <v>0.100571546716873</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0.2920047176097141</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4906383454799652</v>
+        <v>0.236926481127739</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3445957593881561</v>
+        <v>0.2600251379374139</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -2154,10 +2154,10 @@
         <v>0.1892112707317715</v>
       </c>
       <c r="D76" t="n">
-        <v>0.002812093123793602</v>
+        <v>0.07339709252119064</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1469525794418353</v>
+        <v>0.170480912574301</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2174,13 +2174,13 @@
         <v>0.3804437240183593</v>
       </c>
       <c r="D77" t="n">
-        <v>0.867068886756897</v>
+        <v>0.6114559173583984</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5748725173329036</v>
+        <v>0.4896681942000707</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2194,10 +2194,10 @@
         <v>0.4200548999571609</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7984994649887085</v>
+        <v>0.6630949974060059</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6020697567227876</v>
+        <v>0.55693493419522</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -2214,10 +2214,10 @@
         <v>0.1267494327787951</v>
       </c>
       <c r="D79" t="n">
-        <v>0.004208219237625599</v>
+        <v>0.07301819324493408</v>
       </c>
       <c r="E79" t="n">
-        <v>0.08323220495439067</v>
+        <v>0.1061688629568268</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2234,10 +2234,10 @@
         <v>0.1962932164738476</v>
       </c>
       <c r="D80" t="n">
-        <v>0.02054481580853462</v>
+        <v>0.08446995168924332</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1330216392586566</v>
+        <v>0.1543300178855595</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2254,10 +2254,10 @@
         <v>0.4017540561397547</v>
       </c>
       <c r="D81" t="n">
-        <v>0.814975917339325</v>
+        <v>0.6099151372909546</v>
       </c>
       <c r="E81" t="n">
-        <v>0.6166776960178392</v>
+        <v>0.5483241026683824</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -2274,10 +2274,10 @@
         <v>0.3218228931227876</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7820993661880493</v>
+        <v>0.5485585927963257</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4959170914745407</v>
+        <v>0.4180701670106328</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2294,10 +2294,10 @@
         <v>0.1751262384974091</v>
       </c>
       <c r="D83" t="n">
-        <v>0.01259609032422304</v>
+        <v>0.0818362683057785</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1375067091361521</v>
+        <v>0.1605867684633373</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2314,10 +2314,10 @@
         <v>0.1711832488943786</v>
       </c>
       <c r="D84" t="n">
-        <v>0.008708175271749496</v>
+        <v>0.08673667907714844</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1346792494249259</v>
+        <v>0.1606887506933922</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2334,10 +2334,10 @@
         <v>0.1904234827419378</v>
       </c>
       <c r="D85" t="n">
-        <v>0.04044827446341515</v>
+        <v>0.1031477600336075</v>
       </c>
       <c r="E85" t="n">
-        <v>0.1393241779309549</v>
+        <v>0.1602240064543524</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0.1708580585636477</v>
       </c>
       <c r="D86" t="n">
-        <v>0.005259337369352579</v>
+        <v>0.07838915288448334</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1166169084344269</v>
+        <v>0.1409935136061372</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2374,10 +2374,10 @@
         <v>0.1472660721205414</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0053669149056077</v>
+        <v>0.0853777751326561</v>
       </c>
       <c r="E87" t="n">
-        <v>0.09957038568125394</v>
+        <v>0.1262406724236034</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
         <v>0.3709017397346566</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4599567949771881</v>
+        <v>0.4219039082527161</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4287099199379891</v>
+        <v>0.4160256243631651</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -2414,10 +2414,10 @@
         <v>0.1301902088386244</v>
       </c>
       <c r="D89" t="n">
-        <v>0.001899786991998553</v>
+        <v>0.07515495270490646</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1381735567595633</v>
+        <v>0.1625919453305326</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -2434,10 +2434,10 @@
         <v>0.1975660188530602</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0874924436211586</v>
+        <v>0.1755018532276154</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1636641477631518</v>
+        <v>0.1930006176319707</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2454,10 +2454,10 @@
         <v>0.1889628996509349</v>
       </c>
       <c r="D91" t="n">
-        <v>0.007997198030352592</v>
+        <v>0.07644081115722656</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1470820645936405</v>
+        <v>0.1698966023025984</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -2474,10 +2474,10 @@
         <v>0.2911239373211523</v>
       </c>
       <c r="D92" t="n">
-        <v>0.02940996363759041</v>
+        <v>0.09789060056209564</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2370713801955857</v>
+        <v>0.2598982591704208</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -2491,13 +2491,13 @@
         <v>0.2472722554754759</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2474922151837859</v>
+        <v>0.2474922151837858</v>
       </c>
       <c r="D93" t="n">
-        <v>0.003771704854443669</v>
+        <v>0.07839572429656982</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1661787251712351</v>
+        <v>0.1910533983186105</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0.2555660616980943</v>
       </c>
       <c r="D94" t="n">
-        <v>0.03502223640680313</v>
+        <v>0.09299923479557037</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2140013972625015</v>
+        <v>0.2333270633920906</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -2534,10 +2534,10 @@
         <v>0.1798141515235379</v>
       </c>
       <c r="D95" t="n">
-        <v>0.012605513446033</v>
+        <v>0.09445273131132126</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1232449824363338</v>
+        <v>0.1505273883914299</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -2554,10 +2554,10 @@
         <v>0.1771546349215245</v>
       </c>
       <c r="D96" t="n">
-        <v>0.001745969406329095</v>
+        <v>0.07266898453235626</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1194223532985192</v>
+        <v>0.1430633583405283</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -2574,10 +2574,10 @@
         <v>0.1595057475653789</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0004080365470144898</v>
+        <v>0.0701524019241333</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0933049860655536</v>
+        <v>0.1165531078579265</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         <v>0.1409172694869817</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1475701462337581</v>
+        <v>0.1475701462337582</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0005163749447092414</v>
+        <v>0.07008317112922668</v>
       </c>
       <c r="E98" t="n">
-        <v>0.096334596888483</v>
+        <v>0.1195235289499888</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
         <v>0.148472505311266</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0007181570399552584</v>
+        <v>0.0710771307349205</v>
       </c>
       <c r="E99" t="n">
-        <v>0.09865232429303254</v>
+        <v>0.1221053155246876</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -2634,10 +2634,10 @@
         <v>0.255094110227886</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0194055549800396</v>
+        <v>0.07703628391027451</v>
       </c>
       <c r="E100" t="n">
-        <v>0.2064376286101077</v>
+        <v>0.2256478715868527</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0.2432298588647352</v>
       </c>
       <c r="D101" t="n">
-        <v>0.006568604614585638</v>
+        <v>0.07608881592750549</v>
       </c>
       <c r="E101" t="n">
-        <v>0.1696393878779215</v>
+        <v>0.1928127916488948</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -2674,10 +2674,10 @@
         <v>0.1456012503208176</v>
       </c>
       <c r="D102" t="n">
-        <v>0.003778595477342606</v>
+        <v>0.08946750313043594</v>
       </c>
       <c r="E102" t="n">
-        <v>0.08488381573647974</v>
+        <v>0.1134467849541775</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -2694,10 +2694,10 @@
         <v>0.1760676424483896</v>
       </c>
       <c r="D103" t="n">
-        <v>0.002059787744656205</v>
+        <v>0.07065773010253906</v>
       </c>
       <c r="E103" t="n">
-        <v>0.1369683821258147</v>
+        <v>0.1598343629117757</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -2714,10 +2714,10 @@
         <v>0.2905927271854694</v>
       </c>
       <c r="D104" t="n">
-        <v>0.03202971816062927</v>
+        <v>0.09468602389097214</v>
       </c>
       <c r="E104" t="n">
-        <v>0.251871462351294</v>
+        <v>0.2727568975947417</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -2731,13 +2731,13 @@
         <v>0.3515973281640457</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2443707586665065</v>
+        <v>0.2443707586665064</v>
       </c>
       <c r="D105" t="n">
-        <v>0.03178349509835243</v>
+        <v>0.09915785491466522</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2092505273096349</v>
+        <v>0.2317086472484058</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -2754,10 +2754,10 @@
         <v>0.2233666653368904</v>
       </c>
       <c r="D106" t="n">
-        <v>0.04076407104730606</v>
+        <v>0.09554047137498856</v>
       </c>
       <c r="E106" t="n">
-        <v>0.1840429433782573</v>
+        <v>0.2023017434874848</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -2774,10 +2774,10 @@
         <v>0.2821254175158009</v>
       </c>
       <c r="D107" t="n">
-        <v>0.01457046251744032</v>
+        <v>0.08447602391242981</v>
       </c>
       <c r="E107" t="n">
-        <v>0.2230541109216706</v>
+        <v>0.2463559647200004</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -2794,10 +2794,10 @@
         <v>0.2317550636568133</v>
       </c>
       <c r="D108" t="n">
-        <v>0.001548610860481858</v>
+        <v>0.07028724253177643</v>
       </c>
       <c r="E108" t="n">
-        <v>0.192245130814699</v>
+        <v>0.2151580080384639</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -2811,13 +2811,13 @@
         <v>0.2603288772160174</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2156516811085384</v>
+        <v>0.2156516811085383</v>
       </c>
       <c r="D109" t="n">
-        <v>0.001491953036747873</v>
+        <v>0.07045983523130417</v>
       </c>
       <c r="E109" t="n">
-        <v>0.1591575037871012</v>
+        <v>0.1821467978519533</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0.15975732027634</v>
       </c>
       <c r="D110" t="n">
-        <v>0.002451690612360835</v>
+        <v>0.07214613258838654</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1050248173873269</v>
+        <v>0.1282562980460022</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -2854,10 +2854,10 @@
         <v>0.191629637334344</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0010364621412009</v>
+        <v>0.0699920654296875</v>
       </c>
       <c r="E111" t="n">
-        <v>0.1249501539737607</v>
+        <v>0.1479353550699229</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -2874,10 +2874,10 @@
         <v>0.2034825107820868</v>
       </c>
       <c r="D112" t="n">
-        <v>0.004509586840867996</v>
+        <v>0.07369934767484665</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1456553992107709</v>
+        <v>0.1687186528220971</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -2894,10 +2894,10 @@
         <v>0.18789105618562</v>
       </c>
       <c r="D113" t="n">
-        <v>0.009890615940093994</v>
+        <v>0.07635805755853653</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1357467429333735</v>
+        <v>0.1579025568061877</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -2914,10 +2914,10 @@
         <v>0.2681175478448671</v>
       </c>
       <c r="D114" t="n">
-        <v>0.05269386619329453</v>
+        <v>0.1143877133727074</v>
       </c>
       <c r="E114" t="n">
-        <v>0.2340950480723792</v>
+        <v>0.2546596637988501</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -2931,13 +2931,13 @@
         <v>0.3215744765622564</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2423932088510731</v>
+        <v>0.2423932088510732</v>
       </c>
       <c r="D115" t="n">
-        <v>0.005007356870919466</v>
+        <v>0.07206692546606064</v>
       </c>
       <c r="E115" t="n">
-        <v>0.189658347428083</v>
+        <v>0.2120115369597967</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -2954,10 +2954,10 @@
         <v>0.2836388660180196</v>
       </c>
       <c r="D116" t="n">
-        <v>0.296814501285553</v>
+        <v>0.2965664267539978</v>
       </c>
       <c r="E116" t="n">
-        <v>0.3125171377957968</v>
+        <v>0.3124344462852783</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -2974,10 +2974,10 @@
         <v>0.1892403695594683</v>
       </c>
       <c r="D117" t="n">
-        <v>0.001467709895223379</v>
+        <v>0.07142986357212067</v>
       </c>
       <c r="E117" t="n">
-        <v>0.1429973229073222</v>
+        <v>0.1663180407996213</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -2994,10 +2994,10 @@
         <v>0.2317462925673377</v>
       </c>
       <c r="D118" t="n">
-        <v>0.07801272720098495</v>
+        <v>0.1214723587036133</v>
       </c>
       <c r="E118" t="n">
-        <v>0.1938190727238126</v>
+        <v>0.208305616558022</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -3014,10 +3014,10 @@
         <v>0.2306415165859474</v>
       </c>
       <c r="D119" t="n">
-        <v>0.03227423876523972</v>
+        <v>0.08458475768566132</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1659198593953393</v>
+        <v>0.1833566990354798</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -3034,10 +3034,10 @@
         <v>0.2004457546413801</v>
       </c>
       <c r="D120" t="n">
-        <v>0.006442068610340357</v>
+        <v>0.07241100817918777</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1317201351493017</v>
+        <v>0.1537097816722508</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -3054,10 +3054,10 @@
         <v>0.1909750892752477</v>
       </c>
       <c r="D121" t="n">
-        <v>0.0003757661033887416</v>
+        <v>0.07125640660524368</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1245098188866539</v>
+        <v>0.1481366990539389</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -3074,10 +3074,10 @@
         <v>0.2000629247124529</v>
       </c>
       <c r="D122" t="n">
-        <v>0.007078282535076141</v>
+        <v>0.07914195954799652</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1485483218642515</v>
+        <v>0.1725695475352249</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3094,10 +3094,10 @@
         <v>0.1394654242105447</v>
       </c>
       <c r="D123" t="n">
-        <v>0.001645088545046747</v>
+        <v>0.07812701910734177</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1113134488308432</v>
+        <v>0.1368074256849416</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -3114,10 +3114,10 @@
         <v>0.2359694029676137</v>
       </c>
       <c r="D124" t="n">
-        <v>0.007771477103233337</v>
+        <v>0.0963645875453949</v>
       </c>
       <c r="E124" t="n">
-        <v>0.1906369041735045</v>
+        <v>0.2201679409875584</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -3134,10 +3134,10 @@
         <v>0.179046639407559</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0005861816462129354</v>
+        <v>0.07212742418050766</v>
       </c>
       <c r="E125" t="n">
-        <v>0.1153667656716927</v>
+        <v>0.1392138465164576</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -3154,10 +3154,10 @@
         <v>0.2330861127280797</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0009962121257558465</v>
+        <v>0.07226640731096268</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1595513395262933</v>
+        <v>0.1833080712546956</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -3174,10 +3174,10 @@
         <v>0.2373465158695374</v>
       </c>
       <c r="D127" t="n">
-        <v>0.01783658191561699</v>
+        <v>0.07362531870603561</v>
       </c>
       <c r="E127" t="n">
-        <v>0.1860641448943245</v>
+        <v>0.2046603904911307</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -3194,10 +3194,10 @@
         <v>0.199092305431018</v>
       </c>
       <c r="D128" t="n">
-        <v>0.002643202198669314</v>
+        <v>0.07002798467874527</v>
       </c>
       <c r="E128" t="n">
-        <v>0.1363679779447249</v>
+        <v>0.1588295721047502</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -3214,10 +3214,10 @@
         <v>0.4485568648841595</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4378467500209808</v>
+        <v>0.2380578219890594</v>
       </c>
       <c r="E129" t="n">
-        <v>0.4731133740262144</v>
+        <v>0.4065170646822406</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -3234,10 +3234,10 @@
         <v>0.2157166560496045</v>
       </c>
       <c r="D130" t="n">
-        <v>0.002151068300008774</v>
+        <v>0.0722600594162941</v>
       </c>
       <c r="E130" t="n">
-        <v>0.1526277306502006</v>
+        <v>0.175997394355629</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -3254,10 +3254,10 @@
         <v>0.4264580341449077</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3549827039241791</v>
+        <v>0.3548914790153503</v>
       </c>
       <c r="E131" t="n">
-        <v>0.4443662164479039</v>
+        <v>0.444335808144961</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -3274,10 +3274,10 @@
         <v>0.1910253129829357</v>
       </c>
       <c r="D132" t="n">
-        <v>0.185399979352951</v>
+        <v>0.2038851678371429</v>
       </c>
       <c r="E132" t="n">
-        <v>0.1996193743019462</v>
+        <v>0.2057811037966768</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0.2115912711167978</v>
       </c>
       <c r="D133" t="n">
-        <v>7.040111995593179e-06</v>
+        <v>0.06772357225418091</v>
       </c>
       <c r="E133" t="n">
-        <v>0.147314908482984</v>
+        <v>0.1698870858637125</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0.2196491282492932</v>
       </c>
       <c r="D134" t="n">
-        <v>0.002849457086995244</v>
+        <v>0.07038605213165283</v>
       </c>
       <c r="E134" t="n">
-        <v>0.1418832926678329</v>
+        <v>0.1643954910160521</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -3331,13 +3331,13 @@
         <v>0.1738114454667323</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1590450461436954</v>
+        <v>0.1590450461436953</v>
       </c>
       <c r="D135" t="n">
-        <v>1.487391818955075e-05</v>
+        <v>0.06834141165018082</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1109571218428724</v>
+        <v>0.1337326344202028</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -3354,10 +3354,10 @@
         <v>0.2993281109743333</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1535634994506836</v>
+        <v>0.1777370274066925</v>
       </c>
       <c r="E136" t="n">
-        <v>0.2594907551228036</v>
+        <v>0.2675485977748066</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -3374,10 +3374,10 @@
         <v>0.1661793614500213</v>
       </c>
       <c r="D137" t="n">
-        <v>0.009283474646508694</v>
+        <v>0.08638016134500504</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1411012376169005</v>
+        <v>0.1668001331830659</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -3391,13 +3391,13 @@
         <v>0.1722812657161885</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1585635638678708</v>
+        <v>0.1585635638678709</v>
       </c>
       <c r="D138" t="n">
-        <v>0.006905104033648968</v>
+        <v>0.08318991959095001</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1125833112059028</v>
+        <v>0.1380115830583365</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -3414,10 +3414,10 @@
         <v>0.1543721827596509</v>
       </c>
       <c r="D139" t="n">
-        <v>0.01597924716770649</v>
+        <v>0.1151774078607559</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1172724421787777</v>
+        <v>0.1503384957431275</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -3431,13 +3431,13 @@
         <v>0.2331993948741976</v>
       </c>
       <c r="C140" t="n">
-        <v>0.167381568212546</v>
+        <v>0.1673815682125459</v>
       </c>
       <c r="D140" t="n">
-        <v>0.006950265262275934</v>
+        <v>0.07988183200359344</v>
       </c>
       <c r="E140" t="n">
-        <v>0.1358437427830065</v>
+        <v>0.1601542650301123</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -3454,10 +3454,10 @@
         <v>0.198524606922231</v>
       </c>
       <c r="D141" t="n">
-        <v>0.00706800352782011</v>
+        <v>0.08546959608793259</v>
       </c>
       <c r="E141" t="n">
-        <v>0.1453584515034554</v>
+        <v>0.1714923156901596</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -3474,10 +3474,10 @@
         <v>0.2575697482213986</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1466910094022751</v>
+        <v>0.1720794290304184</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2287966971898659</v>
+        <v>0.2372595037325803</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0.1746891479959272</v>
       </c>
       <c r="D143" t="n">
-        <v>0.2296700775623322</v>
+        <v>0.2027149945497513</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1800430939190188</v>
+        <v>0.1710580662481585</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -3514,10 +3514,10 @@
         <v>0.1449903401267535</v>
       </c>
       <c r="D144" t="n">
-        <v>0.0001892353320727125</v>
+        <v>0.06982019543647766</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1098699235358978</v>
+        <v>0.1330802435706994</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -3534,10 +3534,10 @@
         <v>0.1369719748235891</v>
       </c>
       <c r="D145" t="n">
-        <v>0.0001256874529644847</v>
+        <v>0.06998136639595032</v>
       </c>
       <c r="E145" t="n">
-        <v>0.09703671313446431</v>
+        <v>0.1203219394487929</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -3554,10 +3554,10 @@
         <v>0.1884448058691281</v>
       </c>
       <c r="D146" t="n">
-        <v>0.01101752184331417</v>
+        <v>0.0805114358663559</v>
       </c>
       <c r="E146" t="n">
-        <v>0.1360610702885261</v>
+        <v>0.1592257082962066</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -3574,10 +3574,10 @@
         <v>0.2075805812152529</v>
       </c>
       <c r="D147" t="n">
-        <v>0.006291518919169903</v>
+        <v>0.08113721013069153</v>
       </c>
       <c r="E147" t="n">
-        <v>0.1491196540836797</v>
+        <v>0.1740682178208536</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0.1335388221987244</v>
       </c>
       <c r="D148" t="n">
-        <v>0.054457176476717</v>
+        <v>0.1056578606367111</v>
       </c>
       <c r="E148" t="n">
-        <v>0.1248078682972784</v>
+        <v>0.1418747630172764</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -3614,10 +3614,10 @@
         <v>0.1735058048497894</v>
       </c>
       <c r="D149" t="n">
-        <v>0.1107948049902916</v>
+        <v>0.1599076241254807</v>
       </c>
       <c r="E149" t="n">
-        <v>0.1751757873841379</v>
+        <v>0.1915467270958676</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -3634,10 +3634,10 @@
         <v>0.1776650698259835</v>
       </c>
       <c r="D150" t="n">
-        <v>0.06342144310474396</v>
+        <v>0.101912721991539</v>
       </c>
       <c r="E150" t="n">
-        <v>0.1566910449201854</v>
+        <v>0.1695214712157837</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -3651,13 +3651,13 @@
         <v>0.3669104695542092</v>
       </c>
       <c r="C151" t="n">
-        <v>0.2249794545071618</v>
+        <v>0.2249794545071617</v>
       </c>
       <c r="D151" t="n">
-        <v>0.01228868030011654</v>
+        <v>0.08132614195346832</v>
       </c>
       <c r="E151" t="n">
-        <v>0.2013928681204958</v>
+        <v>0.2244053553382797</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -3674,10 +3674,10 @@
         <v>0.1718083442958885</v>
       </c>
       <c r="D152" t="n">
-        <v>0.002039075363427401</v>
+        <v>0.07656924426555634</v>
       </c>
       <c r="E152" t="n">
-        <v>0.1312164826822337</v>
+        <v>0.1560598723162766</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -3691,13 +3691,13 @@
         <v>0.3874402527425424</v>
       </c>
       <c r="C153" t="n">
-        <v>0.3597703716678771</v>
+        <v>0.3597703716678772</v>
       </c>
       <c r="D153" t="n">
-        <v>0.7815949320793152</v>
+        <v>0.5084904432296753</v>
       </c>
       <c r="E153" t="n">
-        <v>0.5096018521632449</v>
+        <v>0.4185670225466983</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -3714,10 +3714,10 @@
         <v>0.1691316468433855</v>
       </c>
       <c r="D154" t="n">
-        <v>0.01177742797881365</v>
+        <v>0.09823407232761383</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1197682773257368</v>
+        <v>0.1485871587753368</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -3734,10 +3734,10 @@
         <v>0.1890634753554935</v>
       </c>
       <c r="D155" t="n">
-        <v>0.007053972221910954</v>
+        <v>0.08624998480081558</v>
       </c>
       <c r="E155" t="n">
-        <v>0.1381268038566005</v>
+        <v>0.1645254747162354</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -3751,13 +3751,13 @@
         <v>0.2073956179896051</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1975913140972196</v>
+        <v>0.1975913140972195</v>
       </c>
       <c r="D156" t="n">
-        <v>0.03591520711779594</v>
+        <v>0.09612976759672165</v>
       </c>
       <c r="E156" t="n">
-        <v>0.1469673797348735</v>
+        <v>0.1670388998945155</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -3771,13 +3771,13 @@
         <v>0.138518206701358</v>
       </c>
       <c r="C157" t="n">
-        <v>0.158655479513384</v>
+        <v>0.1586554795133839</v>
       </c>
       <c r="D157" t="n">
-        <v>0.0003380635171197355</v>
+        <v>0.06914457678794861</v>
       </c>
       <c r="E157" t="n">
-        <v>0.09917058324395389</v>
+        <v>0.1221060876675635</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -3794,10 +3794,10 @@
         <v>0.2052757870355309</v>
       </c>
       <c r="D158" t="n">
-        <v>0.04785756394267082</v>
+        <v>0.08742403239011765</v>
       </c>
       <c r="E158" t="n">
-        <v>0.1436707849099163</v>
+        <v>0.1568596077257319</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -3814,10 +3814,10 @@
         <v>0.2131209901496757</v>
       </c>
       <c r="D159" t="n">
-        <v>0.07141271978616714</v>
+        <v>0.1072807535529137</v>
       </c>
       <c r="E159" t="n">
-        <v>0.1567111057710584</v>
+        <v>0.1686671170266406</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -3834,10 +3834,10 @@
         <v>0.1781868163924507</v>
       </c>
       <c r="D160" t="n">
-        <v>0.003129287157207727</v>
+        <v>0.08007387816905975</v>
       </c>
       <c r="E160" t="n">
-        <v>0.1370313824333385</v>
+        <v>0.1626795794372891</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -3851,13 +3851,13 @@
         <v>0.5776623423806377</v>
       </c>
       <c r="C161" t="n">
-        <v>0.2929229842412049</v>
+        <v>0.2929229842412048</v>
       </c>
       <c r="D161" t="n">
-        <v>0.01386689860373735</v>
+        <v>0.09072653949260712</v>
       </c>
       <c r="E161" t="n">
-        <v>0.2948174084085267</v>
+        <v>0.3204372887048166</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -3874,10 +3874,10 @@
         <v>0.1599006425528003</v>
       </c>
       <c r="D162" t="n">
-        <v>0.004289933945983648</v>
+        <v>0.08112360537052155</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1113745649053432</v>
+        <v>0.1369857887135225</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -3894,10 +3894,10 @@
         <v>0.2301300373611239</v>
       </c>
       <c r="D163" t="n">
-        <v>0.03229798004031181</v>
+        <v>0.1206997409462929</v>
       </c>
       <c r="E163" t="n">
-        <v>0.2108665260229536</v>
+        <v>0.2403337796582806</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -3914,10 +3914,10 @@
         <v>0.1687292697776077</v>
       </c>
       <c r="D164" t="n">
-        <v>0.0001946550764841959</v>
+        <v>0.07084742933511734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1223429784692885</v>
+        <v>0.1458939032221662</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0.2053471984365973</v>
       </c>
       <c r="D165" t="n">
-        <v>0.04421139135956764</v>
+        <v>0.0977192148566246</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1476269004594375</v>
+        <v>0.1654628416251231</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -3954,10 +3954,10 @@
         <v>0.1859560871239771</v>
       </c>
       <c r="D166" t="n">
-        <v>0.007877207361161709</v>
+        <v>0.08848439902067184</v>
       </c>
       <c r="E166" t="n">
-        <v>0.1470380123933714</v>
+        <v>0.1739070762798748</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -3971,13 +3971,13 @@
         <v>0.2865348751146375</v>
       </c>
       <c r="C167" t="n">
-        <v>0.2446251107431703</v>
+        <v>0.2446251107431704</v>
       </c>
       <c r="D167" t="n">
-        <v>0.06357564032077789</v>
+        <v>0.1712179332971573</v>
       </c>
       <c r="E167" t="n">
-        <v>0.1982452087261952</v>
+        <v>0.2341259730516551</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -3994,10 +3994,10 @@
         <v>0.2488826847840804</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1034052595496178</v>
+        <v>0.08652105927467346</v>
       </c>
       <c r="E168" t="n">
-        <v>0.2295231667243979</v>
+        <v>0.2238950999660831</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -4014,10 +4014,10 @@
         <v>0.291444952216988</v>
       </c>
       <c r="D169" t="n">
-        <v>0.103356696665287</v>
+        <v>0.1314288824796677</v>
       </c>
       <c r="E169" t="n">
-        <v>0.2576697402604804</v>
+        <v>0.2670271355319406</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0.2162049916127085</v>
       </c>
       <c r="D170" t="n">
-        <v>2.923235297203064e-05</v>
+        <v>0.06843748688697815</v>
       </c>
       <c r="E170" t="n">
-        <v>0.143195080330749</v>
+        <v>0.1659978318420844</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -4054,10 +4054,10 @@
         <v>0.1661486473477525</v>
       </c>
       <c r="D171" t="n">
-        <v>0.00266004609875381</v>
+        <v>0.07726748287677765</v>
       </c>
       <c r="E171" t="n">
-        <v>0.1381539526933285</v>
+        <v>0.1630230982860031</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
@@ -4074,10 +4074,10 @@
         <v>0.2457879211277599</v>
       </c>
       <c r="D172" t="n">
-        <v>0.01830104552209377</v>
+        <v>0.07579245418310165</v>
       </c>
       <c r="E172" t="n">
-        <v>0.1950492206232067</v>
+        <v>0.2142130235102093</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -4094,10 +4094,10 @@
         <v>0.1854929978226296</v>
       </c>
       <c r="D173" t="n">
-        <v>4.323240864323452e-05</v>
+        <v>0.06839931011199951</v>
       </c>
       <c r="E173" t="n">
-        <v>0.1348496482877421</v>
+        <v>0.1576350075221942</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -4114,10 +4114,10 @@
         <v>0.2572098595958555</v>
       </c>
       <c r="D174" t="n">
-        <v>0.04150685667991638</v>
+        <v>0.1128570660948753</v>
       </c>
       <c r="E174" t="n">
-        <v>0.1789027814585086</v>
+        <v>0.2026861845968283</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -4134,10 +4134,10 @@
         <v>0.2349197204200388</v>
       </c>
       <c r="D175" t="n">
-        <v>0.1647454500198364</v>
+        <v>0.2246080935001373</v>
       </c>
       <c r="E175" t="n">
-        <v>0.2381222717050407</v>
+        <v>0.2580764861984743</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0.1911935837207522</v>
       </c>
       <c r="C176" t="n">
-        <v>0.2025522931057314</v>
+        <v>0.2025522931057313</v>
       </c>
       <c r="D176" t="n">
-        <v>0.01759307458996773</v>
+        <v>0.08093564212322235</v>
       </c>
       <c r="E176" t="n">
-        <v>0.1371129838054838</v>
+        <v>0.1582271729832353</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>0.1970402185098704</v>
       </c>
       <c r="D177" t="n">
-        <v>0.0004415439907461405</v>
+        <v>0.06888270378112793</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1380118090085062</v>
+        <v>0.1608255289386334</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -4194,10 +4194,10 @@
         <v>0.2240024759412333</v>
       </c>
       <c r="D178" t="n">
-        <v>0.06734587252140045</v>
+        <v>0.08731731027364731</v>
       </c>
       <c r="E178" t="n">
-        <v>0.181827457325801</v>
+        <v>0.1884846032432166</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
@@ -4214,10 +4214,10 @@
         <v>0.2191116220077852</v>
       </c>
       <c r="D179" t="n">
-        <v>0.02196581289172173</v>
+        <v>0.1089776158332825</v>
       </c>
       <c r="E179" t="n">
-        <v>0.1662508115904843</v>
+        <v>0.1952547459043379</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
@@ -4234,10 +4234,10 @@
         <v>0.4354003290122679</v>
       </c>
       <c r="D180" t="n">
-        <v>0.9444926977157593</v>
+        <v>0.7689080238342285</v>
       </c>
       <c r="E180" t="n">
-        <v>0.6696820488141605</v>
+        <v>0.6111538241869835</v>
       </c>
       <c r="F180" t="n">
         <v>1</v>
@@ -4254,10 +4254,10 @@
         <v>0.177277556843938</v>
       </c>
       <c r="D181" t="n">
-        <v>0.003574077039957047</v>
+        <v>0.07419835031032562</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1302685016079602</v>
+        <v>0.1538099260314164</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0.1769390008680137</v>
       </c>
       <c r="D182" t="n">
-        <v>0.001586274825967848</v>
+        <v>0.07600628584623337</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1332202960685541</v>
+        <v>0.1580269664086426</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -4294,10 +4294,10 @@
         <v>0.2131808155509465</v>
       </c>
       <c r="D183" t="n">
-        <v>0.03411171585321426</v>
+        <v>0.07521801441907883</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1664334587138736</v>
+        <v>0.1801355582358285</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0.286695580837637</v>
       </c>
       <c r="D184" t="n">
-        <v>0.1384590566158295</v>
+        <v>0.1355031281709671</v>
       </c>
       <c r="E184" t="n">
-        <v>0.2351286237523725</v>
+        <v>0.2341433142707517</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
@@ -4334,10 +4334,10 @@
         <v>0.1773561806791862</v>
       </c>
       <c r="D185" t="n">
-        <v>0.004614813718944788</v>
+        <v>0.0834244042634964</v>
       </c>
       <c r="E185" t="n">
-        <v>0.1294408305185092</v>
+        <v>0.1557106940333598</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
@@ -4354,10 +4354,10 @@
         <v>0.1831151409898754</v>
       </c>
       <c r="D186" t="n">
-        <v>0.002539233071729541</v>
+        <v>0.07937627285718918</v>
       </c>
       <c r="E186" t="n">
-        <v>0.1325319970682262</v>
+        <v>0.1581443436633794</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -4374,10 +4374,10 @@
         <v>0.1760849947590262</v>
       </c>
       <c r="D187" t="n">
-        <v>0.000133631459902972</v>
+        <v>0.06846772879362106</v>
       </c>
       <c r="E187" t="n">
-        <v>0.1172434710769959</v>
+        <v>0.1400215035215686</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -4394,10 +4394,10 @@
         <v>0.1679463078283981</v>
       </c>
       <c r="D188" t="n">
-        <v>0.002849379787221551</v>
+        <v>0.07448526471853256</v>
       </c>
       <c r="E188" t="n">
-        <v>0.1237295175953165</v>
+        <v>0.1476081459057535</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
@@ -4414,10 +4414,10 @@
         <v>0.2423868672446111</v>
       </c>
       <c r="D189" t="n">
-        <v>0.1298584789037704</v>
+        <v>0.1476301848888397</v>
       </c>
       <c r="E189" t="n">
-        <v>0.2093004671738542</v>
+        <v>0.2152243691688772</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -4434,10 +4434,10 @@
         <v>0.1199860881616681</v>
       </c>
       <c r="D190" t="n">
-        <v>3.26319714076817e-05</v>
+        <v>0.06969462335109711</v>
       </c>
       <c r="E190" t="n">
-        <v>0.08327700863621922</v>
+        <v>0.106497672429449</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
@@ -4454,10 +4454,10 @@
         <v>0.3486316687780635</v>
       </c>
       <c r="D191" t="n">
-        <v>0.02714811824262142</v>
+        <v>0.07720349729061127</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2979771526623225</v>
+        <v>0.3146622790116524</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -4474,10 +4474,10 @@
         <v>0.1688192095890889</v>
       </c>
       <c r="D192" t="n">
-        <v>0.02626415155827999</v>
+        <v>0.1056512221693993</v>
       </c>
       <c r="E192" t="n">
-        <v>0.1301879253374911</v>
+        <v>0.1566502822078642</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>0.1329203079871629</v>
       </c>
       <c r="D193" t="n">
-        <v>0.04238059744238853</v>
+        <v>0.1203698366880417</v>
       </c>
       <c r="E193" t="n">
-        <v>0.09565184410801253</v>
+        <v>0.1216482571898969</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -4514,10 +4514,10 @@
         <v>0.1646347172833459</v>
       </c>
       <c r="D194" t="n">
-        <v>0.01252851355820894</v>
+        <v>0.08127390593290329</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1016695359210383</v>
+        <v>0.1245846667126031</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
@@ -4534,10 +4534,10 @@
         <v>0.1690222026487901</v>
       </c>
       <c r="D195" t="n">
-        <v>0.000352966773789376</v>
+        <v>0.06947235763072968</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1174653366616495</v>
+        <v>0.140505133613963</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
@@ -4554,10 +4554,10 @@
         <v>0.1310797943846707</v>
       </c>
       <c r="D196" t="n">
-        <v>0.005569968372583389</v>
+        <v>0.07927682995796204</v>
       </c>
       <c r="E196" t="n">
-        <v>0.08443935315403532</v>
+        <v>0.1090083070158282</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
@@ -4574,10 +4574,10 @@
         <v>0.1086716773384964</v>
       </c>
       <c r="D197" t="n">
-        <v>0.01354396529495716</v>
+        <v>0.08707365393638611</v>
       </c>
       <c r="E197" t="n">
-        <v>0.07596250393027908</v>
+        <v>0.1004724001440887</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -4594,10 +4594,10 @@
         <v>0.2688405001313958</v>
       </c>
       <c r="D198" t="n">
-        <v>0.3122029304504395</v>
+        <v>0.3545889556407928</v>
       </c>
       <c r="E198" t="n">
-        <v>0.3142128223358557</v>
+        <v>0.3283414973993068</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -4614,10 +4614,10 @@
         <v>0.1367383533817442</v>
       </c>
       <c r="D199" t="n">
-        <v>0.002859922591596842</v>
+        <v>0.08025576919317245</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1110789533570814</v>
+        <v>0.1368775688909399</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
@@ -4634,13 +4634,13 @@
         <v>0.4155069904549825</v>
       </c>
       <c r="D200" t="n">
-        <v>0.7464140653610229</v>
+        <v>0.7117158770561218</v>
       </c>
       <c r="E200" t="n">
-        <v>0.5371285559097345</v>
+        <v>0.5255624931414341</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -4651,16 +4651,16 @@
         <v>0.6637708410519579</v>
       </c>
       <c r="C201" t="n">
-        <v>0.3801786252879711</v>
+        <v>0.3801786252879712</v>
       </c>
       <c r="D201" t="n">
-        <v>0.6453999280929565</v>
+        <v>0.5110436677932739</v>
       </c>
       <c r="E201" t="n">
-        <v>0.5631164648109619</v>
+        <v>0.5183310447110677</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
@@ -4674,13 +4674,13 @@
         <v>0.3992724598585664</v>
       </c>
       <c r="D202" t="n">
-        <v>0.8552601933479309</v>
+        <v>0.5513283014297485</v>
       </c>
       <c r="E202" t="n">
-        <v>0.5769781292736852</v>
+        <v>0.4756674986342911</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -4694,10 +4694,10 @@
         <v>0.1947897823566847</v>
       </c>
       <c r="D203" t="n">
-        <v>0.06963777542114258</v>
+        <v>0.1071415320038795</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1590276183029981</v>
+        <v>0.1715288704972438</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -4714,10 +4714,10 @@
         <v>0.3433269610355117</v>
       </c>
       <c r="D204" t="n">
-        <v>0.5634319186210632</v>
+        <v>0.4253006875514984</v>
       </c>
       <c r="E204" t="n">
-        <v>0.4563713734138526</v>
+        <v>0.4103276297239976</v>
       </c>
       <c r="F204" t="n">
         <v>0</v>
@@ -4734,10 +4734,10 @@
         <v>0.2142102301421978</v>
       </c>
       <c r="D205" t="n">
-        <v>0.0001699623244348913</v>
+        <v>0.07129607349634171</v>
       </c>
       <c r="E205" t="n">
-        <v>0.1563267912688356</v>
+        <v>0.1800354949928046</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
@@ -4754,10 +4754,10 @@
         <v>0.3187157970167481</v>
       </c>
       <c r="D206" t="n">
-        <v>0.1601885855197906</v>
+        <v>0.2040483504533768</v>
       </c>
       <c r="E206" t="n">
-        <v>0.3032830651340125</v>
+        <v>0.3179029867785412</v>
       </c>
       <c r="F206" t="n">
         <v>0</v>
@@ -4774,10 +4774,10 @@
         <v>0.4718198786719</v>
       </c>
       <c r="D207" t="n">
-        <v>0.8313325047492981</v>
+        <v>0.7477684020996094</v>
       </c>
       <c r="E207" t="n">
-        <v>0.6459680564472708</v>
+        <v>0.6181133555640413</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -4794,10 +4794,10 @@
         <v>0.2550295013516793</v>
       </c>
       <c r="D208" t="n">
-        <v>0.2826966941356659</v>
+        <v>0.2342405319213867</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2825555191085018</v>
+        <v>0.2664034650370754</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0.1923531620543562</v>
       </c>
       <c r="D209" t="n">
-        <v>0.001259941840544343</v>
+        <v>0.07500551640987396</v>
       </c>
       <c r="E209" t="n">
-        <v>0.1563107363407673</v>
+        <v>0.1808925945305439</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
@@ -4834,10 +4834,10 @@
         <v>0.3151230138154562</v>
       </c>
       <c r="D210" t="n">
-        <v>0.7912012934684753</v>
+        <v>0.5653230547904968</v>
       </c>
       <c r="E210" t="n">
-        <v>0.5163430486925499</v>
+        <v>0.4410503024665571</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -4854,10 +4854,10 @@
         <v>0.4161992186869769</v>
       </c>
       <c r="D211" t="n">
-        <v>0.5638378858566284</v>
+        <v>0.3160125017166138</v>
       </c>
       <c r="E211" t="n">
-        <v>0.4780635857731883</v>
+        <v>0.3954551243931834</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
@@ -4874,10 +4874,10 @@
         <v>0.3620200728603185</v>
       </c>
       <c r="D212" t="n">
-        <v>0.6082373857498169</v>
+        <v>0.4419897198677063</v>
       </c>
       <c r="E212" t="n">
-        <v>0.4711672740199334</v>
+        <v>0.4157513853925631</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
@@ -4894,10 +4894,10 @@
         <v>0.2199955210197621</v>
       </c>
       <c r="D213" t="n">
-        <v>0.005098613910377026</v>
+        <v>0.07649944722652435</v>
       </c>
       <c r="E213" t="n">
-        <v>0.1713121808671572</v>
+        <v>0.1951124586392063</v>
       </c>
       <c r="F213" t="n">
         <v>0</v>
@@ -4914,10 +4914,10 @@
         <v>0.3907217493540841</v>
       </c>
       <c r="D214" t="n">
-        <v>0.8382552266120911</v>
+        <v>0.5075387954711914</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6032666416189999</v>
+        <v>0.4930278312387</v>
       </c>
       <c r="F214" t="n">
         <v>1</v>
@@ -4934,10 +4934,10 @@
         <v>0.1769897430601229</v>
       </c>
       <c r="D215" t="n">
-        <v>0.006634782068431377</v>
+        <v>0.08407799899578094</v>
       </c>
       <c r="E215" t="n">
-        <v>0.1532720606587077</v>
+        <v>0.1790864663011575</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
@@ -4954,10 +4954,10 @@
         <v>0.2902224609793662</v>
       </c>
       <c r="D216" t="n">
-        <v>0.2210657894611359</v>
+        <v>0.386243611574173</v>
       </c>
       <c r="E216" t="n">
-        <v>0.2686037699277919</v>
+        <v>0.323663043965471</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
@@ -4974,10 +4974,10 @@
         <v>0.2570242167310633</v>
       </c>
       <c r="D217" t="n">
-        <v>0.7822309732437134</v>
+        <v>0.4968445897102356</v>
       </c>
       <c r="E217" t="n">
-        <v>0.4721434466319375</v>
+        <v>0.3770146521207782</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
@@ -4994,10 +4994,10 @@
         <v>0.1319515001019295</v>
       </c>
       <c r="D218" t="n">
-        <v>0.001759489299729466</v>
+        <v>0.08055673539638519</v>
       </c>
       <c r="E218" t="n">
-        <v>0.1032909718282338</v>
+        <v>0.129556720527119</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -5011,13 +5011,13 @@
         <v>0.4084509420954645</v>
       </c>
       <c r="C219" t="n">
-        <v>0.3250439347719394</v>
+        <v>0.3250439347719393</v>
       </c>
       <c r="D219" t="n">
-        <v>0.3843143284320831</v>
+        <v>0.234020471572876</v>
       </c>
       <c r="E219" t="n">
-        <v>0.3726030684331623</v>
+        <v>0.3225051161467599</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
@@ -5031,13 +5031,13 @@
         <v>0.1898224301411141</v>
       </c>
       <c r="C220" t="n">
-        <v>0.1682233588921065</v>
+        <v>0.1682233588921066</v>
       </c>
       <c r="D220" t="n">
-        <v>0.007354126777499914</v>
+        <v>0.09508281946182251</v>
       </c>
       <c r="E220" t="n">
-        <v>0.1217999719369069</v>
+        <v>0.1510428694983477</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
@@ -5054,10 +5054,10 @@
         <v>0.2482800606555355</v>
       </c>
       <c r="D221" t="n">
-        <v>0.002156462054699659</v>
+        <v>0.08261888474225998</v>
       </c>
       <c r="E221" t="n">
-        <v>0.1771424137211811</v>
+        <v>0.2039632212837012</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
@@ -5074,10 +5074,10 @@
         <v>0.373767189956124</v>
       </c>
       <c r="D222" t="n">
-        <v>0.6610747575759888</v>
+        <v>0.3227922022342682</v>
       </c>
       <c r="E222" t="n">
-        <v>0.499402527214184</v>
+        <v>0.3866416754336106</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0.1261725959023785</v>
       </c>
       <c r="D223" t="n">
-        <v>0.02837597206234932</v>
+        <v>0.1291402876377106</v>
       </c>
       <c r="E223" t="n">
-        <v>0.1084042105110338</v>
+        <v>0.1419923157028209</v>
       </c>
       <c r="F223" t="n">
         <v>0</v>
@@ -5111,13 +5111,13 @@
         <v>0.3735534658901575</v>
       </c>
       <c r="C224" t="n">
-        <v>0.2819243124247555</v>
+        <v>0.2819243124247554</v>
       </c>
       <c r="D224" t="n">
-        <v>0.8099119067192078</v>
+        <v>0.7054473757743835</v>
       </c>
       <c r="E224" t="n">
-        <v>0.4884632283447068</v>
+        <v>0.4536417180297654</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
@@ -5131,13 +5131,13 @@
         <v>0.4137265016073279</v>
       </c>
       <c r="C225" t="n">
-        <v>0.3678176128793121</v>
+        <v>0.3678176128793122</v>
       </c>
       <c r="D225" t="n">
-        <v>0.3989344239234924</v>
+        <v>0.4554597735404968</v>
       </c>
       <c r="E225" t="n">
-        <v>0.3934928461367108</v>
+        <v>0.4123346293423789</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
@@ -5151,13 +5151,13 @@
         <v>0.421681055583582</v>
       </c>
       <c r="C226" t="n">
-        <v>0.3846254505714858</v>
+        <v>0.3846254505714859</v>
       </c>
       <c r="D226" t="n">
-        <v>0.7150325775146484</v>
+        <v>0.6008991003036499</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5071130278899054</v>
+        <v>0.4690685354862392</v>
       </c>
       <c r="F226" t="n">
         <v>0</v>
@@ -5171,13 +5171,13 @@
         <v>0.4085081077569097</v>
       </c>
       <c r="C227" t="n">
-        <v>0.3591292818176217</v>
+        <v>0.3591292818176218</v>
       </c>
       <c r="D227" t="n">
-        <v>0.2644297480583191</v>
+        <v>0.2742202877998352</v>
       </c>
       <c r="E227" t="n">
-        <v>0.3440223792109502</v>
+        <v>0.3472858924581222</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -5194,10 +5194,10 @@
         <v>0.2036246066488215</v>
       </c>
       <c r="D228" t="n">
-        <v>0.007328466977924109</v>
+        <v>0.07723234593868256</v>
       </c>
       <c r="E228" t="n">
-        <v>0.1533919660448017</v>
+        <v>0.1766932590317212</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
@@ -5214,10 +5214,10 @@
         <v>0.1648734010380797</v>
       </c>
       <c r="D229" t="n">
-        <v>9.369522740598768e-05</v>
+        <v>0.06934261322021484</v>
       </c>
       <c r="E229" t="n">
-        <v>0.1110498125770311</v>
+        <v>0.1341327852413007</v>
       </c>
       <c r="F229" t="n">
         <v>0</v>
@@ -5234,10 +5234,10 @@
         <v>0.4161244868753172</v>
       </c>
       <c r="D230" t="n">
-        <v>0.8038098216056824</v>
+        <v>0.6640883684158325</v>
       </c>
       <c r="E230" t="n">
-        <v>0.6128624401844964</v>
+        <v>0.5662886224545465</v>
       </c>
       <c r="F230" t="n">
         <v>1</v>
@@ -5254,10 +5254,10 @@
         <v>0.3235275812482772</v>
       </c>
       <c r="D231" t="n">
-        <v>0.561307966709137</v>
+        <v>0.5811320543289185</v>
       </c>
       <c r="E231" t="n">
-        <v>0.421152897530887</v>
+        <v>0.4277609267374808</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
@@ -5274,10 +5274,10 @@
         <v>0.2994786747738144</v>
       </c>
       <c r="D232" t="n">
-        <v>0.6077280044555664</v>
+        <v>0.3699126839637756</v>
       </c>
       <c r="E232" t="n">
-        <v>0.4125354459735302</v>
+        <v>0.3332636724762666</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
@@ -5294,10 +5294,10 @@
         <v>0.4990505806971714</v>
       </c>
       <c r="D233" t="n">
-        <v>0.8981500864028931</v>
+        <v>0.8109335899353027</v>
       </c>
       <c r="E233" t="n">
-        <v>0.7105914437698964</v>
+        <v>0.6815192782806996</v>
       </c>
       <c r="F233" t="n">
         <v>1</v>
@@ -5314,10 +5314,10 @@
         <v>0.2264685587260181</v>
       </c>
       <c r="D234" t="n">
-        <v>0.0003715945058502257</v>
+        <v>0.07039369642734528</v>
       </c>
       <c r="E234" t="n">
-        <v>0.1596392092229708</v>
+        <v>0.1829799098634692</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
@@ -5334,10 +5334,10 @@
         <v>0.1516911561738614</v>
       </c>
       <c r="D235" t="n">
-        <v>0.007843248546123505</v>
+        <v>0.1011115312576294</v>
       </c>
       <c r="E235" t="n">
-        <v>0.1265352870214375</v>
+        <v>0.1576247145919394</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0.1909047351971768</v>
       </c>
       <c r="D236" t="n">
-        <v>0.01474622450768948</v>
+        <v>0.1073566898703575</v>
       </c>
       <c r="E236" t="n">
-        <v>0.1675565048337812</v>
+        <v>0.1984266599546705</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -5374,10 +5374,10 @@
         <v>0.1981556837950725</v>
       </c>
       <c r="D237" t="n">
-        <v>0.006969102658331394</v>
+        <v>0.08343465626239777</v>
       </c>
       <c r="E237" t="n">
-        <v>0.156989485681614</v>
+        <v>0.1824780035496361</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
@@ -5391,13 +5391,13 @@
         <v>0.2281291225059785</v>
       </c>
       <c r="C238" t="n">
-        <v>0.1778260335415141</v>
+        <v>0.1778260335415142</v>
       </c>
       <c r="D238" t="n">
-        <v>0.003339972347021103</v>
+        <v>0.07864760607481003</v>
       </c>
       <c r="E238" t="n">
-        <v>0.1364317094648379</v>
+        <v>0.1615342540407676</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -5414,10 +5414,10 @@
         <v>0.1873435289918541</v>
       </c>
       <c r="D239" t="n">
-        <v>0.004050787072628736</v>
+        <v>0.0830690935254097</v>
       </c>
       <c r="E239" t="n">
-        <v>0.1419700593304642</v>
+        <v>0.1683094948147245</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -5434,10 +5434,10 @@
         <v>0.3395414982170507</v>
       </c>
       <c r="D240" t="n">
-        <v>0.03872617706656456</v>
+        <v>0.09880206733942032</v>
       </c>
       <c r="E240" t="n">
-        <v>0.2797103002418435</v>
+        <v>0.2997355969994621</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -5454,10 +5454,10 @@
         <v>0.2222254044849644</v>
       </c>
       <c r="D241" t="n">
-        <v>0.06753431260585785</v>
+        <v>0.1813520640134811</v>
       </c>
       <c r="E241" t="n">
-        <v>0.1977302854699589</v>
+        <v>0.2356695359391666</v>
       </c>
       <c r="F241" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0.200449741286107</v>
       </c>
       <c r="D242" t="n">
-        <v>0.08873680979013443</v>
+        <v>0.184178039431572</v>
       </c>
       <c r="E242" t="n">
-        <v>0.1879497569327616</v>
+        <v>0.2197635001465742</v>
       </c>
       <c r="F242" t="n">
         <v>0</v>
@@ -5494,10 +5494,10 @@
         <v>0.1912181260769634</v>
       </c>
       <c r="D243" t="n">
-        <v>0.01154619175940752</v>
+        <v>0.09632100909948349</v>
       </c>
       <c r="E243" t="n">
-        <v>0.1585621950678101</v>
+        <v>0.1868204675145021</v>
       </c>
       <c r="F243" t="n">
         <v>0</v>
@@ -5514,10 +5514,10 @@
         <v>0.186696717570394</v>
       </c>
       <c r="D244" t="n">
-        <v>0.003715720493346453</v>
+        <v>0.09021563827991486</v>
       </c>
       <c r="E244" t="n">
-        <v>0.1649618830795504</v>
+        <v>0.1937951890084065</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0.1639942596504271</v>
       </c>
       <c r="D245" t="n">
-        <v>0.009240282699465752</v>
+        <v>0.08729932457208633</v>
       </c>
       <c r="E245" t="n">
-        <v>0.1227792542873432</v>
+        <v>0.1487989349115501</v>
       </c>
       <c r="F245" t="n">
         <v>0</v>
@@ -5554,10 +5554,10 @@
         <v>0.1611153175351719</v>
       </c>
       <c r="D246" t="n">
-        <v>0.0006370523478835821</v>
+        <v>0.07798473536968231</v>
       </c>
       <c r="E246" t="n">
-        <v>0.1355090799650664</v>
+        <v>0.1612916409723326</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0.1262667783113349</v>
       </c>
       <c r="D247" t="n">
-        <v>0.02108827978372574</v>
+        <v>0.1179822236299515</v>
       </c>
       <c r="E247" t="n">
-        <v>0.1036918384210289</v>
+        <v>0.1359898197031041</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
@@ -5594,10 +5594,10 @@
         <v>0.1585615125826117</v>
       </c>
       <c r="D248" t="n">
-        <v>0.0004938862402923405</v>
+        <v>0.0745239332318306</v>
       </c>
       <c r="E248" t="n">
-        <v>0.1247876180773861</v>
+        <v>0.1494643004078989</v>
       </c>
       <c r="F248" t="n">
         <v>0</v>
@@ -5614,10 +5614,10 @@
         <v>0.2011124846606545</v>
       </c>
       <c r="D249" t="n">
-        <v>0.0003034737310372293</v>
+        <v>0.07253451645374298</v>
       </c>
       <c r="E249" t="n">
-        <v>0.1657004541088666</v>
+        <v>0.1897774683497685</v>
       </c>
       <c r="F249" t="n">
         <v>0</v>
@@ -5634,10 +5634,10 @@
         <v>0.1806149396947223</v>
       </c>
       <c r="D250" t="n">
-        <v>0.00136008660774678</v>
+        <v>0.07544011622667313</v>
       </c>
       <c r="E250" t="n">
-        <v>0.142814952060862</v>
+        <v>0.1675082952671708</v>
       </c>
       <c r="F250" t="n">
         <v>0</v>
@@ -5651,13 +5651,13 @@
         <v>0.2792796919928957</v>
       </c>
       <c r="C251" t="n">
-        <v>0.2611231350126408</v>
+        <v>0.2611231350126407</v>
       </c>
       <c r="D251" t="n">
-        <v>0.02034502848982811</v>
+        <v>0.08035232126712799</v>
       </c>
       <c r="E251" t="n">
-        <v>0.1869159518317882</v>
+        <v>0.2069183827575548</v>
       </c>
       <c r="F251" t="n">
         <v>0</v>
@@ -5674,10 +5674,10 @@
         <v>0.1865138317694517</v>
       </c>
       <c r="D252" t="n">
-        <v>0.009187973104417324</v>
+        <v>0.1018126383423805</v>
       </c>
       <c r="E252" t="n">
-        <v>0.1692382938361669</v>
+        <v>0.2001131822488213</v>
       </c>
       <c r="F252" t="n">
         <v>0</v>
@@ -5694,10 +5694,10 @@
         <v>0.1920183397833584</v>
       </c>
       <c r="D253" t="n">
-        <v>0.5520892143249512</v>
+        <v>0.3167373538017273</v>
       </c>
       <c r="E253" t="n">
-        <v>0.3419645405317024</v>
+        <v>0.2635139203572945</v>
       </c>
       <c r="F253" t="n">
         <v>0</v>
@@ -5714,10 +5714,10 @@
         <v>0.2805390912298826</v>
       </c>
       <c r="D254" t="n">
-        <v>0.3322289884090424</v>
+        <v>0.2095842659473419</v>
       </c>
       <c r="E254" t="n">
-        <v>0.3478288866528785</v>
+        <v>0.3069473124989783</v>
       </c>
       <c r="F254" t="n">
         <v>0</v>
@@ -5731,13 +5731,13 @@
         <v>0.2725856581182082</v>
       </c>
       <c r="C255" t="n">
-        <v>0.2502262604231769</v>
+        <v>0.2502262604231768</v>
       </c>
       <c r="D255" t="n">
-        <v>0.01072320900857449</v>
+        <v>0.08276654034852982</v>
       </c>
       <c r="E255" t="n">
-        <v>0.1778450425166532</v>
+        <v>0.2018594862966383</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -5754,10 +5754,10 @@
         <v>0.390845594733193</v>
       </c>
       <c r="D256" t="n">
-        <v>0.4711893200874329</v>
+        <v>0.3012786507606506</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4243260350645474</v>
+        <v>0.3676891452889533</v>
       </c>
       <c r="F256" t="n">
         <v>0</v>
@@ -5774,10 +5774,10 @@
         <v>0.175026102636015</v>
       </c>
       <c r="D257" t="n">
-        <v>0.001164573943242431</v>
+        <v>0.07738165557384491</v>
       </c>
       <c r="E257" t="n">
-        <v>0.1241637095150436</v>
+        <v>0.149569403391911</v>
       </c>
       <c r="F257" t="n">
         <v>0</v>
@@ -5794,13 +5794,13 @@
         <v>0.4088206154703263</v>
       </c>
       <c r="D258" t="n">
-        <v>0.6299753189086914</v>
+        <v>0.6291292309761047</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5470427862866907</v>
+        <v>0.5467607569758285</v>
       </c>
       <c r="F258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -5814,10 +5814,10 @@
         <v>0.1572447750368471</v>
       </c>
       <c r="D259" t="n">
-        <v>0.007263834588229656</v>
+        <v>0.08730572462081909</v>
       </c>
       <c r="E259" t="n">
-        <v>0.1077645122424729</v>
+        <v>0.1344451422533361</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
@@ -5834,10 +5834,10 @@
         <v>0.1750358055755912</v>
       </c>
       <c r="D260" t="n">
-        <v>0.002504072617739439</v>
+        <v>0.07753260433673859</v>
       </c>
       <c r="E260" t="n">
-        <v>0.1581260011045285</v>
+        <v>0.1831355116775282</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
@@ -5854,10 +5854,10 @@
         <v>0.3073905915730032</v>
       </c>
       <c r="D261" t="n">
-        <v>0.6006551384925842</v>
+        <v>0.2967298626899719</v>
       </c>
       <c r="E261" t="n">
-        <v>0.4323754294655997</v>
+        <v>0.3310670041980623</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0.348265197130379</v>
       </c>
       <c r="D262" t="n">
-        <v>0.7362231612205505</v>
+        <v>0.408133327960968</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5210942407036608</v>
+        <v>0.4117309629504666</v>
       </c>
       <c r="F262" t="n">
         <v>0</v>
@@ -5894,10 +5894,10 @@
         <v>0.2504449997864151</v>
       </c>
       <c r="D263" t="n">
-        <v>0.001459901919588447</v>
+        <v>0.07018271088600159</v>
       </c>
       <c r="E263" t="n">
-        <v>0.1858823261550921</v>
+        <v>0.2087899291438965</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
@@ -5914,10 +5914,10 @@
         <v>0.2487859847002488</v>
       </c>
       <c r="D264" t="n">
-        <v>0.03673926740884781</v>
+        <v>0.1209422722458839</v>
       </c>
       <c r="E264" t="n">
-        <v>0.2050298029519344</v>
+        <v>0.2330974712309465</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
@@ -5934,10 +5934,10 @@
         <v>0.245107876141323</v>
       </c>
       <c r="D265" t="n">
-        <v>0.2528724074363708</v>
+        <v>0.1988900005817413</v>
       </c>
       <c r="E265" t="n">
-        <v>0.2554796669580934</v>
+        <v>0.2374855313398836</v>
       </c>
       <c r="F265" t="n">
         <v>0</v>
@@ -5954,10 +5954,10 @@
         <v>0.1913112978050115</v>
       </c>
       <c r="D266" t="n">
-        <v>0.01344284601509571</v>
+        <v>0.09084881097078323</v>
       </c>
       <c r="E266" t="n">
-        <v>0.1231637189567831</v>
+        <v>0.1489657072753456</v>
       </c>
       <c r="F266" t="n">
         <v>0</v>
@@ -5974,10 +5974,10 @@
         <v>0.4767168787500561</v>
       </c>
       <c r="D267" t="n">
-        <v>0.9331678152084351</v>
+        <v>0.8241285085678101</v>
       </c>
       <c r="E267" t="n">
-        <v>0.7023100903460392</v>
+        <v>0.6659636547991642</v>
       </c>
       <c r="F267" t="n">
         <v>1</v>
@@ -5994,10 +5994,10 @@
         <v>0.1485705963770307</v>
       </c>
       <c r="D268" t="n">
-        <v>0.005845656152814627</v>
+        <v>0.07865413278341293</v>
       </c>
       <c r="E268" t="n">
-        <v>0.1126355453542035</v>
+        <v>0.1369050375644029</v>
       </c>
       <c r="F268" t="n">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         <v>0.1601275692817329</v>
       </c>
       <c r="D269" t="n">
-        <v>0.02911767736077309</v>
+        <v>0.1156532317399979</v>
       </c>
       <c r="E269" t="n">
-        <v>0.1364970165955175</v>
+        <v>0.1653422013885925</v>
       </c>
       <c r="F269" t="n">
         <v>0</v>
@@ -6031,13 +6031,13 @@
         <v>0.2955514954491868</v>
       </c>
       <c r="C270" t="n">
-        <v>0.2502690299836346</v>
+        <v>0.2502690299836345</v>
       </c>
       <c r="D270" t="n">
-        <v>0.1064830794930458</v>
+        <v>0.1683726608753204</v>
       </c>
       <c r="E270" t="n">
-        <v>0.2174345349752891</v>
+        <v>0.2380643954360473</v>
       </c>
       <c r="F270" t="n">
         <v>0</v>
@@ -6054,10 +6054,10 @@
         <v>0.1386278460007433</v>
       </c>
       <c r="D271" t="n">
-        <v>0.001734850229695439</v>
+        <v>0.07488934695720673</v>
       </c>
       <c r="E271" t="n">
-        <v>0.09213086629191425</v>
+        <v>0.116515698534418</v>
       </c>
       <c r="F271" t="n">
         <v>0</v>
@@ -6074,10 +6074,10 @@
         <v>0.4528366273550077</v>
       </c>
       <c r="D272" t="n">
-        <v>0.7470617294311523</v>
+        <v>0.6812846064567566</v>
       </c>
       <c r="E272" t="n">
-        <v>0.5719848289107862</v>
+        <v>0.5500591212526543</v>
       </c>
       <c r="F272" t="n">
         <v>1</v>
@@ -6094,10 +6094,10 @@
         <v>0.1026299458137512</v>
       </c>
       <c r="D273" t="n">
-        <v>0.0007317227427847683</v>
+        <v>0.073642298579216</v>
       </c>
       <c r="E273" t="n">
-        <v>0.0752455625760925</v>
+        <v>0.09954908785490291</v>
       </c>
       <c r="F273" t="n">
         <v>0</v>
@@ -6114,10 +6114,10 @@
         <v>0.1961761291495085</v>
       </c>
       <c r="D274" t="n">
-        <v>0.007599769625812769</v>
+        <v>0.08125106245279312</v>
       </c>
       <c r="E274" t="n">
-        <v>0.1503744795207108</v>
+        <v>0.1749249104630376</v>
       </c>
       <c r="F274" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0.1702911462513545</v>
       </c>
       <c r="D275" t="n">
-        <v>0.02939063683152199</v>
+        <v>0.09726913273334503</v>
       </c>
       <c r="E275" t="n">
-        <v>0.1515651831278765</v>
+        <v>0.1741913484284841</v>
       </c>
       <c r="F275" t="n">
         <v>0</v>
@@ -6154,10 +6154,10 @@
         <v>0.1655900415348071</v>
       </c>
       <c r="D276" t="n">
-        <v>0.0534062571823597</v>
+        <v>0.1006211787462234</v>
       </c>
       <c r="E276" t="n">
-        <v>0.1469747547207587</v>
+        <v>0.1627130619087133</v>
       </c>
       <c r="F276" t="n">
         <v>0</v>
@@ -6171,13 +6171,13 @@
         <v>0.1414273348854358</v>
       </c>
       <c r="C277" t="n">
-        <v>0.1391266762847934</v>
+        <v>0.1391266762847933</v>
       </c>
       <c r="D277" t="n">
-        <v>0.0001541202655062079</v>
+        <v>0.06998039036989212</v>
       </c>
       <c r="E277" t="n">
-        <v>0.09356937714524512</v>
+        <v>0.1168448005133738</v>
       </c>
       <c r="F277" t="n">
         <v>0</v>
@@ -6194,10 +6194,10 @@
         <v>0.1867271243655948</v>
       </c>
       <c r="D278" t="n">
-        <v>0.03635748848319054</v>
+        <v>0.1109280735254288</v>
       </c>
       <c r="E278" t="n">
-        <v>0.1537658371545396</v>
+        <v>0.1786226988352857</v>
       </c>
       <c r="F278" t="n">
         <v>0</v>
@@ -6214,10 +6214,10 @@
         <v>0.1873945171855534</v>
       </c>
       <c r="D279" t="n">
-        <v>0.009842800907790661</v>
+        <v>0.08337802439928055</v>
       </c>
       <c r="E279" t="n">
-        <v>0.1567707897218575</v>
+        <v>0.1812825308856875</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
@@ -6234,10 +6234,10 @@
         <v>0.1714025339107549</v>
       </c>
       <c r="D280" t="n">
-        <v>0.0009422712028026581</v>
+        <v>0.07341708987951279</v>
       </c>
       <c r="E280" t="n">
-        <v>0.113429002462621</v>
+        <v>0.1375872753548577</v>
       </c>
       <c r="F280" t="n">
         <v>0</v>
@@ -6254,10 +6254,10 @@
         <v>0.1779010965527104</v>
       </c>
       <c r="D281" t="n">
-        <v>0.08394143730401993</v>
+        <v>0.1636182069778442</v>
       </c>
       <c r="E281" t="n">
-        <v>0.1630298678249045</v>
+        <v>0.1895887910495127</v>
       </c>
       <c r="F281" t="n">
         <v>0</v>
@@ -6274,10 +6274,10 @@
         <v>0.3903902560229622</v>
       </c>
       <c r="D282" t="n">
-        <v>0.6036926507949829</v>
+        <v>0.4102032780647278</v>
       </c>
       <c r="E282" t="n">
-        <v>0.5328809484813082</v>
+        <v>0.4683844909045565</v>
       </c>
       <c r="F282" t="n">
         <v>0</v>
@@ -6294,10 +6294,10 @@
         <v>0.3574356327946343</v>
       </c>
       <c r="D283" t="n">
-        <v>0.4954567849636078</v>
+        <v>0.5187364816665649</v>
       </c>
       <c r="E283" t="n">
-        <v>0.4677895076428751</v>
+        <v>0.4755494065438608</v>
       </c>
       <c r="F283" t="n">
         <v>0</v>
@@ -6314,10 +6314,10 @@
         <v>0.4490935707747756</v>
       </c>
       <c r="D284" t="n">
-        <v>0.4335697293281555</v>
+        <v>0.2414169311523438</v>
       </c>
       <c r="E284" t="n">
-        <v>0.5464929955069151</v>
+        <v>0.4824420627816445</v>
       </c>
       <c r="F284" t="n">
         <v>0</v>
@@ -6334,10 +6334,10 @@
         <v>0.2380236721138009</v>
       </c>
       <c r="D285" t="n">
-        <v>0.0103455139324069</v>
+        <v>0.0844900980591774</v>
       </c>
       <c r="E285" t="n">
-        <v>0.201388804976003</v>
+        <v>0.2261036663515932</v>
       </c>
       <c r="F285" t="n">
         <v>0</v>
@@ -6354,10 +6354,10 @@
         <v>0.2593752177619165</v>
       </c>
       <c r="D286" t="n">
-        <v>0.0181169044226408</v>
+        <v>0.09189854562282562</v>
       </c>
       <c r="E286" t="n">
-        <v>0.2084600549050866</v>
+        <v>0.2330539353051482</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
@@ -6371,13 +6371,13 @@
         <v>0.6307942581508617</v>
       </c>
       <c r="C287" t="n">
-        <v>0.4315749329320094</v>
+        <v>0.4315749329320095</v>
       </c>
       <c r="D287" t="n">
-        <v>0.9490795135498047</v>
+        <v>0.7731422185897827</v>
       </c>
       <c r="E287" t="n">
-        <v>0.6704829015442253</v>
+        <v>0.6118371365575513</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
@@ -6391,13 +6391,13 @@
         <v>0.1444448890072123</v>
       </c>
       <c r="C288" t="n">
-        <v>0.1598507118839609</v>
+        <v>0.159850711883961</v>
       </c>
       <c r="D288" t="n">
-        <v>0.003827119711786509</v>
+        <v>0.07598410546779633</v>
       </c>
       <c r="E288" t="n">
-        <v>0.1027075735343199</v>
+        <v>0.1267599021196565</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0.2106448104099659</v>
       </c>
       <c r="D289" t="n">
-        <v>0.000674943788908422</v>
+        <v>0.07523656636476517</v>
       </c>
       <c r="E289" t="n">
-        <v>0.1684746946305471</v>
+        <v>0.1933285688224994</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
@@ -6434,10 +6434,10 @@
         <v>0.29810412999737</v>
       </c>
       <c r="D290" t="n">
-        <v>0.5506076812744141</v>
+        <v>0.2895554304122925</v>
       </c>
       <c r="E290" t="n">
-        <v>0.3880533225338458</v>
+        <v>0.3010359055798053</v>
       </c>
       <c r="F290" t="n">
         <v>0</v>
@@ -6454,10 +6454,10 @@
         <v>0.1278534693806734</v>
       </c>
       <c r="D291" t="n">
-        <v>0.0001998046354856342</v>
+        <v>0.06955866515636444</v>
       </c>
       <c r="E291" t="n">
-        <v>0.09060646544521138</v>
+        <v>0.1137260856188376</v>
       </c>
       <c r="F291" t="n">
         <v>0</v>
@@ -6474,10 +6474,10 @@
         <v>0.1689148276301773</v>
       </c>
       <c r="D292" t="n">
-        <v>0.0006467222119681537</v>
+        <v>0.07208804786205292</v>
       </c>
       <c r="E292" t="n">
-        <v>0.1344566514051142</v>
+        <v>0.1582704266218092</v>
       </c>
       <c r="F292" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0.1748389942594712</v>
       </c>
       <c r="D293" t="n">
-        <v>0.07091544568538666</v>
+        <v>0.1011514440178871</v>
       </c>
       <c r="E293" t="n">
-        <v>0.1461527172466706</v>
+        <v>0.1562313833575041</v>
       </c>
       <c r="F293" t="n">
         <v>0</v>
@@ -6514,10 +6514,10 @@
         <v>0.529715019254259</v>
       </c>
       <c r="D294" t="n">
-        <v>0.9290617704391479</v>
+        <v>0.8156825304031372</v>
       </c>
       <c r="E294" t="n">
-        <v>0.7168051040155866</v>
+        <v>0.679012024003583</v>
       </c>
       <c r="F294" t="n">
         <v>1</v>
@@ -6534,10 +6534,10 @@
         <v>0.153782093213373</v>
       </c>
       <c r="D295" t="n">
-        <v>0.005749867297708988</v>
+        <v>0.08363698422908783</v>
       </c>
       <c r="E295" t="n">
-        <v>0.1090560345645784</v>
+        <v>0.135018406875038</v>
       </c>
       <c r="F295" t="n">
         <v>0</v>
@@ -6554,10 +6554,10 @@
         <v>0.2003185159287818</v>
       </c>
       <c r="D296" t="n">
-        <v>0.01781269907951355</v>
+        <v>0.1124139651656151</v>
       </c>
       <c r="E296" t="n">
-        <v>0.1620087020837368</v>
+        <v>0.1935424574457706</v>
       </c>
       <c r="F296" t="n">
         <v>0</v>
@@ -6574,10 +6574,10 @@
         <v>0.1328378555273835</v>
       </c>
       <c r="D297" t="n">
-        <v>0.01123248040676117</v>
+        <v>0.09672679007053375</v>
       </c>
       <c r="E297" t="n">
-        <v>0.09162203150508312</v>
+        <v>0.1201201347263406</v>
       </c>
       <c r="F297" t="n">
         <v>0</v>
@@ -6594,10 +6594,10 @@
         <v>0.152367616981154</v>
       </c>
       <c r="D298" t="n">
-        <v>0.009567131288349628</v>
+        <v>0.08706791698932648</v>
       </c>
       <c r="E298" t="n">
-        <v>0.1035731627815098</v>
+        <v>0.1294067580151687</v>
       </c>
       <c r="F298" t="n">
         <v>0</v>
@@ -6614,10 +6614,10 @@
         <v>0.1561182812334015</v>
       </c>
       <c r="D299" t="n">
-        <v>0.02235047891736031</v>
+        <v>0.09971628338098526</v>
       </c>
       <c r="E299" t="n">
-        <v>0.1053437658197755</v>
+        <v>0.1311323673076505</v>
       </c>
       <c r="F299" t="n">
         <v>0</v>
@@ -6634,10 +6634,10 @@
         <v>0.1221284937013063</v>
       </c>
       <c r="D300" t="n">
-        <v>0.00122591876424849</v>
+        <v>0.07431492954492569</v>
       </c>
       <c r="E300" t="n">
-        <v>0.07781874305942736</v>
+        <v>0.1021817466529864</v>
       </c>
       <c r="F300" t="n">
         <v>0</v>
@@ -6654,13 +6654,13 @@
         <v>0.4459142746254918</v>
       </c>
       <c r="D301" t="n">
-        <v>0.5532085299491882</v>
+        <v>0.4253687262535095</v>
       </c>
       <c r="E301" t="n">
-        <v>0.5337175249629605</v>
+        <v>0.491104257064401</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
@@ -6674,10 +6674,10 @@
         <v>0.1967689619748836</v>
       </c>
       <c r="D302" t="n">
-        <v>0.006284228526055813</v>
+        <v>0.08897315710783005</v>
       </c>
       <c r="E302" t="n">
-        <v>0.1407618307418419</v>
+        <v>0.1683248069357667</v>
       </c>
       <c r="F302" t="n">
         <v>0</v>
@@ -6694,10 +6694,10 @@
         <v>0.2268953908848247</v>
       </c>
       <c r="D303" t="n">
-        <v>0.1429446488618851</v>
+        <v>0.2179907858371735</v>
       </c>
       <c r="E303" t="n">
-        <v>0.2354296903099835</v>
+        <v>0.2604450693017463</v>
       </c>
       <c r="F303" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0.5030306303959471</v>
       </c>
       <c r="C304" t="n">
-        <v>0.387546198657211</v>
+        <v>0.3875461986572109</v>
       </c>
       <c r="D304" t="n">
-        <v>0.2978194057941437</v>
+        <v>0.1404279768466949</v>
       </c>
       <c r="E304" t="n">
-        <v>0.3961320782824339</v>
+        <v>0.3436682686332843</v>
       </c>
       <c r="F304" t="n">
         <v>0</v>
@@ -6731,13 +6731,13 @@
         <v>0.511353524532968</v>
       </c>
       <c r="C305" t="n">
-        <v>0.3298059032701909</v>
+        <v>0.3298059032701908</v>
       </c>
       <c r="D305" t="n">
-        <v>0.5368747711181641</v>
+        <v>0.2528530359268188</v>
       </c>
       <c r="E305" t="n">
-        <v>0.4593447329737743</v>
+        <v>0.3646708212433259</v>
       </c>
       <c r="F305" t="n">
         <v>0</v>
@@ -6754,10 +6754,10 @@
         <v>0.1390007768131399</v>
       </c>
       <c r="D306" t="n">
-        <v>0.02275156788527966</v>
+        <v>0.1103818565607071</v>
       </c>
       <c r="E306" t="n">
-        <v>0.1121453591059313</v>
+        <v>0.1413554553310738</v>
       </c>
       <c r="F306" t="n">
         <v>0</v>
@@ -6774,10 +6774,10 @@
         <v>0.2811656234643408</v>
       </c>
       <c r="D307" t="n">
-        <v>0.1310698091983795</v>
+        <v>0.1801097095012665</v>
       </c>
       <c r="E307" t="n">
-        <v>0.2225495239773277</v>
+        <v>0.2388961574116234</v>
       </c>
       <c r="F307" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0.163399945556621</v>
       </c>
       <c r="D308" t="n">
-        <v>0.03269189596176147</v>
+        <v>0.1273003667593002</v>
       </c>
       <c r="E308" t="n">
-        <v>0.1263315473084744</v>
+        <v>0.1578677042409873</v>
       </c>
       <c r="F308" t="n">
         <v>0</v>
@@ -6814,10 +6814,10 @@
         <v>0.2079452509647242</v>
       </c>
       <c r="D309" t="n">
-        <v>0.02295833453536034</v>
+        <v>0.1012865081429482</v>
       </c>
       <c r="E309" t="n">
-        <v>0.1637210141179282</v>
+        <v>0.1898304053204574</v>
       </c>
       <c r="F309" t="n">
         <v>0</v>
@@ -6834,10 +6834,10 @@
         <v>0.1504283477011669</v>
       </c>
       <c r="D310" t="n">
-        <v>0.02550317347049713</v>
+        <v>0.1311550587415695</v>
       </c>
       <c r="E310" t="n">
-        <v>0.1285588393286422</v>
+        <v>0.1637761344189997</v>
       </c>
       <c r="F310" t="n">
         <v>0</v>
@@ -6854,10 +6854,10 @@
         <v>0.1958254314160678</v>
       </c>
       <c r="D311" t="n">
-        <v>0.002740442054346204</v>
+        <v>0.07764309644699097</v>
       </c>
       <c r="E311" t="n">
-        <v>0.1372493238060205</v>
+        <v>0.1622168752702355</v>
       </c>
       <c r="F311" t="n">
         <v>0</v>
@@ -6871,13 +6871,13 @@
         <v>0.2956139429909411</v>
       </c>
       <c r="C312" t="n">
-        <v>0.1856010182455338</v>
+        <v>0.1856010182455337</v>
       </c>
       <c r="D312" t="n">
-        <v>0.009317364543676376</v>
+        <v>0.08948908746242523</v>
       </c>
       <c r="E312" t="n">
-        <v>0.1635107752600504</v>
+        <v>0.1902346828996334</v>
       </c>
       <c r="F312" t="n">
         <v>0</v>
@@ -6894,10 +6894,10 @@
         <v>0.1738268190782112</v>
       </c>
       <c r="D313" t="n">
-        <v>0.005068528465926647</v>
+        <v>0.08182069659233093</v>
       </c>
       <c r="E313" t="n">
-        <v>0.12668665134498</v>
+        <v>0.1522707073871148</v>
       </c>
       <c r="F313" t="n">
         <v>0</v>
@@ -6914,10 +6914,10 @@
         <v>0.211142588207578</v>
       </c>
       <c r="D314" t="n">
-        <v>0.05186793208122253</v>
+        <v>0.1334736049175262</v>
       </c>
       <c r="E314" t="n">
-        <v>0.1708993793285989</v>
+        <v>0.1981012702740335</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
@@ -6934,10 +6934,10 @@
         <v>0.360788607596815</v>
       </c>
       <c r="D315" t="n">
-        <v>0.3988410234451294</v>
+        <v>0.2969556152820587</v>
       </c>
       <c r="E315" t="n">
-        <v>0.4190603456573268</v>
+        <v>0.3850985429363032</v>
       </c>
       <c r="F315" t="n">
         <v>0</v>
@@ -6954,10 +6954,10 @@
         <v>0.4406345163130966</v>
       </c>
       <c r="D316" t="n">
-        <v>0.5868356823921204</v>
+        <v>0.242593914270401</v>
       </c>
       <c r="E316" t="n">
-        <v>0.5554767164508934</v>
+        <v>0.4407294604103202</v>
       </c>
       <c r="F316" t="n">
         <v>0</v>
@@ -6971,13 +6971,13 @@
         <v>0.2097969378868546</v>
       </c>
       <c r="C317" t="n">
-        <v>0.2561149226411029</v>
+        <v>0.256114922641103</v>
       </c>
       <c r="D317" t="n">
-        <v>0.07382340729236603</v>
+        <v>0.1404961943626404</v>
       </c>
       <c r="E317" t="n">
-        <v>0.1799117559401079</v>
+        <v>0.202136018296866</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
@@ -6994,10 +6994,10 @@
         <v>0.1604986786266021</v>
       </c>
       <c r="D318" t="n">
-        <v>0.008480402640998363</v>
+        <v>0.08003890514373779</v>
       </c>
       <c r="E318" t="n">
-        <v>0.1116983964615661</v>
+        <v>0.1355512306291459</v>
       </c>
       <c r="F318" t="n">
         <v>0</v>
@@ -7014,10 +7014,10 @@
         <v>0.3296289512356696</v>
       </c>
       <c r="D319" t="n">
-        <v>0.7945693731307983</v>
+        <v>0.5691872835159302</v>
       </c>
       <c r="E319" t="n">
-        <v>0.5380960282317976</v>
+        <v>0.4629686650268415</v>
       </c>
       <c r="F319" t="n">
         <v>0</v>
@@ -7034,10 +7034,10 @@
         <v>0.252909947726533</v>
       </c>
       <c r="D320" t="n">
-        <v>0.009557528421282768</v>
+        <v>0.1001055240631104</v>
       </c>
       <c r="E320" t="n">
-        <v>0.1928819819361805</v>
+        <v>0.2230646471501231</v>
       </c>
       <c r="F320" t="n">
         <v>0</v>
@@ -7054,10 +7054,10 @@
         <v>0.2845608243306739</v>
       </c>
       <c r="D321" t="n">
-        <v>0.0640675351023674</v>
+        <v>0.09966985881328583</v>
       </c>
       <c r="E321" t="n">
-        <v>0.2539580647144769</v>
+        <v>0.2658255059514497</v>
       </c>
       <c r="F321" t="n">
         <v>0</v>
@@ -7074,10 +7074,10 @@
         <v>0.3167438016021331</v>
       </c>
       <c r="D322" t="n">
-        <v>0.4297438561916351</v>
+        <v>0.2711133360862732</v>
       </c>
       <c r="E322" t="n">
-        <v>0.395545451895476</v>
+        <v>0.3426686118603553</v>
       </c>
       <c r="F322" t="n">
         <v>0</v>
@@ -7094,10 +7094,10 @@
         <v>0.1672527111503965</v>
       </c>
       <c r="D323" t="n">
-        <v>5.918590613873675e-05</v>
+        <v>0.06956822425127029</v>
       </c>
       <c r="E323" t="n">
-        <v>0.132717626939644</v>
+        <v>0.1558873063880211</v>
       </c>
       <c r="F323" t="n">
         <v>0</v>
@@ -7114,10 +7114,10 @@
         <v>0.2274029563986385</v>
       </c>
       <c r="D324" t="n">
-        <v>0.06475023925304413</v>
+        <v>0.1143343448638916</v>
       </c>
       <c r="E324" t="n">
-        <v>0.2153844890458614</v>
+        <v>0.2319125242494772</v>
       </c>
       <c r="F324" t="n">
         <v>0</v>
@@ -7134,10 +7134,10 @@
         <v>0.1784560160977895</v>
       </c>
       <c r="D325" t="n">
-        <v>0.00132004776969552</v>
+        <v>0.07509391009807587</v>
       </c>
       <c r="E325" t="n">
-        <v>0.1372114985620979</v>
+        <v>0.1618027860048913</v>
       </c>
       <c r="F325" t="n">
         <v>0</v>
@@ -7154,10 +7154,10 @@
         <v>0.3456614133170233</v>
       </c>
       <c r="D326" t="n">
-        <v>0.5201010704040527</v>
+        <v>0.294018030166626</v>
       </c>
       <c r="E326" t="n">
-        <v>0.4441570698084834</v>
+        <v>0.3687960563960078</v>
       </c>
       <c r="F326" t="n">
         <v>0</v>
@@ -7174,10 +7174,10 @@
         <v>0.1883110964159422</v>
       </c>
       <c r="D327" t="n">
-        <v>0.02260873094201088</v>
+        <v>0.0731484666466713</v>
       </c>
       <c r="E327" t="n">
-        <v>0.1165919668226336</v>
+        <v>0.1334385453908538</v>
       </c>
       <c r="F327" t="n">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0.1601434475957625</v>
       </c>
       <c r="D328" t="n">
-        <v>0.000683480582665652</v>
+        <v>0.08045828342437744</v>
       </c>
       <c r="E328" t="n">
-        <v>0.1224353716100087</v>
+        <v>0.149026972557246</v>
       </c>
       <c r="F328" t="n">
         <v>0</v>
@@ -7214,10 +7214,10 @@
         <v>0.3021918347781463</v>
       </c>
       <c r="D329" t="n">
-        <v>0.4126993715763092</v>
+        <v>0.2685330212116241</v>
       </c>
       <c r="E329" t="n">
-        <v>0.3700694611170061</v>
+        <v>0.3220140109954444</v>
       </c>
       <c r="F329" t="n">
         <v>0</v>
@@ -7231,13 +7231,13 @@
         <v>0.4533135724407669</v>
       </c>
       <c r="C330" t="n">
-        <v>0.3074533186148799</v>
+        <v>0.30745331861488</v>
       </c>
       <c r="D330" t="n">
-        <v>0.1142477542161942</v>
+        <v>0.1384633779525757</v>
       </c>
       <c r="E330" t="n">
-        <v>0.291671548423947</v>
+        <v>0.2997434230027409</v>
       </c>
       <c r="F330" t="n">
         <v>0</v>
@@ -7254,10 +7254,10 @@
         <v>0.2136383502321311</v>
       </c>
       <c r="D331" t="n">
-        <v>7.844428910175338e-05</v>
+        <v>0.06972009688615799</v>
       </c>
       <c r="E331" t="n">
-        <v>0.1706320951429232</v>
+        <v>0.1938459793419419</v>
       </c>
       <c r="F331" t="n">
         <v>0</v>
@@ -7274,10 +7274,10 @@
         <v>0.1458729905124276</v>
       </c>
       <c r="D332" t="n">
-        <v>0.01936561614274979</v>
+        <v>0.09176170825958252</v>
       </c>
       <c r="E332" t="n">
-        <v>0.1157675438011434</v>
+        <v>0.1398995745067543</v>
       </c>
       <c r="F332" t="n">
         <v>0</v>
@@ -7294,10 +7294,10 @@
         <v>0.1997967681243279</v>
       </c>
       <c r="D333" t="n">
-        <v>0.02484229207038879</v>
+        <v>0.1213887184858322</v>
       </c>
       <c r="E333" t="n">
-        <v>0.1609470337119054</v>
+        <v>0.1931291758503866</v>
       </c>
       <c r="F333" t="n">
         <v>0</v>
@@ -7314,10 +7314,10 @@
         <v>0.1936305639931817</v>
       </c>
       <c r="D334" t="n">
-        <v>0.0006208947743289173</v>
+        <v>0.08385764807462692</v>
       </c>
       <c r="E334" t="n">
-        <v>0.1161848835640959</v>
+        <v>0.1439304679975286</v>
       </c>
       <c r="F334" t="n">
         <v>0</v>
@@ -7334,10 +7334,10 @@
         <v>0.22345007058196</v>
       </c>
       <c r="D335" t="n">
-        <v>0.008851064369082451</v>
+        <v>0.09444044530391693</v>
       </c>
       <c r="E335" t="n">
-        <v>0.1797169046816319</v>
+        <v>0.2082466983265767</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
@@ -7354,10 +7354,10 @@
         <v>0.3080437267160764</v>
       </c>
       <c r="D336" t="n">
-        <v>0.1428109258413315</v>
+        <v>0.1192271336913109</v>
       </c>
       <c r="E336" t="n">
-        <v>0.2956849263044982</v>
+        <v>0.2878236622544914</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
@@ -7374,10 +7374,10 @@
         <v>0.1396434426258715</v>
       </c>
       <c r="D337" t="n">
-        <v>0.00757583836093545</v>
+        <v>0.07945443689823151</v>
       </c>
       <c r="E337" t="n">
-        <v>0.09617877184816066</v>
+        <v>0.120138304693926</v>
       </c>
       <c r="F337" t="n">
         <v>0</v>
@@ -7394,10 +7394,10 @@
         <v>0.2244373896237448</v>
       </c>
       <c r="D338" t="n">
-        <v>0.07580826431512833</v>
+        <v>0.1538756340742111</v>
       </c>
       <c r="E338" t="n">
-        <v>0.218783612004369</v>
+        <v>0.24480606859073</v>
       </c>
       <c r="F338" t="n">
         <v>0</v>
@@ -7414,10 +7414,10 @@
         <v>0.283209351425923</v>
       </c>
       <c r="D339" t="n">
-        <v>0.04234002158045769</v>
+        <v>0.09142465889453888</v>
       </c>
       <c r="E339" t="n">
-        <v>0.2183059480436462</v>
+        <v>0.2346674938150066</v>
       </c>
       <c r="F339" t="n">
         <v>0</v>
@@ -7434,10 +7434,10 @@
         <v>0.2077499720116928</v>
       </c>
       <c r="D340" t="n">
-        <v>0.006006040144711733</v>
+        <v>0.07150884717702866</v>
       </c>
       <c r="E340" t="n">
-        <v>0.1410115632698035</v>
+        <v>0.1628458322805758</v>
       </c>
       <c r="F340" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0.2466391656695625</v>
       </c>
       <c r="D341" t="n">
-        <v>0.005515526980161667</v>
+        <v>0.09646593779325485</v>
       </c>
       <c r="E341" t="n">
-        <v>0.2093211152049142</v>
+        <v>0.2396379188092786</v>
       </c>
       <c r="F341" t="n">
         <v>0</v>
@@ -7474,10 +7474,10 @@
         <v>0.1834007276203239</v>
       </c>
       <c r="D342" t="n">
-        <v>0.0007232059724628925</v>
+        <v>0.07643570750951767</v>
       </c>
       <c r="E342" t="n">
-        <v>0.1243562102626947</v>
+        <v>0.1495937107750462</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
@@ -7494,10 +7494,10 @@
         <v>0.2110750036838882</v>
       </c>
       <c r="D343" t="n">
-        <v>0.1374697238206863</v>
+        <v>0.2368126809597015</v>
       </c>
       <c r="E343" t="n">
-        <v>0.1967251362150727</v>
+        <v>0.2298394552614111</v>
       </c>
       <c r="F343" t="n">
         <v>0</v>
@@ -7514,10 +7514,10 @@
         <v>0.1701332961107747</v>
       </c>
       <c r="D344" t="n">
-        <v>0.01607757993042469</v>
+        <v>0.09698940813541412</v>
       </c>
       <c r="E344" t="n">
-        <v>0.1201266788929756</v>
+        <v>0.1470972882946387</v>
       </c>
       <c r="F344" t="n">
         <v>0</v>
@@ -7534,10 +7534,10 @@
         <v>0.1631228374510302</v>
       </c>
       <c r="D345" t="n">
-        <v>0.01374964602291584</v>
+        <v>0.09971655160188675</v>
       </c>
       <c r="E345" t="n">
-        <v>0.151068843881944</v>
+        <v>0.1797244790749343</v>
       </c>
       <c r="F345" t="n">
         <v>0</v>
@@ -7554,10 +7554,10 @@
         <v>0.2121078237503132</v>
       </c>
       <c r="D346" t="n">
-        <v>0.003094628918915987</v>
+        <v>0.07923673093318939</v>
       </c>
       <c r="E346" t="n">
-        <v>0.1627132879699311</v>
+        <v>0.1880939886413555</v>
       </c>
       <c r="F346" t="n">
         <v>0</v>
@@ -7574,10 +7574,10 @@
         <v>0.2020880758263718</v>
       </c>
       <c r="D347" t="n">
-        <v>1.751318268361501e-05</v>
+        <v>0.06832520663738251</v>
       </c>
       <c r="E347" t="n">
-        <v>0.1457835289228645</v>
+        <v>0.1685527600744308</v>
       </c>
       <c r="F347" t="n">
         <v>0</v>
@@ -7594,10 +7594,10 @@
         <v>0.2546876041861252</v>
       </c>
       <c r="D348" t="n">
-        <v>0.01632943190634251</v>
+        <v>0.1054892167448997</v>
       </c>
       <c r="E348" t="n">
-        <v>0.2141302888008382</v>
+        <v>0.2438502170803573</v>
       </c>
       <c r="F348" t="n">
         <v>0</v>
@@ -7614,10 +7614,10 @@
         <v>0.3161943389451863</v>
       </c>
       <c r="D349" t="n">
-        <v>0.3478564321994781</v>
+        <v>0.2000764310359955</v>
       </c>
       <c r="E349" t="n">
-        <v>0.3309372465322118</v>
+        <v>0.2816772461443842</v>
       </c>
       <c r="F349" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0.2207397406038883</v>
       </c>
       <c r="D350" t="n">
-        <v>0.003785699140280485</v>
+        <v>0.07453347742557526</v>
       </c>
       <c r="E350" t="n">
-        <v>0.1740885558046564</v>
+        <v>0.1976711485664213</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
@@ -7651,16 +7651,16 @@
         <v>0.520356211392224</v>
       </c>
       <c r="C351" t="n">
-        <v>0.3659763161259019</v>
+        <v>0.365976316125902</v>
       </c>
       <c r="D351" t="n">
-        <v>0.678344190120697</v>
+        <v>0.6534706354141235</v>
       </c>
       <c r="E351" t="n">
-        <v>0.5215589058796076</v>
+        <v>0.5132677209774165</v>
       </c>
       <c r="F351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
@@ -7674,10 +7674,10 @@
         <v>0.1264076750509179</v>
       </c>
       <c r="D352" t="n">
-        <v>0.0001270641369046643</v>
+        <v>0.07116667181253433</v>
       </c>
       <c r="E352" t="n">
-        <v>0.07551501965148126</v>
+        <v>0.09919488887669115</v>
       </c>
       <c r="F352" t="n">
         <v>0</v>
@@ -7694,10 +7694,10 @@
         <v>0.1720775936789294</v>
       </c>
       <c r="D353" t="n">
-        <v>0.0001576315407874063</v>
+        <v>0.07055987417697906</v>
       </c>
       <c r="E353" t="n">
-        <v>0.1153527874392405</v>
+        <v>0.1388202016513044</v>
       </c>
       <c r="F353" t="n">
         <v>0</v>
@@ -7714,10 +7714,10 @@
         <v>0.2440190853233989</v>
       </c>
       <c r="D354" t="n">
-        <v>0.2605370581150055</v>
+        <v>0.1716596782207489</v>
       </c>
       <c r="E354" t="n">
-        <v>0.2403101839270984</v>
+        <v>0.2106843906290128</v>
       </c>
       <c r="F354" t="n">
         <v>0</v>
@@ -7734,10 +7734,10 @@
         <v>0.1985070884957957</v>
       </c>
       <c r="D355" t="n">
-        <v>0.2108025252819061</v>
+        <v>0.1518760174512863</v>
       </c>
       <c r="E355" t="n">
-        <v>0.1978778400997588</v>
+        <v>0.1782356708228855</v>
       </c>
       <c r="F355" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0.1389995342007893</v>
       </c>
       <c r="D356" t="n">
-        <v>0.002438020426779985</v>
+        <v>0.07942656427621841</v>
       </c>
       <c r="E356" t="n">
-        <v>0.1008147290498171</v>
+        <v>0.1264775769996299</v>
       </c>
       <c r="F356" t="n">
         <v>0</v>
@@ -7774,10 +7774,10 @@
         <v>0.2028237531849048</v>
       </c>
       <c r="D357" t="n">
-        <v>0.003070397768169641</v>
+        <v>0.08465567231178284</v>
       </c>
       <c r="E357" t="n">
-        <v>0.1551457356980674</v>
+        <v>0.1823408272126051</v>
       </c>
       <c r="F357" t="n">
         <v>0</v>
@@ -7794,10 +7794,10 @@
         <v>0.3595630951327164</v>
       </c>
       <c r="D358" t="n">
-        <v>0.7389410734176636</v>
+        <v>0.4918052554130554</v>
       </c>
       <c r="E358" t="n">
-        <v>0.5622442873333076</v>
+        <v>0.4798656813317715</v>
       </c>
       <c r="F358" t="n">
         <v>0</v>
@@ -7814,10 +7814,10 @@
         <v>0.4263509213265251</v>
       </c>
       <c r="D359" t="n">
-        <v>0.09517713636159897</v>
+        <v>0.1652258485555649</v>
       </c>
       <c r="E359" t="n">
-        <v>0.3713742293731497</v>
+        <v>0.3947238001044717</v>
       </c>
       <c r="F359" t="n">
         <v>0</v>
@@ -7834,10 +7834,10 @@
         <v>0.2599309387281244</v>
       </c>
       <c r="D360" t="n">
-        <v>0.05140084773302078</v>
+        <v>0.1121445298194885</v>
       </c>
       <c r="E360" t="n">
-        <v>0.2466892434835803</v>
+        <v>0.2669371375124028</v>
       </c>
       <c r="F360" t="n">
         <v>0</v>
@@ -7854,10 +7854,10 @@
         <v>0.1395222394041264</v>
       </c>
       <c r="D361" t="n">
-        <v>0.000355315045453608</v>
+        <v>0.07171179354190826</v>
       </c>
       <c r="E361" t="n">
-        <v>0.1118514066300614</v>
+        <v>0.1356368994622129</v>
       </c>
       <c r="F361" t="n">
         <v>0</v>
@@ -7874,10 +7874,10 @@
         <v>0.3360344552869404</v>
       </c>
       <c r="D362" t="n">
-        <v>0.5687354207038879</v>
+        <v>0.2887772917747498</v>
       </c>
       <c r="E362" t="n">
-        <v>0.4531256345717726</v>
+        <v>0.3598062582620599</v>
       </c>
       <c r="F362" t="n">
         <v>0</v>
@@ -7894,10 +7894,10 @@
         <v>0.2468609538649147</v>
       </c>
       <c r="D363" t="n">
-        <v>0.2211678028106689</v>
+        <v>0.2433619499206543</v>
       </c>
       <c r="E363" t="n">
-        <v>0.2672895274421777</v>
+        <v>0.2746875764788395</v>
       </c>
       <c r="F363" t="n">
         <v>0</v>
@@ -7914,10 +7914,10 @@
         <v>0.270059796455745</v>
       </c>
       <c r="D364" t="n">
-        <v>0.2592461705207825</v>
+        <v>0.1350765824317932</v>
       </c>
       <c r="E364" t="n">
-        <v>0.2457787263529533</v>
+        <v>0.2043888636566236</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         <v>0.1541696428485134</v>
       </c>
       <c r="C365" t="n">
-        <v>0.1765666227222856</v>
+        <v>0.1765666227222857</v>
       </c>
       <c r="D365" t="n">
-        <v>0.02522634342312813</v>
+        <v>0.08850008249282837</v>
       </c>
       <c r="E365" t="n">
-        <v>0.1186542029979757</v>
+        <v>0.1397454493545425</v>
       </c>
       <c r="F365" t="n">
         <v>0</v>
@@ -7954,10 +7954,10 @@
         <v>0.1595701629983918</v>
       </c>
       <c r="D366" t="n">
-        <v>0.09052391350269318</v>
+        <v>0.1137158125638962</v>
       </c>
       <c r="E366" t="n">
-        <v>0.1476993595831565</v>
+        <v>0.1554299926035575</v>
       </c>
       <c r="F366" t="n">
         <v>0</v>
@@ -7971,13 +7971,13 @@
         <v>0.2953056566032289</v>
       </c>
       <c r="C367" t="n">
-        <v>0.2254987095801282</v>
+        <v>0.2254987095801283</v>
       </c>
       <c r="D367" t="n">
-        <v>8.208425424527377e-05</v>
+        <v>0.06995604932308197</v>
       </c>
       <c r="E367" t="n">
-        <v>0.1736288168125341</v>
+        <v>0.1969201385021464</v>
       </c>
       <c r="F367" t="n">
         <v>0</v>
@@ -7994,10 +7994,10 @@
         <v>0.2994431663109915</v>
       </c>
       <c r="D368" t="n">
-        <v>0.004808249417692423</v>
+        <v>0.07687624543905258</v>
       </c>
       <c r="E368" t="n">
-        <v>0.2394335237598735</v>
+        <v>0.2634561891003269</v>
       </c>
       <c r="F368" t="n">
         <v>0</v>
@@ -8014,10 +8014,10 @@
         <v>0.1741719378395016</v>
       </c>
       <c r="D369" t="n">
-        <v>0.02133238688111305</v>
+        <v>0.08271059393882751</v>
       </c>
       <c r="E369" t="n">
-        <v>0.1358632732895544</v>
+        <v>0.1563226756421258</v>
       </c>
       <c r="F369" t="n">
         <v>0</v>
@@ -8034,10 +8034,10 @@
         <v>0.1798384744288231</v>
       </c>
       <c r="D370" t="n">
-        <v>0.001721614273265004</v>
+        <v>0.0765896812081337</v>
       </c>
       <c r="E370" t="n">
-        <v>0.1518398203505924</v>
+        <v>0.1767958426622153</v>
       </c>
       <c r="F370" t="n">
         <v>0</v>
@@ -8054,10 +8054,10 @@
         <v>0.1739304088231993</v>
       </c>
       <c r="D371" t="n">
-        <v>0.3915858566761017</v>
+        <v>0.1548161208629608</v>
       </c>
       <c r="E371" t="n">
-        <v>0.2441434429148367</v>
+        <v>0.1652201976437898</v>
       </c>
       <c r="F371" t="n">
         <v>0</v>
@@ -8074,10 +8074,10 @@
         <v>0.1370753474343921</v>
       </c>
       <c r="D372" t="n">
-        <v>0.0004337720456533134</v>
+        <v>0.07309138029813766</v>
       </c>
       <c r="E372" t="n">
-        <v>0.09997355721481534</v>
+        <v>0.1241927599656435</v>
       </c>
       <c r="F372" t="n">
         <v>0</v>
@@ -8094,10 +8094,10 @@
         <v>0.1412973528926903</v>
       </c>
       <c r="D373" t="n">
-        <v>0.004186898469924927</v>
+        <v>0.07289459556341171</v>
       </c>
       <c r="E373" t="n">
-        <v>0.116254943038969</v>
+        <v>0.139157508736798</v>
       </c>
       <c r="F373" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0.1691431399637203</v>
       </c>
       <c r="D374" t="n">
-        <v>0.0245132502168417</v>
+        <v>0.09926066547632217</v>
       </c>
       <c r="E374" t="n">
-        <v>0.1305344068911735</v>
+        <v>0.155450211977667</v>
       </c>
       <c r="F374" t="n">
         <v>0</v>
@@ -8134,10 +8134,10 @@
         <v>0.1052892364383654</v>
       </c>
       <c r="D375" t="n">
-        <v>0.002064136322587729</v>
+        <v>0.07991179823875427</v>
       </c>
       <c r="E375" t="n">
-        <v>0.1028386185328045</v>
+        <v>0.1287878391715267</v>
       </c>
       <c r="F375" t="n">
         <v>0</v>
@@ -8154,10 +8154,10 @@
         <v>0.2696032742796808</v>
       </c>
       <c r="D376" t="n">
-        <v>0.02997564151883125</v>
+        <v>0.09191969782114029</v>
       </c>
       <c r="E376" t="n">
-        <v>0.2303680172776743</v>
+        <v>0.2510160360451106</v>
       </c>
       <c r="F376" t="n">
         <v>0</v>
@@ -8174,10 +8174,10 @@
         <v>0.1828416191914569</v>
       </c>
       <c r="D377" t="n">
-        <v>0.0002340240171179175</v>
+        <v>0.07250047475099564</v>
       </c>
       <c r="E377" t="n">
-        <v>0.1150495288270818</v>
+        <v>0.1391383457383744</v>
       </c>
       <c r="F377" t="n">
         <v>0</v>
@@ -8194,10 +8194,10 @@
         <v>0.1573012072151023</v>
       </c>
       <c r="D378" t="n">
-        <v>0.001264168415218592</v>
+        <v>0.07656170427799225</v>
       </c>
       <c r="E378" t="n">
-        <v>0.1030426093069123</v>
+        <v>0.1281417879278368</v>
       </c>
       <c r="F378" t="n">
         <v>0</v>
@@ -8214,10 +8214,10 @@
         <v>0.1979168143936013</v>
       </c>
       <c r="D379" t="n">
-        <v>0.3548492193222046</v>
+        <v>0.2729851603507996</v>
       </c>
       <c r="E379" t="n">
-        <v>0.2525218693047104</v>
+        <v>0.2252338496475754</v>
       </c>
       <c r="F379" t="n">
         <v>0</v>
@@ -8234,10 +8234,10 @@
         <v>0.3951778616586796</v>
       </c>
       <c r="D380" t="n">
-        <v>0.4325044751167297</v>
+        <v>0.4178499281406403</v>
       </c>
       <c r="E380" t="n">
-        <v>0.4220672433221644</v>
+        <v>0.4171823943301345</v>
       </c>
       <c r="F380" t="n">
         <v>0</v>
@@ -8254,10 +8254,10 @@
         <v>0.3056208754025039</v>
       </c>
       <c r="D381" t="n">
-        <v>0.6313949823379517</v>
+        <v>0.4603724479675293</v>
       </c>
       <c r="E381" t="n">
-        <v>0.4171738555445387</v>
+        <v>0.3601663440877312</v>
       </c>
       <c r="F381" t="n">
         <v>0</v>
@@ -8274,10 +8274,10 @@
         <v>0.2201093997738111</v>
       </c>
       <c r="D382" t="n">
-        <v>0.1421291828155518</v>
+        <v>0.09646923840045929</v>
       </c>
       <c r="E382" t="n">
-        <v>0.1951992118805204</v>
+        <v>0.1799792304088229</v>
       </c>
       <c r="F382" t="n">
         <v>0</v>
@@ -8294,10 +8294,10 @@
         <v>0.2295245798726985</v>
       </c>
       <c r="D383" t="n">
-        <v>0.04087569564580917</v>
+        <v>0.1081742793321609</v>
       </c>
       <c r="E383" t="n">
-        <v>0.1645399673149463</v>
+        <v>0.1869728285437302</v>
       </c>
       <c r="F383" t="n">
         <v>0</v>
@@ -8314,10 +8314,10 @@
         <v>0.321646146623849</v>
       </c>
       <c r="D384" t="n">
-        <v>0.09238956123590469</v>
+        <v>0.1731357574462891</v>
       </c>
       <c r="E384" t="n">
-        <v>0.2588541497879982</v>
+        <v>0.285769548524793</v>
       </c>
       <c r="F384" t="n">
         <v>0</v>
@@ -8334,10 +8334,10 @@
         <v>0.1541845311681382</v>
       </c>
       <c r="D385" t="n">
-        <v>0.005669549573212862</v>
+        <v>0.07392682135105133</v>
       </c>
       <c r="E385" t="n">
-        <v>0.09441577454557333</v>
+        <v>0.1171681984715195</v>
       </c>
       <c r="F385" t="n">
         <v>0</v>
@@ -8354,10 +8354,10 @@
         <v>0.2916479817323466</v>
       </c>
       <c r="D386" t="n">
-        <v>0.1210959926247597</v>
+        <v>0.1361304223537445</v>
       </c>
       <c r="E386" t="n">
-        <v>0.2833957999685615</v>
+        <v>0.2884072765448897</v>
       </c>
       <c r="F386" t="n">
         <v>0</v>
@@ -8374,10 +8374,10 @@
         <v>0.3600650269622542</v>
       </c>
       <c r="D387" t="n">
-        <v>0.7444862127304077</v>
+        <v>0.6518110036849976</v>
       </c>
       <c r="E387" t="n">
-        <v>0.5157133682154272</v>
+        <v>0.4848216318669572</v>
       </c>
       <c r="F387" t="n">
         <v>0</v>
@@ -8394,10 +8394,10 @@
         <v>0.3166279714005419</v>
       </c>
       <c r="D388" t="n">
-        <v>0.4454097747802734</v>
+        <v>0.2289565354585648</v>
       </c>
       <c r="E388" t="n">
-        <v>0.3952469277030337</v>
+        <v>0.3230958479291308</v>
       </c>
       <c r="F388" t="n">
         <v>0</v>
@@ -8414,10 +8414,10 @@
         <v>0.2240966464282289</v>
       </c>
       <c r="D389" t="n">
-        <v>0.2748691141605377</v>
+        <v>0.176185742020607</v>
       </c>
       <c r="E389" t="n">
-        <v>0.2458592612457871</v>
+        <v>0.2129648038658102</v>
       </c>
       <c r="F389" t="n">
         <v>0</v>
@@ -8434,10 +8434,10 @@
         <v>0.3244848459106048</v>
       </c>
       <c r="D390" t="n">
-        <v>0.1387932300567627</v>
+        <v>0.1369571685791016</v>
       </c>
       <c r="E390" t="n">
-        <v>0.2603070628312563</v>
+        <v>0.2596950423387026</v>
       </c>
       <c r="F390" t="n">
         <v>0</v>
@@ -8454,10 +8454,10 @@
         <v>0.1856114466420517</v>
       </c>
       <c r="D391" t="n">
-        <v>0.01874219067394733</v>
+        <v>0.1260299533605576</v>
       </c>
       <c r="E391" t="n">
-        <v>0.1181985336643941</v>
+        <v>0.1539611212265976</v>
       </c>
       <c r="F391" t="n">
         <v>0</v>
@@ -8474,10 +8474,10 @@
         <v>0.4728141752586971</v>
       </c>
       <c r="D392" t="n">
-        <v>0.9083989858627319</v>
+        <v>0.716367244720459</v>
       </c>
       <c r="E392" t="n">
-        <v>0.6914785097341406</v>
+        <v>0.6274679293533828</v>
       </c>
       <c r="F392" t="n">
         <v>1</v>
@@ -8494,10 +8494,10 @@
         <v>0.2677654629129281</v>
       </c>
       <c r="D393" t="n">
-        <v>0.1884398013353348</v>
+        <v>0.2900653779506683</v>
       </c>
       <c r="E393" t="n">
-        <v>0.2861481076931396</v>
+        <v>0.3200232998982508</v>
       </c>
       <c r="F393" t="n">
         <v>0</v>
@@ -8514,10 +8514,10 @@
         <v>0.6363583389339815</v>
       </c>
       <c r="D394" t="n">
-        <v>0.9866858720779419</v>
+        <v>0.8462345004081726</v>
       </c>
       <c r="E394" t="n">
-        <v>0.7715523513165259</v>
+        <v>0.7247352274266028</v>
       </c>
       <c r="F394" t="n">
         <v>1</v>
@@ -8534,10 +8534,10 @@
         <v>0.6864692785718601</v>
       </c>
       <c r="D395" t="n">
-        <v>0.9892808198928833</v>
+        <v>0.8586807250976562</v>
       </c>
       <c r="E395" t="n">
-        <v>0.8158946635947341</v>
+        <v>0.7723612986629917</v>
       </c>
       <c r="F395" t="n">
         <v>1</v>
@@ -8554,10 +8554,10 @@
         <v>0.5562953687400907</v>
       </c>
       <c r="D396" t="n">
-        <v>0.8161889314651489</v>
+        <v>0.6620104908943176</v>
       </c>
       <c r="E396" t="n">
-        <v>0.6752099703579111</v>
+        <v>0.6238171568343006</v>
       </c>
       <c r="F396" t="n">
         <v>1</v>
@@ -8571,13 +8571,13 @@
         <v>0.787978039840299</v>
       </c>
       <c r="C397" t="n">
-        <v>0.7135040611718857</v>
+        <v>0.7135040611718858</v>
       </c>
       <c r="D397" t="n">
-        <v>0.993527889251709</v>
+        <v>0.8612961769104004</v>
       </c>
       <c r="E397" t="n">
-        <v>0.8316699967546312</v>
+        <v>0.7875927593075284</v>
       </c>
       <c r="F397" t="n">
         <v>1</v>
@@ -8594,10 +8594,10 @@
         <v>0.72208061785221</v>
       </c>
       <c r="D398" t="n">
-        <v>0.9886825680732727</v>
+        <v>0.8508273363113403</v>
       </c>
       <c r="E398" t="n">
-        <v>0.8464188767631065</v>
+        <v>0.8004671328424623</v>
       </c>
       <c r="F398" t="n">
         <v>1</v>
@@ -8614,10 +8614,10 @@
         <v>0.8470791486319997</v>
       </c>
       <c r="D399" t="n">
-        <v>0.9984939694404602</v>
+        <v>0.8661917448043823</v>
       </c>
       <c r="E399" t="n">
-        <v>0.8984350862894684</v>
+        <v>0.8543343447441091</v>
       </c>
       <c r="F399" t="n">
         <v>1</v>
@@ -8634,10 +8634,10 @@
         <v>0.8009019741469826</v>
       </c>
       <c r="D400" t="n">
-        <v>0.9904884099960327</v>
+        <v>0.8621533513069153</v>
       </c>
       <c r="E400" t="n">
-        <v>0.8614116082658038</v>
+        <v>0.8186332553694312</v>
       </c>
       <c r="F400" t="n">
         <v>1</v>
@@ -8654,10 +8654,10 @@
         <v>0.502995945556844</v>
       </c>
       <c r="D401" t="n">
-        <v>0.8791829943656921</v>
+        <v>0.5424315333366394</v>
       </c>
       <c r="E401" t="n">
-        <v>0.6541051635210525</v>
+        <v>0.5418546765113682</v>
       </c>
       <c r="F401" t="n">
         <v>1</v>
@@ -8671,13 +8671,13 @@
         <v>0.7418033458940942</v>
       </c>
       <c r="C402" t="n">
-        <v>0.7574872279660374</v>
+        <v>0.7574872279660375</v>
       </c>
       <c r="D402" t="n">
-        <v>0.9931848645210266</v>
+        <v>0.8546494245529175</v>
       </c>
       <c r="E402" t="n">
-        <v>0.8308251461270527</v>
+        <v>0.7846466661376831</v>
       </c>
       <c r="F402" t="n">
         <v>1</v>
@@ -8694,10 +8694,10 @@
         <v>0.7936473596863918</v>
       </c>
       <c r="D403" t="n">
-        <v>0.9943626523017883</v>
+        <v>0.8575764894485474</v>
       </c>
       <c r="E403" t="n">
-        <v>0.8581647332942216</v>
+        <v>0.8125693456764745</v>
       </c>
       <c r="F403" t="n">
         <v>1</v>
@@ -8714,10 +8714,10 @@
         <v>0.7771040206235172</v>
       </c>
       <c r="D404" t="n">
-        <v>0.9960794448852539</v>
+        <v>0.8604474067687988</v>
       </c>
       <c r="E404" t="n">
-        <v>0.8503709341285394</v>
+        <v>0.8051602547563877</v>
       </c>
       <c r="F404" t="n">
         <v>1</v>
@@ -8734,10 +8734,10 @@
         <v>0.7833007033817825</v>
       </c>
       <c r="D405" t="n">
-        <v>0.9961131811141968</v>
+        <v>0.8613079786300659</v>
       </c>
       <c r="E405" t="n">
-        <v>0.8548658909355241</v>
+        <v>0.8099308234408138</v>
       </c>
       <c r="F405" t="n">
         <v>1</v>
@@ -8754,10 +8754,10 @@
         <v>0.7479820533627246</v>
       </c>
       <c r="D406" t="n">
-        <v>0.9953027963638306</v>
+        <v>0.8532625436782837</v>
       </c>
       <c r="E406" t="n">
-        <v>0.8232224303106545</v>
+        <v>0.7758756794154721</v>
       </c>
       <c r="F406" t="n">
         <v>1</v>
@@ -8771,13 +8771,13 @@
         <v>0.7930430639474374</v>
       </c>
       <c r="C407" t="n">
-        <v>0.8208268376309634</v>
+        <v>0.8208268376309636</v>
       </c>
       <c r="D407" t="n">
-        <v>0.9965326189994812</v>
+        <v>0.8594182729721069</v>
       </c>
       <c r="E407" t="n">
-        <v>0.8701341735259606</v>
+        <v>0.824429391516836</v>
       </c>
       <c r="F407" t="n">
         <v>1</v>
@@ -8794,10 +8794,10 @@
         <v>0.8244830903733057</v>
       </c>
       <c r="D408" t="n">
-        <v>0.9946688413619995</v>
+        <v>0.8583051562309265</v>
       </c>
       <c r="E408" t="n">
-        <v>0.8725259545060514</v>
+        <v>0.8270713927956937</v>
       </c>
       <c r="F408" t="n">
         <v>1</v>
@@ -8811,13 +8811,13 @@
         <v>0.7133755643709148</v>
       </c>
       <c r="C409" t="n">
-        <v>0.6039945885371903</v>
+        <v>0.6039945885371905</v>
       </c>
       <c r="D409" t="n">
-        <v>0.9885141253471375</v>
+        <v>0.8549318313598633</v>
       </c>
       <c r="E409" t="n">
-        <v>0.7686280927517476</v>
+        <v>0.7241006614226562</v>
       </c>
       <c r="F409" t="n">
         <v>1</v>
@@ -8834,10 +8834,10 @@
         <v>0.3786423026145093</v>
       </c>
       <c r="D410" t="n">
-        <v>0.6667500138282776</v>
+        <v>0.4178156852722168</v>
       </c>
       <c r="E410" t="n">
-        <v>0.4684499743234631</v>
+        <v>0.3854718648047762</v>
       </c>
       <c r="F410" t="n">
         <v>0</v>
@@ -8854,10 +8854,10 @@
         <v>0.6006316212384999</v>
       </c>
       <c r="D411" t="n">
-        <v>0.9604487419128418</v>
+        <v>0.8462163805961609</v>
       </c>
       <c r="E411" t="n">
-        <v>0.7280668568947609</v>
+        <v>0.6899894031225339</v>
       </c>
       <c r="F411" t="n">
         <v>1</v>
@@ -8874,10 +8874,10 @@
         <v>0.7126136619189759</v>
       </c>
       <c r="D412" t="n">
-        <v>0.9966498613357544</v>
+        <v>0.8639394044876099</v>
       </c>
       <c r="E412" t="n">
-        <v>0.8345889377372743</v>
+        <v>0.7903521187878928</v>
       </c>
       <c r="F412" t="n">
         <v>1</v>
@@ -8894,10 +8894,10 @@
         <v>0.8798552417242412</v>
       </c>
       <c r="D413" t="n">
-        <v>0.9973646402359009</v>
+        <v>0.8645535707473755</v>
       </c>
       <c r="E413" t="n">
-        <v>0.9134944373944965</v>
+        <v>0.8692240808983214</v>
       </c>
       <c r="F413" t="n">
         <v>1</v>
@@ -8914,10 +8914,10 @@
         <v>0.7650165969208393</v>
       </c>
       <c r="D414" t="n">
-        <v>0.9963279962539673</v>
+        <v>0.8640632629394531</v>
       </c>
       <c r="E414" t="n">
-        <v>0.8628824287581517</v>
+        <v>0.8187941843199803</v>
       </c>
       <c r="F414" t="n">
         <v>1</v>
@@ -8934,10 +8934,10 @@
         <v>0.859869174747425</v>
       </c>
       <c r="D415" t="n">
-        <v>0.9987711906433105</v>
+        <v>0.8664324879646301</v>
       </c>
       <c r="E415" t="n">
-        <v>0.9009376972698764</v>
+        <v>0.8568247963769829</v>
       </c>
       <c r="F415" t="n">
         <v>1</v>
@@ -8954,10 +8954,10 @@
         <v>0.7880362334235065</v>
       </c>
       <c r="D416" t="n">
-        <v>0.9971254467964172</v>
+        <v>0.8665767908096313</v>
       </c>
       <c r="E416" t="n">
-        <v>0.8563226345686893</v>
+        <v>0.8128064159064273</v>
       </c>
       <c r="F416" t="n">
         <v>1</v>
@@ -8974,10 +8974,10 @@
         <v>0.6868049413319295</v>
       </c>
       <c r="D417" t="n">
-        <v>0.9964599609375</v>
+        <v>0.8656506538391113</v>
       </c>
       <c r="E417" t="n">
-        <v>0.8213153681278996</v>
+        <v>0.7777122657617701</v>
       </c>
       <c r="F417" t="n">
         <v>1</v>
@@ -8994,10 +8994,10 @@
         <v>0.8686777703504157</v>
       </c>
       <c r="D418" t="n">
-        <v>0.989209771156311</v>
+        <v>0.8531869053840637</v>
       </c>
       <c r="E418" t="n">
-        <v>0.9068540270118174</v>
+        <v>0.8615130717544016</v>
       </c>
       <c r="F418" t="n">
         <v>1</v>
@@ -9011,13 +9011,13 @@
         <v>0.7145033430729841</v>
       </c>
       <c r="C419" t="n">
-        <v>0.6308293235235162</v>
+        <v>0.6308293235235161</v>
       </c>
       <c r="D419" t="n">
-        <v>0.8841019868850708</v>
+        <v>0.7270396947860718</v>
       </c>
       <c r="E419" t="n">
-        <v>0.743144884493857</v>
+        <v>0.690790787127524</v>
       </c>
       <c r="F419" t="n">
         <v>1</v>
@@ -9034,10 +9034,10 @@
         <v>0.6517866745386142</v>
       </c>
       <c r="D420" t="n">
-        <v>0.9874672889709473</v>
+        <v>0.8553786277770996</v>
       </c>
       <c r="E420" t="n">
-        <v>0.8061410134306213</v>
+        <v>0.7621114596993387</v>
       </c>
       <c r="F420" t="n">
         <v>1</v>
@@ -9051,13 +9051,13 @@
         <v>0.7135967912399742</v>
       </c>
       <c r="C421" t="n">
-        <v>0.5415980555611343</v>
+        <v>0.5415980555611344</v>
       </c>
       <c r="D421" t="n">
-        <v>0.9561630487442017</v>
+        <v>0.8199061155319214</v>
       </c>
       <c r="E421" t="n">
-        <v>0.7371192985151035</v>
+        <v>0.6917003207776767</v>
       </c>
       <c r="F421" t="n">
         <v>1</v>
@@ -9071,13 +9071,13 @@
         <v>0.6859772041078788</v>
       </c>
       <c r="C422" t="n">
-        <v>0.662200214252108</v>
+        <v>0.6622002142521078</v>
       </c>
       <c r="D422" t="n">
-        <v>0.9454229474067688</v>
+        <v>0.8204558491706848</v>
       </c>
       <c r="E422" t="n">
-        <v>0.7645334552555852</v>
+        <v>0.7228777558435571</v>
       </c>
       <c r="F422" t="n">
         <v>1</v>
@@ -9094,10 +9094,10 @@
         <v>0.6757789996253505</v>
       </c>
       <c r="D423" t="n">
-        <v>0.975914478302002</v>
+        <v>0.8353549242019653</v>
       </c>
       <c r="E423" t="n">
-        <v>0.7882270081789909</v>
+        <v>0.7413738234789787</v>
       </c>
       <c r="F423" t="n">
         <v>1</v>
@@ -9114,10 +9114,10 @@
         <v>0.8291009180445436</v>
       </c>
       <c r="D424" t="n">
-        <v>0.9925235509872437</v>
+        <v>0.8619383573532104</v>
       </c>
       <c r="E424" t="n">
-        <v>0.8814369134452863</v>
+        <v>0.8379085155672752</v>
       </c>
       <c r="F424" t="n">
         <v>1</v>
@@ -9131,13 +9131,13 @@
         <v>0.8482116567794409</v>
       </c>
       <c r="C425" t="n">
-        <v>0.831284053472201</v>
+        <v>0.8312840534722012</v>
       </c>
       <c r="D425" t="n">
-        <v>0.9956901669502258</v>
+        <v>0.8623650670051575</v>
       </c>
       <c r="E425" t="n">
-        <v>0.8917286257339558</v>
+        <v>0.8472869257522665</v>
       </c>
       <c r="F425" t="n">
         <v>1</v>
@@ -9154,10 +9154,10 @@
         <v>0.8115896037647703</v>
       </c>
       <c r="D426" t="n">
-        <v>0.9857944250106812</v>
+        <v>0.8563973307609558</v>
       </c>
       <c r="E426" t="n">
-        <v>0.8795774859950306</v>
+        <v>0.8364451212451222</v>
       </c>
       <c r="F426" t="n">
         <v>1</v>
@@ -9174,10 +9174,10 @@
         <v>0.7982182249223835</v>
       </c>
       <c r="D427" t="n">
-        <v>0.9892711639404297</v>
+        <v>0.8600137829780579</v>
       </c>
       <c r="E427" t="n">
-        <v>0.868975370044515</v>
+        <v>0.8258895763903911</v>
       </c>
       <c r="F427" t="n">
         <v>1</v>
@@ -9194,10 +9194,10 @@
         <v>0.8268900933199909</v>
       </c>
       <c r="D428" t="n">
-        <v>0.9859081506729126</v>
+        <v>0.8546501398086548</v>
       </c>
       <c r="E428" t="n">
-        <v>0.8758439571577042</v>
+        <v>0.8320912868696183</v>
       </c>
       <c r="F428" t="n">
         <v>1</v>
@@ -9211,13 +9211,13 @@
         <v>0.7409991849871445</v>
       </c>
       <c r="C429" t="n">
-        <v>0.7199336933378517</v>
+        <v>0.7199336933378516</v>
       </c>
       <c r="D429" t="n">
-        <v>0.9691435694694519</v>
+        <v>0.8506466150283813</v>
       </c>
       <c r="E429" t="n">
-        <v>0.8100254825981494</v>
+        <v>0.7705264977844591</v>
       </c>
       <c r="F429" t="n">
         <v>1</v>
@@ -9234,10 +9234,10 @@
         <v>0.8197207957888043</v>
       </c>
       <c r="D430" t="n">
-        <v>0.991702675819397</v>
+        <v>0.859566330909729</v>
       </c>
       <c r="E430" t="n">
-        <v>0.8845572605739355</v>
+        <v>0.8405118122707128</v>
       </c>
       <c r="F430" t="n">
         <v>1</v>
@@ -9254,10 +9254,10 @@
         <v>0.7198258502273462</v>
       </c>
       <c r="D431" t="n">
-        <v>0.9858384132385254</v>
+        <v>0.8440331220626831</v>
       </c>
       <c r="E431" t="n">
-        <v>0.8139527224087942</v>
+        <v>0.7666842920168468</v>
       </c>
       <c r="F431" t="n">
         <v>1</v>
@@ -9274,10 +9274,10 @@
         <v>0.8184575387066209</v>
       </c>
       <c r="D432" t="n">
-        <v>0.9793519973754883</v>
+        <v>0.8537769317626953</v>
       </c>
       <c r="E432" t="n">
-        <v>0.8678249752389889</v>
+        <v>0.8259666200347247</v>
       </c>
       <c r="F432" t="n">
         <v>1</v>
@@ -9294,10 +9294,10 @@
         <v>0.8584211747340416</v>
       </c>
       <c r="D433" t="n">
-        <v>0.9912605285644531</v>
+        <v>0.860348105430603</v>
       </c>
       <c r="E433" t="n">
-        <v>0.8952349773031734</v>
+        <v>0.8515975029252233</v>
       </c>
       <c r="F433" t="n">
         <v>1</v>
@@ -9311,13 +9311,13 @@
         <v>0.7752135500054844</v>
       </c>
       <c r="C434" t="n">
-        <v>0.7627177089442388</v>
+        <v>0.762717708944239</v>
       </c>
       <c r="D434" t="n">
-        <v>0.9889510869979858</v>
+        <v>0.8499051332473755</v>
       </c>
       <c r="E434" t="n">
-        <v>0.842294115315903</v>
+        <v>0.7959454640656997</v>
       </c>
       <c r="F434" t="n">
         <v>1</v>
@@ -9334,10 +9334,10 @@
         <v>0.8224363253052356</v>
       </c>
       <c r="D435" t="n">
-        <v>0.9943609237670898</v>
+        <v>0.858842670917511</v>
       </c>
       <c r="E435" t="n">
-        <v>0.8782272793980841</v>
+        <v>0.8330545284482245</v>
       </c>
       <c r="F435" t="n">
         <v>1</v>
@@ -9354,10 +9354,10 @@
         <v>0.7247207094063886</v>
       </c>
       <c r="D436" t="n">
-        <v>0.986178994178772</v>
+        <v>0.8497333526611328</v>
       </c>
       <c r="E436" t="n">
-        <v>0.8388229963327504</v>
+        <v>0.7933411158268706</v>
       </c>
       <c r="F436" t="n">
         <v>1</v>
@@ -9374,10 +9374,10 @@
         <v>0.8216754545103029</v>
       </c>
       <c r="D437" t="n">
-        <v>0.9924775958061218</v>
+        <v>0.861672043800354</v>
       </c>
       <c r="E437" t="n">
-        <v>0.8850075850119343</v>
+        <v>0.8414057343433451</v>
       </c>
       <c r="F437" t="n">
         <v>1</v>
@@ -9394,10 +9394,10 @@
         <v>0.800931950076599</v>
       </c>
       <c r="D438" t="n">
-        <v>0.9827893972396851</v>
+        <v>0.8575212359428406</v>
       </c>
       <c r="E438" t="n">
-        <v>0.8683061224333732</v>
+        <v>0.8265500686677584</v>
       </c>
       <c r="F438" t="n">
         <v>1</v>
@@ -9411,13 +9411,13 @@
         <v>0.8134696906291824</v>
       </c>
       <c r="C439" t="n">
-        <v>0.7926208262448645</v>
+        <v>0.7926208262448644</v>
       </c>
       <c r="D439" t="n">
-        <v>0.9851514101028442</v>
+        <v>0.8498517274856567</v>
       </c>
       <c r="E439" t="n">
-        <v>0.863747308992297</v>
+        <v>0.8186474147865678</v>
       </c>
       <c r="F439" t="n">
         <v>1</v>
@@ -9431,13 +9431,13 @@
         <v>0.7885729067093337</v>
       </c>
       <c r="C440" t="n">
-        <v>0.7815909786712015</v>
+        <v>0.7815909786712013</v>
       </c>
       <c r="D440" t="n">
-        <v>0.992489218711853</v>
+        <v>0.8599184155464172</v>
       </c>
       <c r="E440" t="n">
-        <v>0.8542177013641293</v>
+        <v>0.8100274336423174</v>
       </c>
       <c r="F440" t="n">
         <v>1</v>
@@ -9454,10 +9454,10 @@
         <v>0.4836415638953584</v>
       </c>
       <c r="D441" t="n">
-        <v>0.8982813954353333</v>
+        <v>0.7140305638313293</v>
       </c>
       <c r="E441" t="n">
-        <v>0.7046655035942778</v>
+        <v>0.6432485597262766</v>
       </c>
       <c r="F441" t="n">
         <v>1</v>
@@ -9471,13 +9471,13 @@
         <v>0.3562836353687553</v>
       </c>
       <c r="C442" t="n">
-        <v>0.4470473771108646</v>
+        <v>0.4470473771108645</v>
       </c>
       <c r="D442" t="n">
-        <v>0.7716215848922729</v>
+        <v>0.4591713547706604</v>
       </c>
       <c r="E442" t="n">
-        <v>0.5249841991239643</v>
+        <v>0.42083412241676</v>
       </c>
       <c r="F442" t="n">
         <v>0</v>
@@ -9494,10 +9494,10 @@
         <v>0.6026311141473918</v>
       </c>
       <c r="D443" t="n">
-        <v>0.9312773942947388</v>
+        <v>0.8239958882331848</v>
       </c>
       <c r="E443" t="n">
-        <v>0.7192708422469708</v>
+        <v>0.6835103402264529</v>
       </c>
       <c r="F443" t="n">
         <v>1</v>
@@ -9514,10 +9514,10 @@
         <v>0.9004654559839228</v>
       </c>
       <c r="D444" t="n">
-        <v>0.9971410632133484</v>
+        <v>0.8644468188285828</v>
       </c>
       <c r="E444" t="n">
-        <v>0.9238369017873297</v>
+        <v>0.8796054869924078</v>
       </c>
       <c r="F444" t="n">
         <v>1</v>
@@ -9534,10 +9534,10 @@
         <v>0.8335159636057974</v>
       </c>
       <c r="D445" t="n">
-        <v>0.9922496676445007</v>
+        <v>0.8573156595230103</v>
       </c>
       <c r="E445" t="n">
-        <v>0.8948339914100667</v>
+        <v>0.8498559887029032</v>
       </c>
       <c r="F445" t="n">
         <v>1</v>
@@ -9554,10 +9554,10 @@
         <v>0.8287411572927386</v>
       </c>
       <c r="D446" t="n">
-        <v>0.9875429272651672</v>
+        <v>0.8529621362686157</v>
       </c>
       <c r="E446" t="n">
-        <v>0.8901030683863084</v>
+        <v>0.8452428047207912</v>
       </c>
       <c r="F446" t="n">
         <v>1</v>
@@ -9574,10 +9574,10 @@
         <v>0.7806574793310066</v>
       </c>
       <c r="D447" t="n">
-        <v>0.9873068928718567</v>
+        <v>0.8533104658126831</v>
       </c>
       <c r="E447" t="n">
-        <v>0.8650181084238815</v>
+        <v>0.8203526327374903</v>
       </c>
       <c r="F447" t="n">
         <v>1</v>
@@ -9594,10 +9594,10 @@
         <v>0.6685473547061577</v>
       </c>
       <c r="D448" t="n">
-        <v>0.9827615022659302</v>
+        <v>0.8388373255729675</v>
       </c>
       <c r="E448" t="n">
-        <v>0.8205930775366429</v>
+        <v>0.772618351972322</v>
       </c>
       <c r="F448" t="n">
         <v>1</v>
@@ -9614,10 +9614,10 @@
         <v>0.8291550998153276</v>
       </c>
       <c r="D449" t="n">
-        <v>0.987705409526825</v>
+        <v>0.8491109013557434</v>
       </c>
       <c r="E449" t="n">
-        <v>0.8918630362528926</v>
+        <v>0.8456648668625322</v>
       </c>
       <c r="F449" t="n">
         <v>1</v>
@@ -9634,10 +9634,10 @@
         <v>0.7715708617829298</v>
       </c>
       <c r="D450" t="n">
-        <v>0.9866011738777161</v>
+        <v>0.8490026593208313</v>
       </c>
       <c r="E450" t="n">
-        <v>0.8656592064487701</v>
+        <v>0.8197930349298086</v>
       </c>
       <c r="F450" t="n">
         <v>1</v>
@@ -9654,10 +9654,10 @@
         <v>0.6244529473438611</v>
       </c>
       <c r="D451" t="n">
-        <v>0.9810260534286499</v>
+        <v>0.8313407897949219</v>
       </c>
       <c r="E451" t="n">
-        <v>0.7840338483113016</v>
+        <v>0.7341387604333923</v>
       </c>
       <c r="F451" t="n">
         <v>1</v>
@@ -9674,10 +9674,10 @@
         <v>0.5581548593975223</v>
       </c>
       <c r="D452" t="n">
-        <v>0.9914830923080444</v>
+        <v>0.8435249328613281</v>
       </c>
       <c r="E452" t="n">
-        <v>0.7523086189554703</v>
+        <v>0.7029892324732315</v>
       </c>
       <c r="F452" t="n">
         <v>1</v>
@@ -9694,10 +9694,10 @@
         <v>0.7900343587070606</v>
       </c>
       <c r="D453" t="n">
-        <v>0.9853440523147583</v>
+        <v>0.8466750979423523</v>
       </c>
       <c r="E453" t="n">
-        <v>0.8747339875906412</v>
+        <v>0.8285110027998392</v>
       </c>
       <c r="F453" t="n">
         <v>1</v>
@@ -9714,10 +9714,10 @@
         <v>0.8727687094200464</v>
       </c>
       <c r="D454" t="n">
-        <v>0.9910991787910461</v>
+        <v>0.854863166809082</v>
       </c>
       <c r="E454" t="n">
-        <v>0.9125071165661205</v>
+        <v>0.8670951125721325</v>
       </c>
       <c r="F454" t="n">
         <v>1</v>
@@ -9734,10 +9734,10 @@
         <v>0.8595648567249625</v>
       </c>
       <c r="D455" t="n">
-        <v>0.9974894523620605</v>
+        <v>0.8641499280929565</v>
       </c>
       <c r="E455" t="n">
-        <v>0.8993504866071653</v>
+        <v>0.854903978517464</v>
       </c>
       <c r="F455" t="n">
         <v>1</v>
@@ -9754,10 +9754,10 @@
         <v>0.8748318617716411</v>
       </c>
       <c r="D456" t="n">
-        <v>0.9948153495788574</v>
+        <v>0.8608554005622864</v>
       </c>
       <c r="E456" t="n">
-        <v>0.9088335152825185</v>
+        <v>0.8641801989436616</v>
       </c>
       <c r="F456" t="n">
         <v>1</v>
@@ -9774,10 +9774,10 @@
         <v>0.7429713629347702</v>
       </c>
       <c r="D457" t="n">
-        <v>0.992911159992218</v>
+        <v>0.8522483706474304</v>
       </c>
       <c r="E457" t="n">
-        <v>0.8400046871746856</v>
+        <v>0.793117090726423</v>
       </c>
       <c r="F457" t="n">
         <v>1</v>
@@ -9791,13 +9791,13 @@
         <v>0.810431171330606</v>
       </c>
       <c r="C458" t="n">
-        <v>0.7576538612573916</v>
+        <v>0.7576538612573918</v>
       </c>
       <c r="D458" t="n">
-        <v>0.9853591918945312</v>
+        <v>0.8464530110359192</v>
       </c>
       <c r="E458" t="n">
-        <v>0.8511480748275096</v>
+        <v>0.8048460145413058</v>
       </c>
       <c r="F458" t="n">
         <v>1</v>
@@ -9814,10 +9814,10 @@
         <v>0.8614416402453047</v>
       </c>
       <c r="D459" t="n">
-        <v>0.997148871421814</v>
+        <v>0.8626841306686401</v>
       </c>
       <c r="E459" t="n">
-        <v>0.9019159743297332</v>
+        <v>0.8570943940786754</v>
       </c>
       <c r="F459" t="n">
         <v>1</v>
@@ -9834,10 +9834,10 @@
         <v>0.7661670651755109</v>
       </c>
       <c r="D460" t="n">
-        <v>0.9968263506889343</v>
+        <v>0.8623013496398926</v>
       </c>
       <c r="E460" t="n">
-        <v>0.8511304541126045</v>
+        <v>0.8062887870962573</v>
       </c>
       <c r="F460" t="n">
         <v>1</v>
@@ -9854,10 +9854,10 @@
         <v>0.8099725594903948</v>
       </c>
       <c r="D461" t="n">
-        <v>0.9973225593566895</v>
+        <v>0.8610869646072388</v>
       </c>
       <c r="E461" t="n">
-        <v>0.8811265121948062</v>
+        <v>0.8357146472783227</v>
       </c>
       <c r="F461" t="n">
         <v>1</v>
@@ -9874,10 +9874,10 @@
         <v>0.7954073643862394</v>
       </c>
       <c r="D462" t="n">
-        <v>0.9953752756118774</v>
+        <v>0.8601789474487305</v>
       </c>
       <c r="E462" t="n">
-        <v>0.8605705271675764</v>
+        <v>0.8155050844465275</v>
       </c>
       <c r="F462" t="n">
         <v>1</v>
@@ -9891,13 +9891,13 @@
         <v>0.8085978832990787</v>
       </c>
       <c r="C463" t="n">
-        <v>0.818496641342648</v>
+        <v>0.8184966413426482</v>
       </c>
       <c r="D463" t="n">
-        <v>0.9910047650337219</v>
+        <v>0.8596627116203308</v>
       </c>
       <c r="E463" t="n">
-        <v>0.8726997632251495</v>
+        <v>0.8289190787540193</v>
       </c>
       <c r="F463" t="n">
         <v>1</v>
@@ -9914,10 +9914,10 @@
         <v>0.7328605791333827</v>
       </c>
       <c r="D464" t="n">
-        <v>0.9912261962890625</v>
+        <v>0.8553325533866882</v>
       </c>
       <c r="E464" t="n">
-        <v>0.8299889803944535</v>
+        <v>0.7846910994269954</v>
       </c>
       <c r="F464" t="n">
         <v>1</v>
@@ -9934,10 +9934,10 @@
         <v>0.8355287317066251</v>
       </c>
       <c r="D465" t="n">
-        <v>0.9947642087936401</v>
+        <v>0.8619686365127563</v>
       </c>
       <c r="E465" t="n">
-        <v>0.8857059743279035</v>
+        <v>0.841440783567609</v>
       </c>
       <c r="F465" t="n">
         <v>1</v>
@@ -9954,10 +9954,10 @@
         <v>0.858713517873759</v>
       </c>
       <c r="D466" t="n">
-        <v>0.9938785433769226</v>
+        <v>0.8562424778938293</v>
       </c>
       <c r="E466" t="n">
-        <v>0.9035402775978421</v>
+        <v>0.8576615891034777</v>
       </c>
       <c r="F466" t="n">
         <v>1</v>
@@ -9974,10 +9974,10 @@
         <v>0.6697785509851986</v>
       </c>
       <c r="D467" t="n">
-        <v>0.9852485656738281</v>
+        <v>0.8462797999382019</v>
       </c>
       <c r="E467" t="n">
-        <v>0.8169132487227313</v>
+        <v>0.7705903268108559</v>
       </c>
       <c r="F467" t="n">
         <v>1</v>

--- a/ensemble/eval_results/ensemble_eval_result.xlsx
+++ b/ensemble/eval_results/ensemble_eval_result.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Comparison" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Predictions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CNN_Loss_History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +481,11 @@
           <t>MCC (Test)</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Min CV Loss</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -514,6 +520,7 @@
       <c r="J2" t="n">
         <v>0.8239</v>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -548,6 +555,7 @@
       <c r="J3" t="n">
         <v>0.8554</v>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -556,31 +564,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8421</v>
+        <v>0.9408</v>
       </c>
       <c r="D4" t="n">
-        <v>0.472</v>
+        <v>0.576</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9942</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.973</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6545</v>
+        <v>0.6116</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7826</v>
+        <v>0.759</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9142</v>
+        <v>0.8991</v>
       </c>
       <c r="J4" t="n">
-        <v>0.754</v>
+        <v>0.7337</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.381</v>
       </c>
     </row>
     <row r="5">
@@ -590,32 +601,33 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9564</v>
+        <v>0.9902</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9258</v>
+        <v>0.9383</v>
       </c>
       <c r="D5" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9956</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>0.973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7423</v>
+        <v>0.766</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8421</v>
+        <v>0.8571</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9421</v>
+        <v>0.9485</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8185</v>
-      </c>
+        <v>0.8351</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -674,13 +686,13 @@
         <v>0.3840620868297284</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6401544809341431</v>
+        <v>0.7640960812568665</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4927047919833665</v>
+        <v>0.5340186587576077</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -694,10 +706,10 @@
         <v>0.5733754884752394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8106477856636047</v>
+        <v>0.8802544474601746</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7096565152938826</v>
+        <v>0.7328587358927393</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -714,10 +726,10 @@
         <v>0.3362632856158089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5343343019485474</v>
+        <v>0.8109527826309204</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4005425994289453</v>
+        <v>0.4927487596564029</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -734,10 +746,10 @@
         <v>0.197416943404845</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07995949685573578</v>
+        <v>0.006774462759494781</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1712765534836484</v>
+        <v>0.1468815421182348</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -754,10 +766,10 @@
         <v>0.1304129038381526</v>
       </c>
       <c r="D6" t="n">
-        <v>0.082851842045784</v>
+        <v>0.002893198048695922</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1062360821795112</v>
+        <v>0.07958320084714854</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -774,10 +786,10 @@
         <v>0.1749632749314859</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07148779183626175</v>
+        <v>0.0005258172168396413</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1240139724174709</v>
+        <v>0.1003599808776636</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -794,10 +806,10 @@
         <v>0.1620237434290886</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1018553152680397</v>
+        <v>0.01377213560044765</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1479968797774513</v>
+        <v>0.118635819888254</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -814,10 +826,10 @@
         <v>0.2067114025008345</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1624566614627838</v>
+        <v>0.180578425526619</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2073317991531692</v>
+        <v>0.2133723871744476</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -834,10 +846,10 @@
         <v>0.2094139514215262</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09507719427347183</v>
+        <v>0.01162613462656736</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1894164421183323</v>
+        <v>0.1615994222360308</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -854,10 +866,10 @@
         <v>0.3121416345283932</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09311451762914658</v>
+        <v>0.1023872345685959</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3284254710977554</v>
+        <v>0.3315163767442385</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -871,13 +883,13 @@
         <v>0.467609268054578</v>
       </c>
       <c r="C12" t="n">
-        <v>0.34482818316826</v>
+        <v>0.3448281831682601</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4074588716030121</v>
+        <v>0.3318856656551361</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4066321076086167</v>
+        <v>0.3814410389593247</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -894,10 +906,10 @@
         <v>0.1363991400315087</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07669267803430557</v>
+        <v>0.00314352591522038</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1243579645454831</v>
+        <v>0.09984158050578806</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -914,10 +926,10 @@
         <v>0.1328238651082339</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08403961360454559</v>
+        <v>0.007772163953632116</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1102253996655401</v>
+        <v>0.08480291644856892</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -934,10 +946,10 @@
         <v>0.1570568250298337</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08036602288484573</v>
+        <v>0.002460514428094029</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1343884531633704</v>
+        <v>0.1084199503444532</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -954,10 +966,10 @@
         <v>0.1738206865066103</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1260222643613815</v>
+        <v>0.06969129294157028</v>
       </c>
       <c r="E16" t="n">
-        <v>0.175798533112714</v>
+        <v>0.1570215426394435</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -974,10 +986,10 @@
         <v>0.4454146041673416</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7301503419876099</v>
+        <v>0.9036062955856323</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5691817273156614</v>
+        <v>0.6270003785150022</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -994,10 +1006,10 @@
         <v>0.1063094770430837</v>
       </c>
       <c r="D18" t="n">
-        <v>0.07430438697338104</v>
+        <v>0.001144084730185568</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08941082806436668</v>
+        <v>0.06502406064996819</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1011,13 +1023,13 @@
         <v>0.4501171343442</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3300317782652731</v>
+        <v>0.3300317782652732</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1774915903806686</v>
+        <v>0.1115614771842957</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3192135009967139</v>
+        <v>0.297236796597923</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1034,10 +1046,10 @@
         <v>0.2254710742981195</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1683749258518219</v>
+        <v>0.1004083156585693</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2174273602198042</v>
+        <v>0.19477182348872</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1054,10 +1066,10 @@
         <v>0.371430941548388</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3201504349708557</v>
+        <v>0.5323368310928345</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3487193973004567</v>
+        <v>0.4194481960077829</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1074,10 +1086,10 @@
         <v>0.2076885775679576</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08038441836833954</v>
+        <v>0.01321571506559849</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1952623403300092</v>
+        <v>0.1728727725624288</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1094,10 +1106,10 @@
         <v>0.2466677054434032</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08228681981563568</v>
+        <v>0.01177948899567127</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1926210724622038</v>
+        <v>0.169118628855549</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1114,10 +1126,10 @@
         <v>0.2037462076810409</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0772460550069809</v>
+        <v>0.003638957161456347</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1764995527911066</v>
+        <v>0.1519638535092651</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1134,10 +1146,10 @@
         <v>0.1141275809874744</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1044724434614182</v>
+        <v>0.007823584601283073</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1218023588594851</v>
+        <v>0.0895860725727734</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1154,10 +1166,10 @@
         <v>0.2108669414302069</v>
       </c>
       <c r="D26" t="n">
-        <v>0.09751566499471664</v>
+        <v>0.04197414964437485</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1862311329290062</v>
+        <v>0.1677172944788923</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1174,10 +1186,10 @@
         <v>0.1522052698006219</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0811070054769516</v>
+        <v>0.01285972911864519</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1227895667465703</v>
+        <v>0.1000404746271348</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1194,10 +1206,10 @@
         <v>0.434211807854486</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6532812118530273</v>
+        <v>0.7813240885734558</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5508876088974239</v>
+        <v>0.5935685678042334</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -1211,13 +1223,13 @@
         <v>0.6963319065420144</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4888966980041123</v>
+        <v>0.4888966980041124</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8433486819267273</v>
+        <v>0.9840186238288879</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6761924288242845</v>
+        <v>0.7230824094583382</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -1234,10 +1246,10 @@
         <v>0.2780810266264825</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1993528604507446</v>
+        <v>0.420736700296402</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3484729604761252</v>
+        <v>0.422267573758011</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1254,10 +1266,10 @@
         <v>0.2871319729310349</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3110226988792419</v>
+        <v>0.3247651159763336</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3169432711549667</v>
+        <v>0.3215240768539973</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1274,10 +1286,10 @@
         <v>0.257434799193592</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3355513215065002</v>
+        <v>0.8382196426391602</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3168826554649961</v>
+        <v>0.4844387625092161</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1294,13 +1306,13 @@
         <v>0.3253541959000909</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4675439894199371</v>
+        <v>0.9380861520767212</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4138180606623145</v>
+        <v>0.5706654482145759</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1314,10 +1326,10 @@
         <v>0.2684088577622227</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4146960377693176</v>
+        <v>0.6514846682548523</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3769206728308603</v>
+        <v>0.4558502163260386</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1334,10 +1346,10 @@
         <v>0.4028275028754815</v>
       </c>
       <c r="D35" t="n">
-        <v>0.779198944568634</v>
+        <v>0.9141210317611694</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5851188455509323</v>
+        <v>0.6300928746151108</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -1354,10 +1366,10 @@
         <v>0.1350934922589146</v>
       </c>
       <c r="D36" t="n">
-        <v>0.09160153567790985</v>
+        <v>0.01555389352142811</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1312164213473964</v>
+        <v>0.1058672072952358</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1374,10 +1386,10 @@
         <v>0.4501275090499132</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7377341985702515</v>
+        <v>0.8811548352241516</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5983226070746389</v>
+        <v>0.6461294859592723</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -1391,13 +1403,13 @@
         <v>0.3694870253573097</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3120200740474516</v>
+        <v>0.3120200740474515</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1271708011627197</v>
+        <v>0.08257676661014557</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2695593001891603</v>
+        <v>0.2546946220049689</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1414,10 +1426,10 @@
         <v>0.1525936185354979</v>
       </c>
       <c r="D39" t="n">
-        <v>0.07603143155574799</v>
+        <v>0.004447101149708033</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1190913063226372</v>
+        <v>0.09522986285395725</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1434,10 +1446,10 @@
         <v>0.3782246135494279</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1030887216329575</v>
+        <v>0.07040233910083771</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3395864619003129</v>
+        <v>0.328691001056273</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1451,13 +1463,13 @@
         <v>0.2974227048719745</v>
       </c>
       <c r="C41" t="n">
-        <v>0.230841141912028</v>
+        <v>0.2308411419120279</v>
       </c>
       <c r="D41" t="n">
-        <v>0.124691866338253</v>
+        <v>0.03389675170183182</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2176519043740852</v>
+        <v>0.1873868661619447</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1474,10 +1486,10 @@
         <v>0.1465028461098328</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09147782623767853</v>
+        <v>0.008187382481992245</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1275849596308341</v>
+        <v>0.09982147837893864</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1494,10 +1506,10 @@
         <v>0.1623377990685961</v>
       </c>
       <c r="D43" t="n">
-        <v>0.08016782253980637</v>
+        <v>0.009114032611250877</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1418849571147085</v>
+        <v>0.1182003604718567</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1514,10 +1526,10 @@
         <v>0.1315338020594521</v>
       </c>
       <c r="D44" t="n">
-        <v>0.07677610963582993</v>
+        <v>0.006044634617865086</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1459137041035189</v>
+        <v>0.1223365457641972</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1534,10 +1546,10 @@
         <v>0.2784166040675529</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4199314117431641</v>
+        <v>0.3633109629154205</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3521446185644958</v>
+        <v>0.3332711356219146</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1551,13 +1563,13 @@
         <v>0.1695897593892664</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2378057669481435</v>
+        <v>0.2378057669481436</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1347412019968033</v>
+        <v>0.04393613710999489</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1807122427780711</v>
+        <v>0.1504438878158016</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1574,10 +1586,10 @@
         <v>0.2457921807875107</v>
       </c>
       <c r="D47" t="n">
-        <v>0.09939192235469818</v>
+        <v>0.0224878191947937</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2230326095707867</v>
+        <v>0.1973979085174852</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1594,10 +1606,10 @@
         <v>0.209244585855142</v>
       </c>
       <c r="D48" t="n">
-        <v>0.07859568297863007</v>
+        <v>0.001748386537656188</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2043784977854509</v>
+        <v>0.1787627323051263</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1614,10 +1626,10 @@
         <v>0.1427439829623747</v>
       </c>
       <c r="D49" t="n">
-        <v>0.07710108160972595</v>
+        <v>0.004057799465954304</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1168597294754114</v>
+        <v>0.09251196876082089</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1634,10 +1646,10 @@
         <v>0.1509608933820573</v>
       </c>
       <c r="D50" t="n">
-        <v>0.08196831494569778</v>
+        <v>0.004881610162556171</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1318835163386028</v>
+        <v>0.1061879480775556</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1654,10 +1666,10 @@
         <v>0.1139518175910539</v>
       </c>
       <c r="D51" t="n">
-        <v>0.07833297550678253</v>
+        <v>0.007151809986680746</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1094572274153282</v>
+        <v>0.085730172241961</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1671,13 +1683,13 @@
         <v>0.6082610657672887</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3900875671990131</v>
+        <v>0.390087567199013</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3464239239692688</v>
+        <v>0.4771513342857361</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4482575189785235</v>
+        <v>0.4918333224173459</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1694,10 +1706,10 @@
         <v>0.2054801333693836</v>
       </c>
       <c r="D53" t="n">
-        <v>0.09190525859594345</v>
+        <v>0.007350748870521784</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1991714927436041</v>
+        <v>0.1709866561684636</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1714,10 +1726,10 @@
         <v>0.1484410092213372</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0754503458738327</v>
+        <v>0.00146501581184566</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1055216634767056</v>
+        <v>0.08085988678937654</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1734,10 +1746,10 @@
         <v>0.1625413550263328</v>
       </c>
       <c r="D55" t="n">
-        <v>0.07501175254583359</v>
+        <v>0.01120107807219028</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1403287519632405</v>
+        <v>0.1190585271386927</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1754,10 +1766,10 @@
         <v>0.1639039215304618</v>
       </c>
       <c r="D56" t="n">
-        <v>0.07161860167980194</v>
+        <v>0.0006005787290632725</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1325021214172118</v>
+        <v>0.1088294471002989</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1774,10 +1786,10 @@
         <v>0.4164246332943039</v>
       </c>
       <c r="D57" t="n">
-        <v>0.603712260723114</v>
+        <v>0.8579200506210327</v>
       </c>
       <c r="E57" t="n">
-        <v>0.524928898666604</v>
+        <v>0.6096648286325769</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -1794,10 +1806,10 @@
         <v>0.2283001683073818</v>
       </c>
       <c r="D58" t="n">
-        <v>0.08009590208530426</v>
+        <v>0.004553993232548237</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1975379496082138</v>
+        <v>0.1723573133239618</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -1814,10 +1826,10 @@
         <v>0.1627608839275426</v>
       </c>
       <c r="D59" t="n">
-        <v>0.09685248136520386</v>
+        <v>0.009782582521438599</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1825764291349813</v>
+        <v>0.1535531295203929</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -1831,13 +1843,13 @@
         <v>0.3275477716064862</v>
       </c>
       <c r="C60" t="n">
-        <v>0.3481202592206568</v>
+        <v>0.3481202592206567</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2289982289075851</v>
+        <v>0.1363774985074997</v>
       </c>
       <c r="E60" t="n">
-        <v>0.301555419911576</v>
+        <v>0.2706818431115475</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -1854,10 +1866,10 @@
         <v>0.218892973261877</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1315983235836029</v>
+        <v>0.09915418922901154</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1801974734069997</v>
+        <v>0.1693827619554692</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -1874,10 +1886,10 @@
         <v>0.1169476007559232</v>
       </c>
       <c r="D62" t="n">
-        <v>0.07247041910886765</v>
+        <v>0.003251437796279788</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1057029947398442</v>
+        <v>0.08263000096898161</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -1894,10 +1906,10 @@
         <v>0.1779025379235713</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1133854761719704</v>
+        <v>0.04029678553342819</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1584307801732988</v>
+        <v>0.1340678832937848</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -1914,10 +1926,10 @@
         <v>0.1582499449966986</v>
       </c>
       <c r="D64" t="n">
-        <v>0.07683394104242325</v>
+        <v>0.0005237373989075422</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1343043683859162</v>
+        <v>0.1088676338380776</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -1934,10 +1946,10 @@
         <v>0.1125542101685188</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0715283527970314</v>
+        <v>0.0005953896907158196</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0971269999660006</v>
+        <v>0.07348267893056208</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -1954,10 +1966,10 @@
         <v>0.1136698268734273</v>
       </c>
       <c r="D66" t="n">
-        <v>0.07287000119686127</v>
+        <v>0.0009417893597856164</v>
       </c>
       <c r="E66" t="n">
-        <v>0.09375602907963332</v>
+        <v>0.06977995846727476</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -1974,10 +1986,10 @@
         <v>0.1649059773822238</v>
       </c>
       <c r="D67" t="n">
-        <v>0.07812841236591339</v>
+        <v>0.01061465404927731</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1490798204316086</v>
+        <v>0.1265752343260632</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -1994,10 +2006,10 @@
         <v>0.1927099488155739</v>
       </c>
       <c r="D68" t="n">
-        <v>0.07923229783773422</v>
+        <v>0.002247888594865799</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1544434370701258</v>
+        <v>0.128781967322503</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2014,10 +2026,10 @@
         <v>0.1937242343187526</v>
       </c>
       <c r="D69" t="n">
-        <v>0.08510554581880569</v>
+        <v>0.001773500815033913</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1858539772691374</v>
+        <v>0.1580766289345469</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2034,10 +2046,10 @@
         <v>0.2330012744726119</v>
       </c>
       <c r="D70" t="n">
-        <v>0.08363978564739227</v>
+        <v>0.0458260104060173</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1724775745401443</v>
+        <v>0.1598729827930194</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -2051,13 +2063,13 @@
         <v>0.1253760391814873</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1325738335290409</v>
+        <v>0.132573833529041</v>
       </c>
       <c r="D71" t="n">
-        <v>0.07056868076324463</v>
+        <v>0.0004237395187374204</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1095061844912576</v>
+        <v>0.08612453740975523</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2074,10 +2086,10 @@
         <v>0.1325738538236776</v>
       </c>
       <c r="D72" t="n">
-        <v>0.07237669080495834</v>
+        <v>0.0031516975723207</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1229815557361792</v>
+        <v>0.09990655799196664</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -2094,10 +2106,10 @@
         <v>0.1698225480092422</v>
       </c>
       <c r="D73" t="n">
-        <v>0.07290973514318466</v>
+        <v>0.003110484685748816</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1464781889260097</v>
+        <v>0.1232117721068644</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -2114,10 +2126,10 @@
         <v>0.11612651888992</v>
       </c>
       <c r="D74" t="n">
-        <v>0.07825128734111786</v>
+        <v>0.005948095116764307</v>
       </c>
       <c r="E74" t="n">
-        <v>0.100571546716873</v>
+        <v>0.07647048264208844</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -2134,10 +2146,10 @@
         <v>0.2920047176097141</v>
       </c>
       <c r="D75" t="n">
-        <v>0.236926481127739</v>
+        <v>0.4906383454799652</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2600251379374139</v>
+        <v>0.3445957593881561</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -2151,13 +2163,13 @@
         <v>0.2488343744699408</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1892112707317715</v>
+        <v>0.1892112707317714</v>
       </c>
       <c r="D76" t="n">
-        <v>0.07339709252119064</v>
+        <v>0.002812093123793602</v>
       </c>
       <c r="E76" t="n">
-        <v>0.170480912574301</v>
+        <v>0.1469525794418353</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2174,13 +2186,13 @@
         <v>0.3804437240183593</v>
       </c>
       <c r="D77" t="n">
-        <v>0.6114559173583984</v>
+        <v>0.867068886756897</v>
       </c>
       <c r="E77" t="n">
-        <v>0.4896681942000707</v>
+        <v>0.5748725173329036</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2194,10 +2206,10 @@
         <v>0.4200548999571609</v>
       </c>
       <c r="D78" t="n">
-        <v>0.6630949974060059</v>
+        <v>0.7984994649887085</v>
       </c>
       <c r="E78" t="n">
-        <v>0.55693493419522</v>
+        <v>0.6020697567227876</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -2214,10 +2226,10 @@
         <v>0.1267494327787951</v>
       </c>
       <c r="D79" t="n">
-        <v>0.07301819324493408</v>
+        <v>0.004208219237625599</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1061688629568268</v>
+        <v>0.08323220495439067</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2234,10 +2246,10 @@
         <v>0.1962932164738476</v>
       </c>
       <c r="D80" t="n">
-        <v>0.08446995168924332</v>
+        <v>0.02054481580853462</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1543300178855595</v>
+        <v>0.1330216392586566</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2254,10 +2266,10 @@
         <v>0.4017540561397547</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6099151372909546</v>
+        <v>0.814975917339325</v>
       </c>
       <c r="E81" t="n">
-        <v>0.5483241026683824</v>
+        <v>0.6166776960178392</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -2271,13 +2283,13 @@
         <v>0.3838290151127853</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3218228931227876</v>
+        <v>0.3218228931227875</v>
       </c>
       <c r="D82" t="n">
-        <v>0.5485585927963257</v>
+        <v>0.7820993661880493</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4180701670106328</v>
+        <v>0.4959170914745407</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2294,10 +2306,10 @@
         <v>0.1751262384974091</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0818362683057785</v>
+        <v>0.01259609032422304</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1605867684633373</v>
+        <v>0.1375067091361521</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2314,10 +2326,10 @@
         <v>0.1711832488943786</v>
       </c>
       <c r="D84" t="n">
-        <v>0.08673667907714844</v>
+        <v>0.008708175271749496</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1606887506933922</v>
+        <v>0.1346792494249259</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2334,10 +2346,10 @@
         <v>0.1904234827419378</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1031477600336075</v>
+        <v>0.04044827446341515</v>
       </c>
       <c r="E85" t="n">
-        <v>0.1602240064543524</v>
+        <v>0.1393241779309549</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2351,13 +2363,13 @@
         <v>0.1737333293702804</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1708580585636477</v>
+        <v>0.1708580585636476</v>
       </c>
       <c r="D86" t="n">
-        <v>0.07838915288448334</v>
+        <v>0.005259337369352579</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1409935136061372</v>
+        <v>0.1166169084344269</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2374,10 +2386,10 @@
         <v>0.1472660721205414</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0853777751326561</v>
+        <v>0.0053669149056077</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1262406724236034</v>
+        <v>0.09957038568125394</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2394,10 +2406,10 @@
         <v>0.3709017397346566</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4219039082527161</v>
+        <v>0.4599567949771881</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4160256243631651</v>
+        <v>0.4287099199379891</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -2411,13 +2423,13 @@
         <v>0.2824306744480671</v>
       </c>
       <c r="C89" t="n">
-        <v>0.1301902088386244</v>
+        <v>0.1301902088386243</v>
       </c>
       <c r="D89" t="n">
-        <v>0.07515495270490646</v>
+        <v>0.001899786991998553</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1625919453305326</v>
+        <v>0.1381735567595633</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -2434,10 +2446,10 @@
         <v>0.1975660188530602</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1755018532276154</v>
+        <v>0.0874924436211586</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1930006176319707</v>
+        <v>0.1636641477631518</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2454,10 +2466,10 @@
         <v>0.1889628996509349</v>
       </c>
       <c r="D91" t="n">
-        <v>0.07644081115722656</v>
+        <v>0.007997198030352592</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1698966023025984</v>
+        <v>0.1470820645936405</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -2474,10 +2486,10 @@
         <v>0.2911239373211523</v>
       </c>
       <c r="D92" t="n">
-        <v>0.09789060056209564</v>
+        <v>0.02940996363759041</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2598982591704208</v>
+        <v>0.2370713801955857</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -2491,13 +2503,13 @@
         <v>0.2472722554754759</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2474922151837858</v>
+        <v>0.2474922151837859</v>
       </c>
       <c r="D93" t="n">
-        <v>0.07839572429656982</v>
+        <v>0.003771704854443669</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1910533983186105</v>
+        <v>0.1661787251712351</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -2514,10 +2526,10 @@
         <v>0.2555660616980943</v>
       </c>
       <c r="D94" t="n">
-        <v>0.09299923479557037</v>
+        <v>0.03502223640680313</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2333270633920906</v>
+        <v>0.2140013972625015</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -2534,10 +2546,10 @@
         <v>0.1798141515235379</v>
       </c>
       <c r="D95" t="n">
-        <v>0.09445273131132126</v>
+        <v>0.012605513446033</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1505273883914299</v>
+        <v>0.1232449824363338</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -2554,10 +2566,10 @@
         <v>0.1771546349215245</v>
       </c>
       <c r="D96" t="n">
-        <v>0.07266898453235626</v>
+        <v>0.001745969406329095</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1430633583405283</v>
+        <v>0.1194223532985192</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -2574,10 +2586,10 @@
         <v>0.1595057475653789</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0701524019241333</v>
+        <v>0.0004080365470144898</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1165531078579265</v>
+        <v>0.0933049860655536</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -2594,10 +2606,10 @@
         <v>0.1475701462337582</v>
       </c>
       <c r="D98" t="n">
-        <v>0.07008317112922668</v>
+        <v>0.0005163749447092414</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1195235289499888</v>
+        <v>0.09633459688848302</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -2614,10 +2626,10 @@
         <v>0.148472505311266</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0710771307349205</v>
+        <v>0.0007181570399552584</v>
       </c>
       <c r="E99" t="n">
-        <v>0.1221053155246876</v>
+        <v>0.09865232429303257</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -2634,10 +2646,10 @@
         <v>0.255094110227886</v>
       </c>
       <c r="D100" t="n">
-        <v>0.07703628391027451</v>
+        <v>0.0194055549800396</v>
       </c>
       <c r="E100" t="n">
-        <v>0.2256478715868527</v>
+        <v>0.2064376286101077</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -2654,10 +2666,10 @@
         <v>0.2432298588647352</v>
       </c>
       <c r="D101" t="n">
-        <v>0.07608881592750549</v>
+        <v>0.006568604614585638</v>
       </c>
       <c r="E101" t="n">
-        <v>0.1928127916488948</v>
+        <v>0.1696393878779215</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -2674,10 +2686,10 @@
         <v>0.1456012503208176</v>
       </c>
       <c r="D102" t="n">
-        <v>0.08946750313043594</v>
+        <v>0.003778595477342606</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1134467849541775</v>
+        <v>0.08488381573647974</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -2694,10 +2706,10 @@
         <v>0.1760676424483896</v>
       </c>
       <c r="D103" t="n">
-        <v>0.07065773010253906</v>
+        <v>0.002059787744656205</v>
       </c>
       <c r="E103" t="n">
-        <v>0.1598343629117757</v>
+        <v>0.1369683821258147</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -2714,10 +2726,10 @@
         <v>0.2905927271854694</v>
       </c>
       <c r="D104" t="n">
-        <v>0.09468602389097214</v>
+        <v>0.03202971816062927</v>
       </c>
       <c r="E104" t="n">
-        <v>0.2727568975947417</v>
+        <v>0.251871462351294</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -2731,13 +2743,13 @@
         <v>0.3515973281640457</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2443707586665064</v>
+        <v>0.2443707586665065</v>
       </c>
       <c r="D105" t="n">
-        <v>0.09915785491466522</v>
+        <v>0.03178349509835243</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2317086472484058</v>
+        <v>0.2092505273096349</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -2754,10 +2766,10 @@
         <v>0.2233666653368904</v>
       </c>
       <c r="D106" t="n">
-        <v>0.09554047137498856</v>
+        <v>0.04076407104730606</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2023017434874848</v>
+        <v>0.1840429433782573</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -2774,10 +2786,10 @@
         <v>0.2821254175158009</v>
       </c>
       <c r="D107" t="n">
-        <v>0.08447602391242981</v>
+        <v>0.01457046251744032</v>
       </c>
       <c r="E107" t="n">
-        <v>0.2463559647200004</v>
+        <v>0.2230541109216706</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -2794,10 +2806,10 @@
         <v>0.2317550636568133</v>
       </c>
       <c r="D108" t="n">
-        <v>0.07028724253177643</v>
+        <v>0.001548610860481858</v>
       </c>
       <c r="E108" t="n">
-        <v>0.2151580080384639</v>
+        <v>0.192245130814699</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -2814,10 +2826,10 @@
         <v>0.2156516811085383</v>
       </c>
       <c r="D109" t="n">
-        <v>0.07045983523130417</v>
+        <v>0.001491953036747873</v>
       </c>
       <c r="E109" t="n">
-        <v>0.1821467978519533</v>
+        <v>0.1591575037871012</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -2834,10 +2846,10 @@
         <v>0.15975732027634</v>
       </c>
       <c r="D110" t="n">
-        <v>0.07214613258838654</v>
+        <v>0.002451690612360835</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1282562980460022</v>
+        <v>0.1050248173873269</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -2851,13 +2863,13 @@
         <v>0.1821843624457373</v>
       </c>
       <c r="C111" t="n">
-        <v>0.191629637334344</v>
+        <v>0.1916296373343441</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0699920654296875</v>
+        <v>0.0010364621412009</v>
       </c>
       <c r="E111" t="n">
-        <v>0.1479353550699229</v>
+        <v>0.1249501539737607</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -2874,10 +2886,10 @@
         <v>0.2034825107820868</v>
       </c>
       <c r="D112" t="n">
-        <v>0.07369934767484665</v>
+        <v>0.004509586840867996</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1687186528220971</v>
+        <v>0.1456553992107709</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -2894,10 +2906,10 @@
         <v>0.18789105618562</v>
       </c>
       <c r="D113" t="n">
-        <v>0.07635805755853653</v>
+        <v>0.009890615940093994</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1579025568061877</v>
+        <v>0.1357467429333735</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -2914,10 +2926,10 @@
         <v>0.2681175478448671</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1143877133727074</v>
+        <v>0.05269386619329453</v>
       </c>
       <c r="E114" t="n">
-        <v>0.2546596637988501</v>
+        <v>0.2340950480723792</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -2934,10 +2946,10 @@
         <v>0.2423932088510732</v>
       </c>
       <c r="D115" t="n">
-        <v>0.07206692546606064</v>
+        <v>0.005007356870919466</v>
       </c>
       <c r="E115" t="n">
-        <v>0.2120115369597967</v>
+        <v>0.189658347428083</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -2954,10 +2966,10 @@
         <v>0.2836388660180196</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2965664267539978</v>
+        <v>0.296814501285553</v>
       </c>
       <c r="E116" t="n">
-        <v>0.3124344462852783</v>
+        <v>0.3125171377957968</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -2974,10 +2986,10 @@
         <v>0.1892403695594683</v>
       </c>
       <c r="D117" t="n">
-        <v>0.07142986357212067</v>
+        <v>0.001467709895223379</v>
       </c>
       <c r="E117" t="n">
-        <v>0.1663180407996213</v>
+        <v>0.1429973229073222</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -2994,10 +3006,10 @@
         <v>0.2317462925673377</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1214723587036133</v>
+        <v>0.07801272720098495</v>
       </c>
       <c r="E118" t="n">
-        <v>0.208305616558022</v>
+        <v>0.1938190727238126</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -3014,10 +3026,10 @@
         <v>0.2306415165859474</v>
       </c>
       <c r="D119" t="n">
-        <v>0.08458475768566132</v>
+        <v>0.03227423876523972</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1833566990354798</v>
+        <v>0.1659198593953393</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -3034,10 +3046,10 @@
         <v>0.2004457546413801</v>
       </c>
       <c r="D120" t="n">
-        <v>0.07241100817918777</v>
+        <v>0.006442068610340357</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1537097816722508</v>
+        <v>0.1317201351493017</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -3054,10 +3066,10 @@
         <v>0.1909750892752477</v>
       </c>
       <c r="D121" t="n">
-        <v>0.07125640660524368</v>
+        <v>0.0003757661033887416</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1481366990539389</v>
+        <v>0.1245098188866539</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -3074,10 +3086,10 @@
         <v>0.2000629247124529</v>
       </c>
       <c r="D122" t="n">
-        <v>0.07914195954799652</v>
+        <v>0.007078282535076141</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1725695475352249</v>
+        <v>0.1485483218642515</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3094,10 +3106,10 @@
         <v>0.1394654242105447</v>
       </c>
       <c r="D123" t="n">
-        <v>0.07812701910734177</v>
+        <v>0.001645088545046747</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1368074256849416</v>
+        <v>0.1113134488308432</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -3114,10 +3126,10 @@
         <v>0.2359694029676137</v>
       </c>
       <c r="D124" t="n">
-        <v>0.0963645875453949</v>
+        <v>0.007771477103233337</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2201679409875584</v>
+        <v>0.1906369041735045</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -3134,10 +3146,10 @@
         <v>0.179046639407559</v>
       </c>
       <c r="D125" t="n">
-        <v>0.07212742418050766</v>
+        <v>0.0005861816462129354</v>
       </c>
       <c r="E125" t="n">
-        <v>0.1392138465164576</v>
+        <v>0.1153667656716927</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -3154,10 +3166,10 @@
         <v>0.2330861127280797</v>
       </c>
       <c r="D126" t="n">
-        <v>0.07226640731096268</v>
+        <v>0.0009962121257558465</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1833080712546956</v>
+        <v>0.1595513395262933</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -3174,10 +3186,10 @@
         <v>0.2373465158695374</v>
       </c>
       <c r="D127" t="n">
-        <v>0.07362531870603561</v>
+        <v>0.01783658191561699</v>
       </c>
       <c r="E127" t="n">
-        <v>0.2046603904911307</v>
+        <v>0.1860641448943245</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -3194,10 +3206,10 @@
         <v>0.199092305431018</v>
       </c>
       <c r="D128" t="n">
-        <v>0.07002798467874527</v>
+        <v>0.002643202198669314</v>
       </c>
       <c r="E128" t="n">
-        <v>0.1588295721047502</v>
+        <v>0.1363679779447249</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -3214,10 +3226,10 @@
         <v>0.4485568648841595</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2380578219890594</v>
+        <v>0.4378467500209808</v>
       </c>
       <c r="E129" t="n">
-        <v>0.4065170646822406</v>
+        <v>0.4731133740262144</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -3234,10 +3246,10 @@
         <v>0.2157166560496045</v>
       </c>
       <c r="D130" t="n">
-        <v>0.0722600594162941</v>
+        <v>0.002151068300008774</v>
       </c>
       <c r="E130" t="n">
-        <v>0.175997394355629</v>
+        <v>0.1526277306502006</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -3254,10 +3266,10 @@
         <v>0.4264580341449077</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3548914790153503</v>
+        <v>0.3549827039241791</v>
       </c>
       <c r="E131" t="n">
-        <v>0.444335808144961</v>
+        <v>0.4443662164479039</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -3274,10 +3286,10 @@
         <v>0.1910253129829357</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2038851678371429</v>
+        <v>0.185399979352951</v>
       </c>
       <c r="E132" t="n">
-        <v>0.2057811037966768</v>
+        <v>0.1996193743019462</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -3294,10 +3306,10 @@
         <v>0.2115912711167978</v>
       </c>
       <c r="D133" t="n">
-        <v>0.06772357225418091</v>
+        <v>7.040111995593179e-06</v>
       </c>
       <c r="E133" t="n">
-        <v>0.1698870858637125</v>
+        <v>0.147314908482984</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -3314,10 +3326,10 @@
         <v>0.2196491282492932</v>
       </c>
       <c r="D134" t="n">
-        <v>0.07038605213165283</v>
+        <v>0.002849457086995244</v>
       </c>
       <c r="E134" t="n">
-        <v>0.1643954910160521</v>
+        <v>0.1418832926678329</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -3331,13 +3343,13 @@
         <v>0.1738114454667323</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1590450461436953</v>
+        <v>0.1590450461436954</v>
       </c>
       <c r="D135" t="n">
-        <v>0.06834141165018082</v>
+        <v>1.487391818955075e-05</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1337326344202028</v>
+        <v>0.1109571218428724</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -3354,10 +3366,10 @@
         <v>0.2993281109743333</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1777370274066925</v>
+        <v>0.1535634994506836</v>
       </c>
       <c r="E136" t="n">
-        <v>0.2675485977748066</v>
+        <v>0.2594907551228036</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -3374,10 +3386,10 @@
         <v>0.1661793614500213</v>
       </c>
       <c r="D137" t="n">
-        <v>0.08638016134500504</v>
+        <v>0.009283474646508694</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1668001331830659</v>
+        <v>0.1411012376169004</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -3391,13 +3403,13 @@
         <v>0.1722812657161885</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1585635638678709</v>
+        <v>0.1585635638678708</v>
       </c>
       <c r="D138" t="n">
-        <v>0.08318991959095001</v>
+        <v>0.006905104033648968</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1380115830583365</v>
+        <v>0.1125833112059028</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -3414,10 +3426,10 @@
         <v>0.1543721827596509</v>
       </c>
       <c r="D139" t="n">
-        <v>0.1151774078607559</v>
+        <v>0.01597924716770649</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1503384957431275</v>
+        <v>0.1172724421787777</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -3431,13 +3443,13 @@
         <v>0.2331993948741976</v>
       </c>
       <c r="C140" t="n">
-        <v>0.1673815682125459</v>
+        <v>0.167381568212546</v>
       </c>
       <c r="D140" t="n">
-        <v>0.07988183200359344</v>
+        <v>0.006950265262275934</v>
       </c>
       <c r="E140" t="n">
-        <v>0.1601542650301123</v>
+        <v>0.1358437427830065</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -3454,10 +3466,10 @@
         <v>0.198524606922231</v>
       </c>
       <c r="D141" t="n">
-        <v>0.08546959608793259</v>
+        <v>0.00706800352782011</v>
       </c>
       <c r="E141" t="n">
-        <v>0.1714923156901596</v>
+        <v>0.1453584515034554</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -3471,13 +3483,13 @@
         <v>0.282129333945924</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2575697482213986</v>
+        <v>0.2575697482213987</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1720794290304184</v>
+        <v>0.1466910094022751</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2372595037325803</v>
+        <v>0.2287966971898659</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -3494,10 +3506,10 @@
         <v>0.1746891479959272</v>
       </c>
       <c r="D143" t="n">
-        <v>0.2027149945497513</v>
+        <v>0.2296700775623322</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1710580662481585</v>
+        <v>0.1800430939190188</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -3514,10 +3526,10 @@
         <v>0.1449903401267535</v>
       </c>
       <c r="D144" t="n">
-        <v>0.06982019543647766</v>
+        <v>0.0001892353320727125</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1330802435706994</v>
+        <v>0.1098699235358978</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -3534,10 +3546,10 @@
         <v>0.1369719748235891</v>
       </c>
       <c r="D145" t="n">
-        <v>0.06998136639595032</v>
+        <v>0.0001256874529644847</v>
       </c>
       <c r="E145" t="n">
-        <v>0.1203219394487929</v>
+        <v>0.09703671313446431</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -3554,10 +3566,10 @@
         <v>0.1884448058691281</v>
       </c>
       <c r="D146" t="n">
-        <v>0.0805114358663559</v>
+        <v>0.01101752184331417</v>
       </c>
       <c r="E146" t="n">
-        <v>0.1592257082962066</v>
+        <v>0.1360610702885261</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -3574,10 +3586,10 @@
         <v>0.2075805812152529</v>
       </c>
       <c r="D147" t="n">
-        <v>0.08113721013069153</v>
+        <v>0.006291518919169903</v>
       </c>
       <c r="E147" t="n">
-        <v>0.1740682178208536</v>
+        <v>0.1491196540836797</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -3594,10 +3606,10 @@
         <v>0.1335388221987244</v>
       </c>
       <c r="D148" t="n">
-        <v>0.1056578606367111</v>
+        <v>0.054457176476717</v>
       </c>
       <c r="E148" t="n">
-        <v>0.1418747630172764</v>
+        <v>0.1248078682972784</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -3614,10 +3626,10 @@
         <v>0.1735058048497894</v>
       </c>
       <c r="D149" t="n">
-        <v>0.1599076241254807</v>
+        <v>0.1107948049902916</v>
       </c>
       <c r="E149" t="n">
-        <v>0.1915467270958676</v>
+        <v>0.1751757873841379</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -3634,10 +3646,10 @@
         <v>0.1776650698259835</v>
       </c>
       <c r="D150" t="n">
-        <v>0.101912721991539</v>
+        <v>0.06342144310474396</v>
       </c>
       <c r="E150" t="n">
-        <v>0.1695214712157837</v>
+        <v>0.1566910449201854</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -3654,10 +3666,10 @@
         <v>0.2249794545071617</v>
       </c>
       <c r="D151" t="n">
-        <v>0.08132614195346832</v>
+        <v>0.01228868030011654</v>
       </c>
       <c r="E151" t="n">
-        <v>0.2244053553382797</v>
+        <v>0.2013928681204958</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -3674,10 +3686,10 @@
         <v>0.1718083442958885</v>
       </c>
       <c r="D152" t="n">
-        <v>0.07656924426555634</v>
+        <v>0.002039075363427401</v>
       </c>
       <c r="E152" t="n">
-        <v>0.1560598723162766</v>
+        <v>0.1312164826822337</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -3694,10 +3706,10 @@
         <v>0.3597703716678772</v>
       </c>
       <c r="D153" t="n">
-        <v>0.5084904432296753</v>
+        <v>0.7815949320793152</v>
       </c>
       <c r="E153" t="n">
-        <v>0.4185670225466983</v>
+        <v>0.5096018521632449</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -3714,10 +3726,10 @@
         <v>0.1691316468433855</v>
       </c>
       <c r="D154" t="n">
-        <v>0.09823407232761383</v>
+        <v>0.01177742797881365</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1485871587753368</v>
+        <v>0.1197682773257368</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -3734,10 +3746,10 @@
         <v>0.1890634753554935</v>
       </c>
       <c r="D155" t="n">
-        <v>0.08624998480081558</v>
+        <v>0.007053972221910954</v>
       </c>
       <c r="E155" t="n">
-        <v>0.1645254747162354</v>
+        <v>0.1381268038566006</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -3751,13 +3763,13 @@
         <v>0.2073956179896051</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1975913140972195</v>
+        <v>0.1975913140972196</v>
       </c>
       <c r="D156" t="n">
-        <v>0.09612976759672165</v>
+        <v>0.03591520711779594</v>
       </c>
       <c r="E156" t="n">
-        <v>0.1670388998945155</v>
+        <v>0.1469673797348735</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -3771,13 +3783,13 @@
         <v>0.138518206701358</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1586554795133839</v>
+        <v>0.158655479513384</v>
       </c>
       <c r="D157" t="n">
-        <v>0.06914457678794861</v>
+        <v>0.0003380635171197355</v>
       </c>
       <c r="E157" t="n">
-        <v>0.1221060876675635</v>
+        <v>0.09917058324395389</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -3794,10 +3806,10 @@
         <v>0.2052757870355309</v>
       </c>
       <c r="D158" t="n">
-        <v>0.08742403239011765</v>
+        <v>0.04785756394267082</v>
       </c>
       <c r="E158" t="n">
-        <v>0.1568596077257319</v>
+        <v>0.1436707849099163</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -3814,10 +3826,10 @@
         <v>0.2131209901496757</v>
       </c>
       <c r="D159" t="n">
-        <v>0.1072807535529137</v>
+        <v>0.07141271978616714</v>
       </c>
       <c r="E159" t="n">
-        <v>0.1686671170266406</v>
+        <v>0.1567111057710584</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -3834,10 +3846,10 @@
         <v>0.1781868163924507</v>
       </c>
       <c r="D160" t="n">
-        <v>0.08007387816905975</v>
+        <v>0.003129287157207727</v>
       </c>
       <c r="E160" t="n">
-        <v>0.1626795794372891</v>
+        <v>0.1370313824333385</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -3851,13 +3863,13 @@
         <v>0.5776623423806377</v>
       </c>
       <c r="C161" t="n">
-        <v>0.2929229842412048</v>
+        <v>0.2929229842412049</v>
       </c>
       <c r="D161" t="n">
-        <v>0.09072653949260712</v>
+        <v>0.01386689860373735</v>
       </c>
       <c r="E161" t="n">
-        <v>0.3204372887048166</v>
+        <v>0.2948174084085267</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -3871,13 +3883,13 @@
         <v>0.1699331182172456</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1599006425528003</v>
+        <v>0.1599006425528004</v>
       </c>
       <c r="D162" t="n">
-        <v>0.08112360537052155</v>
+        <v>0.004289933945983648</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1369857887135225</v>
+        <v>0.1113745649053432</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -3894,10 +3906,10 @@
         <v>0.2301300373611239</v>
       </c>
       <c r="D163" t="n">
-        <v>0.1206997409462929</v>
+        <v>0.03229798004031181</v>
       </c>
       <c r="E163" t="n">
-        <v>0.2403337796582806</v>
+        <v>0.2108665260229536</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -3914,10 +3926,10 @@
         <v>0.1687292697776077</v>
       </c>
       <c r="D164" t="n">
-        <v>0.07084742933511734</v>
+        <v>0.0001946550764841959</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1458939032221662</v>
+        <v>0.1223429784692885</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -3934,10 +3946,10 @@
         <v>0.2053471984365973</v>
       </c>
       <c r="D165" t="n">
-        <v>0.0977192148566246</v>
+        <v>0.04421139135956764</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1654628416251231</v>
+        <v>0.1476269004594375</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -3954,10 +3966,10 @@
         <v>0.1859560871239771</v>
       </c>
       <c r="D166" t="n">
-        <v>0.08848439902067184</v>
+        <v>0.007877207361161709</v>
       </c>
       <c r="E166" t="n">
-        <v>0.1739070762798748</v>
+        <v>0.1470380123933714</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -3971,13 +3983,13 @@
         <v>0.2865348751146375</v>
       </c>
       <c r="C167" t="n">
-        <v>0.2446251107431704</v>
+        <v>0.2446251107431703</v>
       </c>
       <c r="D167" t="n">
-        <v>0.1712179332971573</v>
+        <v>0.06357564032077789</v>
       </c>
       <c r="E167" t="n">
-        <v>0.2341259730516551</v>
+        <v>0.1982452087261952</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -3994,10 +4006,10 @@
         <v>0.2488826847840804</v>
       </c>
       <c r="D168" t="n">
-        <v>0.08652105927467346</v>
+        <v>0.1034052595496178</v>
       </c>
       <c r="E168" t="n">
-        <v>0.2238950999660831</v>
+        <v>0.2295231667243979</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -4011,13 +4023,13 @@
         <v>0.3782075718991662</v>
       </c>
       <c r="C169" t="n">
-        <v>0.291444952216988</v>
+        <v>0.2914449522169881</v>
       </c>
       <c r="D169" t="n">
-        <v>0.1314288824796677</v>
+        <v>0.103356696665287</v>
       </c>
       <c r="E169" t="n">
-        <v>0.2670271355319406</v>
+        <v>0.2576697402604804</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -4034,10 +4046,10 @@
         <v>0.2162049916127085</v>
       </c>
       <c r="D170" t="n">
-        <v>0.06843748688697815</v>
+        <v>2.923235297203064e-05</v>
       </c>
       <c r="E170" t="n">
-        <v>0.1659978318420844</v>
+        <v>0.143195080330749</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -4054,10 +4066,10 @@
         <v>0.1661486473477525</v>
       </c>
       <c r="D171" t="n">
-        <v>0.07726748287677765</v>
+        <v>0.00266004609875381</v>
       </c>
       <c r="E171" t="n">
-        <v>0.1630230982860031</v>
+        <v>0.1381539526933285</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
@@ -4074,10 +4086,10 @@
         <v>0.2457879211277599</v>
       </c>
       <c r="D172" t="n">
-        <v>0.07579245418310165</v>
+        <v>0.01830104552209377</v>
       </c>
       <c r="E172" t="n">
-        <v>0.2142130235102093</v>
+        <v>0.1950492206232067</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -4094,10 +4106,10 @@
         <v>0.1854929978226296</v>
       </c>
       <c r="D173" t="n">
-        <v>0.06839931011199951</v>
+        <v>4.323240864323452e-05</v>
       </c>
       <c r="E173" t="n">
-        <v>0.1576350075221942</v>
+        <v>0.1348496482877421</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -4114,10 +4126,10 @@
         <v>0.2572098595958555</v>
       </c>
       <c r="D174" t="n">
-        <v>0.1128570660948753</v>
+        <v>0.04150685667991638</v>
       </c>
       <c r="E174" t="n">
-        <v>0.2026861845968283</v>
+        <v>0.1789027814585086</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -4134,10 +4146,10 @@
         <v>0.2349197204200388</v>
       </c>
       <c r="D175" t="n">
-        <v>0.2246080935001373</v>
+        <v>0.1647454500198364</v>
       </c>
       <c r="E175" t="n">
-        <v>0.2580764861984743</v>
+        <v>0.2381222717050407</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
@@ -4151,13 +4163,13 @@
         <v>0.1911935837207522</v>
       </c>
       <c r="C176" t="n">
-        <v>0.2025522931057313</v>
+        <v>0.2025522931057314</v>
       </c>
       <c r="D176" t="n">
-        <v>0.08093564212322235</v>
+        <v>0.01759307458996773</v>
       </c>
       <c r="E176" t="n">
-        <v>0.1582271729832353</v>
+        <v>0.1371129838054838</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
@@ -4174,10 +4186,10 @@
         <v>0.1970402185098704</v>
       </c>
       <c r="D177" t="n">
-        <v>0.06888270378112793</v>
+        <v>0.0004415439907461405</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1608255289386334</v>
+        <v>0.1380118090085062</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -4194,10 +4206,10 @@
         <v>0.2240024759412333</v>
       </c>
       <c r="D178" t="n">
-        <v>0.08731731027364731</v>
+        <v>0.06734587252140045</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1884846032432166</v>
+        <v>0.181827457325801</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
@@ -4214,10 +4226,10 @@
         <v>0.2191116220077852</v>
       </c>
       <c r="D179" t="n">
-        <v>0.1089776158332825</v>
+        <v>0.02196581289172173</v>
       </c>
       <c r="E179" t="n">
-        <v>0.1952547459043379</v>
+        <v>0.1662508115904843</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
@@ -4234,10 +4246,10 @@
         <v>0.4354003290122679</v>
       </c>
       <c r="D180" t="n">
-        <v>0.7689080238342285</v>
+        <v>0.9444926977157593</v>
       </c>
       <c r="E180" t="n">
-        <v>0.6111538241869835</v>
+        <v>0.6696820488141605</v>
       </c>
       <c r="F180" t="n">
         <v>1</v>
@@ -4254,10 +4266,10 @@
         <v>0.177277556843938</v>
       </c>
       <c r="D181" t="n">
-        <v>0.07419835031032562</v>
+        <v>0.003574077039957047</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1538099260314164</v>
+        <v>0.1302685016079602</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
@@ -4274,10 +4286,10 @@
         <v>0.1769390008680137</v>
       </c>
       <c r="D182" t="n">
-        <v>0.07600628584623337</v>
+        <v>0.001586274825967848</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1580269664086426</v>
+        <v>0.1332202960685542</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -4294,10 +4306,10 @@
         <v>0.2131808155509465</v>
       </c>
       <c r="D183" t="n">
-        <v>0.07521801441907883</v>
+        <v>0.03411171585321426</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1801355582358285</v>
+        <v>0.1664334587138736</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
@@ -4314,10 +4326,10 @@
         <v>0.286695580837637</v>
       </c>
       <c r="D184" t="n">
-        <v>0.1355031281709671</v>
+        <v>0.1384590566158295</v>
       </c>
       <c r="E184" t="n">
-        <v>0.2341433142707517</v>
+        <v>0.2351286237523725</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
@@ -4334,10 +4346,10 @@
         <v>0.1773561806791862</v>
       </c>
       <c r="D185" t="n">
-        <v>0.0834244042634964</v>
+        <v>0.004614813718944788</v>
       </c>
       <c r="E185" t="n">
-        <v>0.1557106940333598</v>
+        <v>0.1294408305185092</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
@@ -4354,10 +4366,10 @@
         <v>0.1831151409898754</v>
       </c>
       <c r="D186" t="n">
-        <v>0.07937627285718918</v>
+        <v>0.002539233071729541</v>
       </c>
       <c r="E186" t="n">
-        <v>0.1581443436633794</v>
+        <v>0.1325319970682262</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -4374,10 +4386,10 @@
         <v>0.1760849947590262</v>
       </c>
       <c r="D187" t="n">
-        <v>0.06846772879362106</v>
+        <v>0.000133631459902972</v>
       </c>
       <c r="E187" t="n">
-        <v>0.1400215035215686</v>
+        <v>0.1172434710769959</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -4394,10 +4406,10 @@
         <v>0.1679463078283981</v>
       </c>
       <c r="D188" t="n">
-        <v>0.07448526471853256</v>
+        <v>0.002849379787221551</v>
       </c>
       <c r="E188" t="n">
-        <v>0.1476081459057535</v>
+        <v>0.1237295175953165</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
@@ -4414,10 +4426,10 @@
         <v>0.2423868672446111</v>
       </c>
       <c r="D189" t="n">
-        <v>0.1476301848888397</v>
+        <v>0.1298584789037704</v>
       </c>
       <c r="E189" t="n">
-        <v>0.2152243691688772</v>
+        <v>0.2093004671738542</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -4431,13 +4443,13 @@
         <v>0.1298123057755818</v>
       </c>
       <c r="C190" t="n">
-        <v>0.1199860881616681</v>
+        <v>0.1199860881616682</v>
       </c>
       <c r="D190" t="n">
-        <v>0.06969462335109711</v>
+        <v>3.26319714076817e-05</v>
       </c>
       <c r="E190" t="n">
-        <v>0.106497672429449</v>
+        <v>0.08327700863621923</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
@@ -4454,10 +4466,10 @@
         <v>0.3486316687780635</v>
       </c>
       <c r="D191" t="n">
-        <v>0.07720349729061127</v>
+        <v>0.02714811824262142</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3146622790116524</v>
+        <v>0.2979771526623225</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -4474,10 +4486,10 @@
         <v>0.1688192095890889</v>
       </c>
       <c r="D192" t="n">
-        <v>0.1056512221693993</v>
+        <v>0.02626415155827999</v>
       </c>
       <c r="E192" t="n">
-        <v>0.1566502822078642</v>
+        <v>0.1301879253374911</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -4494,10 +4506,10 @@
         <v>0.1329203079871629</v>
       </c>
       <c r="D193" t="n">
-        <v>0.1203698366880417</v>
+        <v>0.04238059744238853</v>
       </c>
       <c r="E193" t="n">
-        <v>0.1216482571898969</v>
+        <v>0.09565184410801253</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -4514,10 +4526,10 @@
         <v>0.1646347172833459</v>
       </c>
       <c r="D194" t="n">
-        <v>0.08127390593290329</v>
+        <v>0.01252851355820894</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1245846667126031</v>
+        <v>0.1016695359210383</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
@@ -4534,10 +4546,10 @@
         <v>0.1690222026487901</v>
       </c>
       <c r="D195" t="n">
-        <v>0.06947235763072968</v>
+        <v>0.000352966773789376</v>
       </c>
       <c r="E195" t="n">
-        <v>0.140505133613963</v>
+        <v>0.1174653366616495</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
@@ -4554,10 +4566,10 @@
         <v>0.1310797943846707</v>
       </c>
       <c r="D196" t="n">
-        <v>0.07927682995796204</v>
+        <v>0.005569968372583389</v>
       </c>
       <c r="E196" t="n">
-        <v>0.1090083070158282</v>
+        <v>0.08443935315403532</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
@@ -4574,10 +4586,10 @@
         <v>0.1086716773384964</v>
       </c>
       <c r="D197" t="n">
-        <v>0.08707365393638611</v>
+        <v>0.01354396529495716</v>
       </c>
       <c r="E197" t="n">
-        <v>0.1004724001440887</v>
+        <v>0.07596250393027908</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -4594,10 +4606,10 @@
         <v>0.2688405001313958</v>
       </c>
       <c r="D198" t="n">
-        <v>0.3545889556407928</v>
+        <v>0.3122029304504395</v>
       </c>
       <c r="E198" t="n">
-        <v>0.3283414973993068</v>
+        <v>0.3142128223358557</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -4614,10 +4626,10 @@
         <v>0.1367383533817442</v>
       </c>
       <c r="D199" t="n">
-        <v>0.08025576919317245</v>
+        <v>0.002859922591596842</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1368775688909399</v>
+        <v>0.1110789533570814</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
@@ -4634,13 +4646,13 @@
         <v>0.4155069904549825</v>
       </c>
       <c r="D200" t="n">
-        <v>0.7117158770561218</v>
+        <v>0.7464140653610229</v>
       </c>
       <c r="E200" t="n">
-        <v>0.5255624931414341</v>
+        <v>0.5371285559097345</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -4651,16 +4663,16 @@
         <v>0.6637708410519579</v>
       </c>
       <c r="C201" t="n">
-        <v>0.3801786252879712</v>
+        <v>0.3801786252879711</v>
       </c>
       <c r="D201" t="n">
-        <v>0.5110436677932739</v>
+        <v>0.6453999280929565</v>
       </c>
       <c r="E201" t="n">
-        <v>0.5183310447110677</v>
+        <v>0.5631164648109619</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -4671,16 +4683,16 @@
         <v>0.4764017346145583</v>
       </c>
       <c r="C202" t="n">
-        <v>0.3992724598585664</v>
+        <v>0.3992724598585663</v>
       </c>
       <c r="D202" t="n">
-        <v>0.5513283014297485</v>
+        <v>0.8552601933479309</v>
       </c>
       <c r="E202" t="n">
-        <v>0.4756674986342911</v>
+        <v>0.5769781292736852</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -4694,10 +4706,10 @@
         <v>0.1947897823566847</v>
       </c>
       <c r="D203" t="n">
-        <v>0.1071415320038795</v>
+        <v>0.06963777542114258</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1715288704972438</v>
+        <v>0.1590276183029981</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -4714,10 +4726,10 @@
         <v>0.3433269610355117</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4253006875514984</v>
+        <v>0.5634319186210632</v>
       </c>
       <c r="E204" t="n">
-        <v>0.4103276297239976</v>
+        <v>0.4563713734138526</v>
       </c>
       <c r="F204" t="n">
         <v>0</v>
@@ -4734,10 +4746,10 @@
         <v>0.2142102301421978</v>
       </c>
       <c r="D205" t="n">
-        <v>0.07129607349634171</v>
+        <v>0.0001699623244348913</v>
       </c>
       <c r="E205" t="n">
-        <v>0.1800354949928046</v>
+        <v>0.1563267912688356</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
@@ -4754,10 +4766,10 @@
         <v>0.3187157970167481</v>
       </c>
       <c r="D206" t="n">
-        <v>0.2040483504533768</v>
+        <v>0.1601885855197906</v>
       </c>
       <c r="E206" t="n">
-        <v>0.3179029867785412</v>
+        <v>0.3032830651340125</v>
       </c>
       <c r="F206" t="n">
         <v>0</v>
@@ -4774,10 +4786,10 @@
         <v>0.4718198786719</v>
       </c>
       <c r="D207" t="n">
-        <v>0.7477684020996094</v>
+        <v>0.8313325047492981</v>
       </c>
       <c r="E207" t="n">
-        <v>0.6181133555640413</v>
+        <v>0.6459680564472708</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -4794,10 +4806,10 @@
         <v>0.2550295013516793</v>
       </c>
       <c r="D208" t="n">
-        <v>0.2342405319213867</v>
+        <v>0.2826966941356659</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2664034650370754</v>
+        <v>0.2825555191085018</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
@@ -4814,10 +4826,10 @@
         <v>0.1923531620543562</v>
       </c>
       <c r="D209" t="n">
-        <v>0.07500551640987396</v>
+        <v>0.001259941840544343</v>
       </c>
       <c r="E209" t="n">
-        <v>0.1808925945305439</v>
+        <v>0.1563107363407673</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
@@ -4834,10 +4846,10 @@
         <v>0.3151230138154562</v>
       </c>
       <c r="D210" t="n">
-        <v>0.5653230547904968</v>
+        <v>0.7912012934684753</v>
       </c>
       <c r="E210" t="n">
-        <v>0.4410503024665571</v>
+        <v>0.5163430486925499</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -4854,10 +4866,10 @@
         <v>0.4161992186869769</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3160125017166138</v>
+        <v>0.5638378858566284</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3954551243931834</v>
+        <v>0.4780635857731883</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
@@ -4874,10 +4886,10 @@
         <v>0.3620200728603185</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4419897198677063</v>
+        <v>0.6082373857498169</v>
       </c>
       <c r="E212" t="n">
-        <v>0.4157513853925631</v>
+        <v>0.4711672740199334</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
@@ -4894,10 +4906,10 @@
         <v>0.2199955210197621</v>
       </c>
       <c r="D213" t="n">
-        <v>0.07649944722652435</v>
+        <v>0.005098613910377026</v>
       </c>
       <c r="E213" t="n">
-        <v>0.1951124586392063</v>
+        <v>0.1713121808671572</v>
       </c>
       <c r="F213" t="n">
         <v>0</v>
@@ -4914,10 +4926,10 @@
         <v>0.3907217493540841</v>
       </c>
       <c r="D214" t="n">
-        <v>0.5075387954711914</v>
+        <v>0.8382552266120911</v>
       </c>
       <c r="E214" t="n">
-        <v>0.4930278312387</v>
+        <v>0.6032666416189999</v>
       </c>
       <c r="F214" t="n">
         <v>1</v>
@@ -4934,10 +4946,10 @@
         <v>0.1769897430601229</v>
       </c>
       <c r="D215" t="n">
-        <v>0.08407799899578094</v>
+        <v>0.006634782068431377</v>
       </c>
       <c r="E215" t="n">
-        <v>0.1790864663011575</v>
+        <v>0.1532720606587077</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
@@ -4954,10 +4966,10 @@
         <v>0.2902224609793662</v>
       </c>
       <c r="D216" t="n">
-        <v>0.386243611574173</v>
+        <v>0.2210657894611359</v>
       </c>
       <c r="E216" t="n">
-        <v>0.323663043965471</v>
+        <v>0.2686037699277919</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
@@ -4974,10 +4986,10 @@
         <v>0.2570242167310633</v>
       </c>
       <c r="D217" t="n">
-        <v>0.4968445897102356</v>
+        <v>0.7822309732437134</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3770146521207782</v>
+        <v>0.4721434466319375</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
@@ -4994,10 +5006,10 @@
         <v>0.1319515001019295</v>
       </c>
       <c r="D218" t="n">
-        <v>0.08055673539638519</v>
+        <v>0.001759489299729466</v>
       </c>
       <c r="E218" t="n">
-        <v>0.129556720527119</v>
+        <v>0.1032909718282338</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -5011,13 +5023,13 @@
         <v>0.4084509420954645</v>
       </c>
       <c r="C219" t="n">
-        <v>0.3250439347719393</v>
+        <v>0.3250439347719394</v>
       </c>
       <c r="D219" t="n">
-        <v>0.234020471572876</v>
+        <v>0.3843143284320831</v>
       </c>
       <c r="E219" t="n">
-        <v>0.3225051161467599</v>
+        <v>0.3726030684331623</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
@@ -5031,13 +5043,13 @@
         <v>0.1898224301411141</v>
       </c>
       <c r="C220" t="n">
-        <v>0.1682233588921066</v>
+        <v>0.1682233588921065</v>
       </c>
       <c r="D220" t="n">
-        <v>0.09508281946182251</v>
+        <v>0.007354126777499914</v>
       </c>
       <c r="E220" t="n">
-        <v>0.1510428694983477</v>
+        <v>0.1217999719369069</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
@@ -5054,10 +5066,10 @@
         <v>0.2482800606555355</v>
       </c>
       <c r="D221" t="n">
-        <v>0.08261888474225998</v>
+        <v>0.002156462054699659</v>
       </c>
       <c r="E221" t="n">
-        <v>0.2039632212837012</v>
+        <v>0.1771424137211811</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
@@ -5074,10 +5086,10 @@
         <v>0.373767189956124</v>
       </c>
       <c r="D222" t="n">
-        <v>0.3227922022342682</v>
+        <v>0.6610747575759888</v>
       </c>
       <c r="E222" t="n">
-        <v>0.3866416754336106</v>
+        <v>0.499402527214184</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
@@ -5094,10 +5106,10 @@
         <v>0.1261725959023785</v>
       </c>
       <c r="D223" t="n">
-        <v>0.1291402876377106</v>
+        <v>0.02837597206234932</v>
       </c>
       <c r="E223" t="n">
-        <v>0.1419923157028209</v>
+        <v>0.1084042105110338</v>
       </c>
       <c r="F223" t="n">
         <v>0</v>
@@ -5114,10 +5126,10 @@
         <v>0.2819243124247554</v>
       </c>
       <c r="D224" t="n">
-        <v>0.7054473757743835</v>
+        <v>0.8099119067192078</v>
       </c>
       <c r="E224" t="n">
-        <v>0.4536417180297654</v>
+        <v>0.4884632283447068</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
@@ -5134,10 +5146,10 @@
         <v>0.3678176128793122</v>
       </c>
       <c r="D225" t="n">
-        <v>0.4554597735404968</v>
+        <v>0.3989344239234924</v>
       </c>
       <c r="E225" t="n">
-        <v>0.4123346293423789</v>
+        <v>0.3934928461367108</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
@@ -5154,10 +5166,10 @@
         <v>0.3846254505714859</v>
       </c>
       <c r="D226" t="n">
-        <v>0.6008991003036499</v>
+        <v>0.7150325775146484</v>
       </c>
       <c r="E226" t="n">
-        <v>0.4690685354862392</v>
+        <v>0.5071130278899054</v>
       </c>
       <c r="F226" t="n">
         <v>0</v>
@@ -5174,10 +5186,10 @@
         <v>0.3591292818176218</v>
       </c>
       <c r="D227" t="n">
-        <v>0.2742202877998352</v>
+        <v>0.2644297480583191</v>
       </c>
       <c r="E227" t="n">
-        <v>0.3472858924581222</v>
+        <v>0.3440223792109502</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -5194,10 +5206,10 @@
         <v>0.2036246066488215</v>
       </c>
       <c r="D228" t="n">
-        <v>0.07723234593868256</v>
+        <v>0.007328466977924109</v>
       </c>
       <c r="E228" t="n">
-        <v>0.1766932590317212</v>
+        <v>0.1533919660448017</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
@@ -5211,13 +5223,13 @@
         <v>0.1681823414656075</v>
       </c>
       <c r="C229" t="n">
-        <v>0.1648734010380797</v>
+        <v>0.1648734010380796</v>
       </c>
       <c r="D229" t="n">
-        <v>0.06934261322021484</v>
+        <v>9.369522740598768e-05</v>
       </c>
       <c r="E229" t="n">
-        <v>0.1341327852413007</v>
+        <v>0.1110498125770311</v>
       </c>
       <c r="F229" t="n">
         <v>0</v>
@@ -5234,10 +5246,10 @@
         <v>0.4161244868753172</v>
       </c>
       <c r="D230" t="n">
-        <v>0.6640883684158325</v>
+        <v>0.8038098216056824</v>
       </c>
       <c r="E230" t="n">
-        <v>0.5662886224545465</v>
+        <v>0.6128624401844964</v>
       </c>
       <c r="F230" t="n">
         <v>1</v>
@@ -5254,10 +5266,10 @@
         <v>0.3235275812482772</v>
       </c>
       <c r="D231" t="n">
-        <v>0.5811320543289185</v>
+        <v>0.561307966709137</v>
       </c>
       <c r="E231" t="n">
-        <v>0.4277609267374808</v>
+        <v>0.421152897530887</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
@@ -5274,10 +5286,10 @@
         <v>0.2994786747738144</v>
       </c>
       <c r="D232" t="n">
-        <v>0.3699126839637756</v>
+        <v>0.6077280044555664</v>
       </c>
       <c r="E232" t="n">
-        <v>0.3332636724762666</v>
+        <v>0.4125354459735302</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
@@ -5294,10 +5306,10 @@
         <v>0.4990505806971714</v>
       </c>
       <c r="D233" t="n">
-        <v>0.8109335899353027</v>
+        <v>0.8981500864028931</v>
       </c>
       <c r="E233" t="n">
-        <v>0.6815192782806996</v>
+        <v>0.7105914437698964</v>
       </c>
       <c r="F233" t="n">
         <v>1</v>
@@ -5314,10 +5326,10 @@
         <v>0.2264685587260181</v>
       </c>
       <c r="D234" t="n">
-        <v>0.07039369642734528</v>
+        <v>0.0003715945058502257</v>
       </c>
       <c r="E234" t="n">
-        <v>0.1829799098634692</v>
+        <v>0.1596392092229708</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
@@ -5334,10 +5346,10 @@
         <v>0.1516911561738614</v>
       </c>
       <c r="D235" t="n">
-        <v>0.1011115312576294</v>
+        <v>0.007843248546123505</v>
       </c>
       <c r="E235" t="n">
-        <v>0.1576247145919394</v>
+        <v>0.1265352870214375</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -5354,10 +5366,10 @@
         <v>0.1909047351971768</v>
       </c>
       <c r="D236" t="n">
-        <v>0.1073566898703575</v>
+        <v>0.01474622450768948</v>
       </c>
       <c r="E236" t="n">
-        <v>0.1984266599546705</v>
+        <v>0.1675565048337812</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -5374,10 +5386,10 @@
         <v>0.1981556837950725</v>
       </c>
       <c r="D237" t="n">
-        <v>0.08343465626239777</v>
+        <v>0.006969102658331394</v>
       </c>
       <c r="E237" t="n">
-        <v>0.1824780035496361</v>
+        <v>0.156989485681614</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
@@ -5394,10 +5406,10 @@
         <v>0.1778260335415142</v>
       </c>
       <c r="D238" t="n">
-        <v>0.07864760607481003</v>
+        <v>0.003339972347021103</v>
       </c>
       <c r="E238" t="n">
-        <v>0.1615342540407676</v>
+        <v>0.1364317094648379</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -5414,10 +5426,10 @@
         <v>0.1873435289918541</v>
       </c>
       <c r="D239" t="n">
-        <v>0.0830690935254097</v>
+        <v>0.004050787072628736</v>
       </c>
       <c r="E239" t="n">
-        <v>0.1683094948147245</v>
+        <v>0.1419700593304642</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -5434,10 +5446,10 @@
         <v>0.3395414982170507</v>
       </c>
       <c r="D240" t="n">
-        <v>0.09880206733942032</v>
+        <v>0.03872617706656456</v>
       </c>
       <c r="E240" t="n">
-        <v>0.2997355969994621</v>
+        <v>0.2797103002418435</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -5454,10 +5466,10 @@
         <v>0.2222254044849644</v>
       </c>
       <c r="D241" t="n">
-        <v>0.1813520640134811</v>
+        <v>0.06753431260585785</v>
       </c>
       <c r="E241" t="n">
-        <v>0.2356695359391666</v>
+        <v>0.1977302854699589</v>
       </c>
       <c r="F241" t="n">
         <v>0</v>
@@ -5474,10 +5486,10 @@
         <v>0.200449741286107</v>
       </c>
       <c r="D242" t="n">
-        <v>0.184178039431572</v>
+        <v>0.08873680979013443</v>
       </c>
       <c r="E242" t="n">
-        <v>0.2197635001465742</v>
+        <v>0.1879497569327616</v>
       </c>
       <c r="F242" t="n">
         <v>0</v>
@@ -5494,10 +5506,10 @@
         <v>0.1912181260769634</v>
       </c>
       <c r="D243" t="n">
-        <v>0.09632100909948349</v>
+        <v>0.01154619175940752</v>
       </c>
       <c r="E243" t="n">
-        <v>0.1868204675145021</v>
+        <v>0.1585621950678101</v>
       </c>
       <c r="F243" t="n">
         <v>0</v>
@@ -5514,10 +5526,10 @@
         <v>0.186696717570394</v>
       </c>
       <c r="D244" t="n">
-        <v>0.09021563827991486</v>
+        <v>0.003715720493346453</v>
       </c>
       <c r="E244" t="n">
-        <v>0.1937951890084065</v>
+        <v>0.1649618830795504</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
@@ -5534,10 +5546,10 @@
         <v>0.1639942596504271</v>
       </c>
       <c r="D245" t="n">
-        <v>0.08729932457208633</v>
+        <v>0.009240282699465752</v>
       </c>
       <c r="E245" t="n">
-        <v>0.1487989349115501</v>
+        <v>0.1227792542873432</v>
       </c>
       <c r="F245" t="n">
         <v>0</v>
@@ -5554,10 +5566,10 @@
         <v>0.1611153175351719</v>
       </c>
       <c r="D246" t="n">
-        <v>0.07798473536968231</v>
+        <v>0.0006370523478835821</v>
       </c>
       <c r="E246" t="n">
-        <v>0.1612916409723326</v>
+        <v>0.1355090799650664</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
@@ -5574,10 +5586,10 @@
         <v>0.1262667783113349</v>
       </c>
       <c r="D247" t="n">
-        <v>0.1179822236299515</v>
+        <v>0.02108827978372574</v>
       </c>
       <c r="E247" t="n">
-        <v>0.1359898197031041</v>
+        <v>0.1036918384210289</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
@@ -5594,10 +5606,10 @@
         <v>0.1585615125826117</v>
       </c>
       <c r="D248" t="n">
-        <v>0.0745239332318306</v>
+        <v>0.0004938862402923405</v>
       </c>
       <c r="E248" t="n">
-        <v>0.1494643004078989</v>
+        <v>0.1247876180773861</v>
       </c>
       <c r="F248" t="n">
         <v>0</v>
@@ -5614,10 +5626,10 @@
         <v>0.2011124846606545</v>
       </c>
       <c r="D249" t="n">
-        <v>0.07253451645374298</v>
+        <v>0.0003034737310372293</v>
       </c>
       <c r="E249" t="n">
-        <v>0.1897774683497685</v>
+        <v>0.1657004541088666</v>
       </c>
       <c r="F249" t="n">
         <v>0</v>
@@ -5634,10 +5646,10 @@
         <v>0.1806149396947223</v>
       </c>
       <c r="D250" t="n">
-        <v>0.07544011622667313</v>
+        <v>0.00136008660774678</v>
       </c>
       <c r="E250" t="n">
-        <v>0.1675082952671708</v>
+        <v>0.142814952060862</v>
       </c>
       <c r="F250" t="n">
         <v>0</v>
@@ -5651,13 +5663,13 @@
         <v>0.2792796919928957</v>
       </c>
       <c r="C251" t="n">
-        <v>0.2611231350126407</v>
+        <v>0.2611231350126408</v>
       </c>
       <c r="D251" t="n">
-        <v>0.08035232126712799</v>
+        <v>0.02034502848982811</v>
       </c>
       <c r="E251" t="n">
-        <v>0.2069183827575548</v>
+        <v>0.1869159518317882</v>
       </c>
       <c r="F251" t="n">
         <v>0</v>
@@ -5671,13 +5683,13 @@
         <v>0.3120130766346317</v>
       </c>
       <c r="C252" t="n">
-        <v>0.1865138317694517</v>
+        <v>0.1865138317694516</v>
       </c>
       <c r="D252" t="n">
-        <v>0.1018126383423805</v>
+        <v>0.009187973104417324</v>
       </c>
       <c r="E252" t="n">
-        <v>0.2001131822488213</v>
+        <v>0.1692382938361669</v>
       </c>
       <c r="F252" t="n">
         <v>0</v>
@@ -5694,10 +5706,10 @@
         <v>0.1920183397833584</v>
       </c>
       <c r="D253" t="n">
-        <v>0.3167373538017273</v>
+        <v>0.5520892143249512</v>
       </c>
       <c r="E253" t="n">
-        <v>0.2635139203572945</v>
+        <v>0.3419645405317024</v>
       </c>
       <c r="F253" t="n">
         <v>0</v>
@@ -5714,10 +5726,10 @@
         <v>0.2805390912298826</v>
       </c>
       <c r="D254" t="n">
-        <v>0.2095842659473419</v>
+        <v>0.3322289884090424</v>
       </c>
       <c r="E254" t="n">
-        <v>0.3069473124989783</v>
+        <v>0.3478288866528785</v>
       </c>
       <c r="F254" t="n">
         <v>0</v>
@@ -5734,10 +5746,10 @@
         <v>0.2502262604231768</v>
       </c>
       <c r="D255" t="n">
-        <v>0.08276654034852982</v>
+        <v>0.01072320900857449</v>
       </c>
       <c r="E255" t="n">
-        <v>0.2018594862966383</v>
+        <v>0.1778450425166531</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -5754,10 +5766,10 @@
         <v>0.390845594733193</v>
       </c>
       <c r="D256" t="n">
-        <v>0.3012786507606506</v>
+        <v>0.4711893200874329</v>
       </c>
       <c r="E256" t="n">
-        <v>0.3676891452889533</v>
+        <v>0.4243260350645474</v>
       </c>
       <c r="F256" t="n">
         <v>0</v>
@@ -5774,10 +5786,10 @@
         <v>0.175026102636015</v>
       </c>
       <c r="D257" t="n">
-        <v>0.07738165557384491</v>
+        <v>0.001164573943242431</v>
       </c>
       <c r="E257" t="n">
-        <v>0.149569403391911</v>
+        <v>0.1241637095150436</v>
       </c>
       <c r="F257" t="n">
         <v>0</v>
@@ -5794,13 +5806,13 @@
         <v>0.4088206154703263</v>
       </c>
       <c r="D258" t="n">
-        <v>0.6291292309761047</v>
+        <v>0.6299753189086914</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5467607569758285</v>
+        <v>0.5470427862866907</v>
       </c>
       <c r="F258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -5814,10 +5826,10 @@
         <v>0.1572447750368471</v>
       </c>
       <c r="D259" t="n">
-        <v>0.08730572462081909</v>
+        <v>0.007263834588229656</v>
       </c>
       <c r="E259" t="n">
-        <v>0.1344451422533361</v>
+        <v>0.1077645122424729</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
@@ -5834,10 +5846,10 @@
         <v>0.1750358055755912</v>
       </c>
       <c r="D260" t="n">
-        <v>0.07753260433673859</v>
+        <v>0.002504072617739439</v>
       </c>
       <c r="E260" t="n">
-        <v>0.1831355116775282</v>
+        <v>0.1581260011045285</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
@@ -5854,10 +5866,10 @@
         <v>0.3073905915730032</v>
       </c>
       <c r="D261" t="n">
-        <v>0.2967298626899719</v>
+        <v>0.6006551384925842</v>
       </c>
       <c r="E261" t="n">
-        <v>0.3310670041980623</v>
+        <v>0.4323754294655997</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
@@ -5874,10 +5886,10 @@
         <v>0.348265197130379</v>
       </c>
       <c r="D262" t="n">
-        <v>0.408133327960968</v>
+        <v>0.7362231612205505</v>
       </c>
       <c r="E262" t="n">
-        <v>0.4117309629504666</v>
+        <v>0.5210942407036608</v>
       </c>
       <c r="F262" t="n">
         <v>0</v>
@@ -5894,10 +5906,10 @@
         <v>0.2504449997864151</v>
       </c>
       <c r="D263" t="n">
-        <v>0.07018271088600159</v>
+        <v>0.001459901919588447</v>
       </c>
       <c r="E263" t="n">
-        <v>0.2087899291438965</v>
+        <v>0.1858823261550921</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
@@ -5914,10 +5926,10 @@
         <v>0.2487859847002488</v>
       </c>
       <c r="D264" t="n">
-        <v>0.1209422722458839</v>
+        <v>0.03673926740884781</v>
       </c>
       <c r="E264" t="n">
-        <v>0.2330974712309465</v>
+        <v>0.2050298029519344</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
@@ -5934,10 +5946,10 @@
         <v>0.245107876141323</v>
       </c>
       <c r="D265" t="n">
-        <v>0.1988900005817413</v>
+        <v>0.2528724074363708</v>
       </c>
       <c r="E265" t="n">
-        <v>0.2374855313398836</v>
+        <v>0.2554796669580934</v>
       </c>
       <c r="F265" t="n">
         <v>0</v>
@@ -5954,10 +5966,10 @@
         <v>0.1913112978050115</v>
       </c>
       <c r="D266" t="n">
-        <v>0.09084881097078323</v>
+        <v>0.01344284601509571</v>
       </c>
       <c r="E266" t="n">
-        <v>0.1489657072753456</v>
+        <v>0.1231637189567831</v>
       </c>
       <c r="F266" t="n">
         <v>0</v>
@@ -5974,10 +5986,10 @@
         <v>0.4767168787500561</v>
       </c>
       <c r="D267" t="n">
-        <v>0.8241285085678101</v>
+        <v>0.9331678152084351</v>
       </c>
       <c r="E267" t="n">
-        <v>0.6659636547991642</v>
+        <v>0.7023100903460392</v>
       </c>
       <c r="F267" t="n">
         <v>1</v>
@@ -5994,10 +6006,10 @@
         <v>0.1485705963770307</v>
       </c>
       <c r="D268" t="n">
-        <v>0.07865413278341293</v>
+        <v>0.005845656152814627</v>
       </c>
       <c r="E268" t="n">
-        <v>0.1369050375644029</v>
+        <v>0.1126355453542035</v>
       </c>
       <c r="F268" t="n">
         <v>0</v>
@@ -6014,10 +6026,10 @@
         <v>0.1601275692817329</v>
       </c>
       <c r="D269" t="n">
-        <v>0.1156532317399979</v>
+        <v>0.02911767736077309</v>
       </c>
       <c r="E269" t="n">
-        <v>0.1653422013885925</v>
+        <v>0.1364970165955175</v>
       </c>
       <c r="F269" t="n">
         <v>0</v>
@@ -6031,13 +6043,13 @@
         <v>0.2955514954491868</v>
       </c>
       <c r="C270" t="n">
-        <v>0.2502690299836345</v>
+        <v>0.2502690299836346</v>
       </c>
       <c r="D270" t="n">
-        <v>0.1683726608753204</v>
+        <v>0.1064830794930458</v>
       </c>
       <c r="E270" t="n">
-        <v>0.2380643954360473</v>
+        <v>0.2174345349752891</v>
       </c>
       <c r="F270" t="n">
         <v>0</v>
@@ -6054,10 +6066,10 @@
         <v>0.1386278460007433</v>
       </c>
       <c r="D271" t="n">
-        <v>0.07488934695720673</v>
+        <v>0.001734850229695439</v>
       </c>
       <c r="E271" t="n">
-        <v>0.116515698534418</v>
+        <v>0.09213086629191425</v>
       </c>
       <c r="F271" t="n">
         <v>0</v>
@@ -6074,10 +6086,10 @@
         <v>0.4528366273550077</v>
       </c>
       <c r="D272" t="n">
-        <v>0.6812846064567566</v>
+        <v>0.7470617294311523</v>
       </c>
       <c r="E272" t="n">
-        <v>0.5500591212526543</v>
+        <v>0.5719848289107862</v>
       </c>
       <c r="F272" t="n">
         <v>1</v>
@@ -6094,10 +6106,10 @@
         <v>0.1026299458137512</v>
       </c>
       <c r="D273" t="n">
-        <v>0.073642298579216</v>
+        <v>0.0007317227427847683</v>
       </c>
       <c r="E273" t="n">
-        <v>0.09954908785490291</v>
+        <v>0.0752455625760925</v>
       </c>
       <c r="F273" t="n">
         <v>0</v>
@@ -6114,10 +6126,10 @@
         <v>0.1961761291495085</v>
       </c>
       <c r="D274" t="n">
-        <v>0.08125106245279312</v>
+        <v>0.007599769625812769</v>
       </c>
       <c r="E274" t="n">
-        <v>0.1749249104630376</v>
+        <v>0.1503744795207108</v>
       </c>
       <c r="F274" t="n">
         <v>0</v>
@@ -6134,10 +6146,10 @@
         <v>0.1702911462513545</v>
       </c>
       <c r="D275" t="n">
-        <v>0.09726913273334503</v>
+        <v>0.02939063683152199</v>
       </c>
       <c r="E275" t="n">
-        <v>0.1741913484284841</v>
+        <v>0.1515651831278765</v>
       </c>
       <c r="F275" t="n">
         <v>0</v>
@@ -6154,10 +6166,10 @@
         <v>0.1655900415348071</v>
       </c>
       <c r="D276" t="n">
-        <v>0.1006211787462234</v>
+        <v>0.0534062571823597</v>
       </c>
       <c r="E276" t="n">
-        <v>0.1627130619087133</v>
+        <v>0.1469747547207587</v>
       </c>
       <c r="F276" t="n">
         <v>0</v>
@@ -6174,10 +6186,10 @@
         <v>0.1391266762847933</v>
       </c>
       <c r="D277" t="n">
-        <v>0.06998039036989212</v>
+        <v>0.0001541202655062079</v>
       </c>
       <c r="E277" t="n">
-        <v>0.1168448005133738</v>
+        <v>0.09356937714524512</v>
       </c>
       <c r="F277" t="n">
         <v>0</v>
@@ -6194,10 +6206,10 @@
         <v>0.1867271243655948</v>
       </c>
       <c r="D278" t="n">
-        <v>0.1109280735254288</v>
+        <v>0.03635748848319054</v>
       </c>
       <c r="E278" t="n">
-        <v>0.1786226988352857</v>
+        <v>0.1537658371545396</v>
       </c>
       <c r="F278" t="n">
         <v>0</v>
@@ -6214,10 +6226,10 @@
         <v>0.1873945171855534</v>
       </c>
       <c r="D279" t="n">
-        <v>0.08337802439928055</v>
+        <v>0.009842800907790661</v>
       </c>
       <c r="E279" t="n">
-        <v>0.1812825308856875</v>
+        <v>0.1567707897218575</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
@@ -6234,10 +6246,10 @@
         <v>0.1714025339107549</v>
       </c>
       <c r="D280" t="n">
-        <v>0.07341708987951279</v>
+        <v>0.0009422712028026581</v>
       </c>
       <c r="E280" t="n">
-        <v>0.1375872753548577</v>
+        <v>0.113429002462621</v>
       </c>
       <c r="F280" t="n">
         <v>0</v>
@@ -6254,10 +6266,10 @@
         <v>0.1779010965527104</v>
       </c>
       <c r="D281" t="n">
-        <v>0.1636182069778442</v>
+        <v>0.08394143730401993</v>
       </c>
       <c r="E281" t="n">
-        <v>0.1895887910495127</v>
+        <v>0.1630298678249045</v>
       </c>
       <c r="F281" t="n">
         <v>0</v>
@@ -6274,10 +6286,10 @@
         <v>0.3903902560229622</v>
       </c>
       <c r="D282" t="n">
-        <v>0.4102032780647278</v>
+        <v>0.6036926507949829</v>
       </c>
       <c r="E282" t="n">
-        <v>0.4683844909045565</v>
+        <v>0.5328809484813082</v>
       </c>
       <c r="F282" t="n">
         <v>0</v>
@@ -6291,13 +6303,13 @@
         <v>0.550476105170383</v>
       </c>
       <c r="C283" t="n">
-        <v>0.3574356327946343</v>
+        <v>0.3574356327946342</v>
       </c>
       <c r="D283" t="n">
-        <v>0.5187364816665649</v>
+        <v>0.4954567849636078</v>
       </c>
       <c r="E283" t="n">
-        <v>0.4755494065438608</v>
+        <v>0.467789507642875</v>
       </c>
       <c r="F283" t="n">
         <v>0</v>
@@ -6311,13 +6323,13 @@
         <v>0.7568156864178142</v>
       </c>
       <c r="C284" t="n">
-        <v>0.4490935707747756</v>
+        <v>0.4490935707747755</v>
       </c>
       <c r="D284" t="n">
-        <v>0.2414169311523438</v>
+        <v>0.4335697293281555</v>
       </c>
       <c r="E284" t="n">
-        <v>0.4824420627816445</v>
+        <v>0.546492995506915</v>
       </c>
       <c r="F284" t="n">
         <v>0</v>
@@ -6334,10 +6346,10 @@
         <v>0.2380236721138009</v>
       </c>
       <c r="D285" t="n">
-        <v>0.0844900980591774</v>
+        <v>0.0103455139324069</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2261036663515932</v>
+        <v>0.201388804976003</v>
       </c>
       <c r="F285" t="n">
         <v>0</v>
@@ -6354,10 +6366,10 @@
         <v>0.2593752177619165</v>
       </c>
       <c r="D286" t="n">
-        <v>0.09189854562282562</v>
+        <v>0.0181169044226408</v>
       </c>
       <c r="E286" t="n">
-        <v>0.2330539353051482</v>
+        <v>0.2084600549050866</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
@@ -6374,10 +6386,10 @@
         <v>0.4315749329320095</v>
       </c>
       <c r="D287" t="n">
-        <v>0.7731422185897827</v>
+        <v>0.9490795135498047</v>
       </c>
       <c r="E287" t="n">
-        <v>0.6118371365575513</v>
+        <v>0.6704829015442253</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
@@ -6391,13 +6403,13 @@
         <v>0.1444448890072123</v>
       </c>
       <c r="C288" t="n">
-        <v>0.159850711883961</v>
+        <v>0.1598507118839609</v>
       </c>
       <c r="D288" t="n">
-        <v>0.07598410546779633</v>
+        <v>0.003827119711786509</v>
       </c>
       <c r="E288" t="n">
-        <v>0.1267599021196565</v>
+        <v>0.1027075735343199</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
@@ -6414,10 +6426,10 @@
         <v>0.2106448104099659</v>
       </c>
       <c r="D289" t="n">
-        <v>0.07523656636476517</v>
+        <v>0.000674943788908422</v>
       </c>
       <c r="E289" t="n">
-        <v>0.1933285688224994</v>
+        <v>0.1684746946305471</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
@@ -6434,10 +6446,10 @@
         <v>0.29810412999737</v>
       </c>
       <c r="D290" t="n">
-        <v>0.2895554304122925</v>
+        <v>0.5506076812744141</v>
       </c>
       <c r="E290" t="n">
-        <v>0.3010359055798053</v>
+        <v>0.3880533225338458</v>
       </c>
       <c r="F290" t="n">
         <v>0</v>
@@ -6454,10 +6466,10 @@
         <v>0.1278534693806734</v>
       </c>
       <c r="D291" t="n">
-        <v>0.06955866515636444</v>
+        <v>0.0001998046354856342</v>
       </c>
       <c r="E291" t="n">
-        <v>0.1137260856188376</v>
+        <v>0.09060646544521138</v>
       </c>
       <c r="F291" t="n">
         <v>0</v>
@@ -6474,10 +6486,10 @@
         <v>0.1689148276301773</v>
       </c>
       <c r="D292" t="n">
-        <v>0.07208804786205292</v>
+        <v>0.0006467222119681537</v>
       </c>
       <c r="E292" t="n">
-        <v>0.1582704266218092</v>
+        <v>0.1344566514051142</v>
       </c>
       <c r="F292" t="n">
         <v>0</v>
@@ -6494,10 +6506,10 @@
         <v>0.1748389942594712</v>
       </c>
       <c r="D293" t="n">
-        <v>0.1011514440178871</v>
+        <v>0.07091544568538666</v>
       </c>
       <c r="E293" t="n">
-        <v>0.1562313833575041</v>
+        <v>0.1461527172466706</v>
       </c>
       <c r="F293" t="n">
         <v>0</v>
@@ -6514,10 +6526,10 @@
         <v>0.529715019254259</v>
       </c>
       <c r="D294" t="n">
-        <v>0.8156825304031372</v>
+        <v>0.9290617704391479</v>
       </c>
       <c r="E294" t="n">
-        <v>0.679012024003583</v>
+        <v>0.7168051040155866</v>
       </c>
       <c r="F294" t="n">
         <v>1</v>
@@ -6534,10 +6546,10 @@
         <v>0.153782093213373</v>
       </c>
       <c r="D295" t="n">
-        <v>0.08363698422908783</v>
+        <v>0.005749867297708988</v>
       </c>
       <c r="E295" t="n">
-        <v>0.135018406875038</v>
+        <v>0.1090560345645784</v>
       </c>
       <c r="F295" t="n">
         <v>0</v>
@@ -6554,10 +6566,10 @@
         <v>0.2003185159287818</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1124139651656151</v>
+        <v>0.01781269907951355</v>
       </c>
       <c r="E296" t="n">
-        <v>0.1935424574457706</v>
+        <v>0.1620087020837368</v>
       </c>
       <c r="F296" t="n">
         <v>0</v>
@@ -6574,10 +6586,10 @@
         <v>0.1328378555273835</v>
       </c>
       <c r="D297" t="n">
-        <v>0.09672679007053375</v>
+        <v>0.01123248040676117</v>
       </c>
       <c r="E297" t="n">
-        <v>0.1201201347263406</v>
+        <v>0.09162203150508312</v>
       </c>
       <c r="F297" t="n">
         <v>0</v>
@@ -6594,10 +6606,10 @@
         <v>0.152367616981154</v>
       </c>
       <c r="D298" t="n">
-        <v>0.08706791698932648</v>
+        <v>0.009567131288349628</v>
       </c>
       <c r="E298" t="n">
-        <v>0.1294067580151687</v>
+        <v>0.1035731627815098</v>
       </c>
       <c r="F298" t="n">
         <v>0</v>
@@ -6614,10 +6626,10 @@
         <v>0.1561182812334015</v>
       </c>
       <c r="D299" t="n">
-        <v>0.09971628338098526</v>
+        <v>0.02235047891736031</v>
       </c>
       <c r="E299" t="n">
-        <v>0.1311323673076505</v>
+        <v>0.1053437658197755</v>
       </c>
       <c r="F299" t="n">
         <v>0</v>
@@ -6634,10 +6646,10 @@
         <v>0.1221284937013063</v>
       </c>
       <c r="D300" t="n">
-        <v>0.07431492954492569</v>
+        <v>0.00122591876424849</v>
       </c>
       <c r="E300" t="n">
-        <v>0.1021817466529864</v>
+        <v>0.07781874305942736</v>
       </c>
       <c r="F300" t="n">
         <v>0</v>
@@ -6654,13 +6666,13 @@
         <v>0.4459142746254918</v>
       </c>
       <c r="D301" t="n">
-        <v>0.4253687262535095</v>
+        <v>0.5532085299491882</v>
       </c>
       <c r="E301" t="n">
-        <v>0.491104257064401</v>
+        <v>0.5337175249629605</v>
       </c>
       <c r="F301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -6674,10 +6686,10 @@
         <v>0.1967689619748836</v>
       </c>
       <c r="D302" t="n">
-        <v>0.08897315710783005</v>
+        <v>0.006284228526055813</v>
       </c>
       <c r="E302" t="n">
-        <v>0.1683248069357667</v>
+        <v>0.1407618307418419</v>
       </c>
       <c r="F302" t="n">
         <v>0</v>
@@ -6694,10 +6706,10 @@
         <v>0.2268953908848247</v>
       </c>
       <c r="D303" t="n">
-        <v>0.2179907858371735</v>
+        <v>0.1429446488618851</v>
       </c>
       <c r="E303" t="n">
-        <v>0.2604450693017463</v>
+        <v>0.2354296903099835</v>
       </c>
       <c r="F303" t="n">
         <v>0</v>
@@ -6711,13 +6723,13 @@
         <v>0.5030306303959471</v>
       </c>
       <c r="C304" t="n">
-        <v>0.3875461986572109</v>
+        <v>0.387546198657211</v>
       </c>
       <c r="D304" t="n">
-        <v>0.1404279768466949</v>
+        <v>0.2978194057941437</v>
       </c>
       <c r="E304" t="n">
-        <v>0.3436682686332843</v>
+        <v>0.3961320782824339</v>
       </c>
       <c r="F304" t="n">
         <v>0</v>
@@ -6734,10 +6746,10 @@
         <v>0.3298059032701908</v>
       </c>
       <c r="D305" t="n">
-        <v>0.2528530359268188</v>
+        <v>0.5368747711181641</v>
       </c>
       <c r="E305" t="n">
-        <v>0.3646708212433259</v>
+        <v>0.4593447329737743</v>
       </c>
       <c r="F305" t="n">
         <v>0</v>
@@ -6754,10 +6766,10 @@
         <v>0.1390007768131399</v>
       </c>
       <c r="D306" t="n">
-        <v>0.1103818565607071</v>
+        <v>0.02275156788527966</v>
       </c>
       <c r="E306" t="n">
-        <v>0.1413554553310738</v>
+        <v>0.1121453591059313</v>
       </c>
       <c r="F306" t="n">
         <v>0</v>
@@ -6771,13 +6783,13 @@
         <v>0.255413139269263</v>
       </c>
       <c r="C307" t="n">
-        <v>0.2811656234643408</v>
+        <v>0.2811656234643407</v>
       </c>
       <c r="D307" t="n">
-        <v>0.1801097095012665</v>
+        <v>0.1310698091983795</v>
       </c>
       <c r="E307" t="n">
-        <v>0.2388961574116234</v>
+        <v>0.2225495239773277</v>
       </c>
       <c r="F307" t="n">
         <v>0</v>
@@ -6794,10 +6806,10 @@
         <v>0.163399945556621</v>
       </c>
       <c r="D308" t="n">
-        <v>0.1273003667593002</v>
+        <v>0.03269189596176147</v>
       </c>
       <c r="E308" t="n">
-        <v>0.1578677042409873</v>
+        <v>0.1263315473084744</v>
       </c>
       <c r="F308" t="n">
         <v>0</v>
@@ -6814,10 +6826,10 @@
         <v>0.2079452509647242</v>
       </c>
       <c r="D309" t="n">
-        <v>0.1012865081429482</v>
+        <v>0.02295833453536034</v>
       </c>
       <c r="E309" t="n">
-        <v>0.1898304053204574</v>
+        <v>0.1637210141179282</v>
       </c>
       <c r="F309" t="n">
         <v>0</v>
@@ -6834,10 +6846,10 @@
         <v>0.1504283477011669</v>
       </c>
       <c r="D310" t="n">
-        <v>0.1311550587415695</v>
+        <v>0.02550317347049713</v>
       </c>
       <c r="E310" t="n">
-        <v>0.1637761344189997</v>
+        <v>0.1285588393286422</v>
       </c>
       <c r="F310" t="n">
         <v>0</v>
@@ -6854,10 +6866,10 @@
         <v>0.1958254314160678</v>
       </c>
       <c r="D311" t="n">
-        <v>0.07764309644699097</v>
+        <v>0.002740442054346204</v>
       </c>
       <c r="E311" t="n">
-        <v>0.1622168752702355</v>
+        <v>0.1372493238060205</v>
       </c>
       <c r="F311" t="n">
         <v>0</v>
@@ -6874,10 +6886,10 @@
         <v>0.1856010182455337</v>
       </c>
       <c r="D312" t="n">
-        <v>0.08948908746242523</v>
+        <v>0.009317364543676376</v>
       </c>
       <c r="E312" t="n">
-        <v>0.1902346828996334</v>
+        <v>0.1635107752600504</v>
       </c>
       <c r="F312" t="n">
         <v>0</v>
@@ -6894,10 +6906,10 @@
         <v>0.1738268190782112</v>
       </c>
       <c r="D313" t="n">
-        <v>0.08182069659233093</v>
+        <v>0.005068528465926647</v>
       </c>
       <c r="E313" t="n">
-        <v>0.1522707073871148</v>
+        <v>0.12668665134498</v>
       </c>
       <c r="F313" t="n">
         <v>0</v>
@@ -6911,13 +6923,13 @@
         <v>0.2496876176969962</v>
       </c>
       <c r="C314" t="n">
-        <v>0.211142588207578</v>
+        <v>0.2111425882075779</v>
       </c>
       <c r="D314" t="n">
-        <v>0.1334736049175262</v>
+        <v>0.05186793208122253</v>
       </c>
       <c r="E314" t="n">
-        <v>0.1981012702740335</v>
+        <v>0.1708993793285989</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
@@ -6934,10 +6946,10 @@
         <v>0.360788607596815</v>
       </c>
       <c r="D315" t="n">
-        <v>0.2969556152820587</v>
+        <v>0.3988410234451294</v>
       </c>
       <c r="E315" t="n">
-        <v>0.3850985429363032</v>
+        <v>0.4190603456573268</v>
       </c>
       <c r="F315" t="n">
         <v>0</v>
@@ -6954,10 +6966,10 @@
         <v>0.4406345163130966</v>
       </c>
       <c r="D316" t="n">
-        <v>0.242593914270401</v>
+        <v>0.5868356823921204</v>
       </c>
       <c r="E316" t="n">
-        <v>0.4407294604103202</v>
+        <v>0.5554767164508934</v>
       </c>
       <c r="F316" t="n">
         <v>0</v>
@@ -6974,10 +6986,10 @@
         <v>0.256114922641103</v>
       </c>
       <c r="D317" t="n">
-        <v>0.1404961943626404</v>
+        <v>0.07382340729236603</v>
       </c>
       <c r="E317" t="n">
-        <v>0.202136018296866</v>
+        <v>0.1799117559401079</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
@@ -6994,10 +7006,10 @@
         <v>0.1604986786266021</v>
       </c>
       <c r="D318" t="n">
-        <v>0.08003890514373779</v>
+        <v>0.008480402640998363</v>
       </c>
       <c r="E318" t="n">
-        <v>0.1355512306291459</v>
+        <v>0.1116983964615661</v>
       </c>
       <c r="F318" t="n">
         <v>0</v>
@@ -7014,10 +7026,10 @@
         <v>0.3296289512356696</v>
       </c>
       <c r="D319" t="n">
-        <v>0.5691872835159302</v>
+        <v>0.7945693731307983</v>
       </c>
       <c r="E319" t="n">
-        <v>0.4629686650268415</v>
+        <v>0.5380960282317976</v>
       </c>
       <c r="F319" t="n">
         <v>0</v>
@@ -7034,10 +7046,10 @@
         <v>0.252909947726533</v>
       </c>
       <c r="D320" t="n">
-        <v>0.1001055240631104</v>
+        <v>0.009557528421282768</v>
       </c>
       <c r="E320" t="n">
-        <v>0.2230646471501231</v>
+        <v>0.1928819819361805</v>
       </c>
       <c r="F320" t="n">
         <v>0</v>
@@ -7054,10 +7066,10 @@
         <v>0.2845608243306739</v>
       </c>
       <c r="D321" t="n">
-        <v>0.09966985881328583</v>
+        <v>0.0640675351023674</v>
       </c>
       <c r="E321" t="n">
-        <v>0.2658255059514497</v>
+        <v>0.2539580647144769</v>
       </c>
       <c r="F321" t="n">
         <v>0</v>
@@ -7071,13 +7083,13 @@
         <v>0.4401486978926595</v>
       </c>
       <c r="C322" t="n">
-        <v>0.3167438016021331</v>
+        <v>0.316743801602133</v>
       </c>
       <c r="D322" t="n">
-        <v>0.2711133360862732</v>
+        <v>0.4297438561916351</v>
       </c>
       <c r="E322" t="n">
-        <v>0.3426686118603553</v>
+        <v>0.3955454518954759</v>
       </c>
       <c r="F322" t="n">
         <v>0</v>
@@ -7094,10 +7106,10 @@
         <v>0.1672527111503965</v>
       </c>
       <c r="D323" t="n">
-        <v>0.06956822425127029</v>
+        <v>5.918590613873675e-05</v>
       </c>
       <c r="E323" t="n">
-        <v>0.1558873063880211</v>
+        <v>0.132717626939644</v>
       </c>
       <c r="F323" t="n">
         <v>0</v>
@@ -7114,10 +7126,10 @@
         <v>0.2274029563986385</v>
       </c>
       <c r="D324" t="n">
-        <v>0.1143343448638916</v>
+        <v>0.06475023925304413</v>
       </c>
       <c r="E324" t="n">
-        <v>0.2319125242494772</v>
+        <v>0.2153844890458614</v>
       </c>
       <c r="F324" t="n">
         <v>0</v>
@@ -7134,10 +7146,10 @@
         <v>0.1784560160977895</v>
       </c>
       <c r="D325" t="n">
-        <v>0.07509391009807587</v>
+        <v>0.00132004776969552</v>
       </c>
       <c r="E325" t="n">
-        <v>0.1618027860048913</v>
+        <v>0.1372114985620979</v>
       </c>
       <c r="F325" t="n">
         <v>0</v>
@@ -7154,10 +7166,10 @@
         <v>0.3456614133170233</v>
       </c>
       <c r="D326" t="n">
-        <v>0.294018030166626</v>
+        <v>0.5201010704040527</v>
       </c>
       <c r="E326" t="n">
-        <v>0.3687960563960078</v>
+        <v>0.4441570698084834</v>
       </c>
       <c r="F326" t="n">
         <v>0</v>
@@ -7174,10 +7186,10 @@
         <v>0.1883110964159422</v>
       </c>
       <c r="D327" t="n">
-        <v>0.0731484666466713</v>
+        <v>0.02260873094201088</v>
       </c>
       <c r="E327" t="n">
-        <v>0.1334385453908538</v>
+        <v>0.1165919668226336</v>
       </c>
       <c r="F327" t="n">
         <v>0</v>
@@ -7194,10 +7206,10 @@
         <v>0.1601434475957625</v>
       </c>
       <c r="D328" t="n">
-        <v>0.08045828342437744</v>
+        <v>0.000683480582665652</v>
       </c>
       <c r="E328" t="n">
-        <v>0.149026972557246</v>
+        <v>0.1224353716100087</v>
       </c>
       <c r="F328" t="n">
         <v>0</v>
@@ -7214,10 +7226,10 @@
         <v>0.3021918347781463</v>
       </c>
       <c r="D329" t="n">
-        <v>0.2685330212116241</v>
+        <v>0.4126993715763092</v>
       </c>
       <c r="E329" t="n">
-        <v>0.3220140109954444</v>
+        <v>0.3700694611170061</v>
       </c>
       <c r="F329" t="n">
         <v>0</v>
@@ -7231,13 +7243,13 @@
         <v>0.4533135724407669</v>
       </c>
       <c r="C330" t="n">
-        <v>0.30745331861488</v>
+        <v>0.3074533186148799</v>
       </c>
       <c r="D330" t="n">
-        <v>0.1384633779525757</v>
+        <v>0.1142477542161942</v>
       </c>
       <c r="E330" t="n">
-        <v>0.2997434230027409</v>
+        <v>0.291671548423947</v>
       </c>
       <c r="F330" t="n">
         <v>0</v>
@@ -7254,10 +7266,10 @@
         <v>0.2136383502321311</v>
       </c>
       <c r="D331" t="n">
-        <v>0.06972009688615799</v>
+        <v>7.844428910175338e-05</v>
       </c>
       <c r="E331" t="n">
-        <v>0.1938459793419419</v>
+        <v>0.1706320951429232</v>
       </c>
       <c r="F331" t="n">
         <v>0</v>
@@ -7274,10 +7286,10 @@
         <v>0.1458729905124276</v>
       </c>
       <c r="D332" t="n">
-        <v>0.09176170825958252</v>
+        <v>0.01936561614274979</v>
       </c>
       <c r="E332" t="n">
-        <v>0.1398995745067543</v>
+        <v>0.1157675438011434</v>
       </c>
       <c r="F332" t="n">
         <v>0</v>
@@ -7294,10 +7306,10 @@
         <v>0.1997967681243279</v>
       </c>
       <c r="D333" t="n">
-        <v>0.1213887184858322</v>
+        <v>0.02484229207038879</v>
       </c>
       <c r="E333" t="n">
-        <v>0.1931291758503866</v>
+        <v>0.1609470337119054</v>
       </c>
       <c r="F333" t="n">
         <v>0</v>
@@ -7314,10 +7326,10 @@
         <v>0.1936305639931817</v>
       </c>
       <c r="D334" t="n">
-        <v>0.08385764807462692</v>
+        <v>0.0006208947743289173</v>
       </c>
       <c r="E334" t="n">
-        <v>0.1439304679975286</v>
+        <v>0.1161848835640959</v>
       </c>
       <c r="F334" t="n">
         <v>0</v>
@@ -7334,10 +7346,10 @@
         <v>0.22345007058196</v>
       </c>
       <c r="D335" t="n">
-        <v>0.09444044530391693</v>
+        <v>0.008851064369082451</v>
       </c>
       <c r="E335" t="n">
-        <v>0.2082466983265767</v>
+        <v>0.1797169046816319</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
@@ -7354,10 +7366,10 @@
         <v>0.3080437267160764</v>
       </c>
       <c r="D336" t="n">
-        <v>0.1192271336913109</v>
+        <v>0.1428109258413315</v>
       </c>
       <c r="E336" t="n">
-        <v>0.2878236622544914</v>
+        <v>0.2956849263044982</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
@@ -7374,10 +7386,10 @@
         <v>0.1396434426258715</v>
       </c>
       <c r="D337" t="n">
-        <v>0.07945443689823151</v>
+        <v>0.00757583836093545</v>
       </c>
       <c r="E337" t="n">
-        <v>0.120138304693926</v>
+        <v>0.09617877184816066</v>
       </c>
       <c r="F337" t="n">
         <v>0</v>
@@ -7394,10 +7406,10 @@
         <v>0.2244373896237448</v>
       </c>
       <c r="D338" t="n">
-        <v>0.1538756340742111</v>
+        <v>0.07580826431512833</v>
       </c>
       <c r="E338" t="n">
-        <v>0.24480606859073</v>
+        <v>0.218783612004369</v>
       </c>
       <c r="F338" t="n">
         <v>0</v>
@@ -7414,10 +7426,10 @@
         <v>0.283209351425923</v>
       </c>
       <c r="D339" t="n">
-        <v>0.09142465889453888</v>
+        <v>0.04234002158045769</v>
       </c>
       <c r="E339" t="n">
-        <v>0.2346674938150066</v>
+        <v>0.2183059480436462</v>
       </c>
       <c r="F339" t="n">
         <v>0</v>
@@ -7434,10 +7446,10 @@
         <v>0.2077499720116928</v>
       </c>
       <c r="D340" t="n">
-        <v>0.07150884717702866</v>
+        <v>0.006006040144711733</v>
       </c>
       <c r="E340" t="n">
-        <v>0.1628458322805758</v>
+        <v>0.1410115632698035</v>
       </c>
       <c r="F340" t="n">
         <v>0</v>
@@ -7454,10 +7466,10 @@
         <v>0.2466391656695625</v>
       </c>
       <c r="D341" t="n">
-        <v>0.09646593779325485</v>
+        <v>0.005515526980161667</v>
       </c>
       <c r="E341" t="n">
-        <v>0.2396379188092786</v>
+        <v>0.2093211152049142</v>
       </c>
       <c r="F341" t="n">
         <v>0</v>
@@ -7474,10 +7486,10 @@
         <v>0.1834007276203239</v>
       </c>
       <c r="D342" t="n">
-        <v>0.07643570750951767</v>
+        <v>0.0007232059724628925</v>
       </c>
       <c r="E342" t="n">
-        <v>0.1495937107750462</v>
+        <v>0.1243562102626947</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
@@ -7494,10 +7506,10 @@
         <v>0.2110750036838882</v>
       </c>
       <c r="D343" t="n">
-        <v>0.2368126809597015</v>
+        <v>0.1374697238206863</v>
       </c>
       <c r="E343" t="n">
-        <v>0.2298394552614111</v>
+        <v>0.1967251362150727</v>
       </c>
       <c r="F343" t="n">
         <v>0</v>
@@ -7514,10 +7526,10 @@
         <v>0.1701332961107747</v>
       </c>
       <c r="D344" t="n">
-        <v>0.09698940813541412</v>
+        <v>0.01607757993042469</v>
       </c>
       <c r="E344" t="n">
-        <v>0.1470972882946387</v>
+        <v>0.1201266788929756</v>
       </c>
       <c r="F344" t="n">
         <v>0</v>
@@ -7534,10 +7546,10 @@
         <v>0.1631228374510302</v>
       </c>
       <c r="D345" t="n">
-        <v>0.09971655160188675</v>
+        <v>0.01374964602291584</v>
       </c>
       <c r="E345" t="n">
-        <v>0.1797244790749343</v>
+        <v>0.151068843881944</v>
       </c>
       <c r="F345" t="n">
         <v>0</v>
@@ -7554,10 +7566,10 @@
         <v>0.2121078237503132</v>
       </c>
       <c r="D346" t="n">
-        <v>0.07923673093318939</v>
+        <v>0.003094628918915987</v>
       </c>
       <c r="E346" t="n">
-        <v>0.1880939886413555</v>
+        <v>0.1627132879699311</v>
       </c>
       <c r="F346" t="n">
         <v>0</v>
@@ -7574,10 +7586,10 @@
         <v>0.2020880758263718</v>
       </c>
       <c r="D347" t="n">
-        <v>0.06832520663738251</v>
+        <v>1.751318268361501e-05</v>
       </c>
       <c r="E347" t="n">
-        <v>0.1685527600744308</v>
+        <v>0.1457835289228645</v>
       </c>
       <c r="F347" t="n">
         <v>0</v>
@@ -7591,13 +7603,13 @@
         <v>0.371373830310047</v>
       </c>
       <c r="C348" t="n">
-        <v>0.2546876041861252</v>
+        <v>0.2546876041861251</v>
       </c>
       <c r="D348" t="n">
-        <v>0.1054892167448997</v>
+        <v>0.01632943190634251</v>
       </c>
       <c r="E348" t="n">
-        <v>0.2438502170803573</v>
+        <v>0.2141302888008382</v>
       </c>
       <c r="F348" t="n">
         <v>0</v>
@@ -7614,10 +7626,10 @@
         <v>0.3161943389451863</v>
       </c>
       <c r="D349" t="n">
-        <v>0.2000764310359955</v>
+        <v>0.3478564321994781</v>
       </c>
       <c r="E349" t="n">
-        <v>0.2816772461443842</v>
+        <v>0.3309372465322118</v>
       </c>
       <c r="F349" t="n">
         <v>0</v>
@@ -7634,10 +7646,10 @@
         <v>0.2207397406038883</v>
       </c>
       <c r="D350" t="n">
-        <v>0.07453347742557526</v>
+        <v>0.003785699140280485</v>
       </c>
       <c r="E350" t="n">
-        <v>0.1976711485664213</v>
+        <v>0.1740885558046564</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
@@ -7651,16 +7663,16 @@
         <v>0.520356211392224</v>
       </c>
       <c r="C351" t="n">
-        <v>0.365976316125902</v>
+        <v>0.3659763161259019</v>
       </c>
       <c r="D351" t="n">
-        <v>0.6534706354141235</v>
+        <v>0.678344190120697</v>
       </c>
       <c r="E351" t="n">
-        <v>0.5132677209774165</v>
+        <v>0.5215589058796076</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
@@ -7674,10 +7686,10 @@
         <v>0.1264076750509179</v>
       </c>
       <c r="D352" t="n">
-        <v>0.07116667181253433</v>
+        <v>0.0001270641369046643</v>
       </c>
       <c r="E352" t="n">
-        <v>0.09919488887669115</v>
+        <v>0.07551501965148126</v>
       </c>
       <c r="F352" t="n">
         <v>0</v>
@@ -7694,10 +7706,10 @@
         <v>0.1720775936789294</v>
       </c>
       <c r="D353" t="n">
-        <v>0.07055987417697906</v>
+        <v>0.0001576315407874063</v>
       </c>
       <c r="E353" t="n">
-        <v>0.1388202016513044</v>
+        <v>0.1153527874392405</v>
       </c>
       <c r="F353" t="n">
         <v>0</v>
@@ -7714,10 +7726,10 @@
         <v>0.2440190853233989</v>
       </c>
       <c r="D354" t="n">
-        <v>0.1716596782207489</v>
+        <v>0.2605370581150055</v>
       </c>
       <c r="E354" t="n">
-        <v>0.2106843906290128</v>
+        <v>0.2403101839270984</v>
       </c>
       <c r="F354" t="n">
         <v>0</v>
@@ -7734,10 +7746,10 @@
         <v>0.1985070884957957</v>
       </c>
       <c r="D355" t="n">
-        <v>0.1518760174512863</v>
+        <v>0.2108025252819061</v>
       </c>
       <c r="E355" t="n">
-        <v>0.1782356708228855</v>
+        <v>0.1978778400997588</v>
       </c>
       <c r="F355" t="n">
         <v>0</v>
@@ -7754,10 +7766,10 @@
         <v>0.1389995342007893</v>
       </c>
       <c r="D356" t="n">
-        <v>0.07942656427621841</v>
+        <v>0.002438020426779985</v>
       </c>
       <c r="E356" t="n">
-        <v>0.1264775769996299</v>
+        <v>0.1008147290498171</v>
       </c>
       <c r="F356" t="n">
         <v>0</v>
@@ -7774,10 +7786,10 @@
         <v>0.2028237531849048</v>
       </c>
       <c r="D357" t="n">
-        <v>0.08465567231178284</v>
+        <v>0.003070397768169641</v>
       </c>
       <c r="E357" t="n">
-        <v>0.1823408272126051</v>
+        <v>0.1551457356980674</v>
       </c>
       <c r="F357" t="n">
         <v>0</v>
@@ -7794,10 +7806,10 @@
         <v>0.3595630951327164</v>
       </c>
       <c r="D358" t="n">
-        <v>0.4918052554130554</v>
+        <v>0.7389410734176636</v>
       </c>
       <c r="E358" t="n">
-        <v>0.4798656813317715</v>
+        <v>0.5622442873333076</v>
       </c>
       <c r="F358" t="n">
         <v>0</v>
@@ -7814,10 +7826,10 @@
         <v>0.4263509213265251</v>
       </c>
       <c r="D359" t="n">
-        <v>0.1652258485555649</v>
+        <v>0.09517713636159897</v>
       </c>
       <c r="E359" t="n">
-        <v>0.3947238001044717</v>
+        <v>0.3713742293731497</v>
       </c>
       <c r="F359" t="n">
         <v>0</v>
@@ -7834,10 +7846,10 @@
         <v>0.2599309387281244</v>
       </c>
       <c r="D360" t="n">
-        <v>0.1121445298194885</v>
+        <v>0.05140084773302078</v>
       </c>
       <c r="E360" t="n">
-        <v>0.2669371375124028</v>
+        <v>0.2466892434835803</v>
       </c>
       <c r="F360" t="n">
         <v>0</v>
@@ -7854,10 +7866,10 @@
         <v>0.1395222394041264</v>
       </c>
       <c r="D361" t="n">
-        <v>0.07171179354190826</v>
+        <v>0.000355315045453608</v>
       </c>
       <c r="E361" t="n">
-        <v>0.1356368994622129</v>
+        <v>0.1118514066300614</v>
       </c>
       <c r="F361" t="n">
         <v>0</v>
@@ -7874,10 +7886,10 @@
         <v>0.3360344552869404</v>
       </c>
       <c r="D362" t="n">
-        <v>0.2887772917747498</v>
+        <v>0.5687354207038879</v>
       </c>
       <c r="E362" t="n">
-        <v>0.3598062582620599</v>
+        <v>0.4531256345717726</v>
       </c>
       <c r="F362" t="n">
         <v>0</v>
@@ -7894,10 +7906,10 @@
         <v>0.2468609538649147</v>
       </c>
       <c r="D363" t="n">
-        <v>0.2433619499206543</v>
+        <v>0.2211678028106689</v>
       </c>
       <c r="E363" t="n">
-        <v>0.2746875764788395</v>
+        <v>0.2672895274421777</v>
       </c>
       <c r="F363" t="n">
         <v>0</v>
@@ -7914,10 +7926,10 @@
         <v>0.270059796455745</v>
       </c>
       <c r="D364" t="n">
-        <v>0.1350765824317932</v>
+        <v>0.2592461705207825</v>
       </c>
       <c r="E364" t="n">
-        <v>0.2043888636566236</v>
+        <v>0.2457787263529533</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
@@ -7934,10 +7946,10 @@
         <v>0.1765666227222857</v>
       </c>
       <c r="D365" t="n">
-        <v>0.08850008249282837</v>
+        <v>0.02522634342312813</v>
       </c>
       <c r="E365" t="n">
-        <v>0.1397454493545425</v>
+        <v>0.1186542029979758</v>
       </c>
       <c r="F365" t="n">
         <v>0</v>
@@ -7954,10 +7966,10 @@
         <v>0.1595701629983918</v>
       </c>
       <c r="D366" t="n">
-        <v>0.1137158125638962</v>
+        <v>0.09052391350269318</v>
       </c>
       <c r="E366" t="n">
-        <v>0.1554299926035575</v>
+        <v>0.1476993595831565</v>
       </c>
       <c r="F366" t="n">
         <v>0</v>
@@ -7971,13 +7983,13 @@
         <v>0.2953056566032289</v>
       </c>
       <c r="C367" t="n">
-        <v>0.2254987095801283</v>
+        <v>0.2254987095801282</v>
       </c>
       <c r="D367" t="n">
-        <v>0.06995604932308197</v>
+        <v>8.208425424527377e-05</v>
       </c>
       <c r="E367" t="n">
-        <v>0.1969201385021464</v>
+        <v>0.1736288168125341</v>
       </c>
       <c r="F367" t="n">
         <v>0</v>
@@ -7994,10 +8006,10 @@
         <v>0.2994431663109915</v>
       </c>
       <c r="D368" t="n">
-        <v>0.07687624543905258</v>
+        <v>0.004808249417692423</v>
       </c>
       <c r="E368" t="n">
-        <v>0.2634561891003269</v>
+        <v>0.2394335237598735</v>
       </c>
       <c r="F368" t="n">
         <v>0</v>
@@ -8014,10 +8026,10 @@
         <v>0.1741719378395016</v>
       </c>
       <c r="D369" t="n">
-        <v>0.08271059393882751</v>
+        <v>0.02133238688111305</v>
       </c>
       <c r="E369" t="n">
-        <v>0.1563226756421258</v>
+        <v>0.1358632732895544</v>
       </c>
       <c r="F369" t="n">
         <v>0</v>
@@ -8034,10 +8046,10 @@
         <v>0.1798384744288231</v>
       </c>
       <c r="D370" t="n">
-        <v>0.0765896812081337</v>
+        <v>0.001721614273265004</v>
       </c>
       <c r="E370" t="n">
-        <v>0.1767958426622153</v>
+        <v>0.1518398203505924</v>
       </c>
       <c r="F370" t="n">
         <v>0</v>
@@ -8054,10 +8066,10 @@
         <v>0.1739304088231993</v>
       </c>
       <c r="D371" t="n">
-        <v>0.1548161208629608</v>
+        <v>0.3915858566761017</v>
       </c>
       <c r="E371" t="n">
-        <v>0.1652201976437898</v>
+        <v>0.2441434429148367</v>
       </c>
       <c r="F371" t="n">
         <v>0</v>
@@ -8074,10 +8086,10 @@
         <v>0.1370753474343921</v>
       </c>
       <c r="D372" t="n">
-        <v>0.07309138029813766</v>
+        <v>0.0004337720456533134</v>
       </c>
       <c r="E372" t="n">
-        <v>0.1241927599656435</v>
+        <v>0.09997355721481536</v>
       </c>
       <c r="F372" t="n">
         <v>0</v>
@@ -8094,10 +8106,10 @@
         <v>0.1412973528926903</v>
       </c>
       <c r="D373" t="n">
-        <v>0.07289459556341171</v>
+        <v>0.004186898469924927</v>
       </c>
       <c r="E373" t="n">
-        <v>0.139157508736798</v>
+        <v>0.116254943038969</v>
       </c>
       <c r="F373" t="n">
         <v>0</v>
@@ -8114,10 +8126,10 @@
         <v>0.1691431399637203</v>
       </c>
       <c r="D374" t="n">
-        <v>0.09926066547632217</v>
+        <v>0.0245132502168417</v>
       </c>
       <c r="E374" t="n">
-        <v>0.155450211977667</v>
+        <v>0.1305344068911735</v>
       </c>
       <c r="F374" t="n">
         <v>0</v>
@@ -8134,10 +8146,10 @@
         <v>0.1052892364383654</v>
       </c>
       <c r="D375" t="n">
-        <v>0.07991179823875427</v>
+        <v>0.002064136322587729</v>
       </c>
       <c r="E375" t="n">
-        <v>0.1287878391715267</v>
+        <v>0.1028386185328045</v>
       </c>
       <c r="F375" t="n">
         <v>0</v>
@@ -8154,10 +8166,10 @@
         <v>0.2696032742796808</v>
       </c>
       <c r="D376" t="n">
-        <v>0.09191969782114029</v>
+        <v>0.02997564151883125</v>
       </c>
       <c r="E376" t="n">
-        <v>0.2510160360451106</v>
+        <v>0.2303680172776743</v>
       </c>
       <c r="F376" t="n">
         <v>0</v>
@@ -8174,10 +8186,10 @@
         <v>0.1828416191914569</v>
       </c>
       <c r="D377" t="n">
-        <v>0.07250047475099564</v>
+        <v>0.0002340240171179175</v>
       </c>
       <c r="E377" t="n">
-        <v>0.1391383457383744</v>
+        <v>0.1150495288270818</v>
       </c>
       <c r="F377" t="n">
         <v>0</v>
@@ -8194,10 +8206,10 @@
         <v>0.1573012072151023</v>
       </c>
       <c r="D378" t="n">
-        <v>0.07656170427799225</v>
+        <v>0.001264168415218592</v>
       </c>
       <c r="E378" t="n">
-        <v>0.1281417879278368</v>
+        <v>0.1030426093069123</v>
       </c>
       <c r="F378" t="n">
         <v>0</v>
@@ -8214,10 +8226,10 @@
         <v>0.1979168143936013</v>
       </c>
       <c r="D379" t="n">
-        <v>0.2729851603507996</v>
+        <v>0.3548492193222046</v>
       </c>
       <c r="E379" t="n">
-        <v>0.2252338496475754</v>
+        <v>0.2525218693047104</v>
       </c>
       <c r="F379" t="n">
         <v>0</v>
@@ -8234,10 +8246,10 @@
         <v>0.3951778616586796</v>
       </c>
       <c r="D380" t="n">
-        <v>0.4178499281406403</v>
+        <v>0.4325044751167297</v>
       </c>
       <c r="E380" t="n">
-        <v>0.4171823943301345</v>
+        <v>0.4220672433221644</v>
       </c>
       <c r="F380" t="n">
         <v>0</v>
@@ -8254,10 +8266,10 @@
         <v>0.3056208754025039</v>
       </c>
       <c r="D381" t="n">
-        <v>0.4603724479675293</v>
+        <v>0.6313949823379517</v>
       </c>
       <c r="E381" t="n">
-        <v>0.3601663440877312</v>
+        <v>0.4171738555445387</v>
       </c>
       <c r="F381" t="n">
         <v>0</v>
@@ -8274,10 +8286,10 @@
         <v>0.2201093997738111</v>
       </c>
       <c r="D382" t="n">
-        <v>0.09646923840045929</v>
+        <v>0.1421291828155518</v>
       </c>
       <c r="E382" t="n">
-        <v>0.1799792304088229</v>
+        <v>0.1951992118805204</v>
       </c>
       <c r="F382" t="n">
         <v>0</v>
@@ -8294,10 +8306,10 @@
         <v>0.2295245798726985</v>
       </c>
       <c r="D383" t="n">
-        <v>0.1081742793321609</v>
+        <v>0.04087569564580917</v>
       </c>
       <c r="E383" t="n">
-        <v>0.1869728285437302</v>
+        <v>0.1645399673149463</v>
       </c>
       <c r="F383" t="n">
         <v>0</v>
@@ -8314,10 +8326,10 @@
         <v>0.321646146623849</v>
       </c>
       <c r="D384" t="n">
-        <v>0.1731357574462891</v>
+        <v>0.09238956123590469</v>
       </c>
       <c r="E384" t="n">
-        <v>0.285769548524793</v>
+        <v>0.2588541497879982</v>
       </c>
       <c r="F384" t="n">
         <v>0</v>
@@ -8334,10 +8346,10 @@
         <v>0.1541845311681382</v>
       </c>
       <c r="D385" t="n">
-        <v>0.07392682135105133</v>
+        <v>0.005669549573212862</v>
       </c>
       <c r="E385" t="n">
-        <v>0.1171681984715195</v>
+        <v>0.09441577454557333</v>
       </c>
       <c r="F385" t="n">
         <v>0</v>
@@ -8354,10 +8366,10 @@
         <v>0.2916479817323466</v>
       </c>
       <c r="D386" t="n">
-        <v>0.1361304223537445</v>
+        <v>0.1210959926247597</v>
       </c>
       <c r="E386" t="n">
-        <v>0.2884072765448897</v>
+        <v>0.2833957999685615</v>
       </c>
       <c r="F386" t="n">
         <v>0</v>
@@ -8374,10 +8386,10 @@
         <v>0.3600650269622542</v>
       </c>
       <c r="D387" t="n">
-        <v>0.6518110036849976</v>
+        <v>0.7444862127304077</v>
       </c>
       <c r="E387" t="n">
-        <v>0.4848216318669572</v>
+        <v>0.5157133682154272</v>
       </c>
       <c r="F387" t="n">
         <v>0</v>
@@ -8394,10 +8406,10 @@
         <v>0.3166279714005419</v>
       </c>
       <c r="D388" t="n">
-        <v>0.2289565354585648</v>
+        <v>0.4454097747802734</v>
       </c>
       <c r="E388" t="n">
-        <v>0.3230958479291308</v>
+        <v>0.3952469277030337</v>
       </c>
       <c r="F388" t="n">
         <v>0</v>
@@ -8414,10 +8426,10 @@
         <v>0.2240966464282289</v>
       </c>
       <c r="D389" t="n">
-        <v>0.176185742020607</v>
+        <v>0.2748691141605377</v>
       </c>
       <c r="E389" t="n">
-        <v>0.2129648038658102</v>
+        <v>0.2458592612457871</v>
       </c>
       <c r="F389" t="n">
         <v>0</v>
@@ -8434,10 +8446,10 @@
         <v>0.3244848459106048</v>
       </c>
       <c r="D390" t="n">
-        <v>0.1369571685791016</v>
+        <v>0.1387932300567627</v>
       </c>
       <c r="E390" t="n">
-        <v>0.2596950423387026</v>
+        <v>0.2603070628312563</v>
       </c>
       <c r="F390" t="n">
         <v>0</v>
@@ -8454,10 +8466,10 @@
         <v>0.1856114466420517</v>
       </c>
       <c r="D391" t="n">
-        <v>0.1260299533605576</v>
+        <v>0.01874219067394733</v>
       </c>
       <c r="E391" t="n">
-        <v>0.1539611212265976</v>
+        <v>0.1181985336643941</v>
       </c>
       <c r="F391" t="n">
         <v>0</v>
@@ -8474,10 +8486,10 @@
         <v>0.4728141752586971</v>
       </c>
       <c r="D392" t="n">
-        <v>0.716367244720459</v>
+        <v>0.9083989858627319</v>
       </c>
       <c r="E392" t="n">
-        <v>0.6274679293533828</v>
+        <v>0.6914785097341406</v>
       </c>
       <c r="F392" t="n">
         <v>1</v>
@@ -8491,13 +8503,13 @@
         <v>0.4022390588311559</v>
       </c>
       <c r="C393" t="n">
-        <v>0.2677654629129281</v>
+        <v>0.2677654629129282</v>
       </c>
       <c r="D393" t="n">
-        <v>0.2900653779506683</v>
+        <v>0.1884398013353348</v>
       </c>
       <c r="E393" t="n">
-        <v>0.3200232998982508</v>
+        <v>0.2861481076931396</v>
       </c>
       <c r="F393" t="n">
         <v>0</v>
@@ -8514,10 +8526,10 @@
         <v>0.6363583389339815</v>
       </c>
       <c r="D394" t="n">
-        <v>0.8462345004081726</v>
+        <v>0.9866858720779419</v>
       </c>
       <c r="E394" t="n">
-        <v>0.7247352274266028</v>
+        <v>0.7715523513165259</v>
       </c>
       <c r="F394" t="n">
         <v>1</v>
@@ -8534,10 +8546,10 @@
         <v>0.6864692785718601</v>
       </c>
       <c r="D395" t="n">
-        <v>0.8586807250976562</v>
+        <v>0.9892808198928833</v>
       </c>
       <c r="E395" t="n">
-        <v>0.7723612986629917</v>
+        <v>0.8158946635947341</v>
       </c>
       <c r="F395" t="n">
         <v>1</v>
@@ -8554,10 +8566,10 @@
         <v>0.5562953687400907</v>
       </c>
       <c r="D396" t="n">
-        <v>0.6620104908943176</v>
+        <v>0.8161889314651489</v>
       </c>
       <c r="E396" t="n">
-        <v>0.6238171568343006</v>
+        <v>0.6752099703579111</v>
       </c>
       <c r="F396" t="n">
         <v>1</v>
@@ -8574,10 +8586,10 @@
         <v>0.7135040611718858</v>
       </c>
       <c r="D397" t="n">
-        <v>0.8612961769104004</v>
+        <v>0.993527889251709</v>
       </c>
       <c r="E397" t="n">
-        <v>0.7875927593075284</v>
+        <v>0.8316699967546312</v>
       </c>
       <c r="F397" t="n">
         <v>1</v>
@@ -8594,10 +8606,10 @@
         <v>0.72208061785221</v>
       </c>
       <c r="D398" t="n">
-        <v>0.8508273363113403</v>
+        <v>0.9886825680732727</v>
       </c>
       <c r="E398" t="n">
-        <v>0.8004671328424623</v>
+        <v>0.8464188767631065</v>
       </c>
       <c r="F398" t="n">
         <v>1</v>
@@ -8614,10 +8626,10 @@
         <v>0.8470791486319997</v>
       </c>
       <c r="D399" t="n">
-        <v>0.8661917448043823</v>
+        <v>0.9984939694404602</v>
       </c>
       <c r="E399" t="n">
-        <v>0.8543343447441091</v>
+        <v>0.8984350862894684</v>
       </c>
       <c r="F399" t="n">
         <v>1</v>
@@ -8634,10 +8646,10 @@
         <v>0.8009019741469826</v>
       </c>
       <c r="D400" t="n">
-        <v>0.8621533513069153</v>
+        <v>0.9904884099960327</v>
       </c>
       <c r="E400" t="n">
-        <v>0.8186332553694312</v>
+        <v>0.8614116082658038</v>
       </c>
       <c r="F400" t="n">
         <v>1</v>
@@ -8654,10 +8666,10 @@
         <v>0.502995945556844</v>
       </c>
       <c r="D401" t="n">
-        <v>0.5424315333366394</v>
+        <v>0.8791829943656921</v>
       </c>
       <c r="E401" t="n">
-        <v>0.5418546765113682</v>
+        <v>0.6541051635210525</v>
       </c>
       <c r="F401" t="n">
         <v>1</v>
@@ -8671,13 +8683,13 @@
         <v>0.7418033458940942</v>
       </c>
       <c r="C402" t="n">
-        <v>0.7574872279660375</v>
+        <v>0.7574872279660374</v>
       </c>
       <c r="D402" t="n">
-        <v>0.8546494245529175</v>
+        <v>0.9931848645210266</v>
       </c>
       <c r="E402" t="n">
-        <v>0.7846466661376831</v>
+        <v>0.8308251461270527</v>
       </c>
       <c r="F402" t="n">
         <v>1</v>
@@ -8694,10 +8706,10 @@
         <v>0.7936473596863918</v>
       </c>
       <c r="D403" t="n">
-        <v>0.8575764894485474</v>
+        <v>0.9943626523017883</v>
       </c>
       <c r="E403" t="n">
-        <v>0.8125693456764745</v>
+        <v>0.8581647332942216</v>
       </c>
       <c r="F403" t="n">
         <v>1</v>
@@ -8714,10 +8726,10 @@
         <v>0.7771040206235172</v>
       </c>
       <c r="D404" t="n">
-        <v>0.8604474067687988</v>
+        <v>0.9960794448852539</v>
       </c>
       <c r="E404" t="n">
-        <v>0.8051602547563877</v>
+        <v>0.8503709341285394</v>
       </c>
       <c r="F404" t="n">
         <v>1</v>
@@ -8734,10 +8746,10 @@
         <v>0.7833007033817825</v>
       </c>
       <c r="D405" t="n">
-        <v>0.8613079786300659</v>
+        <v>0.9961131811141968</v>
       </c>
       <c r="E405" t="n">
-        <v>0.8099308234408138</v>
+        <v>0.8548658909355241</v>
       </c>
       <c r="F405" t="n">
         <v>1</v>
@@ -8751,13 +8763,13 @@
         <v>0.7263824412054082</v>
       </c>
       <c r="C406" t="n">
-        <v>0.7479820533627246</v>
+        <v>0.7479820533627247</v>
       </c>
       <c r="D406" t="n">
-        <v>0.8532625436782837</v>
+        <v>0.9953027963638306</v>
       </c>
       <c r="E406" t="n">
-        <v>0.7758756794154721</v>
+        <v>0.8232224303106545</v>
       </c>
       <c r="F406" t="n">
         <v>1</v>
@@ -8774,10 +8786,10 @@
         <v>0.8208268376309636</v>
       </c>
       <c r="D407" t="n">
-        <v>0.8594182729721069</v>
+        <v>0.9965326189994812</v>
       </c>
       <c r="E407" t="n">
-        <v>0.824429391516836</v>
+        <v>0.8701341735259608</v>
       </c>
       <c r="F407" t="n">
         <v>1</v>
@@ -8794,10 +8806,10 @@
         <v>0.8244830903733057</v>
       </c>
       <c r="D408" t="n">
-        <v>0.8583051562309265</v>
+        <v>0.9946688413619995</v>
       </c>
       <c r="E408" t="n">
-        <v>0.8270713927956937</v>
+        <v>0.8725259545060514</v>
       </c>
       <c r="F408" t="n">
         <v>1</v>
@@ -8811,13 +8823,13 @@
         <v>0.7133755643709148</v>
       </c>
       <c r="C409" t="n">
-        <v>0.6039945885371905</v>
+        <v>0.6039945885371902</v>
       </c>
       <c r="D409" t="n">
-        <v>0.8549318313598633</v>
+        <v>0.9885141253471375</v>
       </c>
       <c r="E409" t="n">
-        <v>0.7241006614226562</v>
+        <v>0.7686280927517476</v>
       </c>
       <c r="F409" t="n">
         <v>1</v>
@@ -8834,10 +8846,10 @@
         <v>0.3786423026145093</v>
       </c>
       <c r="D410" t="n">
-        <v>0.4178156852722168</v>
+        <v>0.6667500138282776</v>
       </c>
       <c r="E410" t="n">
-        <v>0.3854718648047762</v>
+        <v>0.4684499743234631</v>
       </c>
       <c r="F410" t="n">
         <v>0</v>
@@ -8854,10 +8866,10 @@
         <v>0.6006316212384999</v>
       </c>
       <c r="D411" t="n">
-        <v>0.8462163805961609</v>
+        <v>0.9604487419128418</v>
       </c>
       <c r="E411" t="n">
-        <v>0.6899894031225339</v>
+        <v>0.7280668568947609</v>
       </c>
       <c r="F411" t="n">
         <v>1</v>
@@ -8874,10 +8886,10 @@
         <v>0.7126136619189759</v>
       </c>
       <c r="D412" t="n">
-        <v>0.8639394044876099</v>
+        <v>0.9966498613357544</v>
       </c>
       <c r="E412" t="n">
-        <v>0.7903521187878928</v>
+        <v>0.8345889377372743</v>
       </c>
       <c r="F412" t="n">
         <v>1</v>
@@ -8894,10 +8906,10 @@
         <v>0.8798552417242412</v>
       </c>
       <c r="D413" t="n">
-        <v>0.8645535707473755</v>
+        <v>0.9973646402359009</v>
       </c>
       <c r="E413" t="n">
-        <v>0.8692240808983214</v>
+        <v>0.9134944373944965</v>
       </c>
       <c r="F413" t="n">
         <v>1</v>
@@ -8914,10 +8926,10 @@
         <v>0.7650165969208393</v>
       </c>
       <c r="D414" t="n">
-        <v>0.8640632629394531</v>
+        <v>0.9963279962539673</v>
       </c>
       <c r="E414" t="n">
-        <v>0.8187941843199803</v>
+        <v>0.8628824287581517</v>
       </c>
       <c r="F414" t="n">
         <v>1</v>
@@ -8934,10 +8946,10 @@
         <v>0.859869174747425</v>
       </c>
       <c r="D415" t="n">
-        <v>0.8664324879646301</v>
+        <v>0.9987711906433105</v>
       </c>
       <c r="E415" t="n">
-        <v>0.8568247963769829</v>
+        <v>0.9009376972698764</v>
       </c>
       <c r="F415" t="n">
         <v>1</v>
@@ -8951,13 +8963,13 @@
         <v>0.7838062234861441</v>
       </c>
       <c r="C416" t="n">
-        <v>0.7880362334235065</v>
+        <v>0.7880362334235064</v>
       </c>
       <c r="D416" t="n">
-        <v>0.8665767908096313</v>
+        <v>0.9971254467964172</v>
       </c>
       <c r="E416" t="n">
-        <v>0.8128064159064273</v>
+        <v>0.8563226345686893</v>
       </c>
       <c r="F416" t="n">
         <v>1</v>
@@ -8974,10 +8986,10 @@
         <v>0.6868049413319295</v>
       </c>
       <c r="D417" t="n">
-        <v>0.8656506538391113</v>
+        <v>0.9964599609375</v>
       </c>
       <c r="E417" t="n">
-        <v>0.7777122657617701</v>
+        <v>0.8213153681278996</v>
       </c>
       <c r="F417" t="n">
         <v>1</v>
@@ -8994,10 +9006,10 @@
         <v>0.8686777703504157</v>
       </c>
       <c r="D418" t="n">
-        <v>0.8531869053840637</v>
+        <v>0.989209771156311</v>
       </c>
       <c r="E418" t="n">
-        <v>0.8615130717544016</v>
+        <v>0.9068540270118174</v>
       </c>
       <c r="F418" t="n">
         <v>1</v>
@@ -9011,13 +9023,13 @@
         <v>0.7145033430729841</v>
       </c>
       <c r="C419" t="n">
-        <v>0.6308293235235161</v>
+        <v>0.6308293235235162</v>
       </c>
       <c r="D419" t="n">
-        <v>0.7270396947860718</v>
+        <v>0.8841019868850708</v>
       </c>
       <c r="E419" t="n">
-        <v>0.690790787127524</v>
+        <v>0.743144884493857</v>
       </c>
       <c r="F419" t="n">
         <v>1</v>
@@ -9031,13 +9043,13 @@
         <v>0.7791690767823022</v>
       </c>
       <c r="C420" t="n">
-        <v>0.6517866745386142</v>
+        <v>0.6517866745386143</v>
       </c>
       <c r="D420" t="n">
-        <v>0.8553786277770996</v>
+        <v>0.9874672889709473</v>
       </c>
       <c r="E420" t="n">
-        <v>0.7621114596993387</v>
+        <v>0.8061410134306213</v>
       </c>
       <c r="F420" t="n">
         <v>1</v>
@@ -9054,10 +9066,10 @@
         <v>0.5415980555611344</v>
       </c>
       <c r="D421" t="n">
-        <v>0.8199061155319214</v>
+        <v>0.9561630487442017</v>
       </c>
       <c r="E421" t="n">
-        <v>0.6917003207776767</v>
+        <v>0.7371192985151035</v>
       </c>
       <c r="F421" t="n">
         <v>1</v>
@@ -9071,13 +9083,13 @@
         <v>0.6859772041078788</v>
       </c>
       <c r="C422" t="n">
-        <v>0.6622002142521078</v>
+        <v>0.662200214252108</v>
       </c>
       <c r="D422" t="n">
-        <v>0.8204558491706848</v>
+        <v>0.9454229474067688</v>
       </c>
       <c r="E422" t="n">
-        <v>0.7228777558435571</v>
+        <v>0.7645334552555852</v>
       </c>
       <c r="F422" t="n">
         <v>1</v>
@@ -9094,10 +9106,10 @@
         <v>0.6757789996253505</v>
       </c>
       <c r="D423" t="n">
-        <v>0.8353549242019653</v>
+        <v>0.975914478302002</v>
       </c>
       <c r="E423" t="n">
-        <v>0.7413738234789787</v>
+        <v>0.7882270081789909</v>
       </c>
       <c r="F423" t="n">
         <v>1</v>
@@ -9114,10 +9126,10 @@
         <v>0.8291009180445436</v>
       </c>
       <c r="D424" t="n">
-        <v>0.8619383573532104</v>
+        <v>0.9925235509872437</v>
       </c>
       <c r="E424" t="n">
-        <v>0.8379085155672752</v>
+        <v>0.8814369134452863</v>
       </c>
       <c r="F424" t="n">
         <v>1</v>
@@ -9134,10 +9146,10 @@
         <v>0.8312840534722012</v>
       </c>
       <c r="D425" t="n">
-        <v>0.8623650670051575</v>
+        <v>0.9956901669502258</v>
       </c>
       <c r="E425" t="n">
-        <v>0.8472869257522665</v>
+        <v>0.8917286257339559</v>
       </c>
       <c r="F425" t="n">
         <v>1</v>
@@ -9151,13 +9163,13 @@
         <v>0.8413484292096403</v>
       </c>
       <c r="C426" t="n">
-        <v>0.8115896037647703</v>
+        <v>0.8115896037647705</v>
       </c>
       <c r="D426" t="n">
-        <v>0.8563973307609558</v>
+        <v>0.9857944250106812</v>
       </c>
       <c r="E426" t="n">
-        <v>0.8364451212451222</v>
+        <v>0.8795774859950306</v>
       </c>
       <c r="F426" t="n">
         <v>1</v>
@@ -9174,10 +9186,10 @@
         <v>0.7982182249223835</v>
       </c>
       <c r="D427" t="n">
-        <v>0.8600137829780579</v>
+        <v>0.9892711639404297</v>
       </c>
       <c r="E427" t="n">
-        <v>0.8258895763903911</v>
+        <v>0.868975370044515</v>
       </c>
       <c r="F427" t="n">
         <v>1</v>
@@ -9194,10 +9206,10 @@
         <v>0.8268900933199909</v>
       </c>
       <c r="D428" t="n">
-        <v>0.8546501398086548</v>
+        <v>0.9859081506729126</v>
       </c>
       <c r="E428" t="n">
-        <v>0.8320912868696183</v>
+        <v>0.8758439571577042</v>
       </c>
       <c r="F428" t="n">
         <v>1</v>
@@ -9211,13 +9223,13 @@
         <v>0.7409991849871445</v>
       </c>
       <c r="C429" t="n">
-        <v>0.7199336933378516</v>
+        <v>0.7199336933378518</v>
       </c>
       <c r="D429" t="n">
-        <v>0.8506466150283813</v>
+        <v>0.9691435694694519</v>
       </c>
       <c r="E429" t="n">
-        <v>0.7705264977844591</v>
+        <v>0.8100254825981494</v>
       </c>
       <c r="F429" t="n">
         <v>1</v>
@@ -9231,13 +9243,13 @@
         <v>0.842248310113605</v>
       </c>
       <c r="C430" t="n">
-        <v>0.8197207957888043</v>
+        <v>0.8197207957888045</v>
       </c>
       <c r="D430" t="n">
-        <v>0.859566330909729</v>
+        <v>0.991702675819397</v>
       </c>
       <c r="E430" t="n">
-        <v>0.8405118122707128</v>
+        <v>0.8845572605739355</v>
       </c>
       <c r="F430" t="n">
         <v>1</v>
@@ -9254,10 +9266,10 @@
         <v>0.7198258502273462</v>
       </c>
       <c r="D431" t="n">
-        <v>0.8440331220626831</v>
+        <v>0.9858384132385254</v>
       </c>
       <c r="E431" t="n">
-        <v>0.7666842920168468</v>
+        <v>0.8139527224087942</v>
       </c>
       <c r="F431" t="n">
         <v>1</v>
@@ -9274,10 +9286,10 @@
         <v>0.8184575387066209</v>
       </c>
       <c r="D432" t="n">
-        <v>0.8537769317626953</v>
+        <v>0.9793519973754883</v>
       </c>
       <c r="E432" t="n">
-        <v>0.8259666200347247</v>
+        <v>0.8678249752389889</v>
       </c>
       <c r="F432" t="n">
         <v>1</v>
@@ -9294,10 +9306,10 @@
         <v>0.8584211747340416</v>
       </c>
       <c r="D433" t="n">
-        <v>0.860348105430603</v>
+        <v>0.9912605285644531</v>
       </c>
       <c r="E433" t="n">
-        <v>0.8515975029252233</v>
+        <v>0.8952349773031734</v>
       </c>
       <c r="F433" t="n">
         <v>1</v>
@@ -9314,10 +9326,10 @@
         <v>0.762717708944239</v>
       </c>
       <c r="D434" t="n">
-        <v>0.8499051332473755</v>
+        <v>0.9889510869979858</v>
       </c>
       <c r="E434" t="n">
-        <v>0.7959454640656997</v>
+        <v>0.842294115315903</v>
       </c>
       <c r="F434" t="n">
         <v>1</v>
@@ -9334,10 +9346,10 @@
         <v>0.8224363253052356</v>
       </c>
       <c r="D435" t="n">
-        <v>0.858842670917511</v>
+        <v>0.9943609237670898</v>
       </c>
       <c r="E435" t="n">
-        <v>0.8330545284482245</v>
+        <v>0.8782272793980841</v>
       </c>
       <c r="F435" t="n">
         <v>1</v>
@@ -9354,10 +9366,10 @@
         <v>0.7247207094063886</v>
       </c>
       <c r="D436" t="n">
-        <v>0.8497333526611328</v>
+        <v>0.986178994178772</v>
       </c>
       <c r="E436" t="n">
-        <v>0.7933411158268706</v>
+        <v>0.8388229963327504</v>
       </c>
       <c r="F436" t="n">
         <v>1</v>
@@ -9374,10 +9386,10 @@
         <v>0.8216754545103029</v>
       </c>
       <c r="D437" t="n">
-        <v>0.861672043800354</v>
+        <v>0.9924775958061218</v>
       </c>
       <c r="E437" t="n">
-        <v>0.8414057343433451</v>
+        <v>0.8850075850119343</v>
       </c>
       <c r="F437" t="n">
         <v>1</v>
@@ -9391,13 +9403,13 @@
         <v>0.8211970199838354</v>
       </c>
       <c r="C438" t="n">
-        <v>0.800931950076599</v>
+        <v>0.8009319500765992</v>
       </c>
       <c r="D438" t="n">
-        <v>0.8575212359428406</v>
+        <v>0.9827893972396851</v>
       </c>
       <c r="E438" t="n">
-        <v>0.8265500686677584</v>
+        <v>0.8683061224333732</v>
       </c>
       <c r="F438" t="n">
         <v>1</v>
@@ -9411,13 +9423,13 @@
         <v>0.8134696906291824</v>
       </c>
       <c r="C439" t="n">
-        <v>0.7926208262448644</v>
+        <v>0.7926208262448645</v>
       </c>
       <c r="D439" t="n">
-        <v>0.8498517274856567</v>
+        <v>0.9851514101028442</v>
       </c>
       <c r="E439" t="n">
-        <v>0.8186474147865678</v>
+        <v>0.863747308992297</v>
       </c>
       <c r="F439" t="n">
         <v>1</v>
@@ -9434,10 +9446,10 @@
         <v>0.7815909786712013</v>
       </c>
       <c r="D440" t="n">
-        <v>0.8599184155464172</v>
+        <v>0.992489218711853</v>
       </c>
       <c r="E440" t="n">
-        <v>0.8100274336423174</v>
+        <v>0.8542177013641293</v>
       </c>
       <c r="F440" t="n">
         <v>1</v>
@@ -9454,10 +9466,10 @@
         <v>0.4836415638953584</v>
       </c>
       <c r="D441" t="n">
-        <v>0.7140305638313293</v>
+        <v>0.8982813954353333</v>
       </c>
       <c r="E441" t="n">
-        <v>0.6432485597262766</v>
+        <v>0.7046655035942778</v>
       </c>
       <c r="F441" t="n">
         <v>1</v>
@@ -9471,13 +9483,13 @@
         <v>0.3562836353687553</v>
       </c>
       <c r="C442" t="n">
-        <v>0.4470473771108645</v>
+        <v>0.4470473771108646</v>
       </c>
       <c r="D442" t="n">
-        <v>0.4591713547706604</v>
+        <v>0.7716215848922729</v>
       </c>
       <c r="E442" t="n">
-        <v>0.42083412241676</v>
+        <v>0.5249841991239643</v>
       </c>
       <c r="F442" t="n">
         <v>0</v>
@@ -9491,13 +9503,13 @@
         <v>0.6239040182987818</v>
       </c>
       <c r="C443" t="n">
-        <v>0.6026311141473918</v>
+        <v>0.6026311141473919</v>
       </c>
       <c r="D443" t="n">
-        <v>0.8239958882331848</v>
+        <v>0.9312773942947388</v>
       </c>
       <c r="E443" t="n">
-        <v>0.6835103402264529</v>
+        <v>0.7192708422469708</v>
       </c>
       <c r="F443" t="n">
         <v>1</v>
@@ -9514,10 +9526,10 @@
         <v>0.9004654559839228</v>
       </c>
       <c r="D444" t="n">
-        <v>0.8644468188285828</v>
+        <v>0.9971410632133484</v>
       </c>
       <c r="E444" t="n">
-        <v>0.8796054869924078</v>
+        <v>0.9238369017873297</v>
       </c>
       <c r="F444" t="n">
         <v>1</v>
@@ -9531,13 +9543,13 @@
         <v>0.858736342979902</v>
       </c>
       <c r="C445" t="n">
-        <v>0.8335159636057974</v>
+        <v>0.8335159636057975</v>
       </c>
       <c r="D445" t="n">
-        <v>0.8573156595230103</v>
+        <v>0.9922496676445007</v>
       </c>
       <c r="E445" t="n">
-        <v>0.8498559887029032</v>
+        <v>0.8948339914100667</v>
       </c>
       <c r="F445" t="n">
         <v>1</v>
@@ -9554,10 +9566,10 @@
         <v>0.8287411572927386</v>
       </c>
       <c r="D446" t="n">
-        <v>0.8529621362686157</v>
+        <v>0.9875429272651672</v>
       </c>
       <c r="E446" t="n">
-        <v>0.8452428047207912</v>
+        <v>0.8901030683863084</v>
       </c>
       <c r="F446" t="n">
         <v>1</v>
@@ -9574,10 +9586,10 @@
         <v>0.7806574793310066</v>
       </c>
       <c r="D447" t="n">
-        <v>0.8533104658126831</v>
+        <v>0.9873068928718567</v>
       </c>
       <c r="E447" t="n">
-        <v>0.8203526327374903</v>
+        <v>0.8650181084238815</v>
       </c>
       <c r="F447" t="n">
         <v>1</v>
@@ -9594,10 +9606,10 @@
         <v>0.6685473547061577</v>
       </c>
       <c r="D448" t="n">
-        <v>0.8388373255729675</v>
+        <v>0.9827615022659302</v>
       </c>
       <c r="E448" t="n">
-        <v>0.772618351972322</v>
+        <v>0.8205930775366429</v>
       </c>
       <c r="F448" t="n">
         <v>1</v>
@@ -9614,10 +9626,10 @@
         <v>0.8291550998153276</v>
       </c>
       <c r="D449" t="n">
-        <v>0.8491109013557434</v>
+        <v>0.987705409526825</v>
       </c>
       <c r="E449" t="n">
-        <v>0.8456648668625322</v>
+        <v>0.8918630362528926</v>
       </c>
       <c r="F449" t="n">
         <v>1</v>
@@ -9634,10 +9646,10 @@
         <v>0.7715708617829298</v>
       </c>
       <c r="D450" t="n">
-        <v>0.8490026593208313</v>
+        <v>0.9866011738777161</v>
       </c>
       <c r="E450" t="n">
-        <v>0.8197930349298086</v>
+        <v>0.8656592064487701</v>
       </c>
       <c r="F450" t="n">
         <v>1</v>
@@ -9654,10 +9666,10 @@
         <v>0.6244529473438611</v>
       </c>
       <c r="D451" t="n">
-        <v>0.8313407897949219</v>
+        <v>0.9810260534286499</v>
       </c>
       <c r="E451" t="n">
-        <v>0.7341387604333923</v>
+        <v>0.7840338483113016</v>
       </c>
       <c r="F451" t="n">
         <v>1</v>
@@ -9674,10 +9686,10 @@
         <v>0.5581548593975223</v>
       </c>
       <c r="D452" t="n">
-        <v>0.8435249328613281</v>
+        <v>0.9914830923080444</v>
       </c>
       <c r="E452" t="n">
-        <v>0.7029892324732315</v>
+        <v>0.7523086189554703</v>
       </c>
       <c r="F452" t="n">
         <v>1</v>
@@ -9694,10 +9706,10 @@
         <v>0.7900343587070606</v>
       </c>
       <c r="D453" t="n">
-        <v>0.8466750979423523</v>
+        <v>0.9853440523147583</v>
       </c>
       <c r="E453" t="n">
-        <v>0.8285110027998392</v>
+        <v>0.8747339875906412</v>
       </c>
       <c r="F453" t="n">
         <v>1</v>
@@ -9714,10 +9726,10 @@
         <v>0.8727687094200464</v>
       </c>
       <c r="D454" t="n">
-        <v>0.854863166809082</v>
+        <v>0.9910991787910461</v>
       </c>
       <c r="E454" t="n">
-        <v>0.8670951125721325</v>
+        <v>0.9125071165661205</v>
       </c>
       <c r="F454" t="n">
         <v>1</v>
@@ -9734,10 +9746,10 @@
         <v>0.8595648567249625</v>
       </c>
       <c r="D455" t="n">
-        <v>0.8641499280929565</v>
+        <v>0.9974894523620605</v>
       </c>
       <c r="E455" t="n">
-        <v>0.854903978517464</v>
+        <v>0.8993504866071653</v>
       </c>
       <c r="F455" t="n">
         <v>1</v>
@@ -9754,10 +9766,10 @@
         <v>0.8748318617716411</v>
       </c>
       <c r="D456" t="n">
-        <v>0.8608554005622864</v>
+        <v>0.9948153495788574</v>
       </c>
       <c r="E456" t="n">
-        <v>0.8641801989436616</v>
+        <v>0.9088335152825185</v>
       </c>
       <c r="F456" t="n">
         <v>1</v>
@@ -9774,10 +9786,10 @@
         <v>0.7429713629347702</v>
       </c>
       <c r="D457" t="n">
-        <v>0.8522483706474304</v>
+        <v>0.992911159992218</v>
       </c>
       <c r="E457" t="n">
-        <v>0.793117090726423</v>
+        <v>0.8400046871746856</v>
       </c>
       <c r="F457" t="n">
         <v>1</v>
@@ -9791,13 +9803,13 @@
         <v>0.810431171330606</v>
       </c>
       <c r="C458" t="n">
-        <v>0.7576538612573918</v>
+        <v>0.7576538612573916</v>
       </c>
       <c r="D458" t="n">
-        <v>0.8464530110359192</v>
+        <v>0.9853591918945312</v>
       </c>
       <c r="E458" t="n">
-        <v>0.8048460145413058</v>
+        <v>0.8511480748275096</v>
       </c>
       <c r="F458" t="n">
         <v>1</v>
@@ -9811,13 +9823,13 @@
         <v>0.8471574113220812</v>
       </c>
       <c r="C459" t="n">
-        <v>0.8614416402453047</v>
+        <v>0.8614416402453049</v>
       </c>
       <c r="D459" t="n">
-        <v>0.8626841306686401</v>
+        <v>0.997148871421814</v>
       </c>
       <c r="E459" t="n">
-        <v>0.8570943940786754</v>
+        <v>0.9019159743297335</v>
       </c>
       <c r="F459" t="n">
         <v>1</v>
@@ -9834,10 +9846,10 @@
         <v>0.7661670651755109</v>
       </c>
       <c r="D460" t="n">
-        <v>0.8623013496398926</v>
+        <v>0.9968263506889343</v>
       </c>
       <c r="E460" t="n">
-        <v>0.8062887870962573</v>
+        <v>0.8511304541126045</v>
       </c>
       <c r="F460" t="n">
         <v>1</v>
@@ -9854,10 +9866,10 @@
         <v>0.8099725594903948</v>
       </c>
       <c r="D461" t="n">
-        <v>0.8610869646072388</v>
+        <v>0.9973225593566895</v>
       </c>
       <c r="E461" t="n">
-        <v>0.8357146472783227</v>
+        <v>0.8811265121948062</v>
       </c>
       <c r="F461" t="n">
         <v>1</v>
@@ -9874,10 +9886,10 @@
         <v>0.7954073643862394</v>
       </c>
       <c r="D462" t="n">
-        <v>0.8601789474487305</v>
+        <v>0.9953752756118774</v>
       </c>
       <c r="E462" t="n">
-        <v>0.8155050844465275</v>
+        <v>0.8605705271675764</v>
       </c>
       <c r="F462" t="n">
         <v>1</v>
@@ -9894,10 +9906,10 @@
         <v>0.8184966413426482</v>
       </c>
       <c r="D463" t="n">
-        <v>0.8596627116203308</v>
+        <v>0.9910047650337219</v>
       </c>
       <c r="E463" t="n">
-        <v>0.8289190787540193</v>
+        <v>0.8726997632251496</v>
       </c>
       <c r="F463" t="n">
         <v>1</v>
@@ -9914,10 +9926,10 @@
         <v>0.7328605791333827</v>
       </c>
       <c r="D464" t="n">
-        <v>0.8553325533866882</v>
+        <v>0.9912261962890625</v>
       </c>
       <c r="E464" t="n">
-        <v>0.7846910994269954</v>
+        <v>0.8299889803944535</v>
       </c>
       <c r="F464" t="n">
         <v>1</v>
@@ -9934,10 +9946,10 @@
         <v>0.8355287317066251</v>
       </c>
       <c r="D465" t="n">
-        <v>0.8619686365127563</v>
+        <v>0.9947642087936401</v>
       </c>
       <c r="E465" t="n">
-        <v>0.841440783567609</v>
+        <v>0.8857059743279035</v>
       </c>
       <c r="F465" t="n">
         <v>1</v>
@@ -9951,13 +9963,13 @@
         <v>0.8580287715428445</v>
       </c>
       <c r="C466" t="n">
-        <v>0.858713517873759</v>
+        <v>0.8587135178737588</v>
       </c>
       <c r="D466" t="n">
-        <v>0.8562424778938293</v>
+        <v>0.9938785433769226</v>
       </c>
       <c r="E466" t="n">
-        <v>0.8576615891034777</v>
+        <v>0.9035402775978421</v>
       </c>
       <c r="F466" t="n">
         <v>1</v>
@@ -9974,13 +9986,374 @@
         <v>0.6697785509851986</v>
       </c>
       <c r="D467" t="n">
-        <v>0.8462797999382019</v>
+        <v>0.9852485656738281</v>
       </c>
       <c r="E467" t="n">
-        <v>0.7705903268108559</v>
+        <v>0.8169132487227313</v>
       </c>
       <c r="F467" t="n">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Epoch</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Mean_Train_Loss</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mean_CV_Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.044206209664934</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.769503241509534</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7230172553758942</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6233094857649857</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6193679700406749</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5694773940557845</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.5495134353637696</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5094320876544781</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5109713946165664</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.4929476224304585</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.4695689865377513</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4684430891208435</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.4364123725321855</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.4702688049064593</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4276875427599703</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4375419649515259</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.418151169747449</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4303729264086552</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3649108654746179</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4318101511577542</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3654006751735558</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.4379754502284394</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3414933017716649</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4315076377284662</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3376353159379423</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4239523951257214</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3191742117401589</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4288563370537222</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.3043580925866459</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.4219484862316861</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3012673345509539</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4497973667436772</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.3013085873274321</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4332302805413021</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.2965478926311048</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.438092730152473</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.2661777645014645</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4213056752018714</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.2764481553535783</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4417044958204366</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.2677557633164224</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.4413387594681778</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.2555089941520369</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4421000341853399</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.248875933249345</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.4253686194590638</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.2431997255913997</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.4675014374882317</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.2442603400416588</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4522779984085747</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.2430411805681298</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.4498458131310645</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.2441429082680954</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.4394768445009595</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.2410513938143012</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.4327580008279072</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.2483993779574887</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.4338363771693091</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.2473465650436583</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.4392708816555109</v>
       </c>
     </row>
   </sheetData>

--- a/ensemble/eval_results/ensemble_eval_result.xlsx
+++ b/ensemble/eval_results/ensemble_eval_result.xlsx
@@ -564,34 +564,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.999</v>
+        <v>0.9878</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9408</v>
+        <v>0.9197</v>
       </c>
       <c r="D4" t="n">
-        <v>0.576</v>
+        <v>0.518</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9938</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.973</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6116</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.759</v>
+        <v>0.7956</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8991</v>
+        <v>0.9206</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7337</v>
+        <v>0.7679</v>
       </c>
       <c r="K4" t="n">
-        <v>0.381</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="5">
@@ -601,31 +601,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9902</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9383</v>
+        <v>0.9301</v>
       </c>
       <c r="D5" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>0.973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.766</v>
+        <v>0.8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8571</v>
+        <v>0.878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9485</v>
+        <v>0.9571</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8351</v>
+        <v>0.8583</v>
       </c>
       <c r="K5" t="inlineStr"/>
     </row>
@@ -686,10 +686,10 @@
         <v>0.3840620868297284</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7640960812568665</v>
+        <v>0.5480184555053711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5340186587576077</v>
+        <v>0.4619927835071092</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -706,10 +706,10 @@
         <v>0.5733754884752394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8802544474601746</v>
+        <v>0.6917568445205688</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328587358927393</v>
+        <v>0.6700262015795374</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -726,10 +726,10 @@
         <v>0.3362632856158089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8109527826309204</v>
+        <v>0.5705612301826477</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4927487596564029</v>
+        <v>0.4126182421736453</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0.197416943404845</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006774462759494781</v>
+        <v>0.1047137230634689</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1468815421182348</v>
+        <v>0.1795279622195595</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
         <v>0.1304129038381526</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002893198048695922</v>
+        <v>0.08963409811258316</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07958320084714854</v>
+        <v>0.1084968342017776</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -786,10 +786,10 @@
         <v>0.1749632749314859</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0005258172168396413</v>
+        <v>0.07000142335891724</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1003599808776636</v>
+        <v>0.1235185162583561</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -806,10 +806,10 @@
         <v>0.1620237434290886</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01377213560044765</v>
+        <v>0.11043381690979</v>
       </c>
       <c r="E8" t="n">
-        <v>0.118635819888254</v>
+        <v>0.1508563803247014</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -826,10 +826,10 @@
         <v>0.2067114025008345</v>
       </c>
       <c r="D9" t="n">
-        <v>0.180578425526619</v>
+        <v>0.2394518405199051</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2133723871744476</v>
+        <v>0.2329968588388763</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0.2094139514215262</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01162613462656736</v>
+        <v>0.1101484075188637</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1615994222360308</v>
+        <v>0.1944401798667963</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>0.3121416345283932</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1023872345685959</v>
+        <v>0.1224281787872314</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3315163767442385</v>
+        <v>0.3381966914837837</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -883,13 +883,13 @@
         <v>0.467609268054578</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3448281831682601</v>
+        <v>0.34482818316826</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3318856656551361</v>
+        <v>0.4854837357997894</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3814410389593247</v>
+        <v>0.4326403956742091</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -906,10 +906,10 @@
         <v>0.1363991400315087</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00314352591522038</v>
+        <v>0.05890752002596855</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09984158050578806</v>
+        <v>0.1184295785427041</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -926,10 +926,10 @@
         <v>0.1328238651082339</v>
       </c>
       <c r="D14" t="n">
-        <v>0.007772163953632116</v>
+        <v>0.07341472804546356</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08480291644856892</v>
+        <v>0.1066837711458461</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         <v>0.1570568250298337</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002460514428094029</v>
+        <v>0.07258182764053345</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1084199503444532</v>
+        <v>0.1317937214152663</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0.1738206865066103</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06969129294157028</v>
+        <v>0.1423815935850143</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1570215426394435</v>
+        <v>0.1812516428539249</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -983,13 +983,13 @@
         <v>0.5319802357920328</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4454146041673416</v>
+        <v>0.4454146041673417</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9036062955856323</v>
+        <v>0.6899503469467163</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6270003785150022</v>
+        <v>0.5557817289686969</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1006,10 +1006,10 @@
         <v>0.1063094770430837</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001144084730185568</v>
+        <v>0.05721303075551987</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06502406064996819</v>
+        <v>0.08371370932507961</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1026,10 +1026,10 @@
         <v>0.3300317782652732</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1115614771842957</v>
+        <v>0.2882517576217651</v>
       </c>
       <c r="E19" t="n">
-        <v>0.297236796597923</v>
+        <v>0.3561335567437461</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1046,10 +1046,10 @@
         <v>0.2254710742981195</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1004083156585693</v>
+        <v>0.185122013092041</v>
       </c>
       <c r="E20" t="n">
-        <v>0.19477182348872</v>
+        <v>0.2230097226332106</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1066,10 +1066,10 @@
         <v>0.371430941548388</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5323368310928345</v>
+        <v>0.4960145354270935</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4194481960077829</v>
+        <v>0.4073407641192026</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1086,10 +1086,10 @@
         <v>0.2076885775679576</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01321571506559849</v>
+        <v>0.07516895234584808</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1728727725624288</v>
+        <v>0.1935238516558454</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1106,10 +1106,10 @@
         <v>0.2466677054434032</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01177948899567127</v>
+        <v>0.06603121012449265</v>
       </c>
       <c r="E23" t="n">
-        <v>0.169118628855549</v>
+        <v>0.1872025358984895</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1126,10 +1126,10 @@
         <v>0.2037462076810409</v>
       </c>
       <c r="D24" t="n">
-        <v>0.003638957161456347</v>
+        <v>0.05292298644781113</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1519638535092651</v>
+        <v>0.1683918632713834</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1146,10 +1146,10 @@
         <v>0.1141275809874744</v>
       </c>
       <c r="D25" t="n">
-        <v>0.007823584601283073</v>
+        <v>0.08993680775165558</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0895860725727734</v>
+        <v>0.1169571469562309</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1166,10 +1166,10 @@
         <v>0.2108669414302069</v>
       </c>
       <c r="D26" t="n">
-        <v>0.04197414964437485</v>
+        <v>0.1171558499336243</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1677172944788923</v>
+        <v>0.1927778612419754</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1183,13 +1183,13 @@
         <v>0.1350564249621374</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1522052698006219</v>
+        <v>0.1522052698006218</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01285972911864519</v>
+        <v>0.07286187261343002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1000404746271348</v>
+        <v>0.1200411891253964</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
         <v>0.434211807854486</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7813240885734558</v>
+        <v>0.6228697299957275</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5935685678042334</v>
+        <v>0.540750448278324</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -1226,10 +1226,10 @@
         <v>0.4888966980041124</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9840186238288879</v>
+        <v>0.7568185329437256</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7230824094583382</v>
+        <v>0.6473490458299508</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -1246,10 +1246,10 @@
         <v>0.2780810266264825</v>
       </c>
       <c r="D30" t="n">
-        <v>0.420736700296402</v>
+        <v>0.3142246901988983</v>
       </c>
       <c r="E30" t="n">
-        <v>0.422267573758011</v>
+        <v>0.3867635703921765</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>0.2871319729310349</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3247651159763336</v>
+        <v>0.2812934815883636</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3215240768539973</v>
+        <v>0.3070335320580073</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1286,10 +1286,10 @@
         <v>0.257434799193592</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8382196426391602</v>
+        <v>0.3990477323532104</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4844387625092161</v>
+        <v>0.3380481257472328</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1306,13 +1306,13 @@
         <v>0.3253541959000909</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9380861520767212</v>
+        <v>0.3507744669914246</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5706654482145759</v>
+        <v>0.374894886519477</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1326,10 +1326,10 @@
         <v>0.2684088577622227</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6514846682548523</v>
+        <v>0.4365488886833191</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4558502163260386</v>
+        <v>0.3842049564688608</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1346,10 +1346,10 @@
         <v>0.4028275028754815</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9141210317611694</v>
+        <v>0.6872636675834656</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6300928746151108</v>
+        <v>0.5544737532225428</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -1366,10 +1366,10 @@
         <v>0.1350934922589146</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01555389352142811</v>
+        <v>0.08586724847555161</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1058672072952358</v>
+        <v>0.1293049922799437</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1386,10 +1386,10 @@
         <v>0.4501275090499132</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8811548352241516</v>
+        <v>0.6913375854492188</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6461294859592723</v>
+        <v>0.582857069367628</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -1403,13 +1403,13 @@
         <v>0.3694870253573097</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3120200740474515</v>
+        <v>0.3120200740474516</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08257676661014557</v>
+        <v>0.1629454791545868</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2546946220049689</v>
+        <v>0.281484192853116</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
         <v>0.1525936185354979</v>
       </c>
       <c r="D39" t="n">
-        <v>0.004447101149708033</v>
+        <v>0.06588800251483917</v>
       </c>
       <c r="E39" t="n">
-        <v>0.09522986285395725</v>
+        <v>0.115710163309001</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1446,10 +1446,10 @@
         <v>0.3782246135494279</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07040233910083771</v>
+        <v>0.1633563488721848</v>
       </c>
       <c r="E40" t="n">
-        <v>0.328691001056273</v>
+        <v>0.3596756709800553</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1466,10 +1466,10 @@
         <v>0.2308411419120279</v>
       </c>
       <c r="D41" t="n">
-        <v>0.03389675170183182</v>
+        <v>0.177936315536499</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1873868661619447</v>
+        <v>0.2354000541068338</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1486,10 +1486,10 @@
         <v>0.1465028461098328</v>
       </c>
       <c r="D42" t="n">
-        <v>0.008187382481992245</v>
+        <v>0.1440559178590775</v>
       </c>
       <c r="E42" t="n">
-        <v>0.09982147837893864</v>
+        <v>0.1451109901713004</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1506,10 +1506,10 @@
         <v>0.1623377990685961</v>
       </c>
       <c r="D43" t="n">
-        <v>0.009114032611250877</v>
+        <v>0.05984698608517647</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1182003604718567</v>
+        <v>0.1351113449631652</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1526,10 +1526,10 @@
         <v>0.1315338020594521</v>
       </c>
       <c r="D44" t="n">
-        <v>0.006044634617865086</v>
+        <v>0.05486264824867249</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1223365457641972</v>
+        <v>0.1386092169744664</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1546,10 +1546,10 @@
         <v>0.2784166040675529</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3633109629154205</v>
+        <v>0.3526697158813477</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3332711356219146</v>
+        <v>0.3297240532772237</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1566,10 +1566,10 @@
         <v>0.2378057669481436</v>
       </c>
       <c r="D46" t="n">
-        <v>0.04393613710999489</v>
+        <v>0.1149958819150925</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1504438878158016</v>
+        <v>0.1741304694175008</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>0.3239137255701512</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2457921807875107</v>
+        <v>0.2457921807875106</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0224878191947937</v>
+        <v>0.1190437525510788</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1973979085174852</v>
+        <v>0.2295832196362469</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1606,10 +1606,10 @@
         <v>0.209244585855142</v>
       </c>
       <c r="D48" t="n">
-        <v>0.001748386537656188</v>
+        <v>0.05826980993151665</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1787627323051263</v>
+        <v>0.1976032067697464</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1626,10 +1626,10 @@
         <v>0.1427439829623747</v>
       </c>
       <c r="D49" t="n">
-        <v>0.004057799465954304</v>
+        <v>0.07333932816982269</v>
       </c>
       <c r="E49" t="n">
-        <v>0.09251196876082089</v>
+        <v>0.1156058116621104</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0.1509608933820573</v>
       </c>
       <c r="D50" t="n">
-        <v>0.004881610162556171</v>
+        <v>0.08909567445516586</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1061879480775556</v>
+        <v>0.1342593028417589</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1666,10 +1666,10 @@
         <v>0.1139518175910539</v>
       </c>
       <c r="D51" t="n">
-        <v>0.007151809986680746</v>
+        <v>0.04394658654928207</v>
       </c>
       <c r="E51" t="n">
-        <v>0.085730172241961</v>
+        <v>0.09799509776282811</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1686,10 +1686,10 @@
         <v>0.390087567199013</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4771513342857361</v>
+        <v>0.4760576784610748</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4918333224173459</v>
+        <v>0.4914687704757921</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1706,10 +1706,10 @@
         <v>0.2054801333693836</v>
       </c>
       <c r="D53" t="n">
-        <v>0.007350748870521784</v>
+        <v>0.1024506539106369</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1709866561684636</v>
+        <v>0.2026866245151686</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1726,10 +1726,10 @@
         <v>0.1484410092213372</v>
       </c>
       <c r="D54" t="n">
-        <v>0.00146501581184566</v>
+        <v>0.08305485546588898</v>
       </c>
       <c r="E54" t="n">
-        <v>0.08085988678937654</v>
+        <v>0.108056500007391</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0.1625413550263328</v>
       </c>
       <c r="D55" t="n">
-        <v>0.01120107807219028</v>
+        <v>0.05045245960354805</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1190585271386927</v>
+        <v>0.1321423209824786</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1766,10 +1766,10 @@
         <v>0.1639039215304618</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0006005787290632725</v>
+        <v>0.04496576264500618</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1088294471002989</v>
+        <v>0.1236178417389465</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
         <v>0.4164246332943039</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8579200506210327</v>
+        <v>0.6434066891670227</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6096648286325769</v>
+        <v>0.5381603748145736</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -1806,10 +1806,10 @@
         <v>0.2283001683073818</v>
       </c>
       <c r="D58" t="n">
-        <v>0.004553993232548237</v>
+        <v>0.1008164137601852</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1723573133239618</v>
+        <v>0.2044447868331741</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -1826,10 +1826,10 @@
         <v>0.1627608839275426</v>
       </c>
       <c r="D59" t="n">
-        <v>0.009782582521438599</v>
+        <v>0.1088517308235168</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1535531295203929</v>
+        <v>0.1865761789544189</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -1846,10 +1846,10 @@
         <v>0.3481202592206567</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1363774985074997</v>
+        <v>0.2974840998649597</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2706818431115475</v>
+        <v>0.3243840435640342</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
         <v>0.218892973261877</v>
       </c>
       <c r="D61" t="n">
-        <v>0.09915418922901154</v>
+        <v>0.1548318862915039</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1693827619554692</v>
+        <v>0.1879419943096333</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -1886,10 +1886,10 @@
         <v>0.1169476007559232</v>
       </c>
       <c r="D62" t="n">
-        <v>0.003251437796279788</v>
+        <v>0.03936900570988655</v>
       </c>
       <c r="E62" t="n">
-        <v>0.08263000096898161</v>
+        <v>0.09466919027351721</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -1906,10 +1906,10 @@
         <v>0.1779025379235713</v>
       </c>
       <c r="D63" t="n">
-        <v>0.04029678553342819</v>
+        <v>0.1443112641572952</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1340678832937848</v>
+        <v>0.1687393761684071</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -1926,10 +1926,10 @@
         <v>0.1582499449966986</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0005237373989075422</v>
+        <v>0.05421189218759537</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1088676338380776</v>
+        <v>0.1267636854343069</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -1946,10 +1946,10 @@
         <v>0.1125542101685188</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0005953896907158196</v>
+        <v>0.02593222633004189</v>
       </c>
       <c r="E65" t="n">
-        <v>0.07348267893056208</v>
+        <v>0.08192829114367077</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -1966,10 +1966,10 @@
         <v>0.1136698268734273</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0009417893597856164</v>
+        <v>0.03084207698702812</v>
       </c>
       <c r="E66" t="n">
-        <v>0.06977995846727476</v>
+        <v>0.07974672100968894</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -1986,10 +1986,10 @@
         <v>0.1649059773822238</v>
       </c>
       <c r="D67" t="n">
-        <v>0.01061465404927731</v>
+        <v>0.1271537989377975</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1265752343260632</v>
+        <v>0.16542161595557</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         <v>0.1927099488155739</v>
       </c>
       <c r="D68" t="n">
-        <v>0.002247888594865799</v>
+        <v>0.07480202615261078</v>
       </c>
       <c r="E68" t="n">
-        <v>0.128781967322503</v>
+        <v>0.1529666798417514</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2026,10 +2026,10 @@
         <v>0.1937242343187526</v>
       </c>
       <c r="D69" t="n">
-        <v>0.001773500815033913</v>
+        <v>0.06177512556314468</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1580766289345469</v>
+        <v>0.1780771705172504</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2046,10 +2046,10 @@
         <v>0.2330012744726119</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0458260104060173</v>
+        <v>0.06777125597000122</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1598729827930194</v>
+        <v>0.1671880646476807</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -2066,10 +2066,10 @@
         <v>0.132573833529041</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0004237395187374204</v>
+        <v>0.02854494377970695</v>
       </c>
       <c r="E71" t="n">
-        <v>0.08612453740975523</v>
+        <v>0.09549827216341174</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
         <v>0.1325738538236776</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0031516975723207</v>
+        <v>0.04638291150331497</v>
       </c>
       <c r="E72" t="n">
-        <v>0.09990655799196664</v>
+        <v>0.1143169626356314</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -2106,10 +2106,10 @@
         <v>0.1698225480092422</v>
       </c>
       <c r="D73" t="n">
-        <v>0.003110484685748816</v>
+        <v>0.05166326835751534</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1232117721068644</v>
+        <v>0.1393960333307866</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0.11612651888992</v>
       </c>
       <c r="D74" t="n">
-        <v>0.005948095116764307</v>
+        <v>0.05287307500839233</v>
       </c>
       <c r="E74" t="n">
-        <v>0.07647048264208844</v>
+        <v>0.09211214260596445</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -2146,10 +2146,10 @@
         <v>0.2920047176097141</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4906383454799652</v>
+        <v>0.4070721566677094</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3445957593881561</v>
+        <v>0.3167403631174041</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -2166,10 +2166,10 @@
         <v>0.1892112707317714</v>
       </c>
       <c r="D76" t="n">
-        <v>0.002812093123793602</v>
+        <v>0.03315313532948494</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1469525794418353</v>
+        <v>0.1570662601770657</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2186,13 +2186,13 @@
         <v>0.3804437240183593</v>
       </c>
       <c r="D77" t="n">
-        <v>0.867068886756897</v>
+        <v>0.5972049832344055</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5748725173329036</v>
+        <v>0.4849178828254064</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2206,10 +2206,10 @@
         <v>0.4200548999571609</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7984994649887085</v>
+        <v>0.6086451411247253</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6020697567227876</v>
+        <v>0.5387849821014599</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -2226,10 +2226,10 @@
         <v>0.1267494327787951</v>
       </c>
       <c r="D79" t="n">
-        <v>0.004208219237625599</v>
+        <v>0.04436822608113289</v>
       </c>
       <c r="E79" t="n">
-        <v>0.08323220495439067</v>
+        <v>0.09661887390222644</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2246,10 +2246,10 @@
         <v>0.1962932164738476</v>
       </c>
       <c r="D80" t="n">
-        <v>0.02054481580853462</v>
+        <v>0.08640669286251068</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1330216392586566</v>
+        <v>0.1549755982766486</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2266,10 +2266,10 @@
         <v>0.4017540561397547</v>
       </c>
       <c r="D81" t="n">
-        <v>0.814975917339325</v>
+        <v>0.6304978132247925</v>
       </c>
       <c r="E81" t="n">
-        <v>0.6166776960178392</v>
+        <v>0.5551849946463284</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -2283,13 +2283,13 @@
         <v>0.3838290151127853</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3218228931227875</v>
+        <v>0.3218228931227876</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7820993661880493</v>
+        <v>0.5310629606246948</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4959170914745407</v>
+        <v>0.4122382896200893</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0.1751262384974091</v>
       </c>
       <c r="D83" t="n">
-        <v>0.01259609032422304</v>
+        <v>0.08934400975704193</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1375067091361521</v>
+        <v>0.1630893489470918</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2326,10 +2326,10 @@
         <v>0.1711832488943786</v>
       </c>
       <c r="D84" t="n">
-        <v>0.008708175271749496</v>
+        <v>0.1539422124624252</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1346792494249259</v>
+        <v>0.1830905951551511</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2346,10 +2346,10 @@
         <v>0.1904234827419378</v>
       </c>
       <c r="D85" t="n">
-        <v>0.04044827446341515</v>
+        <v>0.2234828025102615</v>
       </c>
       <c r="E85" t="n">
-        <v>0.1393241779309549</v>
+        <v>0.2003356872799037</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2363,13 +2363,13 @@
         <v>0.1737333293702804</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1708580585636476</v>
+        <v>0.1708580585636477</v>
       </c>
       <c r="D86" t="n">
-        <v>0.005259337369352579</v>
+        <v>0.1180859953165054</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1166169084344269</v>
+        <v>0.1542257944168112</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2386,10 +2386,10 @@
         <v>0.1472660721205414</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0053669149056077</v>
+        <v>0.07654327899217606</v>
       </c>
       <c r="E87" t="n">
-        <v>0.09957038568125394</v>
+        <v>0.1232958403767767</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2406,10 +2406,10 @@
         <v>0.3709017397346566</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4599567949771881</v>
+        <v>0.360194593667984</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4287099199379891</v>
+        <v>0.3954558528349211</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -2426,10 +2426,10 @@
         <v>0.1301902088386243</v>
       </c>
       <c r="D89" t="n">
-        <v>0.001899786991998553</v>
+        <v>0.06094458699226379</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1381735567595633</v>
+        <v>0.1578551567596518</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -2446,10 +2446,10 @@
         <v>0.1975660188530602</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0874924436211586</v>
+        <v>0.1470537632703781</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1636641477631518</v>
+        <v>0.1835179209795583</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0.1889628996509349</v>
       </c>
       <c r="D91" t="n">
-        <v>0.007997198030352592</v>
+        <v>0.09290166944265366</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1470820645936405</v>
+        <v>0.1753835550644075</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -2486,10 +2486,10 @@
         <v>0.2911239373211523</v>
       </c>
       <c r="D92" t="n">
-        <v>0.02940996363759041</v>
+        <v>0.1819253712892532</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2370713801955857</v>
+        <v>0.2879098494128067</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -2506,10 +2506,10 @@
         <v>0.2474922151837859</v>
       </c>
       <c r="D93" t="n">
-        <v>0.003771704854443669</v>
+        <v>0.08088134229183197</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1661787251712351</v>
+        <v>0.1918819376503646</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
         <v>0.2555660616980943</v>
       </c>
       <c r="D94" t="n">
-        <v>0.03502223640680313</v>
+        <v>0.1806587427854538</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2140013972625015</v>
+        <v>0.2625468993887184</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -2546,10 +2546,10 @@
         <v>0.1798141515235379</v>
       </c>
       <c r="D95" t="n">
-        <v>0.012605513446033</v>
+        <v>0.1494482308626175</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1232449824363338</v>
+        <v>0.1688592215751953</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -2566,10 +2566,10 @@
         <v>0.1771546349215245</v>
       </c>
       <c r="D96" t="n">
-        <v>0.001745969406329095</v>
+        <v>0.05068237334489822</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1194223532985192</v>
+        <v>0.135734487944709</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -2583,13 +2583,13 @@
         <v>0.1200011740842674</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1595057475653789</v>
+        <v>0.1595057475653788</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0004080365470144898</v>
+        <v>0.04209328442811966</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0933049860655536</v>
+        <v>0.1072000686925886</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         <v>0.1409172694869817</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1475701462337582</v>
+        <v>0.1475701462337581</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0005163749447092414</v>
+        <v>0.04702669754624367</v>
       </c>
       <c r="E98" t="n">
-        <v>0.09633459688848302</v>
+        <v>0.1118380377556611</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -2626,10 +2626,10 @@
         <v>0.148472505311266</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0007181570399552584</v>
+        <v>0.03787142038345337</v>
       </c>
       <c r="E99" t="n">
-        <v>0.09865232429303257</v>
+        <v>0.1110367454075319</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -2646,10 +2646,10 @@
         <v>0.255094110227886</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0194055549800396</v>
+        <v>0.07757040113210678</v>
       </c>
       <c r="E100" t="n">
-        <v>0.2064376286101077</v>
+        <v>0.2258259106607968</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -2666,10 +2666,10 @@
         <v>0.2432298588647352</v>
       </c>
       <c r="D101" t="n">
-        <v>0.006568604614585638</v>
+        <v>0.08137639611959457</v>
       </c>
       <c r="E101" t="n">
-        <v>0.1696393878779215</v>
+        <v>0.1945753183795912</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -2686,10 +2686,10 @@
         <v>0.1456012503208176</v>
       </c>
       <c r="D102" t="n">
-        <v>0.003778595477342606</v>
+        <v>0.07656564563512802</v>
       </c>
       <c r="E102" t="n">
-        <v>0.08488381573647974</v>
+        <v>0.1091461657890749</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -2706,10 +2706,10 @@
         <v>0.1760676424483896</v>
       </c>
       <c r="D103" t="n">
-        <v>0.002059787744656205</v>
+        <v>0.06800888478755951</v>
       </c>
       <c r="E103" t="n">
-        <v>0.1369683821258147</v>
+        <v>0.1589514144734492</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -2726,10 +2726,10 @@
         <v>0.2905927271854694</v>
       </c>
       <c r="D104" t="n">
-        <v>0.03202971816062927</v>
+        <v>0.1270585507154465</v>
       </c>
       <c r="E104" t="n">
-        <v>0.251871462351294</v>
+        <v>0.2835477398695664</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -2746,10 +2746,10 @@
         <v>0.2443707586665065</v>
       </c>
       <c r="D105" t="n">
-        <v>0.03178349509835243</v>
+        <v>0.1124431118369102</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2092505273096349</v>
+        <v>0.2361370662224875</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>0.2233666653368904</v>
       </c>
       <c r="D106" t="n">
-        <v>0.04076407104730606</v>
+        <v>0.0978214219212532</v>
       </c>
       <c r="E106" t="n">
-        <v>0.1840429433782573</v>
+        <v>0.2030620603362397</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -2786,10 +2786,10 @@
         <v>0.2821254175158009</v>
       </c>
       <c r="D107" t="n">
-        <v>0.01457046251744032</v>
+        <v>0.0883021205663681</v>
       </c>
       <c r="E107" t="n">
-        <v>0.2230541109216706</v>
+        <v>0.2476313302713132</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -2806,10 +2806,10 @@
         <v>0.2317550636568133</v>
       </c>
       <c r="D108" t="n">
-        <v>0.001548610860481858</v>
+        <v>0.0539105124771595</v>
       </c>
       <c r="E108" t="n">
-        <v>0.192245130814699</v>
+        <v>0.2096990980202582</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -2826,10 +2826,10 @@
         <v>0.2156516811085383</v>
       </c>
       <c r="D109" t="n">
-        <v>0.001491953036747873</v>
+        <v>0.06313595920801163</v>
       </c>
       <c r="E109" t="n">
-        <v>0.1591575037871012</v>
+        <v>0.1797055058441891</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0.15975732027634</v>
       </c>
       <c r="D110" t="n">
-        <v>0.002451690612360835</v>
+        <v>0.0471537820994854</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1050248173873269</v>
+        <v>0.1199255145497018</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -2863,13 +2863,13 @@
         <v>0.1821843624457373</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1916296373343441</v>
+        <v>0.191629637334344</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0010364621412009</v>
+        <v>0.05058064311742783</v>
       </c>
       <c r="E111" t="n">
-        <v>0.1249501539737607</v>
+        <v>0.1414648809658364</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -2886,10 +2886,10 @@
         <v>0.2034825107820868</v>
       </c>
       <c r="D112" t="n">
-        <v>0.004509586840867996</v>
+        <v>0.0928836464881897</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1456553992107709</v>
+        <v>0.1751134190932114</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -2906,10 +2906,10 @@
         <v>0.18789105618562</v>
       </c>
       <c r="D113" t="n">
-        <v>0.009890615940093994</v>
+        <v>0.07154951989650726</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1357467429333735</v>
+        <v>0.1562997109188446</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>0.2681175478448671</v>
       </c>
       <c r="D114" t="n">
-        <v>0.05269386619329453</v>
+        <v>0.1331165134906769</v>
       </c>
       <c r="E114" t="n">
-        <v>0.2340950480723792</v>
+        <v>0.2609025971715067</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -2943,13 +2943,13 @@
         <v>0.3215744765622564</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2423932088510732</v>
+        <v>0.2423932088510731</v>
       </c>
       <c r="D115" t="n">
-        <v>0.005007356870919466</v>
+        <v>0.09896806627511978</v>
       </c>
       <c r="E115" t="n">
-        <v>0.189658347428083</v>
+        <v>0.2209785838961498</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0.2836388660180196</v>
       </c>
       <c r="D116" t="n">
-        <v>0.296814501285553</v>
+        <v>0.3216975927352905</v>
       </c>
       <c r="E116" t="n">
-        <v>0.3125171377957968</v>
+        <v>0.3208115016123759</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -2986,10 +2986,10 @@
         <v>0.1892403695594683</v>
       </c>
       <c r="D117" t="n">
-        <v>0.001467709895223379</v>
+        <v>0.07636058330535889</v>
       </c>
       <c r="E117" t="n">
-        <v>0.1429973229073222</v>
+        <v>0.1679616140440341</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -3006,10 +3006,10 @@
         <v>0.2317462925673377</v>
       </c>
       <c r="D118" t="n">
-        <v>0.07801272720098495</v>
+        <v>0.1270736157894135</v>
       </c>
       <c r="E118" t="n">
-        <v>0.1938190727238126</v>
+        <v>0.2101727022532887</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -3026,10 +3026,10 @@
         <v>0.2306415165859474</v>
       </c>
       <c r="D119" t="n">
-        <v>0.03227423876523972</v>
+        <v>0.09788663685321808</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1659198593953393</v>
+        <v>0.1877906587579987</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -3046,10 +3046,10 @@
         <v>0.2004457546413801</v>
       </c>
       <c r="D120" t="n">
-        <v>0.006442068610340357</v>
+        <v>0.06027615070343018</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1317201351493017</v>
+        <v>0.1496648291803316</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -3066,10 +3066,10 @@
         <v>0.1909750892752477</v>
       </c>
       <c r="D121" t="n">
-        <v>0.0003757661033887416</v>
+        <v>0.05868737772107124</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1245098188866539</v>
+        <v>0.1439470227592147</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -3086,10 +3086,10 @@
         <v>0.2000629247124529</v>
       </c>
       <c r="D122" t="n">
-        <v>0.007078282535076141</v>
+        <v>0.09681887924671173</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1485483218642515</v>
+        <v>0.1784618541014633</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3106,10 +3106,10 @@
         <v>0.1394654242105447</v>
       </c>
       <c r="D123" t="n">
-        <v>0.001645088545046747</v>
+        <v>0.08740630745887756</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1113134488308432</v>
+        <v>0.1399005218021202</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -3126,10 +3126,10 @@
         <v>0.2359694029676137</v>
       </c>
       <c r="D124" t="n">
-        <v>0.007771477103233337</v>
+        <v>0.1334412544965744</v>
       </c>
       <c r="E124" t="n">
-        <v>0.1906369041735045</v>
+        <v>0.2325268299712849</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>0.1664674759613062</v>
       </c>
       <c r="C125" t="n">
-        <v>0.179046639407559</v>
+        <v>0.1790466394075589</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0005861816462129354</v>
+        <v>0.03753819689154625</v>
       </c>
       <c r="E125" t="n">
-        <v>0.1153667656716927</v>
+        <v>0.1276841040868038</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -3166,10 +3166,10 @@
         <v>0.2330861127280797</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0009962121257558465</v>
+        <v>0.06960944831371307</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1595513395262933</v>
+        <v>0.1824224182556124</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -3186,10 +3186,10 @@
         <v>0.2373465158695374</v>
       </c>
       <c r="D127" t="n">
-        <v>0.01783658191561699</v>
+        <v>0.09124630689620972</v>
       </c>
       <c r="E127" t="n">
-        <v>0.1860641448943245</v>
+        <v>0.2105340532211888</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -3206,10 +3206,10 @@
         <v>0.199092305431018</v>
       </c>
       <c r="D128" t="n">
-        <v>0.002643202198669314</v>
+        <v>0.0557260736823082</v>
       </c>
       <c r="E128" t="n">
-        <v>0.1363679779447249</v>
+        <v>0.1540622684392711</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -3226,10 +3226,10 @@
         <v>0.4485568648841595</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4378467500209808</v>
+        <v>0.3643041551113129</v>
       </c>
       <c r="E129" t="n">
-        <v>0.4731133740262144</v>
+        <v>0.4485991757229917</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>0.2157166560496045</v>
       </c>
       <c r="D130" t="n">
-        <v>0.002151068300008774</v>
+        <v>0.03277043253183365</v>
       </c>
       <c r="E130" t="n">
-        <v>0.1526277306502006</v>
+        <v>0.1628341853941422</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -3266,10 +3266,10 @@
         <v>0.4264580341449077</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3549827039241791</v>
+        <v>0.4105073809623718</v>
       </c>
       <c r="E131" t="n">
-        <v>0.4443662164479039</v>
+        <v>0.4628744421273015</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -3286,10 +3286,10 @@
         <v>0.1910253129829357</v>
       </c>
       <c r="D132" t="n">
-        <v>0.185399979352951</v>
+        <v>0.2916761338710785</v>
       </c>
       <c r="E132" t="n">
-        <v>0.1996193743019462</v>
+        <v>0.235044759141322</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -3306,10 +3306,10 @@
         <v>0.2115912711167978</v>
       </c>
       <c r="D133" t="n">
-        <v>7.040111995593179e-06</v>
+        <v>0.02415648102760315</v>
       </c>
       <c r="E133" t="n">
-        <v>0.147314908482984</v>
+        <v>0.1553647221215199</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         <v>0.2196491282492932</v>
       </c>
       <c r="D134" t="n">
-        <v>0.002849457086995244</v>
+        <v>0.1000388860702515</v>
       </c>
       <c r="E134" t="n">
-        <v>0.1418832926678329</v>
+        <v>0.1742797689955849</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -3343,13 +3343,13 @@
         <v>0.1738114454667323</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1590450461436954</v>
+        <v>0.1590450461436953</v>
       </c>
       <c r="D135" t="n">
-        <v>1.487391818955075e-05</v>
+        <v>0.01743769273161888</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1109571218428724</v>
+        <v>0.1167647281140155</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -3366,10 +3366,10 @@
         <v>0.2993281109743333</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1535634994506836</v>
+        <v>0.2984001338481903</v>
       </c>
       <c r="E136" t="n">
-        <v>0.2594907551228036</v>
+        <v>0.3077696332553059</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0.1661793614500213</v>
       </c>
       <c r="D137" t="n">
-        <v>0.009283474646508694</v>
+        <v>0.09965391457080841</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1411012376169004</v>
+        <v>0.171224717591667</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -3406,10 +3406,10 @@
         <v>0.1585635638678708</v>
       </c>
       <c r="D138" t="n">
-        <v>0.006905104033648968</v>
+        <v>0.1258547008037567</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1125833112059028</v>
+        <v>0.1522331767959387</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -3426,10 +3426,10 @@
         <v>0.1543721827596509</v>
       </c>
       <c r="D139" t="n">
-        <v>0.01597924716770649</v>
+        <v>0.1194690614938736</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1172724421787777</v>
+        <v>0.1517690469541668</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -3443,13 +3443,13 @@
         <v>0.2331993948741976</v>
       </c>
       <c r="C140" t="n">
-        <v>0.167381568212546</v>
+        <v>0.1673815682125459</v>
       </c>
       <c r="D140" t="n">
-        <v>0.006950265262275934</v>
+        <v>0.0735790953040123</v>
       </c>
       <c r="E140" t="n">
-        <v>0.1358437427830065</v>
+        <v>0.1580533527969186</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -3466,10 +3466,10 @@
         <v>0.198524606922231</v>
       </c>
       <c r="D141" t="n">
-        <v>0.00706800352782011</v>
+        <v>0.128958597779274</v>
       </c>
       <c r="E141" t="n">
-        <v>0.1453584515034554</v>
+        <v>0.1859886495872734</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -3483,13 +3483,13 @@
         <v>0.282129333945924</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2575697482213987</v>
+        <v>0.2575697482213986</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1466910094022751</v>
+        <v>0.2417061030864716</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2287966971898659</v>
+        <v>0.2604683950845981</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -3506,10 +3506,10 @@
         <v>0.1746891479959272</v>
       </c>
       <c r="D143" t="n">
-        <v>0.2296700775623322</v>
+        <v>0.2100435048341751</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1800430939190188</v>
+        <v>0.1735009030096331</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -3526,10 +3526,10 @@
         <v>0.1449903401267535</v>
       </c>
       <c r="D144" t="n">
-        <v>0.0001892353320727125</v>
+        <v>0.03373945876955986</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1098699235358978</v>
+        <v>0.1210533313483935</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0.1369719748235891</v>
       </c>
       <c r="D145" t="n">
-        <v>0.0001256874529644847</v>
+        <v>0.02318518236279488</v>
       </c>
       <c r="E145" t="n">
-        <v>0.09703671313446431</v>
+        <v>0.1047232114377411</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -3566,10 +3566,10 @@
         <v>0.1884448058691281</v>
       </c>
       <c r="D146" t="n">
-        <v>0.01101752184331417</v>
+        <v>0.09425767511129379</v>
       </c>
       <c r="E146" t="n">
-        <v>0.1360610702885261</v>
+        <v>0.1638077880445193</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -3586,10 +3586,10 @@
         <v>0.2075805812152529</v>
       </c>
       <c r="D147" t="n">
-        <v>0.006291518919169903</v>
+        <v>0.1072731763124466</v>
       </c>
       <c r="E147" t="n">
-        <v>0.1491196540836797</v>
+        <v>0.1827802065481053</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -3606,10 +3606,10 @@
         <v>0.1335388221987244</v>
       </c>
       <c r="D148" t="n">
-        <v>0.054457176476717</v>
+        <v>0.09967823326587677</v>
       </c>
       <c r="E148" t="n">
-        <v>0.1248078682972784</v>
+        <v>0.139881553893665</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0.1735058048497894</v>
       </c>
       <c r="D149" t="n">
-        <v>0.1107948049902916</v>
+        <v>0.1775254011154175</v>
       </c>
       <c r="E149" t="n">
-        <v>0.1751757873841379</v>
+        <v>0.1974193194258465</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -3646,10 +3646,10 @@
         <v>0.1776650698259835</v>
       </c>
       <c r="D150" t="n">
-        <v>0.06342144310474396</v>
+        <v>0.1439191251993179</v>
       </c>
       <c r="E150" t="n">
-        <v>0.1566910449201854</v>
+        <v>0.1835236056183767</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -3666,10 +3666,10 @@
         <v>0.2249794545071617</v>
       </c>
       <c r="D151" t="n">
-        <v>0.01228868030011654</v>
+        <v>0.09874304383993149</v>
       </c>
       <c r="E151" t="n">
-        <v>0.2013928681204958</v>
+        <v>0.2302109893004341</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0.1718083442958885</v>
       </c>
       <c r="D152" t="n">
-        <v>0.002039075363427401</v>
+        <v>0.05783878639340401</v>
       </c>
       <c r="E152" t="n">
-        <v>0.1312164826822337</v>
+        <v>0.1498163863588925</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -3706,10 +3706,10 @@
         <v>0.3597703716678772</v>
       </c>
       <c r="D153" t="n">
-        <v>0.7815949320793152</v>
+        <v>0.5645391345024109</v>
       </c>
       <c r="E153" t="n">
-        <v>0.5096018521632449</v>
+        <v>0.4372499196376101</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -3723,13 +3723,13 @@
         <v>0.1783957571550112</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1691316468433855</v>
+        <v>0.1691316468433854</v>
       </c>
       <c r="D154" t="n">
-        <v>0.01177742797881365</v>
+        <v>0.131822258234024</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1197682773257368</v>
+        <v>0.1597832207441402</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -3746,10 +3746,10 @@
         <v>0.1890634753554935</v>
       </c>
       <c r="D155" t="n">
-        <v>0.007053972221910954</v>
+        <v>0.09174433350563049</v>
       </c>
       <c r="E155" t="n">
-        <v>0.1381268038566006</v>
+        <v>0.166356924284507</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -3763,13 +3763,13 @@
         <v>0.2073956179896051</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1975913140972196</v>
+        <v>0.1975913140972195</v>
       </c>
       <c r="D156" t="n">
-        <v>0.03591520711779594</v>
+        <v>0.1350509375333786</v>
       </c>
       <c r="E156" t="n">
-        <v>0.1469673797348735</v>
+        <v>0.1800126232067344</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -3783,13 +3783,13 @@
         <v>0.138518206701358</v>
       </c>
       <c r="C157" t="n">
-        <v>0.158655479513384</v>
+        <v>0.1586554795133839</v>
       </c>
       <c r="D157" t="n">
-        <v>0.0003380635171197355</v>
+        <v>0.04647943004965782</v>
       </c>
       <c r="E157" t="n">
-        <v>0.09917058324395389</v>
+        <v>0.1145510387547999</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -3806,10 +3806,10 @@
         <v>0.2052757870355309</v>
       </c>
       <c r="D158" t="n">
-        <v>0.04785756394267082</v>
+        <v>0.1001632958650589</v>
       </c>
       <c r="E158" t="n">
-        <v>0.1436707849099163</v>
+        <v>0.1611060288840457</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -3826,10 +3826,10 @@
         <v>0.2131209901496757</v>
       </c>
       <c r="D159" t="n">
-        <v>0.07141271978616714</v>
+        <v>0.1581255346536636</v>
       </c>
       <c r="E159" t="n">
-        <v>0.1567111057710584</v>
+        <v>0.1856153773935573</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -3846,10 +3846,10 @@
         <v>0.1781868163924507</v>
       </c>
       <c r="D160" t="n">
-        <v>0.003129287157207727</v>
+        <v>0.09510365873575211</v>
       </c>
       <c r="E160" t="n">
-        <v>0.1370313824333385</v>
+        <v>0.1676895062928533</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -3866,10 +3866,10 @@
         <v>0.2929229842412049</v>
       </c>
       <c r="D161" t="n">
-        <v>0.01386689860373735</v>
+        <v>0.119443491101265</v>
       </c>
       <c r="E161" t="n">
-        <v>0.2948174084085267</v>
+        <v>0.3300096059077025</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -3883,13 +3883,13 @@
         <v>0.1699331182172456</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1599006425528004</v>
+        <v>0.1599006425528003</v>
       </c>
       <c r="D162" t="n">
-        <v>0.004289933945983648</v>
+        <v>0.104073166847229</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1113745649053432</v>
+        <v>0.1446356425390916</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -3906,10 +3906,10 @@
         <v>0.2301300373611239</v>
       </c>
       <c r="D163" t="n">
-        <v>0.03229798004031181</v>
+        <v>0.1493432819843292</v>
       </c>
       <c r="E163" t="n">
-        <v>0.2108665260229536</v>
+        <v>0.2498816266709594</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -3926,10 +3926,10 @@
         <v>0.1687292697776077</v>
       </c>
       <c r="D164" t="n">
-        <v>0.0001946550764841959</v>
+        <v>0.04397561401128769</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1223429784692885</v>
+        <v>0.1369366314475564</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -3946,10 +3946,10 @@
         <v>0.2053471984365973</v>
       </c>
       <c r="D165" t="n">
-        <v>0.04421139135956764</v>
+        <v>0.1392484754323959</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1476269004594375</v>
+        <v>0.1793059284837135</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -3966,10 +3966,10 @@
         <v>0.1859560871239771</v>
       </c>
       <c r="D166" t="n">
-        <v>0.007877207361161709</v>
+        <v>0.1170696243643761</v>
       </c>
       <c r="E166" t="n">
-        <v>0.1470380123933714</v>
+        <v>0.1834354847277762</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -3986,10 +3986,10 @@
         <v>0.2446251107431703</v>
       </c>
       <c r="D167" t="n">
-        <v>0.06357564032077789</v>
+        <v>0.1489203125238419</v>
       </c>
       <c r="E167" t="n">
-        <v>0.1982452087261952</v>
+        <v>0.2266934327938832</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -4006,10 +4006,10 @@
         <v>0.2488826847840804</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1034052595496178</v>
+        <v>0.1216466799378395</v>
       </c>
       <c r="E168" t="n">
-        <v>0.2295231667243979</v>
+        <v>0.2356036401871385</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0.3782075718991662</v>
       </c>
       <c r="C169" t="n">
-        <v>0.2914449522169881</v>
+        <v>0.291444952216988</v>
       </c>
       <c r="D169" t="n">
-        <v>0.103356696665287</v>
+        <v>0.1138434186577797</v>
       </c>
       <c r="E169" t="n">
-        <v>0.2576697402604804</v>
+        <v>0.261165314257978</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -4046,10 +4046,10 @@
         <v>0.2162049916127085</v>
       </c>
       <c r="D170" t="n">
-        <v>2.923235297203064e-05</v>
+        <v>0.014892578125</v>
       </c>
       <c r="E170" t="n">
-        <v>0.143195080330749</v>
+        <v>0.148149528921425</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -4066,10 +4066,10 @@
         <v>0.1661486473477525</v>
       </c>
       <c r="D171" t="n">
-        <v>0.00266004609875381</v>
+        <v>0.06398062407970428</v>
       </c>
       <c r="E171" t="n">
-        <v>0.1381539526933285</v>
+        <v>0.1585941453536454</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
@@ -4086,10 +4086,10 @@
         <v>0.2457879211277599</v>
       </c>
       <c r="D172" t="n">
-        <v>0.01830104552209377</v>
+        <v>0.08680689334869385</v>
       </c>
       <c r="E172" t="n">
-        <v>0.1950492206232067</v>
+        <v>0.2178845032320734</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -4106,10 +4106,10 @@
         <v>0.1854929978226296</v>
       </c>
       <c r="D173" t="n">
-        <v>4.323240864323452e-05</v>
+        <v>0.02518993616104126</v>
       </c>
       <c r="E173" t="n">
-        <v>0.1348496482877421</v>
+        <v>0.1432318828718747</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -4126,10 +4126,10 @@
         <v>0.2572098595958555</v>
       </c>
       <c r="D174" t="n">
-        <v>0.04150685667991638</v>
+        <v>0.1440778374671936</v>
       </c>
       <c r="E174" t="n">
-        <v>0.1789027814585086</v>
+        <v>0.213093108387601</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -4146,10 +4146,10 @@
         <v>0.2349197204200388</v>
       </c>
       <c r="D175" t="n">
-        <v>0.1647454500198364</v>
+        <v>0.229485034942627</v>
       </c>
       <c r="E175" t="n">
-        <v>0.2381222717050407</v>
+        <v>0.2597021333459709</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
@@ -4166,10 +4166,10 @@
         <v>0.2025522931057314</v>
       </c>
       <c r="D176" t="n">
-        <v>0.01759307458996773</v>
+        <v>0.08229502290487289</v>
       </c>
       <c r="E176" t="n">
-        <v>0.1371129838054838</v>
+        <v>0.1586802999104522</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
@@ -4186,10 +4186,10 @@
         <v>0.1970402185098704</v>
       </c>
       <c r="D177" t="n">
-        <v>0.0004415439907461405</v>
+        <v>0.02475964091718197</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1380118090085062</v>
+        <v>0.1461178413173181</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -4206,10 +4206,10 @@
         <v>0.2240024759412333</v>
       </c>
       <c r="D178" t="n">
-        <v>0.06734587252140045</v>
+        <v>0.134252518415451</v>
       </c>
       <c r="E178" t="n">
-        <v>0.181827457325801</v>
+        <v>0.2041296726238179</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
@@ -4226,10 +4226,10 @@
         <v>0.2191116220077852</v>
       </c>
       <c r="D179" t="n">
-        <v>0.02196581289172173</v>
+        <v>0.1221204549074173</v>
       </c>
       <c r="E179" t="n">
-        <v>0.1662508115904843</v>
+        <v>0.1996356922623828</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
@@ -4246,10 +4246,10 @@
         <v>0.4354003290122679</v>
       </c>
       <c r="D180" t="n">
-        <v>0.9444926977157593</v>
+        <v>0.6994339227676392</v>
       </c>
       <c r="E180" t="n">
-        <v>0.6696820488141605</v>
+        <v>0.5879957904981205</v>
       </c>
       <c r="F180" t="n">
         <v>1</v>
@@ -4266,10 +4266,10 @@
         <v>0.177277556843938</v>
       </c>
       <c r="D181" t="n">
-        <v>0.003574077039957047</v>
+        <v>0.06042464822530746</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1302685016079602</v>
+        <v>0.149218692003077</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0.1769390008680137</v>
       </c>
       <c r="D182" t="n">
-        <v>0.001586274825967848</v>
+        <v>0.06669972091913223</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1332202960685542</v>
+        <v>0.1549247780996089</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -4306,10 +4306,10 @@
         <v>0.2131808155509465</v>
       </c>
       <c r="D183" t="n">
-        <v>0.03411171585321426</v>
+        <v>0.05560547858476639</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1664334587138736</v>
+        <v>0.1735980462910577</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
@@ -4326,10 +4326,10 @@
         <v>0.286695580837637</v>
       </c>
       <c r="D184" t="n">
-        <v>0.1384590566158295</v>
+        <v>0.1801560074090958</v>
       </c>
       <c r="E184" t="n">
-        <v>0.2351286237523725</v>
+        <v>0.2490276073501279</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
@@ -4346,10 +4346,10 @@
         <v>0.1773561806791862</v>
       </c>
       <c r="D185" t="n">
-        <v>0.004614813718944788</v>
+        <v>0.09784479439258575</v>
       </c>
       <c r="E185" t="n">
-        <v>0.1294408305185092</v>
+        <v>0.1605174907430562</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
@@ -4366,10 +4366,10 @@
         <v>0.1831151409898754</v>
       </c>
       <c r="D186" t="n">
-        <v>0.002539233071729541</v>
+        <v>0.09395071119070053</v>
       </c>
       <c r="E186" t="n">
-        <v>0.1325319970682262</v>
+        <v>0.1630024897745498</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -4386,10 +4386,10 @@
         <v>0.1760849947590262</v>
       </c>
       <c r="D187" t="n">
-        <v>0.000133631459902972</v>
+        <v>0.04444687813520432</v>
       </c>
       <c r="E187" t="n">
-        <v>0.1172434710769959</v>
+        <v>0.1320145533020964</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -4406,10 +4406,10 @@
         <v>0.1679463078283981</v>
       </c>
       <c r="D188" t="n">
-        <v>0.002849379787221551</v>
+        <v>0.07172185182571411</v>
       </c>
       <c r="E188" t="n">
-        <v>0.1237295175953165</v>
+        <v>0.146687008274814</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
@@ -4426,10 +4426,10 @@
         <v>0.2423868672446111</v>
       </c>
       <c r="D189" t="n">
-        <v>0.1298584789037704</v>
+        <v>0.1897652149200439</v>
       </c>
       <c r="E189" t="n">
-        <v>0.2093004671738542</v>
+        <v>0.2292693791792787</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -4443,13 +4443,13 @@
         <v>0.1298123057755818</v>
       </c>
       <c r="C190" t="n">
-        <v>0.1199860881616682</v>
+        <v>0.1199860881616681</v>
       </c>
       <c r="D190" t="n">
-        <v>3.26319714076817e-05</v>
+        <v>0.02535712346434593</v>
       </c>
       <c r="E190" t="n">
-        <v>0.08327700863621923</v>
+        <v>0.09171850580053198</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
@@ -4463,13 +4463,13 @@
         <v>0.5181516709662826</v>
       </c>
       <c r="C191" t="n">
-        <v>0.3486316687780635</v>
+        <v>0.3486316687780634</v>
       </c>
       <c r="D191" t="n">
-        <v>0.02714811824262142</v>
+        <v>0.1301033049821854</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2979771526623225</v>
+        <v>0.3322955482421771</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -4483,13 +4483,13 @@
         <v>0.1954804148651044</v>
       </c>
       <c r="C192" t="n">
-        <v>0.1688192095890889</v>
+        <v>0.1688192095890888</v>
       </c>
       <c r="D192" t="n">
-        <v>0.02626415155827999</v>
+        <v>0.1357305943965912</v>
       </c>
       <c r="E192" t="n">
-        <v>0.1301879253374911</v>
+        <v>0.1666767396169281</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0.1329203079871629</v>
       </c>
       <c r="D193" t="n">
-        <v>0.04238059744238853</v>
+        <v>0.2263370305299759</v>
       </c>
       <c r="E193" t="n">
-        <v>0.09565184410801253</v>
+        <v>0.1569706551372083</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -4526,10 +4526,10 @@
         <v>0.1646347172833459</v>
       </c>
       <c r="D194" t="n">
-        <v>0.01252851355820894</v>
+        <v>0.1332140415906906</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1016695359210383</v>
+        <v>0.1418980452651989</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
@@ -4546,10 +4546,10 @@
         <v>0.1690222026487901</v>
       </c>
       <c r="D195" t="n">
-        <v>0.000352966773789376</v>
+        <v>0.06832589954137802</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1174653366616495</v>
+        <v>0.1401229809175124</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
@@ -4566,10 +4566,10 @@
         <v>0.1310797943846707</v>
       </c>
       <c r="D196" t="n">
-        <v>0.005569968372583389</v>
+        <v>0.05107460543513298</v>
       </c>
       <c r="E196" t="n">
-        <v>0.08443935315403532</v>
+        <v>0.09960756550821852</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0.1086716773384964</v>
       </c>
       <c r="D197" t="n">
-        <v>0.01354396529495716</v>
+        <v>0.08349766582250595</v>
       </c>
       <c r="E197" t="n">
-        <v>0.07596250393027908</v>
+        <v>0.09928040410612866</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -4606,10 +4606,10 @@
         <v>0.2688405001313958</v>
       </c>
       <c r="D198" t="n">
-        <v>0.3122029304504395</v>
+        <v>0.3717413544654846</v>
       </c>
       <c r="E198" t="n">
-        <v>0.3142128223358557</v>
+        <v>0.334058963674204</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -4626,10 +4626,10 @@
         <v>0.1367383533817442</v>
       </c>
       <c r="D199" t="n">
-        <v>0.002859922591596842</v>
+        <v>0.08504392951726913</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1110789533570814</v>
+        <v>0.1384736223323055</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
@@ -4646,10 +4646,10 @@
         <v>0.4155069904549825</v>
       </c>
       <c r="D200" t="n">
-        <v>0.7464140653610229</v>
+        <v>0.5764329433441162</v>
       </c>
       <c r="E200" t="n">
-        <v>0.5371285559097345</v>
+        <v>0.480468181904099</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
@@ -4666,10 +4666,10 @@
         <v>0.3801786252879711</v>
       </c>
       <c r="D201" t="n">
-        <v>0.6453999280929565</v>
+        <v>0.4801514744758606</v>
       </c>
       <c r="E201" t="n">
-        <v>0.5631164648109619</v>
+        <v>0.5080336469385965</v>
       </c>
       <c r="F201" t="n">
         <v>0</v>
@@ -4686,13 +4686,13 @@
         <v>0.3992724598585663</v>
       </c>
       <c r="D202" t="n">
-        <v>0.8552601933479309</v>
+        <v>0.5202752351760864</v>
       </c>
       <c r="E202" t="n">
-        <v>0.5769781292736852</v>
+        <v>0.465316476549737</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -4706,10 +4706,10 @@
         <v>0.1947897823566847</v>
       </c>
       <c r="D203" t="n">
-        <v>0.06963777542114258</v>
+        <v>0.167051836848259</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1590276183029981</v>
+        <v>0.191498972112037</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -4726,10 +4726,10 @@
         <v>0.3433269610355117</v>
       </c>
       <c r="D204" t="n">
-        <v>0.5634319186210632</v>
+        <v>0.4927714467048645</v>
       </c>
       <c r="E204" t="n">
-        <v>0.4563713734138526</v>
+        <v>0.4328178827751197</v>
       </c>
       <c r="F204" t="n">
         <v>0</v>
@@ -4746,10 +4746,10 @@
         <v>0.2142102301421978</v>
       </c>
       <c r="D205" t="n">
-        <v>0.0001699623244348913</v>
+        <v>0.05585967376828194</v>
       </c>
       <c r="E205" t="n">
-        <v>0.1563267912688356</v>
+        <v>0.1748900284167846</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
@@ -4766,10 +4766,10 @@
         <v>0.3187157970167481</v>
       </c>
       <c r="D206" t="n">
-        <v>0.1601885855197906</v>
+        <v>0.2856554090976715</v>
       </c>
       <c r="E206" t="n">
-        <v>0.3032830651340125</v>
+        <v>0.3451053396599728</v>
       </c>
       <c r="F206" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0.4718198786719</v>
       </c>
       <c r="D207" t="n">
-        <v>0.8313325047492981</v>
+        <v>0.6670352220535278</v>
       </c>
       <c r="E207" t="n">
-        <v>0.6459680564472708</v>
+        <v>0.5912022955486808</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -4806,10 +4806,10 @@
         <v>0.2550295013516793</v>
       </c>
       <c r="D208" t="n">
-        <v>0.2826966941356659</v>
+        <v>0.2041709721088409</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2825555191085018</v>
+        <v>0.2563802784328935</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
@@ -4826,10 +4826,10 @@
         <v>0.1923531620543562</v>
       </c>
       <c r="D209" t="n">
-        <v>0.001259941840544343</v>
+        <v>0.0673091858625412</v>
       </c>
       <c r="E209" t="n">
-        <v>0.1563107363407673</v>
+        <v>0.1783271510147663</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
@@ -4846,10 +4846,10 @@
         <v>0.3151230138154562</v>
       </c>
       <c r="D210" t="n">
-        <v>0.7912012934684753</v>
+        <v>0.473172128200531</v>
       </c>
       <c r="E210" t="n">
-        <v>0.5163430486925499</v>
+        <v>0.4103333269365684</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -4866,10 +4866,10 @@
         <v>0.4161992186869769</v>
       </c>
       <c r="D211" t="n">
-        <v>0.5638378858566284</v>
+        <v>0.3205889761447906</v>
       </c>
       <c r="E211" t="n">
-        <v>0.4780635857731883</v>
+        <v>0.3969806158692424</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0.3620200728603185</v>
       </c>
       <c r="D212" t="n">
-        <v>0.6082373857498169</v>
+        <v>0.4915650486946106</v>
       </c>
       <c r="E212" t="n">
-        <v>0.4711672740199334</v>
+        <v>0.4322764950015313</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
@@ -4906,10 +4906,10 @@
         <v>0.2199955210197621</v>
       </c>
       <c r="D213" t="n">
-        <v>0.005098613910377026</v>
+        <v>0.1041309684514999</v>
       </c>
       <c r="E213" t="n">
-        <v>0.1713121808671572</v>
+        <v>0.2043229657141982</v>
       </c>
       <c r="F213" t="n">
         <v>0</v>
@@ -4926,13 +4926,13 @@
         <v>0.3907217493540841</v>
       </c>
       <c r="D214" t="n">
-        <v>0.8382552266120911</v>
+        <v>0.4973194599151611</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6032666416189999</v>
+        <v>0.4896213860533566</v>
       </c>
       <c r="F214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -4946,10 +4946,10 @@
         <v>0.1769897430601229</v>
       </c>
       <c r="D215" t="n">
-        <v>0.006634782068431377</v>
+        <v>0.07454521954059601</v>
       </c>
       <c r="E215" t="n">
-        <v>0.1532720606587077</v>
+        <v>0.1759088731494292</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
@@ -4966,10 +4966,10 @@
         <v>0.2902224609793662</v>
       </c>
       <c r="D216" t="n">
-        <v>0.2210657894611359</v>
+        <v>0.4471235871315002</v>
       </c>
       <c r="E216" t="n">
-        <v>0.2686037699277919</v>
+        <v>0.3439563691512468</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
@@ -4986,10 +4986,10 @@
         <v>0.2570242167310633</v>
       </c>
       <c r="D217" t="n">
-        <v>0.7822309732437134</v>
+        <v>0.5371828079223633</v>
       </c>
       <c r="E217" t="n">
-        <v>0.4721434466319375</v>
+        <v>0.3904607248581541</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
@@ -5006,10 +5006,10 @@
         <v>0.1319515001019295</v>
       </c>
       <c r="D218" t="n">
-        <v>0.001759489299729466</v>
+        <v>0.07341770827770233</v>
       </c>
       <c r="E218" t="n">
-        <v>0.1032909718282338</v>
+        <v>0.1271770448208914</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -5026,10 +5026,10 @@
         <v>0.3250439347719394</v>
       </c>
       <c r="D219" t="n">
-        <v>0.3843143284320831</v>
+        <v>0.2589859366416931</v>
       </c>
       <c r="E219" t="n">
-        <v>0.3726030684331623</v>
+        <v>0.3308269378363657</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
@@ -5046,10 +5046,10 @@
         <v>0.1682233588921065</v>
       </c>
       <c r="D220" t="n">
-        <v>0.007354126777499914</v>
+        <v>0.09908971935510635</v>
       </c>
       <c r="E220" t="n">
-        <v>0.1217999719369069</v>
+        <v>0.152378502796109</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
@@ -5066,10 +5066,10 @@
         <v>0.2482800606555355</v>
       </c>
       <c r="D221" t="n">
-        <v>0.002156462054699659</v>
+        <v>0.1110203266143799</v>
       </c>
       <c r="E221" t="n">
-        <v>0.1771424137211811</v>
+        <v>0.2134303685744079</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
@@ -5086,10 +5086,10 @@
         <v>0.373767189956124</v>
       </c>
       <c r="D222" t="n">
-        <v>0.6610747575759888</v>
+        <v>0.4636591970920563</v>
       </c>
       <c r="E222" t="n">
-        <v>0.499402527214184</v>
+        <v>0.4335973403862066</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
@@ -5106,10 +5106,10 @@
         <v>0.1261725959023785</v>
       </c>
       <c r="D223" t="n">
-        <v>0.02837597206234932</v>
+        <v>0.1068502441048622</v>
       </c>
       <c r="E223" t="n">
-        <v>0.1084042105110338</v>
+        <v>0.1345623011918715</v>
       </c>
       <c r="F223" t="n">
         <v>0</v>
@@ -5123,13 +5123,13 @@
         <v>0.3735534658901575</v>
       </c>
       <c r="C224" t="n">
-        <v>0.2819243124247554</v>
+        <v>0.2819243124247555</v>
       </c>
       <c r="D224" t="n">
-        <v>0.8099119067192078</v>
+        <v>0.6121805906295776</v>
       </c>
       <c r="E224" t="n">
-        <v>0.4884632283447068</v>
+        <v>0.4225527896481635</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
@@ -5143,13 +5143,13 @@
         <v>0.4137265016073279</v>
       </c>
       <c r="C225" t="n">
-        <v>0.3678176128793122</v>
+        <v>0.3678176128793121</v>
       </c>
       <c r="D225" t="n">
-        <v>0.3989344239234924</v>
+        <v>0.3718783259391785</v>
       </c>
       <c r="E225" t="n">
-        <v>0.3934928461367108</v>
+        <v>0.3844741468086061</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
@@ -5166,10 +5166,10 @@
         <v>0.3846254505714859</v>
       </c>
       <c r="D226" t="n">
-        <v>0.7150325775146484</v>
+        <v>0.5614699125289917</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5071130278899054</v>
+        <v>0.4559254728946865</v>
       </c>
       <c r="F226" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0.3591292818176218</v>
       </c>
       <c r="D227" t="n">
-        <v>0.2644297480583191</v>
+        <v>0.501554548740387</v>
       </c>
       <c r="E227" t="n">
-        <v>0.3440223792109502</v>
+        <v>0.4230639794383061</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -5206,10 +5206,10 @@
         <v>0.2036246066488215</v>
       </c>
       <c r="D228" t="n">
-        <v>0.007328466977924109</v>
+        <v>0.08352251350879669</v>
       </c>
       <c r="E228" t="n">
-        <v>0.1533919660448017</v>
+        <v>0.1787899815550925</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
@@ -5223,13 +5223,13 @@
         <v>0.1681823414656075</v>
       </c>
       <c r="C229" t="n">
-        <v>0.1648734010380796</v>
+        <v>0.1648734010380797</v>
       </c>
       <c r="D229" t="n">
-        <v>9.369522740598768e-05</v>
+        <v>0.01693537645041943</v>
       </c>
       <c r="E229" t="n">
-        <v>0.1110498125770311</v>
+        <v>0.1166637063180355</v>
       </c>
       <c r="F229" t="n">
         <v>0</v>
@@ -5246,10 +5246,10 @@
         <v>0.4161244868753172</v>
       </c>
       <c r="D230" t="n">
-        <v>0.8038098216056824</v>
+        <v>0.6130242347717285</v>
       </c>
       <c r="E230" t="n">
-        <v>0.6128624401844964</v>
+        <v>0.5492672445731784</v>
       </c>
       <c r="F230" t="n">
         <v>1</v>
@@ -5266,10 +5266,10 @@
         <v>0.3235275812482772</v>
       </c>
       <c r="D231" t="n">
-        <v>0.561307966709137</v>
+        <v>0.5047569274902344</v>
       </c>
       <c r="E231" t="n">
-        <v>0.421152897530887</v>
+        <v>0.4023025511245861</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
@@ -5286,10 +5286,10 @@
         <v>0.2994786747738144</v>
       </c>
       <c r="D232" t="n">
-        <v>0.6077280044555664</v>
+        <v>0.3912168145179749</v>
       </c>
       <c r="E232" t="n">
-        <v>0.4125354459735302</v>
+        <v>0.3403650493276664</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
@@ -5306,10 +5306,10 @@
         <v>0.4990505806971714</v>
       </c>
       <c r="D233" t="n">
-        <v>0.8981500864028931</v>
+        <v>0.7000892758369446</v>
       </c>
       <c r="E233" t="n">
-        <v>0.7105914437698964</v>
+        <v>0.6445711735812469</v>
       </c>
       <c r="F233" t="n">
         <v>1</v>
@@ -5326,10 +5326,10 @@
         <v>0.2264685587260181</v>
       </c>
       <c r="D234" t="n">
-        <v>0.0003715945058502257</v>
+        <v>0.05792875215411186</v>
       </c>
       <c r="E234" t="n">
-        <v>0.1596392092229708</v>
+        <v>0.178824928439058</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0.1516911561738614</v>
       </c>
       <c r="D235" t="n">
-        <v>0.007843248546123505</v>
+        <v>0.1038642749190331</v>
       </c>
       <c r="E235" t="n">
-        <v>0.1265352870214375</v>
+        <v>0.1585422958124073</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -5363,13 +5363,13 @@
         <v>0.2970185547964772</v>
       </c>
       <c r="C236" t="n">
-        <v>0.1909047351971768</v>
+        <v>0.1909047351971769</v>
       </c>
       <c r="D236" t="n">
-        <v>0.01474622450768948</v>
+        <v>0.162515789270401</v>
       </c>
       <c r="E236" t="n">
-        <v>0.1675565048337812</v>
+        <v>0.2168130264213517</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -5386,10 +5386,10 @@
         <v>0.1981556837950725</v>
       </c>
       <c r="D237" t="n">
-        <v>0.006969102658331394</v>
+        <v>0.05560210347175598</v>
       </c>
       <c r="E237" t="n">
-        <v>0.156989485681614</v>
+        <v>0.1732004859527555</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
@@ -5406,10 +5406,10 @@
         <v>0.1778260335415142</v>
       </c>
       <c r="D238" t="n">
-        <v>0.003339972347021103</v>
+        <v>0.05163391679525375</v>
       </c>
       <c r="E238" t="n">
-        <v>0.1364317094648379</v>
+        <v>0.1525296909475821</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -5426,10 +5426,10 @@
         <v>0.1873435289918541</v>
       </c>
       <c r="D239" t="n">
-        <v>0.004050787072628736</v>
+        <v>0.1387980878353119</v>
       </c>
       <c r="E239" t="n">
-        <v>0.1419700593304642</v>
+        <v>0.1868858262513585</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -5446,10 +5446,10 @@
         <v>0.3395414982170507</v>
       </c>
       <c r="D240" t="n">
-        <v>0.03872617706656456</v>
+        <v>0.2400450706481934</v>
       </c>
       <c r="E240" t="n">
-        <v>0.2797103002418435</v>
+        <v>0.3468165981023865</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -5466,10 +5466,10 @@
         <v>0.2222254044849644</v>
       </c>
       <c r="D241" t="n">
-        <v>0.06753431260585785</v>
+        <v>0.2487552613019943</v>
       </c>
       <c r="E241" t="n">
-        <v>0.1977302854699589</v>
+        <v>0.258137268368671</v>
       </c>
       <c r="F241" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0.200449741286107</v>
       </c>
       <c r="D242" t="n">
-        <v>0.08873680979013443</v>
+        <v>0.2566614747047424</v>
       </c>
       <c r="E242" t="n">
-        <v>0.1879497569327616</v>
+        <v>0.243924645237631</v>
       </c>
       <c r="F242" t="n">
         <v>0</v>
@@ -5506,10 +5506,10 @@
         <v>0.1912181260769634</v>
       </c>
       <c r="D243" t="n">
-        <v>0.01154619175940752</v>
+        <v>0.1472311764955521</v>
       </c>
       <c r="E243" t="n">
-        <v>0.1585621950678101</v>
+        <v>0.2037905233131916</v>
       </c>
       <c r="F243" t="n">
         <v>0</v>
@@ -5526,10 +5526,10 @@
         <v>0.186696717570394</v>
       </c>
       <c r="D244" t="n">
-        <v>0.003715720493346453</v>
+        <v>0.1151327267289162</v>
       </c>
       <c r="E244" t="n">
-        <v>0.1649618830795504</v>
+        <v>0.2021008851580736</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
@@ -5546,10 +5546,10 @@
         <v>0.1639942596504271</v>
       </c>
       <c r="D245" t="n">
-        <v>0.009240282699465752</v>
+        <v>0.1046374291181564</v>
       </c>
       <c r="E245" t="n">
-        <v>0.1227792542873432</v>
+        <v>0.1545783030935734</v>
       </c>
       <c r="F245" t="n">
         <v>0</v>
@@ -5566,10 +5566,10 @@
         <v>0.1611153175351719</v>
       </c>
       <c r="D246" t="n">
-        <v>0.0006370523478835821</v>
+        <v>0.04836058616638184</v>
       </c>
       <c r="E246" t="n">
-        <v>0.1355090799650664</v>
+        <v>0.1514169245712325</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
@@ -5586,10 +5586,10 @@
         <v>0.1262667783113349</v>
       </c>
       <c r="D247" t="n">
-        <v>0.02108827978372574</v>
+        <v>0.1414310783147812</v>
       </c>
       <c r="E247" t="n">
-        <v>0.1036918384210289</v>
+        <v>0.1438061045980474</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0.1585615125826117</v>
       </c>
       <c r="D248" t="n">
-        <v>0.0004938862402923405</v>
+        <v>0.03426948189735413</v>
       </c>
       <c r="E248" t="n">
-        <v>0.1247876180773861</v>
+        <v>0.1360461499630734</v>
       </c>
       <c r="F248" t="n">
         <v>0</v>
@@ -5626,10 +5626,10 @@
         <v>0.2011124846606545</v>
       </c>
       <c r="D249" t="n">
-        <v>0.0003034737310372293</v>
+        <v>0.04361986741423607</v>
       </c>
       <c r="E249" t="n">
-        <v>0.1657004541088666</v>
+        <v>0.1801392520032662</v>
       </c>
       <c r="F249" t="n">
         <v>0</v>
@@ -5646,10 +5646,10 @@
         <v>0.1806149396947223</v>
       </c>
       <c r="D250" t="n">
-        <v>0.00136008660774678</v>
+        <v>0.0889870896935463</v>
       </c>
       <c r="E250" t="n">
-        <v>0.142814952060862</v>
+        <v>0.1720239530894619</v>
       </c>
       <c r="F250" t="n">
         <v>0</v>
@@ -5663,13 +5663,13 @@
         <v>0.2792796919928957</v>
       </c>
       <c r="C251" t="n">
-        <v>0.2611231350126408</v>
+        <v>0.2611231350126407</v>
       </c>
       <c r="D251" t="n">
-        <v>0.02034502848982811</v>
+        <v>0.09601052105426788</v>
       </c>
       <c r="E251" t="n">
-        <v>0.1869159518317882</v>
+        <v>0.2121377826866014</v>
       </c>
       <c r="F251" t="n">
         <v>0</v>
@@ -5686,10 +5686,10 @@
         <v>0.1865138317694516</v>
       </c>
       <c r="D252" t="n">
-        <v>0.009187973104417324</v>
+        <v>0.09980233013629913</v>
       </c>
       <c r="E252" t="n">
-        <v>0.1692382938361669</v>
+        <v>0.1994430795134608</v>
       </c>
       <c r="F252" t="n">
         <v>0</v>
@@ -5706,10 +5706,10 @@
         <v>0.1920183397833584</v>
       </c>
       <c r="D253" t="n">
-        <v>0.5520892143249512</v>
+        <v>0.4326109290122986</v>
       </c>
       <c r="E253" t="n">
-        <v>0.3419645405317024</v>
+        <v>0.3021384454274849</v>
       </c>
       <c r="F253" t="n">
         <v>0</v>
@@ -5726,10 +5726,10 @@
         <v>0.2805390912298826</v>
       </c>
       <c r="D254" t="n">
-        <v>0.3322289884090424</v>
+        <v>0.4095797538757324</v>
       </c>
       <c r="E254" t="n">
-        <v>0.3478288866528785</v>
+        <v>0.3736124751417751</v>
       </c>
       <c r="F254" t="n">
         <v>0</v>
@@ -5743,13 +5743,13 @@
         <v>0.2725856581182082</v>
       </c>
       <c r="C255" t="n">
-        <v>0.2502262604231768</v>
+        <v>0.2502262604231769</v>
       </c>
       <c r="D255" t="n">
-        <v>0.01072320900857449</v>
+        <v>0.1455259472131729</v>
       </c>
       <c r="E255" t="n">
-        <v>0.1778450425166531</v>
+        <v>0.2227792885848527</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -5766,10 +5766,10 @@
         <v>0.390845594733193</v>
       </c>
       <c r="D256" t="n">
-        <v>0.4711893200874329</v>
+        <v>0.378104031085968</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4243260350645474</v>
+        <v>0.3932976053973924</v>
       </c>
       <c r="F256" t="n">
         <v>0</v>
@@ -5786,10 +5786,10 @@
         <v>0.175026102636015</v>
       </c>
       <c r="D257" t="n">
-        <v>0.001164573943242431</v>
+        <v>0.04588595032691956</v>
       </c>
       <c r="E257" t="n">
-        <v>0.1241637095150436</v>
+        <v>0.1390708349762693</v>
       </c>
       <c r="F257" t="n">
         <v>0</v>
@@ -5806,10 +5806,10 @@
         <v>0.4088206154703263</v>
       </c>
       <c r="D258" t="n">
-        <v>0.6299753189086914</v>
+        <v>0.5443600416183472</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5470427862866907</v>
+        <v>0.5185043605232426</v>
       </c>
       <c r="F258" t="n">
         <v>0</v>
@@ -5826,10 +5826,10 @@
         <v>0.1572447750368471</v>
       </c>
       <c r="D259" t="n">
-        <v>0.007263834588229656</v>
+        <v>0.08096903562545776</v>
       </c>
       <c r="E259" t="n">
-        <v>0.1077645122424729</v>
+        <v>0.1323329125882156</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
@@ -5846,10 +5846,10 @@
         <v>0.1750358055755912</v>
       </c>
       <c r="D260" t="n">
-        <v>0.002504072617739439</v>
+        <v>0.08805513381958008</v>
       </c>
       <c r="E260" t="n">
-        <v>0.1581260011045285</v>
+        <v>0.186643021505142</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
@@ -5866,10 +5866,10 @@
         <v>0.3073905915730032</v>
       </c>
       <c r="D261" t="n">
-        <v>0.6006551384925842</v>
+        <v>0.3155582845211029</v>
       </c>
       <c r="E261" t="n">
-        <v>0.4323754294655997</v>
+        <v>0.3373431448084392</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
@@ -5886,10 +5886,10 @@
         <v>0.348265197130379</v>
       </c>
       <c r="D262" t="n">
-        <v>0.7362231612205505</v>
+        <v>0.5278986692428589</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5210942407036608</v>
+        <v>0.4516527433777636</v>
       </c>
       <c r="F262" t="n">
         <v>0</v>
@@ -5906,10 +5906,10 @@
         <v>0.2504449997864151</v>
       </c>
       <c r="D263" t="n">
-        <v>0.001459901919588447</v>
+        <v>0.0285553690046072</v>
       </c>
       <c r="E263" t="n">
-        <v>0.1858823261550921</v>
+        <v>0.1949141485167651</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
@@ -5926,10 +5926,10 @@
         <v>0.2487859847002488</v>
       </c>
       <c r="D264" t="n">
-        <v>0.03673926740884781</v>
+        <v>0.1612711250782013</v>
       </c>
       <c r="E264" t="n">
-        <v>0.2050298029519344</v>
+        <v>0.2465404221750523</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0.2684587172965865</v>
       </c>
       <c r="C265" t="n">
-        <v>0.245107876141323</v>
+        <v>0.2451078761413231</v>
       </c>
       <c r="D265" t="n">
-        <v>0.2528724074363708</v>
+        <v>0.211183100938797</v>
       </c>
       <c r="E265" t="n">
-        <v>0.2554796669580934</v>
+        <v>0.2415832314589022</v>
       </c>
       <c r="F265" t="n">
         <v>0</v>
@@ -5966,10 +5966,10 @@
         <v>0.1913112978050115</v>
       </c>
       <c r="D266" t="n">
-        <v>0.01344284601509571</v>
+        <v>0.1292595416307449</v>
       </c>
       <c r="E266" t="n">
-        <v>0.1231637189567831</v>
+        <v>0.1617692841619995</v>
       </c>
       <c r="F266" t="n">
         <v>0</v>
@@ -5986,10 +5986,10 @@
         <v>0.4767168787500561</v>
       </c>
       <c r="D267" t="n">
-        <v>0.9331678152084351</v>
+        <v>0.7419112920761108</v>
       </c>
       <c r="E267" t="n">
-        <v>0.7023100903460392</v>
+        <v>0.6385579159685978</v>
       </c>
       <c r="F267" t="n">
         <v>1</v>
@@ -6006,10 +6006,10 @@
         <v>0.1485705963770307</v>
       </c>
       <c r="D268" t="n">
-        <v>0.005845656152814627</v>
+        <v>0.06962984055280685</v>
       </c>
       <c r="E268" t="n">
-        <v>0.1126355453542035</v>
+        <v>0.1338969401542009</v>
       </c>
       <c r="F268" t="n">
         <v>0</v>
@@ -6026,10 +6026,10 @@
         <v>0.1601275692817329</v>
       </c>
       <c r="D269" t="n">
-        <v>0.02911767736077309</v>
+        <v>0.1394544541835785</v>
       </c>
       <c r="E269" t="n">
-        <v>0.1364970165955175</v>
+        <v>0.1732759422031193</v>
       </c>
       <c r="F269" t="n">
         <v>0</v>
@@ -6043,13 +6043,13 @@
         <v>0.2955514954491868</v>
       </c>
       <c r="C270" t="n">
-        <v>0.2502690299836346</v>
+        <v>0.2502690299836345</v>
       </c>
       <c r="D270" t="n">
-        <v>0.1064830794930458</v>
+        <v>0.1999837905168533</v>
       </c>
       <c r="E270" t="n">
-        <v>0.2174345349752891</v>
+        <v>0.2486014386498916</v>
       </c>
       <c r="F270" t="n">
         <v>0</v>
@@ -6066,10 +6066,10 @@
         <v>0.1386278460007433</v>
       </c>
       <c r="D271" t="n">
-        <v>0.001734850229695439</v>
+        <v>0.09986397624015808</v>
       </c>
       <c r="E271" t="n">
-        <v>0.09213086629191425</v>
+        <v>0.1248405749620685</v>
       </c>
       <c r="F271" t="n">
         <v>0</v>
@@ -6083,16 +6083,16 @@
         <v>0.5160561299461985</v>
       </c>
       <c r="C272" t="n">
-        <v>0.4528366273550077</v>
+        <v>0.4528366273550076</v>
       </c>
       <c r="D272" t="n">
-        <v>0.7470617294311523</v>
+        <v>0.6125861406326294</v>
       </c>
       <c r="E272" t="n">
-        <v>0.5719848289107862</v>
+        <v>0.5271596326446119</v>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -6106,10 +6106,10 @@
         <v>0.1026299458137512</v>
       </c>
       <c r="D273" t="n">
-        <v>0.0007317227427847683</v>
+        <v>0.05208935588598251</v>
       </c>
       <c r="E273" t="n">
-        <v>0.0752455625760925</v>
+        <v>0.09236477362382507</v>
       </c>
       <c r="F273" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0.1961761291495085</v>
       </c>
       <c r="D274" t="n">
-        <v>0.007599769625812769</v>
+        <v>0.1194621324539185</v>
       </c>
       <c r="E274" t="n">
-        <v>0.1503744795207108</v>
+        <v>0.187661933796746</v>
       </c>
       <c r="F274" t="n">
         <v>0</v>
@@ -6146,10 +6146,10 @@
         <v>0.1702911462513545</v>
       </c>
       <c r="D275" t="n">
-        <v>0.02939063683152199</v>
+        <v>0.12990902364254</v>
       </c>
       <c r="E275" t="n">
-        <v>0.1515651831278765</v>
+        <v>0.1850713120648824</v>
       </c>
       <c r="F275" t="n">
         <v>0</v>
@@ -6166,10 +6166,10 @@
         <v>0.1655900415348071</v>
       </c>
       <c r="D276" t="n">
-        <v>0.0534062571823597</v>
+        <v>0.1451865881681442</v>
       </c>
       <c r="E276" t="n">
-        <v>0.1469747547207587</v>
+        <v>0.1775681983826869</v>
       </c>
       <c r="F276" t="n">
         <v>0</v>
@@ -6186,10 +6186,10 @@
         <v>0.1391266762847933</v>
       </c>
       <c r="D277" t="n">
-        <v>0.0001541202655062079</v>
+        <v>0.04701051115989685</v>
       </c>
       <c r="E277" t="n">
-        <v>0.09356937714524512</v>
+        <v>0.109188174110042</v>
       </c>
       <c r="F277" t="n">
         <v>0</v>
@@ -6206,10 +6206,10 @@
         <v>0.1867271243655948</v>
       </c>
       <c r="D278" t="n">
-        <v>0.03635748848319054</v>
+        <v>0.1101667881011963</v>
       </c>
       <c r="E278" t="n">
-        <v>0.1537658371545396</v>
+        <v>0.1783689370272082</v>
       </c>
       <c r="F278" t="n">
         <v>0</v>
@@ -6226,10 +6226,10 @@
         <v>0.1873945171855534</v>
       </c>
       <c r="D279" t="n">
-        <v>0.009842800907790661</v>
+        <v>0.0774826854467392</v>
       </c>
       <c r="E279" t="n">
-        <v>0.1567707897218575</v>
+        <v>0.179317417901507</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
@@ -6246,10 +6246,10 @@
         <v>0.1714025339107549</v>
       </c>
       <c r="D280" t="n">
-        <v>0.0009422712028026581</v>
+        <v>0.03152411431074142</v>
       </c>
       <c r="E280" t="n">
-        <v>0.113429002462621</v>
+        <v>0.1236229501652673</v>
       </c>
       <c r="F280" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0.1779010965527104</v>
       </c>
       <c r="D281" t="n">
-        <v>0.08394143730401993</v>
+        <v>0.2152561694383621</v>
       </c>
       <c r="E281" t="n">
-        <v>0.1630298678249045</v>
+        <v>0.2068014452030186</v>
       </c>
       <c r="F281" t="n">
         <v>0</v>
@@ -6286,10 +6286,10 @@
         <v>0.3903902560229622</v>
       </c>
       <c r="D282" t="n">
-        <v>0.6036926507949829</v>
+        <v>0.5272260308265686</v>
       </c>
       <c r="E282" t="n">
-        <v>0.5328809484813082</v>
+        <v>0.5073920751585034</v>
       </c>
       <c r="F282" t="n">
         <v>0</v>
@@ -6303,13 +6303,13 @@
         <v>0.550476105170383</v>
       </c>
       <c r="C283" t="n">
-        <v>0.3574356327946342</v>
+        <v>0.3574356327946343</v>
       </c>
       <c r="D283" t="n">
-        <v>0.4954567849636078</v>
+        <v>0.542230486869812</v>
       </c>
       <c r="E283" t="n">
-        <v>0.467789507642875</v>
+        <v>0.4833807416116098</v>
       </c>
       <c r="F283" t="n">
         <v>0</v>
@@ -6326,13 +6326,13 @@
         <v>0.4490935707747755</v>
       </c>
       <c r="D284" t="n">
-        <v>0.4335697293281555</v>
+        <v>0.4620886743068695</v>
       </c>
       <c r="E284" t="n">
-        <v>0.546492995506915</v>
+        <v>0.5559993104998197</v>
       </c>
       <c r="F284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -6346,10 +6346,10 @@
         <v>0.2380236721138009</v>
       </c>
       <c r="D285" t="n">
-        <v>0.0103455139324069</v>
+        <v>0.1098784953355789</v>
       </c>
       <c r="E285" t="n">
-        <v>0.201388804976003</v>
+        <v>0.234566465443727</v>
       </c>
       <c r="F285" t="n">
         <v>0</v>
@@ -6363,13 +6363,13 @@
         <v>0.3478880425307024</v>
       </c>
       <c r="C286" t="n">
-        <v>0.2593752177619165</v>
+        <v>0.2593752177619166</v>
       </c>
       <c r="D286" t="n">
-        <v>0.0181169044226408</v>
+        <v>0.06956682354211807</v>
       </c>
       <c r="E286" t="n">
-        <v>0.2084600549050866</v>
+        <v>0.2256100279449123</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
@@ -6386,10 +6386,10 @@
         <v>0.4315749329320095</v>
       </c>
       <c r="D287" t="n">
-        <v>0.9490795135498047</v>
+        <v>0.6829118728637695</v>
       </c>
       <c r="E287" t="n">
-        <v>0.6704829015442253</v>
+        <v>0.5817603546488802</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
@@ -6403,13 +6403,13 @@
         <v>0.1444448890072123</v>
       </c>
       <c r="C288" t="n">
-        <v>0.1598507118839609</v>
+        <v>0.159850711883961</v>
       </c>
       <c r="D288" t="n">
-        <v>0.003827119711786509</v>
+        <v>0.08981315791606903</v>
       </c>
       <c r="E288" t="n">
-        <v>0.1027075735343199</v>
+        <v>0.1313695862690808</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
@@ -6426,10 +6426,10 @@
         <v>0.2106448104099659</v>
       </c>
       <c r="D289" t="n">
-        <v>0.000674943788908422</v>
+        <v>0.05838083103299141</v>
       </c>
       <c r="E289" t="n">
-        <v>0.1684746946305471</v>
+        <v>0.1877099903785747</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
@@ -6446,10 +6446,10 @@
         <v>0.29810412999737</v>
       </c>
       <c r="D290" t="n">
-        <v>0.5506076812744141</v>
+        <v>0.4800501763820648</v>
       </c>
       <c r="E290" t="n">
-        <v>0.3880533225338458</v>
+        <v>0.3645341542363961</v>
       </c>
       <c r="F290" t="n">
         <v>0</v>
@@ -6466,10 +6466,10 @@
         <v>0.1278534693806734</v>
       </c>
       <c r="D291" t="n">
-        <v>0.0001998046354856342</v>
+        <v>0.03030192293226719</v>
       </c>
       <c r="E291" t="n">
-        <v>0.09060646544521138</v>
+        <v>0.1006405048774719</v>
       </c>
       <c r="F291" t="n">
         <v>0</v>
@@ -6486,10 +6486,10 @@
         <v>0.1689148276301773</v>
       </c>
       <c r="D292" t="n">
-        <v>0.0006467222119681537</v>
+        <v>0.04083758592605591</v>
       </c>
       <c r="E292" t="n">
-        <v>0.1344566514051142</v>
+        <v>0.1478536059764768</v>
       </c>
       <c r="F292" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0.1748389942594712</v>
       </c>
       <c r="D293" t="n">
-        <v>0.07091544568538666</v>
+        <v>0.13362917304039</v>
       </c>
       <c r="E293" t="n">
-        <v>0.1461527172466706</v>
+        <v>0.1670572930316717</v>
       </c>
       <c r="F293" t="n">
         <v>0</v>
@@ -6526,10 +6526,10 @@
         <v>0.529715019254259</v>
       </c>
       <c r="D294" t="n">
-        <v>0.9290617704391479</v>
+        <v>0.706206202507019</v>
       </c>
       <c r="E294" t="n">
-        <v>0.7168051040155866</v>
+        <v>0.6425199147048769</v>
       </c>
       <c r="F294" t="n">
         <v>1</v>
@@ -6546,10 +6546,10 @@
         <v>0.153782093213373</v>
       </c>
       <c r="D295" t="n">
-        <v>0.005749867297708988</v>
+        <v>0.1233995780348778</v>
       </c>
       <c r="E295" t="n">
-        <v>0.1090560345645784</v>
+        <v>0.1482726048103013</v>
       </c>
       <c r="F295" t="n">
         <v>0</v>
@@ -6566,10 +6566,10 @@
         <v>0.2003185159287818</v>
       </c>
       <c r="D296" t="n">
-        <v>0.01781269907951355</v>
+        <v>0.1151161566376686</v>
       </c>
       <c r="E296" t="n">
-        <v>0.1620087020837368</v>
+        <v>0.1944431879364551</v>
       </c>
       <c r="F296" t="n">
         <v>0</v>
@@ -6586,10 +6586,10 @@
         <v>0.1328378555273835</v>
       </c>
       <c r="D297" t="n">
-        <v>0.01123248040676117</v>
+        <v>0.09207123517990112</v>
       </c>
       <c r="E297" t="n">
-        <v>0.09162203150508312</v>
+        <v>0.1185682830961298</v>
       </c>
       <c r="F297" t="n">
         <v>0</v>
@@ -6606,10 +6606,10 @@
         <v>0.152367616981154</v>
       </c>
       <c r="D298" t="n">
-        <v>0.009567131288349628</v>
+        <v>0.07954393327236176</v>
       </c>
       <c r="E298" t="n">
-        <v>0.1035731627815098</v>
+        <v>0.1268987634428471</v>
       </c>
       <c r="F298" t="n">
         <v>0</v>
@@ -6626,10 +6626,10 @@
         <v>0.1561182812334015</v>
       </c>
       <c r="D299" t="n">
-        <v>0.02235047891736031</v>
+        <v>0.1781473755836487</v>
       </c>
       <c r="E299" t="n">
-        <v>0.1053437658197755</v>
+        <v>0.1572760647085383</v>
       </c>
       <c r="F299" t="n">
         <v>0</v>
@@ -6646,10 +6646,10 @@
         <v>0.1221284937013063</v>
       </c>
       <c r="D300" t="n">
-        <v>0.00122591876424849</v>
+        <v>0.04395821690559387</v>
       </c>
       <c r="E300" t="n">
-        <v>0.07781874305942736</v>
+        <v>0.09206284243987582</v>
       </c>
       <c r="F300" t="n">
         <v>0</v>
@@ -6666,10 +6666,10 @@
         <v>0.4459142746254918</v>
       </c>
       <c r="D301" t="n">
-        <v>0.5532085299491882</v>
+        <v>0.4878115057945251</v>
       </c>
       <c r="E301" t="n">
-        <v>0.5337175249629605</v>
+        <v>0.5119185169114062</v>
       </c>
       <c r="F301" t="n">
         <v>0</v>
@@ -6686,10 +6686,10 @@
         <v>0.1967689619748836</v>
       </c>
       <c r="D302" t="n">
-        <v>0.006284228526055813</v>
+        <v>0.07000289857387543</v>
       </c>
       <c r="E302" t="n">
-        <v>0.1407618307418419</v>
+        <v>0.1620013874244484</v>
       </c>
       <c r="F302" t="n">
         <v>0</v>
@@ -6706,10 +6706,10 @@
         <v>0.2268953908848247</v>
       </c>
       <c r="D303" t="n">
-        <v>0.1429446488618851</v>
+        <v>0.2223438024520874</v>
       </c>
       <c r="E303" t="n">
-        <v>0.2354296903099835</v>
+        <v>0.261896074840051</v>
       </c>
       <c r="F303" t="n">
         <v>0</v>
@@ -6723,13 +6723,13 @@
         <v>0.5030306303959471</v>
       </c>
       <c r="C304" t="n">
-        <v>0.387546198657211</v>
+        <v>0.3875461986572109</v>
       </c>
       <c r="D304" t="n">
-        <v>0.2978194057941437</v>
+        <v>0.3270591795444489</v>
       </c>
       <c r="E304" t="n">
-        <v>0.3961320782824339</v>
+        <v>0.4058786695325356</v>
       </c>
       <c r="F304" t="n">
         <v>0</v>
@@ -6746,10 +6746,10 @@
         <v>0.3298059032701908</v>
       </c>
       <c r="D305" t="n">
-        <v>0.5368747711181641</v>
+        <v>0.4231812953948975</v>
       </c>
       <c r="E305" t="n">
-        <v>0.4593447329737743</v>
+        <v>0.4214469077326854</v>
       </c>
       <c r="F305" t="n">
         <v>0</v>
@@ -6766,10 +6766,10 @@
         <v>0.1390007768131399</v>
       </c>
       <c r="D306" t="n">
-        <v>0.02275156788527966</v>
+        <v>0.1325931251049042</v>
       </c>
       <c r="E306" t="n">
-        <v>0.1121453591059313</v>
+        <v>0.1487592115124728</v>
       </c>
       <c r="F306" t="n">
         <v>0</v>
@@ -6786,10 +6786,10 @@
         <v>0.2811656234643407</v>
       </c>
       <c r="D307" t="n">
-        <v>0.1310698091983795</v>
+        <v>0.325047641992569</v>
       </c>
       <c r="E307" t="n">
-        <v>0.2225495239773277</v>
+        <v>0.2872088015753909</v>
       </c>
       <c r="F307" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0.163399945556621</v>
       </c>
       <c r="D308" t="n">
-        <v>0.03269189596176147</v>
+        <v>0.1907561719417572</v>
       </c>
       <c r="E308" t="n">
-        <v>0.1263315473084744</v>
+        <v>0.1790196393018063</v>
       </c>
       <c r="F308" t="n">
         <v>0</v>
@@ -6826,10 +6826,10 @@
         <v>0.2079452509647242</v>
       </c>
       <c r="D309" t="n">
-        <v>0.02295833453536034</v>
+        <v>0.1294256001710892</v>
       </c>
       <c r="E309" t="n">
-        <v>0.1637210141179282</v>
+        <v>0.1992101026631711</v>
       </c>
       <c r="F309" t="n">
         <v>0</v>
@@ -6846,10 +6846,10 @@
         <v>0.1504283477011669</v>
       </c>
       <c r="D310" t="n">
-        <v>0.02550317347049713</v>
+        <v>0.1050618514418602</v>
       </c>
       <c r="E310" t="n">
-        <v>0.1285588393286422</v>
+        <v>0.1550783986524299</v>
       </c>
       <c r="F310" t="n">
         <v>0</v>
@@ -6866,10 +6866,10 @@
         <v>0.1958254314160678</v>
       </c>
       <c r="D311" t="n">
-        <v>0.002740442054346204</v>
+        <v>0.09295562654733658</v>
       </c>
       <c r="E311" t="n">
-        <v>0.1372493238060205</v>
+        <v>0.1673210519703507</v>
       </c>
       <c r="F311" t="n">
         <v>0</v>
@@ -6886,10 +6886,10 @@
         <v>0.1856010182455337</v>
       </c>
       <c r="D312" t="n">
-        <v>0.009317364543676376</v>
+        <v>0.1582192480564117</v>
       </c>
       <c r="E312" t="n">
-        <v>0.1635107752600504</v>
+        <v>0.2131447364309622</v>
       </c>
       <c r="F312" t="n">
         <v>0</v>
@@ -6906,10 +6906,10 @@
         <v>0.1738268190782112</v>
       </c>
       <c r="D313" t="n">
-        <v>0.005068528465926647</v>
+        <v>0.09699518978595734</v>
       </c>
       <c r="E313" t="n">
-        <v>0.12668665134498</v>
+        <v>0.1573288717849902</v>
       </c>
       <c r="F313" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0.2111425882075779</v>
       </c>
       <c r="D314" t="n">
-        <v>0.05186793208122253</v>
+        <v>0.2109585106372833</v>
       </c>
       <c r="E314" t="n">
-        <v>0.1708993793285989</v>
+        <v>0.2239295721806192</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
@@ -6946,10 +6946,10 @@
         <v>0.360788607596815</v>
       </c>
       <c r="D315" t="n">
-        <v>0.3988410234451294</v>
+        <v>0.4266579747200012</v>
       </c>
       <c r="E315" t="n">
-        <v>0.4190603456573268</v>
+        <v>0.4283326627489508</v>
       </c>
       <c r="F315" t="n">
         <v>0</v>
@@ -6966,10 +6966,10 @@
         <v>0.4406345163130966</v>
       </c>
       <c r="D316" t="n">
-        <v>0.5868356823921204</v>
+        <v>0.4394354820251465</v>
       </c>
       <c r="E316" t="n">
-        <v>0.5554767164508934</v>
+        <v>0.5063433163285688</v>
       </c>
       <c r="F316" t="n">
         <v>0</v>
@@ -6983,13 +6983,13 @@
         <v>0.2097969378868546</v>
       </c>
       <c r="C317" t="n">
-        <v>0.256114922641103</v>
+        <v>0.2561149226411029</v>
       </c>
       <c r="D317" t="n">
-        <v>0.07382340729236603</v>
+        <v>0.3014366626739502</v>
       </c>
       <c r="E317" t="n">
-        <v>0.1799117559401079</v>
+        <v>0.2557828410673026</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
@@ -7006,10 +7006,10 @@
         <v>0.1604986786266021</v>
       </c>
       <c r="D318" t="n">
-        <v>0.008480402640998363</v>
+        <v>0.06137438863515854</v>
       </c>
       <c r="E318" t="n">
-        <v>0.1116983964615661</v>
+        <v>0.1293297251262861</v>
       </c>
       <c r="F318" t="n">
         <v>0</v>
@@ -7026,10 +7026,10 @@
         <v>0.3296289512356696</v>
       </c>
       <c r="D319" t="n">
-        <v>0.7945693731307983</v>
+        <v>0.5925583243370056</v>
       </c>
       <c r="E319" t="n">
-        <v>0.5380960282317976</v>
+        <v>0.4707590119672</v>
       </c>
       <c r="F319" t="n">
         <v>0</v>
@@ -7046,10 +7046,10 @@
         <v>0.252909947726533</v>
       </c>
       <c r="D320" t="n">
-        <v>0.009557528421282768</v>
+        <v>0.1898601949214935</v>
       </c>
       <c r="E320" t="n">
-        <v>0.1928819819361805</v>
+        <v>0.2529828707695841</v>
       </c>
       <c r="F320" t="n">
         <v>0</v>
@@ -7063,13 +7063,13 @@
         <v>0.4132458347103894</v>
       </c>
       <c r="C321" t="n">
-        <v>0.2845608243306739</v>
+        <v>0.2845608243306738</v>
       </c>
       <c r="D321" t="n">
-        <v>0.0640675351023674</v>
+        <v>0.2736613154411316</v>
       </c>
       <c r="E321" t="n">
-        <v>0.2539580647144769</v>
+        <v>0.3238226581607316</v>
       </c>
       <c r="F321" t="n">
         <v>0</v>
@@ -7083,13 +7083,13 @@
         <v>0.4401486978926595</v>
       </c>
       <c r="C322" t="n">
-        <v>0.316743801602133</v>
+        <v>0.3167438016021331</v>
       </c>
       <c r="D322" t="n">
-        <v>0.4297438561916351</v>
+        <v>0.3746398985385895</v>
       </c>
       <c r="E322" t="n">
-        <v>0.3955454518954759</v>
+        <v>0.3771774660111273</v>
       </c>
       <c r="F322" t="n">
         <v>0</v>
@@ -7106,10 +7106,10 @@
         <v>0.1672527111503965</v>
       </c>
       <c r="D323" t="n">
-        <v>5.918590613873675e-05</v>
+        <v>0.01210720278322697</v>
       </c>
       <c r="E323" t="n">
-        <v>0.132717626939644</v>
+        <v>0.13673363256534</v>
       </c>
       <c r="F323" t="n">
         <v>0</v>
@@ -7126,10 +7126,10 @@
         <v>0.2274029563986385</v>
       </c>
       <c r="D324" t="n">
-        <v>0.06475023925304413</v>
+        <v>0.1844043433666229</v>
       </c>
       <c r="E324" t="n">
-        <v>0.2153844890458614</v>
+        <v>0.2552691904170543</v>
       </c>
       <c r="F324" t="n">
         <v>0</v>
@@ -7146,10 +7146,10 @@
         <v>0.1784560160977895</v>
       </c>
       <c r="D325" t="n">
-        <v>0.00132004776969552</v>
+        <v>0.0664193257689476</v>
       </c>
       <c r="E325" t="n">
-        <v>0.1372114985620979</v>
+        <v>0.1589112578951819</v>
       </c>
       <c r="F325" t="n">
         <v>0</v>
@@ -7166,10 +7166,10 @@
         <v>0.3456614133170233</v>
       </c>
       <c r="D326" t="n">
-        <v>0.5201010704040527</v>
+        <v>0.3333438336849213</v>
       </c>
       <c r="E326" t="n">
-        <v>0.4441570698084834</v>
+        <v>0.3819046575687728</v>
       </c>
       <c r="F326" t="n">
         <v>0</v>
@@ -7186,10 +7186,10 @@
         <v>0.1883110964159422</v>
       </c>
       <c r="D327" t="n">
-        <v>0.02260873094201088</v>
+        <v>0.07823233306407928</v>
       </c>
       <c r="E327" t="n">
-        <v>0.1165919668226336</v>
+        <v>0.1351331675299897</v>
       </c>
       <c r="F327" t="n">
         <v>0</v>
@@ -7206,10 +7206,10 @@
         <v>0.1601434475957625</v>
       </c>
       <c r="D328" t="n">
-        <v>0.000683480582665652</v>
+        <v>0.04080060869455338</v>
       </c>
       <c r="E328" t="n">
-        <v>0.1224353716100087</v>
+        <v>0.1358077476473047</v>
       </c>
       <c r="F328" t="n">
         <v>0</v>
@@ -7226,10 +7226,10 @@
         <v>0.3021918347781463</v>
       </c>
       <c r="D329" t="n">
-        <v>0.4126993715763092</v>
+        <v>0.338357150554657</v>
       </c>
       <c r="E329" t="n">
-        <v>0.3700694611170061</v>
+        <v>0.3452887207764553</v>
       </c>
       <c r="F329" t="n">
         <v>0</v>
@@ -7246,10 +7246,10 @@
         <v>0.3074533186148799</v>
       </c>
       <c r="D330" t="n">
-        <v>0.1142477542161942</v>
+        <v>0.1865985095500946</v>
       </c>
       <c r="E330" t="n">
-        <v>0.291671548423947</v>
+        <v>0.3157884668685805</v>
       </c>
       <c r="F330" t="n">
         <v>0</v>
@@ -7266,10 +7266,10 @@
         <v>0.2136383502321311</v>
       </c>
       <c r="D331" t="n">
-        <v>7.844428910175338e-05</v>
+        <v>0.0434545986354351</v>
       </c>
       <c r="E331" t="n">
-        <v>0.1706320951429232</v>
+        <v>0.1850908132583677</v>
       </c>
       <c r="F331" t="n">
         <v>0</v>
@@ -7286,10 +7286,10 @@
         <v>0.1458729905124276</v>
       </c>
       <c r="D332" t="n">
-        <v>0.01936561614274979</v>
+        <v>0.09528191387653351</v>
       </c>
       <c r="E332" t="n">
-        <v>0.1157675438011434</v>
+        <v>0.1410729763790713</v>
       </c>
       <c r="F332" t="n">
         <v>0</v>
@@ -7306,10 +7306,10 @@
         <v>0.1997967681243279</v>
       </c>
       <c r="D333" t="n">
-        <v>0.02484229207038879</v>
+        <v>0.1297634989023209</v>
       </c>
       <c r="E333" t="n">
-        <v>0.1609470337119054</v>
+        <v>0.1959207693225495</v>
       </c>
       <c r="F333" t="n">
         <v>0</v>
@@ -7326,10 +7326,10 @@
         <v>0.1936305639931817</v>
       </c>
       <c r="D334" t="n">
-        <v>0.0006208947743289173</v>
+        <v>0.1105505004525185</v>
       </c>
       <c r="E334" t="n">
-        <v>0.1161848835640959</v>
+        <v>0.1528280854568258</v>
       </c>
       <c r="F334" t="n">
         <v>0</v>
@@ -7346,10 +7346,10 @@
         <v>0.22345007058196</v>
       </c>
       <c r="D335" t="n">
-        <v>0.008851064369082451</v>
+        <v>0.1469366848468781</v>
       </c>
       <c r="E335" t="n">
-        <v>0.1797169046816319</v>
+        <v>0.2257454448408971</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
@@ -7366,10 +7366,10 @@
         <v>0.3080437267160764</v>
       </c>
       <c r="D336" t="n">
-        <v>0.1428109258413315</v>
+        <v>0.1373430788516998</v>
       </c>
       <c r="E336" t="n">
-        <v>0.2956849263044982</v>
+        <v>0.2938623106412876</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>0.1396434426258715</v>
       </c>
       <c r="D337" t="n">
-        <v>0.00757583836093545</v>
+        <v>0.09663710743188858</v>
       </c>
       <c r="E337" t="n">
-        <v>0.09617877184816066</v>
+        <v>0.1258658615384784</v>
       </c>
       <c r="F337" t="n">
         <v>0</v>
@@ -7406,10 +7406,10 @@
         <v>0.2244373896237448</v>
       </c>
       <c r="D338" t="n">
-        <v>0.07580826431512833</v>
+        <v>0.190457284450531</v>
       </c>
       <c r="E338" t="n">
-        <v>0.218783612004369</v>
+        <v>0.2569999520495033</v>
       </c>
       <c r="F338" t="n">
         <v>0</v>
@@ -7426,10 +7426,10 @@
         <v>0.283209351425923</v>
       </c>
       <c r="D339" t="n">
-        <v>0.04234002158045769</v>
+        <v>0.1078259497880936</v>
       </c>
       <c r="E339" t="n">
-        <v>0.2183059480436462</v>
+        <v>0.2401345907795248</v>
       </c>
       <c r="F339" t="n">
         <v>0</v>
@@ -7446,10 +7446,10 @@
         <v>0.2077499720116928</v>
       </c>
       <c r="D340" t="n">
-        <v>0.006006040144711733</v>
+        <v>0.07520376145839691</v>
       </c>
       <c r="E340" t="n">
-        <v>0.1410115632698035</v>
+        <v>0.1640774703743653</v>
       </c>
       <c r="F340" t="n">
         <v>0</v>
@@ -7466,10 +7466,10 @@
         <v>0.2466391656695625</v>
       </c>
       <c r="D341" t="n">
-        <v>0.005515526980161667</v>
+        <v>0.2036174982786179</v>
       </c>
       <c r="E341" t="n">
-        <v>0.2093211152049142</v>
+        <v>0.275355105637733</v>
       </c>
       <c r="F341" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0.1834007276203239</v>
       </c>
       <c r="D342" t="n">
-        <v>0.0007232059724628925</v>
+        <v>0.04872710630297661</v>
       </c>
       <c r="E342" t="n">
-        <v>0.1243562102626947</v>
+        <v>0.1403575103728659</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
@@ -7506,10 +7506,10 @@
         <v>0.2110750036838882</v>
       </c>
       <c r="D343" t="n">
-        <v>0.1374697238206863</v>
+        <v>0.2579489946365356</v>
       </c>
       <c r="E343" t="n">
-        <v>0.1967251362150727</v>
+        <v>0.2368848931536891</v>
       </c>
       <c r="F343" t="n">
         <v>0</v>
@@ -7526,10 +7526,10 @@
         <v>0.1701332961107747</v>
       </c>
       <c r="D344" t="n">
-        <v>0.01607757993042469</v>
+        <v>0.1076839119195938</v>
       </c>
       <c r="E344" t="n">
-        <v>0.1201266788929756</v>
+        <v>0.1506621228893653</v>
       </c>
       <c r="F344" t="n">
         <v>0</v>
@@ -7546,10 +7546,10 @@
         <v>0.1631228374510302</v>
       </c>
       <c r="D345" t="n">
-        <v>0.01374964602291584</v>
+        <v>0.1198870912194252</v>
       </c>
       <c r="E345" t="n">
-        <v>0.151068843881944</v>
+        <v>0.1864479922807805</v>
       </c>
       <c r="F345" t="n">
         <v>0</v>
@@ -7566,10 +7566,10 @@
         <v>0.2121078237503132</v>
       </c>
       <c r="D346" t="n">
-        <v>0.003094628918915987</v>
+        <v>0.08744229376316071</v>
       </c>
       <c r="E346" t="n">
-        <v>0.1627132879699311</v>
+        <v>0.190829176251346</v>
       </c>
       <c r="F346" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0.2020880758263718</v>
       </c>
       <c r="D347" t="n">
-        <v>1.751318268361501e-05</v>
+        <v>0.01082188542932272</v>
       </c>
       <c r="E347" t="n">
-        <v>0.1457835289228645</v>
+        <v>0.1493849863384109</v>
       </c>
       <c r="F347" t="n">
         <v>0</v>
@@ -7603,13 +7603,13 @@
         <v>0.371373830310047</v>
       </c>
       <c r="C348" t="n">
-        <v>0.2546876041861251</v>
+        <v>0.2546876041861252</v>
       </c>
       <c r="D348" t="n">
-        <v>0.01632943190634251</v>
+        <v>0.1429039537906647</v>
       </c>
       <c r="E348" t="n">
-        <v>0.2141302888008382</v>
+        <v>0.2563217960956123</v>
       </c>
       <c r="F348" t="n">
         <v>0</v>
@@ -7626,10 +7626,10 @@
         <v>0.3161943389451863</v>
       </c>
       <c r="D349" t="n">
-        <v>0.3478564321994781</v>
+        <v>0.2760223150253296</v>
       </c>
       <c r="E349" t="n">
-        <v>0.3309372465322118</v>
+        <v>0.3069925408074956</v>
       </c>
       <c r="F349" t="n">
         <v>0</v>
@@ -7646,10 +7646,10 @@
         <v>0.2207397406038883</v>
       </c>
       <c r="D350" t="n">
-        <v>0.003785699140280485</v>
+        <v>0.04346685856580734</v>
       </c>
       <c r="E350" t="n">
-        <v>0.1740885558046564</v>
+        <v>0.1873156089464987</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
@@ -7666,10 +7666,10 @@
         <v>0.3659763161259019</v>
       </c>
       <c r="D351" t="n">
-        <v>0.678344190120697</v>
+        <v>0.4523204863071442</v>
       </c>
       <c r="E351" t="n">
-        <v>0.5215589058796076</v>
+        <v>0.44621767127509</v>
       </c>
       <c r="F351" t="n">
         <v>0</v>
@@ -7686,10 +7686,10 @@
         <v>0.1264076750509179</v>
       </c>
       <c r="D352" t="n">
-        <v>0.0001270641369046643</v>
+        <v>0.02852641046047211</v>
       </c>
       <c r="E352" t="n">
-        <v>0.07551501965148126</v>
+        <v>0.08498146842600374</v>
       </c>
       <c r="F352" t="n">
         <v>0</v>
@@ -7706,10 +7706,10 @@
         <v>0.1720775936789294</v>
       </c>
       <c r="D353" t="n">
-        <v>0.0001576315407874063</v>
+        <v>0.03409905359148979</v>
       </c>
       <c r="E353" t="n">
-        <v>0.1153527874392405</v>
+        <v>0.1266665947894746</v>
       </c>
       <c r="F353" t="n">
         <v>0</v>
@@ -7726,10 +7726,10 @@
         <v>0.2440190853233989</v>
       </c>
       <c r="D354" t="n">
-        <v>0.2605370581150055</v>
+        <v>0.1729945838451385</v>
       </c>
       <c r="E354" t="n">
-        <v>0.2403101839270984</v>
+        <v>0.211129359170476</v>
       </c>
       <c r="F354" t="n">
         <v>0</v>
@@ -7746,10 +7746,10 @@
         <v>0.1985070884957957</v>
       </c>
       <c r="D355" t="n">
-        <v>0.2108025252819061</v>
+        <v>0.2191461771726608</v>
       </c>
       <c r="E355" t="n">
-        <v>0.1978778400997588</v>
+        <v>0.200659057396677</v>
       </c>
       <c r="F355" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0.1389995342007893</v>
       </c>
       <c r="D356" t="n">
-        <v>0.002438020426779985</v>
+        <v>0.06924319267272949</v>
       </c>
       <c r="E356" t="n">
-        <v>0.1008147290498171</v>
+        <v>0.1230831197984669</v>
       </c>
       <c r="F356" t="n">
         <v>0</v>
@@ -7786,10 +7786,10 @@
         <v>0.2028237531849048</v>
       </c>
       <c r="D357" t="n">
-        <v>0.003070397768169641</v>
+        <v>0.04040352255105972</v>
       </c>
       <c r="E357" t="n">
-        <v>0.1551457356980674</v>
+        <v>0.1675901106256974</v>
       </c>
       <c r="F357" t="n">
         <v>0</v>
@@ -7803,13 +7803,13 @@
         <v>0.5882286934495428</v>
       </c>
       <c r="C358" t="n">
-        <v>0.3595630951327164</v>
+        <v>0.3595630951327165</v>
       </c>
       <c r="D358" t="n">
-        <v>0.7389410734176636</v>
+        <v>0.4411697387695312</v>
       </c>
       <c r="E358" t="n">
-        <v>0.5622442873333076</v>
+        <v>0.4629871757839302</v>
       </c>
       <c r="F358" t="n">
         <v>0</v>
@@ -7826,10 +7826,10 @@
         <v>0.4263509213265251</v>
       </c>
       <c r="D359" t="n">
-        <v>0.09517713636159897</v>
+        <v>0.1660622805356979</v>
       </c>
       <c r="E359" t="n">
-        <v>0.3713742293731497</v>
+        <v>0.395002610764516</v>
       </c>
       <c r="F359" t="n">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>0.2599309387281244</v>
       </c>
       <c r="D360" t="n">
-        <v>0.05140084773302078</v>
+        <v>0.1172319650650024</v>
       </c>
       <c r="E360" t="n">
-        <v>0.2466892434835803</v>
+        <v>0.2686329492609075</v>
       </c>
       <c r="F360" t="n">
         <v>0</v>
@@ -7866,10 +7866,10 @@
         <v>0.1395222394041264</v>
       </c>
       <c r="D361" t="n">
-        <v>0.000355315045453608</v>
+        <v>0.0450725145637989</v>
       </c>
       <c r="E361" t="n">
-        <v>0.1118514066300614</v>
+        <v>0.1267571398028431</v>
       </c>
       <c r="F361" t="n">
         <v>0</v>
@@ -7886,10 +7886,10 @@
         <v>0.3360344552869404</v>
       </c>
       <c r="D362" t="n">
-        <v>0.5687354207038879</v>
+        <v>0.3444685339927673</v>
       </c>
       <c r="E362" t="n">
-        <v>0.4531256345717726</v>
+        <v>0.3783700056680657</v>
       </c>
       <c r="F362" t="n">
         <v>0</v>
@@ -7906,10 +7906,10 @@
         <v>0.2468609538649147</v>
       </c>
       <c r="D363" t="n">
-        <v>0.2211678028106689</v>
+        <v>0.2509845793247223</v>
       </c>
       <c r="E363" t="n">
-        <v>0.2672895274421777</v>
+        <v>0.2772284529468621</v>
       </c>
       <c r="F363" t="n">
         <v>0</v>
@@ -7926,10 +7926,10 @@
         <v>0.270059796455745</v>
       </c>
       <c r="D364" t="n">
-        <v>0.2592461705207825</v>
+        <v>0.215984433889389</v>
       </c>
       <c r="E364" t="n">
-        <v>0.2457787263529533</v>
+        <v>0.2313581474758222</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
@@ -7946,10 +7946,10 @@
         <v>0.1765666227222857</v>
       </c>
       <c r="D365" t="n">
-        <v>0.02522634342312813</v>
+        <v>0.08056894689798355</v>
       </c>
       <c r="E365" t="n">
-        <v>0.1186542029979758</v>
+        <v>0.1371017374895942</v>
       </c>
       <c r="F365" t="n">
         <v>0</v>
@@ -7966,10 +7966,10 @@
         <v>0.1595701629983918</v>
       </c>
       <c r="D366" t="n">
-        <v>0.09052391350269318</v>
+        <v>0.1036012396216393</v>
       </c>
       <c r="E366" t="n">
-        <v>0.1476993595831565</v>
+        <v>0.1520584682894719</v>
       </c>
       <c r="F366" t="n">
         <v>0</v>
@@ -7986,10 +7986,10 @@
         <v>0.2254987095801282</v>
       </c>
       <c r="D367" t="n">
-        <v>8.208425424527377e-05</v>
+        <v>0.01813911460340023</v>
       </c>
       <c r="E367" t="n">
-        <v>0.1736288168125341</v>
+        <v>0.1796478269289191</v>
       </c>
       <c r="F367" t="n">
         <v>0</v>
@@ -8006,10 +8006,10 @@
         <v>0.2994431663109915</v>
       </c>
       <c r="D368" t="n">
-        <v>0.004808249417692423</v>
+        <v>0.1057377681136131</v>
       </c>
       <c r="E368" t="n">
-        <v>0.2394335237598735</v>
+        <v>0.2730766966585138</v>
       </c>
       <c r="F368" t="n">
         <v>0</v>
@@ -8026,10 +8026,10 @@
         <v>0.1741719378395016</v>
       </c>
       <c r="D369" t="n">
-        <v>0.02133238688111305</v>
+        <v>0.09195295721292496</v>
       </c>
       <c r="E369" t="n">
-        <v>0.1358632732895544</v>
+        <v>0.1594034634001583</v>
       </c>
       <c r="F369" t="n">
         <v>0</v>
@@ -8046,10 +8046,10 @@
         <v>0.1798384744288231</v>
       </c>
       <c r="D370" t="n">
-        <v>0.001721614273265004</v>
+        <v>0.05937477946281433</v>
       </c>
       <c r="E370" t="n">
-        <v>0.1518398203505924</v>
+        <v>0.1710575420804422</v>
       </c>
       <c r="F370" t="n">
         <v>0</v>
@@ -8066,10 +8066,10 @@
         <v>0.1739304088231993</v>
       </c>
       <c r="D371" t="n">
-        <v>0.3915858566761017</v>
+        <v>0.1029871478676796</v>
       </c>
       <c r="E371" t="n">
-        <v>0.2441434429148367</v>
+        <v>0.1479438733120294</v>
       </c>
       <c r="F371" t="n">
         <v>0</v>
@@ -8086,10 +8086,10 @@
         <v>0.1370753474343921</v>
       </c>
       <c r="D372" t="n">
-        <v>0.0004337720456533134</v>
+        <v>0.05858550220727921</v>
       </c>
       <c r="E372" t="n">
-        <v>0.09997355721481536</v>
+        <v>0.1193574672686906</v>
       </c>
       <c r="F372" t="n">
         <v>0</v>
@@ -8106,10 +8106,10 @@
         <v>0.1412973528926903</v>
       </c>
       <c r="D373" t="n">
-        <v>0.004186898469924927</v>
+        <v>0.0601436123251915</v>
       </c>
       <c r="E373" t="n">
-        <v>0.116254943038969</v>
+        <v>0.1349071809907246</v>
       </c>
       <c r="F373" t="n">
         <v>0</v>
@@ -8126,10 +8126,10 @@
         <v>0.1691431399637203</v>
       </c>
       <c r="D374" t="n">
-        <v>0.0245132502168417</v>
+        <v>0.111709401011467</v>
       </c>
       <c r="E374" t="n">
-        <v>0.1305344068911735</v>
+        <v>0.1595997904893819</v>
       </c>
       <c r="F374" t="n">
         <v>0</v>
@@ -8146,10 +8146,10 @@
         <v>0.1052892364383654</v>
       </c>
       <c r="D375" t="n">
-        <v>0.002064136322587729</v>
+        <v>0.09023966640233994</v>
       </c>
       <c r="E375" t="n">
-        <v>0.1028386185328045</v>
+        <v>0.1322304618927219</v>
       </c>
       <c r="F375" t="n">
         <v>0</v>
@@ -8166,10 +8166,10 @@
         <v>0.2696032742796808</v>
       </c>
       <c r="D376" t="n">
-        <v>0.02997564151883125</v>
+        <v>0.1228858828544617</v>
       </c>
       <c r="E376" t="n">
-        <v>0.2303680172776743</v>
+        <v>0.2613380977228845</v>
       </c>
       <c r="F376" t="n">
         <v>0</v>
@@ -8186,10 +8186,10 @@
         <v>0.1828416191914569</v>
       </c>
       <c r="D377" t="n">
-        <v>0.0002340240171179175</v>
+        <v>0.03337999060750008</v>
       </c>
       <c r="E377" t="n">
-        <v>0.1150495288270818</v>
+        <v>0.1260981843572092</v>
       </c>
       <c r="F377" t="n">
         <v>0</v>
@@ -8206,10 +8206,10 @@
         <v>0.1573012072151023</v>
       </c>
       <c r="D378" t="n">
-        <v>0.001264168415218592</v>
+        <v>0.07522718608379364</v>
       </c>
       <c r="E378" t="n">
-        <v>0.1030426093069123</v>
+        <v>0.1276969485297706</v>
       </c>
       <c r="F378" t="n">
         <v>0</v>
@@ -8226,10 +8226,10 @@
         <v>0.1979168143936013</v>
       </c>
       <c r="D379" t="n">
-        <v>0.3548492193222046</v>
+        <v>0.3921816945075989</v>
       </c>
       <c r="E379" t="n">
-        <v>0.2525218693047104</v>
+        <v>0.2649660276998418</v>
       </c>
       <c r="F379" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0.3951778616586796</v>
       </c>
       <c r="D380" t="n">
-        <v>0.4325044751167297</v>
+        <v>0.5299926400184631</v>
       </c>
       <c r="E380" t="n">
-        <v>0.4220672433221644</v>
+        <v>0.4545632982894088</v>
       </c>
       <c r="F380" t="n">
         <v>0</v>
@@ -8266,10 +8266,10 @@
         <v>0.3056208754025039</v>
       </c>
       <c r="D381" t="n">
-        <v>0.6313949823379517</v>
+        <v>0.5034465789794922</v>
       </c>
       <c r="E381" t="n">
-        <v>0.4171738555445387</v>
+        <v>0.3745243877583855</v>
       </c>
       <c r="F381" t="n">
         <v>0</v>
@@ -8286,10 +8286,10 @@
         <v>0.2201093997738111</v>
       </c>
       <c r="D382" t="n">
-        <v>0.1421291828155518</v>
+        <v>0.1385198980569839</v>
       </c>
       <c r="E382" t="n">
-        <v>0.1951992118805204</v>
+        <v>0.1939961169609977</v>
       </c>
       <c r="F382" t="n">
         <v>0</v>
@@ -8306,10 +8306,10 @@
         <v>0.2295245798726985</v>
       </c>
       <c r="D383" t="n">
-        <v>0.04087569564580917</v>
+        <v>0.2003714740276337</v>
       </c>
       <c r="E383" t="n">
-        <v>0.1645399673149463</v>
+        <v>0.2177052267755545</v>
       </c>
       <c r="F383" t="n">
         <v>0</v>
@@ -8326,10 +8326,10 @@
         <v>0.321646146623849</v>
       </c>
       <c r="D384" t="n">
-        <v>0.09238956123590469</v>
+        <v>0.2757976651191711</v>
       </c>
       <c r="E384" t="n">
-        <v>0.2588541497879982</v>
+        <v>0.3199901844157537</v>
       </c>
       <c r="F384" t="n">
         <v>0</v>
@@ -8346,10 +8346,10 @@
         <v>0.1541845311681382</v>
       </c>
       <c r="D385" t="n">
-        <v>0.005669549573212862</v>
+        <v>0.06217483431100845</v>
       </c>
       <c r="E385" t="n">
-        <v>0.09441577454557333</v>
+        <v>0.1132508694581719</v>
       </c>
       <c r="F385" t="n">
         <v>0</v>
@@ -8366,10 +8366,10 @@
         <v>0.2916479817323466</v>
       </c>
       <c r="D386" t="n">
-        <v>0.1210959926247597</v>
+        <v>0.2222385406494141</v>
       </c>
       <c r="E386" t="n">
-        <v>0.2833957999685615</v>
+        <v>0.3171099826434463</v>
       </c>
       <c r="F386" t="n">
         <v>0</v>
@@ -8386,10 +8386,10 @@
         <v>0.3600650269622542</v>
       </c>
       <c r="D387" t="n">
-        <v>0.7444862127304077</v>
+        <v>0.6371176838874817</v>
       </c>
       <c r="E387" t="n">
-        <v>0.5157133682154272</v>
+        <v>0.4799238586011186</v>
       </c>
       <c r="F387" t="n">
         <v>0</v>
@@ -8403,13 +8403,13 @@
         <v>0.4237030369282855</v>
       </c>
       <c r="C388" t="n">
-        <v>0.3166279714005419</v>
+        <v>0.316627971400542</v>
       </c>
       <c r="D388" t="n">
-        <v>0.4454097747802734</v>
+        <v>0.2387958019971848</v>
       </c>
       <c r="E388" t="n">
-        <v>0.3952469277030337</v>
+        <v>0.3263756034420041</v>
       </c>
       <c r="F388" t="n">
         <v>0</v>
@@ -8426,10 +8426,10 @@
         <v>0.2240966464282289</v>
       </c>
       <c r="D389" t="n">
-        <v>0.2748691141605377</v>
+        <v>0.3140198886394501</v>
       </c>
       <c r="E389" t="n">
-        <v>0.2458592612457871</v>
+        <v>0.2589095194054246</v>
       </c>
       <c r="F389" t="n">
         <v>0</v>
@@ -8446,10 +8446,10 @@
         <v>0.3244848459106048</v>
       </c>
       <c r="D390" t="n">
-        <v>0.1387932300567627</v>
+        <v>0.2313778400421143</v>
       </c>
       <c r="E390" t="n">
-        <v>0.2603070628312563</v>
+        <v>0.2911685994930401</v>
       </c>
       <c r="F390" t="n">
         <v>0</v>
@@ -8466,10 +8466,10 @@
         <v>0.1856114466420517</v>
       </c>
       <c r="D391" t="n">
-        <v>0.01874219067394733</v>
+        <v>0.1743578016757965</v>
       </c>
       <c r="E391" t="n">
-        <v>0.1181985336643941</v>
+        <v>0.1700704039983439</v>
       </c>
       <c r="F391" t="n">
         <v>0</v>
@@ -8486,10 +8486,10 @@
         <v>0.4728141752586971</v>
       </c>
       <c r="D392" t="n">
-        <v>0.9083989858627319</v>
+        <v>0.7170804738998413</v>
       </c>
       <c r="E392" t="n">
-        <v>0.6914785097341406</v>
+        <v>0.627705672413177</v>
       </c>
       <c r="F392" t="n">
         <v>1</v>
@@ -8503,13 +8503,13 @@
         <v>0.4022390588311559</v>
       </c>
       <c r="C393" t="n">
-        <v>0.2677654629129282</v>
+        <v>0.2677654629129281</v>
       </c>
       <c r="D393" t="n">
-        <v>0.1884398013353348</v>
+        <v>0.381371021270752</v>
       </c>
       <c r="E393" t="n">
-        <v>0.2861481076931396</v>
+        <v>0.3504585143382786</v>
       </c>
       <c r="F393" t="n">
         <v>0</v>
@@ -8526,10 +8526,10 @@
         <v>0.6363583389339815</v>
       </c>
       <c r="D394" t="n">
-        <v>0.9866858720779419</v>
+        <v>0.7831705212593079</v>
       </c>
       <c r="E394" t="n">
-        <v>0.7715523513165259</v>
+        <v>0.7037139010436478</v>
       </c>
       <c r="F394" t="n">
         <v>1</v>
@@ -8546,10 +8546,10 @@
         <v>0.6864692785718601</v>
       </c>
       <c r="D395" t="n">
-        <v>0.9892808198928833</v>
+        <v>0.7699435949325562</v>
       </c>
       <c r="E395" t="n">
-        <v>0.8158946635947341</v>
+        <v>0.742782255274625</v>
       </c>
       <c r="F395" t="n">
         <v>1</v>
@@ -8563,13 +8563,13 @@
         <v>0.6531456108684935</v>
       </c>
       <c r="C396" t="n">
-        <v>0.5562953687400907</v>
+        <v>0.5562953687400906</v>
       </c>
       <c r="D396" t="n">
-        <v>0.8161889314651489</v>
+        <v>0.5934635996818542</v>
       </c>
       <c r="E396" t="n">
-        <v>0.6752099703579111</v>
+        <v>0.6009681930968128</v>
       </c>
       <c r="F396" t="n">
         <v>1</v>
@@ -8586,10 +8586,10 @@
         <v>0.7135040611718858</v>
       </c>
       <c r="D397" t="n">
-        <v>0.993527889251709</v>
+        <v>0.7965211868286133</v>
       </c>
       <c r="E397" t="n">
-        <v>0.8316699967546312</v>
+        <v>0.7660010959469327</v>
       </c>
       <c r="F397" t="n">
         <v>1</v>
@@ -8603,13 +8603,13 @@
         <v>0.8284934443638365</v>
       </c>
       <c r="C398" t="n">
-        <v>0.72208061785221</v>
+        <v>0.7220806178522101</v>
       </c>
       <c r="D398" t="n">
-        <v>0.9886825680732727</v>
+        <v>0.7797842025756836</v>
       </c>
       <c r="E398" t="n">
-        <v>0.8464188767631065</v>
+        <v>0.77678608826391</v>
       </c>
       <c r="F398" t="n">
         <v>1</v>
@@ -8626,10 +8626,10 @@
         <v>0.8470791486319997</v>
       </c>
       <c r="D399" t="n">
-        <v>0.9984939694404602</v>
+        <v>0.8152593374252319</v>
       </c>
       <c r="E399" t="n">
-        <v>0.8984350862894684</v>
+        <v>0.8373568756177256</v>
       </c>
       <c r="F399" t="n">
         <v>1</v>
@@ -8646,10 +8646,10 @@
         <v>0.8009019741469826</v>
       </c>
       <c r="D400" t="n">
-        <v>0.9904884099960327</v>
+        <v>0.7894757986068726</v>
       </c>
       <c r="E400" t="n">
-        <v>0.8614116082658038</v>
+        <v>0.794407404469417</v>
       </c>
       <c r="F400" t="n">
         <v>1</v>
@@ -8666,10 +8666,10 @@
         <v>0.502995945556844</v>
       </c>
       <c r="D401" t="n">
-        <v>0.8791829943656921</v>
+        <v>0.5086368322372437</v>
       </c>
       <c r="E401" t="n">
-        <v>0.6541051635210525</v>
+        <v>0.530589776144903</v>
       </c>
       <c r="F401" t="n">
         <v>1</v>
@@ -8686,10 +8686,10 @@
         <v>0.7574872279660374</v>
       </c>
       <c r="D402" t="n">
-        <v>0.9931848645210266</v>
+        <v>0.7469063401222229</v>
       </c>
       <c r="E402" t="n">
-        <v>0.8308251461270527</v>
+        <v>0.7487323046607849</v>
       </c>
       <c r="F402" t="n">
         <v>1</v>
@@ -8706,10 +8706,10 @@
         <v>0.7936473596863918</v>
       </c>
       <c r="D403" t="n">
-        <v>0.9943626523017883</v>
+        <v>0.7636206150054932</v>
       </c>
       <c r="E403" t="n">
-        <v>0.8581647332942216</v>
+        <v>0.7812507208621232</v>
       </c>
       <c r="F403" t="n">
         <v>1</v>
@@ -8726,10 +8726,10 @@
         <v>0.7771040206235172</v>
       </c>
       <c r="D404" t="n">
-        <v>0.9960794448852539</v>
+        <v>0.7746264338493347</v>
       </c>
       <c r="E404" t="n">
-        <v>0.8503709341285394</v>
+        <v>0.776553263783233</v>
       </c>
       <c r="F404" t="n">
         <v>1</v>
@@ -8746,10 +8746,10 @@
         <v>0.7833007033817825</v>
       </c>
       <c r="D405" t="n">
-        <v>0.9961131811141968</v>
+        <v>0.7804576754570007</v>
       </c>
       <c r="E405" t="n">
-        <v>0.8548658909355241</v>
+        <v>0.7829807223831254</v>
       </c>
       <c r="F405" t="n">
         <v>1</v>
@@ -8766,10 +8766,10 @@
         <v>0.7479820533627247</v>
       </c>
       <c r="D406" t="n">
-        <v>0.9953027963638306</v>
+        <v>0.7600780725479126</v>
       </c>
       <c r="E406" t="n">
-        <v>0.8232224303106545</v>
+        <v>0.7448141890386818</v>
       </c>
       <c r="F406" t="n">
         <v>1</v>
@@ -8783,13 +8783,13 @@
         <v>0.7930430639474374</v>
       </c>
       <c r="C407" t="n">
-        <v>0.8208268376309636</v>
+        <v>0.8208268376309634</v>
       </c>
       <c r="D407" t="n">
-        <v>0.9965326189994812</v>
+        <v>0.7715867757797241</v>
       </c>
       <c r="E407" t="n">
-        <v>0.8701341735259608</v>
+        <v>0.7951522257860416</v>
       </c>
       <c r="F407" t="n">
         <v>1</v>
@@ -8806,10 +8806,10 @@
         <v>0.8244830903733057</v>
       </c>
       <c r="D408" t="n">
-        <v>0.9946688413619995</v>
+        <v>0.7702873945236206</v>
       </c>
       <c r="E408" t="n">
-        <v>0.8725259545060514</v>
+        <v>0.7977321388932584</v>
       </c>
       <c r="F408" t="n">
         <v>1</v>
@@ -8823,13 +8823,13 @@
         <v>0.7133755643709148</v>
       </c>
       <c r="C409" t="n">
-        <v>0.6039945885371902</v>
+        <v>0.6039945885371903</v>
       </c>
       <c r="D409" t="n">
-        <v>0.9885141253471375</v>
+        <v>0.7675989866256714</v>
       </c>
       <c r="E409" t="n">
-        <v>0.7686280927517476</v>
+        <v>0.6949897131779256</v>
       </c>
       <c r="F409" t="n">
         <v>1</v>
@@ -8846,10 +8846,10 @@
         <v>0.3786423026145093</v>
       </c>
       <c r="D410" t="n">
-        <v>0.6667500138282776</v>
+        <v>0.4433057904243469</v>
       </c>
       <c r="E410" t="n">
-        <v>0.4684499743234631</v>
+        <v>0.3939685665221529</v>
       </c>
       <c r="F410" t="n">
         <v>0</v>
@@ -8866,10 +8866,10 @@
         <v>0.6006316212384999</v>
       </c>
       <c r="D411" t="n">
-        <v>0.9604487419128418</v>
+        <v>0.7550204396247864</v>
       </c>
       <c r="E411" t="n">
-        <v>0.7280668568947609</v>
+        <v>0.6595907561320757</v>
       </c>
       <c r="F411" t="n">
         <v>1</v>
@@ -8886,10 +8886,10 @@
         <v>0.7126136619189759</v>
       </c>
       <c r="D412" t="n">
-        <v>0.9966498613357544</v>
+        <v>0.7948389649391174</v>
       </c>
       <c r="E412" t="n">
-        <v>0.8345889377372743</v>
+        <v>0.7673186389383954</v>
       </c>
       <c r="F412" t="n">
         <v>1</v>
@@ -8906,10 +8906,10 @@
         <v>0.8798552417242412</v>
       </c>
       <c r="D413" t="n">
-        <v>0.9973646402359009</v>
+        <v>0.8066719174385071</v>
       </c>
       <c r="E413" t="n">
-        <v>0.9134944373944965</v>
+        <v>0.8499301964620319</v>
       </c>
       <c r="F413" t="n">
         <v>1</v>
@@ -8926,10 +8926,10 @@
         <v>0.7650165969208393</v>
       </c>
       <c r="D414" t="n">
-        <v>0.9963279962539673</v>
+        <v>0.7990066409111023</v>
       </c>
       <c r="E414" t="n">
-        <v>0.8628824287581517</v>
+        <v>0.7971086436438634</v>
       </c>
       <c r="F414" t="n">
         <v>1</v>
@@ -8946,10 +8946,10 @@
         <v>0.859869174747425</v>
       </c>
       <c r="D415" t="n">
-        <v>0.9987711906433105</v>
+        <v>0.8122339248657227</v>
       </c>
       <c r="E415" t="n">
-        <v>0.9009376972698764</v>
+        <v>0.8387586086773471</v>
       </c>
       <c r="F415" t="n">
         <v>1</v>
@@ -8963,13 +8963,13 @@
         <v>0.7838062234861441</v>
       </c>
       <c r="C416" t="n">
-        <v>0.7880362334235064</v>
+        <v>0.7880362334235065</v>
       </c>
       <c r="D416" t="n">
-        <v>0.9971254467964172</v>
+        <v>0.8143032789230347</v>
       </c>
       <c r="E416" t="n">
-        <v>0.8563226345686893</v>
+        <v>0.7953819119442285</v>
       </c>
       <c r="F416" t="n">
         <v>1</v>
@@ -8986,10 +8986,10 @@
         <v>0.6868049413319295</v>
       </c>
       <c r="D417" t="n">
-        <v>0.9964599609375</v>
+        <v>0.8088809251785278</v>
       </c>
       <c r="E417" t="n">
-        <v>0.8213153681278996</v>
+        <v>0.7587890228749089</v>
       </c>
       <c r="F417" t="n">
         <v>1</v>
@@ -9006,10 +9006,10 @@
         <v>0.8686777703504157</v>
       </c>
       <c r="D418" t="n">
-        <v>0.989209771156311</v>
+        <v>0.7717434763908386</v>
       </c>
       <c r="E418" t="n">
-        <v>0.9068540270118174</v>
+        <v>0.8343652620899933</v>
       </c>
       <c r="F418" t="n">
         <v>1</v>
@@ -9026,10 +9026,10 @@
         <v>0.6308293235235162</v>
       </c>
       <c r="D419" t="n">
-        <v>0.8841019868850708</v>
+        <v>0.6238382458686829</v>
       </c>
       <c r="E419" t="n">
-        <v>0.743144884493857</v>
+        <v>0.6563903041550611</v>
       </c>
       <c r="F419" t="n">
         <v>1</v>
@@ -9043,13 +9043,13 @@
         <v>0.7791690767823022</v>
       </c>
       <c r="C420" t="n">
-        <v>0.6517866745386143</v>
+        <v>0.6517866745386142</v>
       </c>
       <c r="D420" t="n">
-        <v>0.9874672889709473</v>
+        <v>0.7627346515655518</v>
       </c>
       <c r="E420" t="n">
-        <v>0.8061410134306213</v>
+        <v>0.7312301342954894</v>
       </c>
       <c r="F420" t="n">
         <v>1</v>
@@ -9066,10 +9066,10 @@
         <v>0.5415980555611344</v>
       </c>
       <c r="D421" t="n">
-        <v>0.9561630487442017</v>
+        <v>0.697449803352356</v>
       </c>
       <c r="E421" t="n">
-        <v>0.7371192985151035</v>
+        <v>0.6508815500511549</v>
       </c>
       <c r="F421" t="n">
         <v>1</v>
@@ -9086,10 +9086,10 @@
         <v>0.662200214252108</v>
       </c>
       <c r="D422" t="n">
-        <v>0.9454229474067688</v>
+        <v>0.7157111167907715</v>
       </c>
       <c r="E422" t="n">
-        <v>0.7645334552555852</v>
+        <v>0.6879628450502527</v>
       </c>
       <c r="F422" t="n">
         <v>1</v>
@@ -9106,10 +9106,10 @@
         <v>0.6757789996253505</v>
       </c>
       <c r="D423" t="n">
-        <v>0.975914478302002</v>
+        <v>0.7327452898025513</v>
       </c>
       <c r="E423" t="n">
-        <v>0.7882270081789909</v>
+        <v>0.7071706120125074</v>
       </c>
       <c r="F423" t="n">
         <v>1</v>
@@ -9126,10 +9126,10 @@
         <v>0.8291009180445436</v>
       </c>
       <c r="D424" t="n">
-        <v>0.9925235509872437</v>
+        <v>0.799659252166748</v>
       </c>
       <c r="E424" t="n">
-        <v>0.8814369134452863</v>
+        <v>0.8171488138384544</v>
       </c>
       <c r="F424" t="n">
         <v>1</v>
@@ -9143,13 +9143,13 @@
         <v>0.8482116567794409</v>
       </c>
       <c r="C425" t="n">
-        <v>0.8312840534722012</v>
+        <v>0.831284053472201</v>
       </c>
       <c r="D425" t="n">
-        <v>0.9956901669502258</v>
+        <v>0.8001583814620972</v>
       </c>
       <c r="E425" t="n">
-        <v>0.8917286257339559</v>
+        <v>0.8265513639045796</v>
       </c>
       <c r="F425" t="n">
         <v>1</v>
@@ -9166,10 +9166,10 @@
         <v>0.8115896037647705</v>
       </c>
       <c r="D426" t="n">
-        <v>0.9857944250106812</v>
+        <v>0.7865818738937378</v>
       </c>
       <c r="E426" t="n">
-        <v>0.8795774859950306</v>
+        <v>0.8131733022893828</v>
       </c>
       <c r="F426" t="n">
         <v>1</v>
@@ -9186,10 +9186,10 @@
         <v>0.7982182249223835</v>
       </c>
       <c r="D427" t="n">
-        <v>0.9892711639404297</v>
+        <v>0.7883899807929993</v>
       </c>
       <c r="E427" t="n">
-        <v>0.868975370044515</v>
+        <v>0.8020149756620382</v>
       </c>
       <c r="F427" t="n">
         <v>1</v>
@@ -9206,10 +9206,10 @@
         <v>0.8268900933199909</v>
       </c>
       <c r="D428" t="n">
-        <v>0.9859081506729126</v>
+        <v>0.7589805126190186</v>
       </c>
       <c r="E428" t="n">
-        <v>0.8758439571577042</v>
+        <v>0.8002014111397395</v>
       </c>
       <c r="F428" t="n">
         <v>1</v>
@@ -9223,13 +9223,13 @@
         <v>0.7409991849871445</v>
       </c>
       <c r="C429" t="n">
-        <v>0.7199336933378518</v>
+        <v>0.7199336933378517</v>
       </c>
       <c r="D429" t="n">
-        <v>0.9691435694694519</v>
+        <v>0.75993812084198</v>
       </c>
       <c r="E429" t="n">
-        <v>0.8100254825981494</v>
+        <v>0.7402903330556588</v>
       </c>
       <c r="F429" t="n">
         <v>1</v>
@@ -9243,13 +9243,13 @@
         <v>0.842248310113605</v>
       </c>
       <c r="C430" t="n">
-        <v>0.8197207957888045</v>
+        <v>0.8197207957888043</v>
       </c>
       <c r="D430" t="n">
-        <v>0.991702675819397</v>
+        <v>0.7864229083061218</v>
       </c>
       <c r="E430" t="n">
-        <v>0.8845572605739355</v>
+        <v>0.8161306714028438</v>
       </c>
       <c r="F430" t="n">
         <v>1</v>
@@ -9263,13 +9263,13 @@
         <v>0.7361939037605112</v>
       </c>
       <c r="C431" t="n">
-        <v>0.7198258502273462</v>
+        <v>0.7198258502273461</v>
       </c>
       <c r="D431" t="n">
-        <v>0.9858384132385254</v>
+        <v>0.7525700330734253</v>
       </c>
       <c r="E431" t="n">
-        <v>0.8139527224087942</v>
+        <v>0.7361965956870943</v>
       </c>
       <c r="F431" t="n">
         <v>1</v>
@@ -9286,10 +9286,10 @@
         <v>0.8184575387066209</v>
       </c>
       <c r="D432" t="n">
-        <v>0.9793519973754883</v>
+        <v>0.7703701257705688</v>
       </c>
       <c r="E432" t="n">
-        <v>0.8678249752389889</v>
+        <v>0.7981643513706825</v>
       </c>
       <c r="F432" t="n">
         <v>1</v>
@@ -9306,10 +9306,10 @@
         <v>0.8584211747340416</v>
       </c>
       <c r="D433" t="n">
-        <v>0.9912605285644531</v>
+        <v>0.7959979772567749</v>
       </c>
       <c r="E433" t="n">
-        <v>0.8952349773031734</v>
+        <v>0.8301474602006139</v>
       </c>
       <c r="F433" t="n">
         <v>1</v>
@@ -9323,13 +9323,13 @@
         <v>0.7752135500054844</v>
       </c>
       <c r="C434" t="n">
-        <v>0.762717708944239</v>
+        <v>0.7627177089442388</v>
       </c>
       <c r="D434" t="n">
-        <v>0.9889510869979858</v>
+        <v>0.7499321699142456</v>
       </c>
       <c r="E434" t="n">
-        <v>0.842294115315903</v>
+        <v>0.7626211429546563</v>
       </c>
       <c r="F434" t="n">
         <v>1</v>
@@ -9346,10 +9346,10 @@
         <v>0.8224363253052356</v>
       </c>
       <c r="D435" t="n">
-        <v>0.9943609237670898</v>
+        <v>0.7831476926803589</v>
       </c>
       <c r="E435" t="n">
-        <v>0.8782272793980841</v>
+        <v>0.8078228690358404</v>
       </c>
       <c r="F435" t="n">
         <v>1</v>
@@ -9363,13 +9363,13 @@
         <v>0.8055692854130905</v>
       </c>
       <c r="C436" t="n">
-        <v>0.7247207094063886</v>
+        <v>0.7247207094063884</v>
       </c>
       <c r="D436" t="n">
-        <v>0.986178994178772</v>
+        <v>0.7535375952720642</v>
       </c>
       <c r="E436" t="n">
-        <v>0.8388229963327504</v>
+        <v>0.7612758633638478</v>
       </c>
       <c r="F436" t="n">
         <v>1</v>
@@ -9383,13 +9383,13 @@
         <v>0.8408697047193783</v>
       </c>
       <c r="C437" t="n">
-        <v>0.8216754545103029</v>
+        <v>0.8216754545103028</v>
       </c>
       <c r="D437" t="n">
-        <v>0.9924775958061218</v>
+        <v>0.7934936285018921</v>
       </c>
       <c r="E437" t="n">
-        <v>0.8850075850119343</v>
+        <v>0.8186795959105244</v>
       </c>
       <c r="F437" t="n">
         <v>1</v>
@@ -9403,13 +9403,13 @@
         <v>0.8211970199838354</v>
       </c>
       <c r="C438" t="n">
-        <v>0.8009319500765992</v>
+        <v>0.800931950076599</v>
       </c>
       <c r="D438" t="n">
-        <v>0.9827893972396851</v>
+        <v>0.795230507850647</v>
       </c>
       <c r="E438" t="n">
-        <v>0.8683061224333732</v>
+        <v>0.8057864926370272</v>
       </c>
       <c r="F438" t="n">
         <v>1</v>
@@ -9426,10 +9426,10 @@
         <v>0.7926208262448645</v>
       </c>
       <c r="D439" t="n">
-        <v>0.9851514101028442</v>
+        <v>0.7631657123565674</v>
       </c>
       <c r="E439" t="n">
-        <v>0.863747308992297</v>
+        <v>0.7897520764102047</v>
       </c>
       <c r="F439" t="n">
         <v>1</v>
@@ -9446,10 +9446,10 @@
         <v>0.7815909786712013</v>
       </c>
       <c r="D440" t="n">
-        <v>0.992489218711853</v>
+        <v>0.7848934531211853</v>
       </c>
       <c r="E440" t="n">
-        <v>0.8542177013641293</v>
+        <v>0.7850191128339068</v>
       </c>
       <c r="F440" t="n">
         <v>1</v>
@@ -9466,10 +9466,10 @@
         <v>0.4836415638953584</v>
       </c>
       <c r="D441" t="n">
-        <v>0.8982813954353333</v>
+        <v>0.7007809281349182</v>
       </c>
       <c r="E441" t="n">
-        <v>0.7046655035942778</v>
+        <v>0.6388320144941395</v>
       </c>
       <c r="F441" t="n">
         <v>1</v>
@@ -9483,13 +9483,13 @@
         <v>0.3562836353687553</v>
       </c>
       <c r="C442" t="n">
-        <v>0.4470473771108646</v>
+        <v>0.4470473771108645</v>
       </c>
       <c r="D442" t="n">
-        <v>0.7716215848922729</v>
+        <v>0.5258203148841858</v>
       </c>
       <c r="E442" t="n">
-        <v>0.5249841991239643</v>
+        <v>0.4430504424546018</v>
       </c>
       <c r="F442" t="n">
         <v>0</v>
@@ -9503,13 +9503,13 @@
         <v>0.6239040182987818</v>
       </c>
       <c r="C443" t="n">
-        <v>0.6026311141473919</v>
+        <v>0.6026311141473918</v>
       </c>
       <c r="D443" t="n">
-        <v>0.9312773942947388</v>
+        <v>0.7240750193595886</v>
       </c>
       <c r="E443" t="n">
-        <v>0.7192708422469708</v>
+        <v>0.6502033839352541</v>
       </c>
       <c r="F443" t="n">
         <v>1</v>
@@ -9526,10 +9526,10 @@
         <v>0.9004654559839228</v>
       </c>
       <c r="D444" t="n">
-        <v>0.9971410632133484</v>
+        <v>0.8072708249092102</v>
       </c>
       <c r="E444" t="n">
-        <v>0.9238369017873297</v>
+        <v>0.8605468223526169</v>
       </c>
       <c r="F444" t="n">
         <v>1</v>
@@ -9543,13 +9543,13 @@
         <v>0.858736342979902</v>
       </c>
       <c r="C445" t="n">
-        <v>0.8335159636057975</v>
+        <v>0.8335159636057974</v>
       </c>
       <c r="D445" t="n">
-        <v>0.9922496676445007</v>
+        <v>0.793488621711731</v>
       </c>
       <c r="E445" t="n">
-        <v>0.8948339914100667</v>
+        <v>0.8285803094324767</v>
       </c>
       <c r="F445" t="n">
         <v>1</v>
@@ -9566,10 +9566,10 @@
         <v>0.8287411572927386</v>
       </c>
       <c r="D446" t="n">
-        <v>0.9875429272651672</v>
+        <v>0.7699500918388367</v>
       </c>
       <c r="E446" t="n">
-        <v>0.8901030683863084</v>
+        <v>0.8175721232441981</v>
       </c>
       <c r="F446" t="n">
         <v>1</v>
@@ -9586,10 +9586,10 @@
         <v>0.7806574793310066</v>
       </c>
       <c r="D447" t="n">
-        <v>0.9873068928718567</v>
+        <v>0.7780506014823914</v>
       </c>
       <c r="E447" t="n">
-        <v>0.8650181084238815</v>
+        <v>0.7952660112940597</v>
       </c>
       <c r="F447" t="n">
         <v>1</v>
@@ -9606,10 +9606,10 @@
         <v>0.6685473547061577</v>
       </c>
       <c r="D448" t="n">
-        <v>0.9827615022659302</v>
+        <v>0.7565871477127075</v>
       </c>
       <c r="E448" t="n">
-        <v>0.8205930775366429</v>
+        <v>0.7452016260189019</v>
       </c>
       <c r="F448" t="n">
         <v>1</v>
@@ -9626,10 +9626,10 @@
         <v>0.8291550998153276</v>
       </c>
       <c r="D449" t="n">
-        <v>0.987705409526825</v>
+        <v>0.7736541032791138</v>
       </c>
       <c r="E449" t="n">
-        <v>0.8918630362528926</v>
+        <v>0.820512600836989</v>
       </c>
       <c r="F449" t="n">
         <v>1</v>
@@ -9646,10 +9646,10 @@
         <v>0.7715708617829298</v>
       </c>
       <c r="D450" t="n">
-        <v>0.9866011738777161</v>
+        <v>0.7689077258110046</v>
       </c>
       <c r="E450" t="n">
-        <v>0.8656592064487701</v>
+        <v>0.7930947237598663</v>
       </c>
       <c r="F450" t="n">
         <v>1</v>
@@ -9666,10 +9666,10 @@
         <v>0.6244529473438611</v>
       </c>
       <c r="D451" t="n">
-        <v>0.9810260534286499</v>
+        <v>0.7432172298431396</v>
       </c>
       <c r="E451" t="n">
-        <v>0.7840338483113016</v>
+        <v>0.7047642404494648</v>
       </c>
       <c r="F451" t="n">
         <v>1</v>
@@ -9686,10 +9686,10 @@
         <v>0.5581548593975223</v>
       </c>
       <c r="D452" t="n">
-        <v>0.9914830923080444</v>
+        <v>0.7851336598396301</v>
       </c>
       <c r="E452" t="n">
-        <v>0.7523086189554703</v>
+        <v>0.6835254747993322</v>
       </c>
       <c r="F452" t="n">
         <v>1</v>
@@ -9706,10 +9706,10 @@
         <v>0.7900343587070606</v>
       </c>
       <c r="D453" t="n">
-        <v>0.9853440523147583</v>
+        <v>0.7829664945602417</v>
       </c>
       <c r="E453" t="n">
-        <v>0.8747339875906412</v>
+        <v>0.807274801672469</v>
       </c>
       <c r="F453" t="n">
         <v>1</v>
@@ -9726,10 +9726,10 @@
         <v>0.8727687094200464</v>
       </c>
       <c r="D454" t="n">
-        <v>0.9910991787910461</v>
+        <v>0.7853988409042358</v>
       </c>
       <c r="E454" t="n">
-        <v>0.9125071165661205</v>
+        <v>0.8439403372705171</v>
       </c>
       <c r="F454" t="n">
         <v>1</v>
@@ -9746,10 +9746,10 @@
         <v>0.8595648567249625</v>
       </c>
       <c r="D455" t="n">
-        <v>0.9974894523620605</v>
+        <v>0.7987179756164551</v>
       </c>
       <c r="E455" t="n">
-        <v>0.8993504866071653</v>
+        <v>0.8330933276919635</v>
       </c>
       <c r="F455" t="n">
         <v>1</v>
@@ -9766,10 +9766,10 @@
         <v>0.8748318617716411</v>
       </c>
       <c r="D456" t="n">
-        <v>0.9948153495788574</v>
+        <v>0.7927104830741882</v>
       </c>
       <c r="E456" t="n">
-        <v>0.9088335152825185</v>
+        <v>0.8414652264476289</v>
       </c>
       <c r="F456" t="n">
         <v>1</v>
@@ -9783,13 +9783,13 @@
         <v>0.7841315385970687</v>
       </c>
       <c r="C457" t="n">
-        <v>0.7429713629347702</v>
+        <v>0.7429713629347701</v>
       </c>
       <c r="D457" t="n">
-        <v>0.992911159992218</v>
+        <v>0.7789515852928162</v>
       </c>
       <c r="E457" t="n">
-        <v>0.8400046871746856</v>
+        <v>0.7686848289415517</v>
       </c>
       <c r="F457" t="n">
         <v>1</v>
@@ -9803,13 +9803,13 @@
         <v>0.810431171330606</v>
       </c>
       <c r="C458" t="n">
-        <v>0.7576538612573916</v>
+        <v>0.7576538612573918</v>
       </c>
       <c r="D458" t="n">
-        <v>0.9853591918945312</v>
+        <v>0.7600257992744446</v>
       </c>
       <c r="E458" t="n">
-        <v>0.8511480748275096</v>
+        <v>0.7760369439541476</v>
       </c>
       <c r="F458" t="n">
         <v>1</v>
@@ -9823,13 +9823,13 @@
         <v>0.8471574113220812</v>
       </c>
       <c r="C459" t="n">
-        <v>0.8614416402453049</v>
+        <v>0.8614416402453047</v>
       </c>
       <c r="D459" t="n">
-        <v>0.997148871421814</v>
+        <v>0.7954535484313965</v>
       </c>
       <c r="E459" t="n">
-        <v>0.9019159743297335</v>
+        <v>0.8346841999995941</v>
       </c>
       <c r="F459" t="n">
         <v>1</v>
@@ -9846,10 +9846,10 @@
         <v>0.7661670651755109</v>
       </c>
       <c r="D460" t="n">
-        <v>0.9968263506889343</v>
+        <v>0.7902936935424805</v>
       </c>
       <c r="E460" t="n">
-        <v>0.8511304541126045</v>
+        <v>0.7822862350637866</v>
       </c>
       <c r="F460" t="n">
         <v>1</v>
@@ -9866,10 +9866,10 @@
         <v>0.8099725594903948</v>
       </c>
       <c r="D461" t="n">
-        <v>0.9973225593566895</v>
+        <v>0.7895039319992065</v>
       </c>
       <c r="E461" t="n">
-        <v>0.8811265121948062</v>
+        <v>0.8118536364089786</v>
       </c>
       <c r="F461" t="n">
         <v>1</v>
@@ -9883,13 +9883,13 @@
         <v>0.7909289415046126</v>
       </c>
       <c r="C462" t="n">
-        <v>0.7954073643862394</v>
+        <v>0.7954073643862392</v>
       </c>
       <c r="D462" t="n">
-        <v>0.9953752756118774</v>
+        <v>0.7880520820617676</v>
       </c>
       <c r="E462" t="n">
-        <v>0.8605705271675764</v>
+        <v>0.7914627959842063</v>
       </c>
       <c r="F462" t="n">
         <v>1</v>
@@ -9906,10 +9906,10 @@
         <v>0.8184966413426482</v>
       </c>
       <c r="D463" t="n">
-        <v>0.9910047650337219</v>
+        <v>0.7825732231140137</v>
       </c>
       <c r="E463" t="n">
-        <v>0.8726997632251496</v>
+        <v>0.8032225825852469</v>
       </c>
       <c r="F463" t="n">
         <v>1</v>
@@ -9926,10 +9926,10 @@
         <v>0.7328605791333827</v>
       </c>
       <c r="D464" t="n">
-        <v>0.9912261962890625</v>
+        <v>0.7745461463928223</v>
       </c>
       <c r="E464" t="n">
-        <v>0.8299889803944535</v>
+        <v>0.7577622970957067</v>
       </c>
       <c r="F464" t="n">
         <v>1</v>
@@ -9946,10 +9946,10 @@
         <v>0.8355287317066251</v>
       </c>
       <c r="D465" t="n">
-        <v>0.9947642087936401</v>
+        <v>0.789063572883606</v>
       </c>
       <c r="E465" t="n">
-        <v>0.8857059743279035</v>
+        <v>0.8171390956912256</v>
       </c>
       <c r="F465" t="n">
         <v>1</v>
@@ -9963,13 +9963,13 @@
         <v>0.8580287715428445</v>
       </c>
       <c r="C466" t="n">
-        <v>0.8587135178737588</v>
+        <v>0.858713517873759</v>
       </c>
       <c r="D466" t="n">
-        <v>0.9938785433769226</v>
+        <v>0.7875449657440186</v>
       </c>
       <c r="E466" t="n">
-        <v>0.9035402775978421</v>
+        <v>0.834762418386874</v>
       </c>
       <c r="F466" t="n">
         <v>1</v>
@@ -9986,10 +9986,10 @@
         <v>0.6697785509851986</v>
       </c>
       <c r="D467" t="n">
-        <v>0.9852485656738281</v>
+        <v>0.7839639186859131</v>
       </c>
       <c r="E467" t="n">
-        <v>0.8169132487227313</v>
+        <v>0.7498183663934262</v>
       </c>
       <c r="F467" t="n">
         <v>1</v>
@@ -10006,7 +10006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10031,10 +10031,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1.044206209664934</v>
+        <v>0.8856821778115261</v>
       </c>
       <c r="C2" t="n">
-        <v>0.769503241509534</v>
+        <v>0.7995402010639061</v>
       </c>
     </row>
     <row r="3">
@@ -10042,10 +10042,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7230172553758942</v>
+        <v>0.782549448562472</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6233094857649857</v>
+        <v>0.7666234725646759</v>
       </c>
     </row>
     <row r="4">
@@ -10053,10 +10053,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6193679700406749</v>
+        <v>0.7287266377652629</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5694773940557845</v>
+        <v>0.6898145545734449</v>
       </c>
     </row>
     <row r="5">
@@ -10064,10 +10064,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5495134353637696</v>
+        <v>0.6845626342162657</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5094320876544781</v>
+        <v>0.634567572226685</v>
       </c>
     </row>
     <row r="6">
@@ -10075,10 +10075,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5109713946165664</v>
+        <v>0.6310806964890341</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4929476224304585</v>
+        <v>0.6040634284528454</v>
       </c>
     </row>
     <row r="7">
@@ -10086,10 +10086,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4695689865377513</v>
+        <v>0.6171733927860689</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4684430891208435</v>
+        <v>0.5598342985249636</v>
       </c>
     </row>
     <row r="8">
@@ -10097,10 +10097,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4364123725321855</v>
+        <v>0.584209836266014</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4702688049064593</v>
+        <v>0.5326784619454588</v>
       </c>
     </row>
     <row r="9">
@@ -10108,10 +10108,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4276875427599703</v>
+        <v>0.555739258983162</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4375419649515259</v>
+        <v>0.5076197940646932</v>
       </c>
     </row>
     <row r="10">
@@ -10119,10 +10119,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.418151169747449</v>
+        <v>0.556184876835748</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4303729264086552</v>
+        <v>0.4853429804022392</v>
       </c>
     </row>
     <row r="11">
@@ -10130,10 +10130,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3649108654746179</v>
+        <v>0.5381809360860438</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4318101511577542</v>
+        <v>0.4804285410414921</v>
       </c>
     </row>
     <row r="12">
@@ -10141,10 +10141,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3654006751735558</v>
+        <v>0.5347406586234489</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4379754502284394</v>
+        <v>0.4780707490578126</v>
       </c>
     </row>
     <row r="13">
@@ -10152,10 +10152,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3414933017716649</v>
+        <v>0.5186462334702524</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4315076377284662</v>
+        <v>0.4837921358896106</v>
       </c>
     </row>
     <row r="14">
@@ -10163,10 +10163,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3376353159379423</v>
+        <v>0.4960650062962865</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4239523951257214</v>
+        <v>0.4748103499412537</v>
       </c>
     </row>
     <row r="15">
@@ -10174,10 +10174,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3191742117401589</v>
+        <v>0.4874207921242446</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4288563370537222</v>
+        <v>0.4813820487997506</v>
       </c>
     </row>
     <row r="16">
@@ -10185,10 +10185,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3043580925866459</v>
+        <v>0.4979473606254278</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4219484862316861</v>
+        <v>0.5027770448936505</v>
       </c>
     </row>
     <row r="17">
@@ -10196,10 +10196,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3012673345509539</v>
+        <v>0.4867424892240696</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4497973667436772</v>
+        <v>0.4830610666717036</v>
       </c>
     </row>
     <row r="18">
@@ -10207,10 +10207,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3013085873274321</v>
+        <v>0.4934830490457878</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4332302805413021</v>
+        <v>0.5025295873873689</v>
       </c>
     </row>
     <row r="19">
@@ -10218,10 +10218,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2965478926311048</v>
+        <v>0.4990866527463614</v>
       </c>
       <c r="C19" t="n">
-        <v>0.438092730152473</v>
+        <v>0.4865897193383635</v>
       </c>
     </row>
     <row r="20">
@@ -10229,10 +10229,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2661777645014645</v>
+        <v>0.4913674529014009</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4213056752018714</v>
+        <v>0.4752781791298578</v>
       </c>
     </row>
     <row r="21">
@@ -10240,10 +10240,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2764481553535783</v>
+        <v>0.478497019744991</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4417044958204366</v>
+        <v>0.4807237056533943</v>
       </c>
     </row>
     <row r="22">
@@ -10251,10 +10251,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2677557633164224</v>
+        <v>0.4743289288844956</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4413387594681778</v>
+        <v>0.4805260367607803</v>
       </c>
     </row>
     <row r="23">
@@ -10262,10 +10262,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2555089941520369</v>
+        <v>0.4709268046563931</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4421000341853399</v>
+        <v>0.4792891276351522</v>
       </c>
     </row>
     <row r="24">
@@ -10273,10 +10273,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.248875933249345</v>
+        <v>0.478598833820793</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4253686194590638</v>
+        <v>0.4781403022870589</v>
       </c>
     </row>
     <row r="25">
@@ -10284,10 +10284,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.2431997255913997</v>
+        <v>0.4721910068158354</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4675014374882317</v>
+        <v>0.4866854560844015</v>
       </c>
     </row>
     <row r="26">
@@ -10295,10 +10295,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.2442603400416588</v>
+        <v>0.4611518743332852</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4522779984085747</v>
+        <v>0.4846324797426717</v>
       </c>
     </row>
     <row r="27">
@@ -10306,10 +10306,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.2430411805681298</v>
+        <v>0.4598080880521389</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4498458131310645</v>
+        <v>0.4851457293783681</v>
       </c>
     </row>
     <row r="28">
@@ -10317,10 +10317,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.2441429082680954</v>
+        <v>0.4578185847803448</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4394768445009595</v>
+        <v>0.4839797080232856</v>
       </c>
     </row>
     <row r="29">
@@ -10328,10 +10328,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.2410513938143012</v>
+        <v>0.4577920662553123</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4327580008279072</v>
+        <v>0.4856436386537016</v>
       </c>
     </row>
     <row r="30">
@@ -10339,10 +10339,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.2483993779574887</v>
+        <v>0.4563811571745391</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4338363771693091</v>
+        <v>0.4820668214157727</v>
       </c>
     </row>
     <row r="31">
@@ -10350,10 +10350,54 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.2473465650436583</v>
+        <v>0.4566563647784544</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4392708816555109</v>
+        <v>0.4857356425081746</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.4604611869608418</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.485205658399657</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.45966348413671</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.4899283707141876</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.4581139562505016</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.4865396269251791</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.4567028188973331</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.4866133059343595</v>
       </c>
     </row>
   </sheetData>

--- a/ensemble/eval_results/ensemble_eval_result.xlsx
+++ b/ensemble/eval_results/ensemble_eval_result.xlsx
@@ -683,7 +683,7 @@
         <v>0.4538978081862282</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3840620868297284</v>
+        <v>0.3840620868297285</v>
       </c>
       <c r="D2" t="n">
         <v>0.5480184555053711</v>
@@ -1023,7 +1023,7 @@
         <v>0.4501171343442</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3300317782652732</v>
+        <v>0.3300317782652731</v>
       </c>
       <c r="D19" t="n">
         <v>0.2882517576217651</v>
@@ -1163,7 +1163,7 @@
         <v>0.2503107923620951</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2108669414302069</v>
+        <v>0.2108669414302068</v>
       </c>
       <c r="D26" t="n">
         <v>0.1171558499336243</v>
@@ -1183,7 +1183,7 @@
         <v>0.1350564249621374</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1522052698006218</v>
+        <v>0.1522052698006219</v>
       </c>
       <c r="D27" t="n">
         <v>0.07286187261343002</v>
@@ -1343,13 +1343,13 @@
         <v>0.5733300892086813</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4028275028754815</v>
+        <v>0.4028275028754816</v>
       </c>
       <c r="D35" t="n">
         <v>0.6872636675834656</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5544737532225428</v>
+        <v>0.5544737532225429</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -1563,7 +1563,7 @@
         <v>0.1695897593892664</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2378057669481436</v>
+        <v>0.2378057669481435</v>
       </c>
       <c r="D46" t="n">
         <v>0.1149958819150925</v>
@@ -1583,7 +1583,7 @@
         <v>0.3239137255701512</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2457921807875106</v>
+        <v>0.2457921807875107</v>
       </c>
       <c r="D47" t="n">
         <v>0.1190437525510788</v>
@@ -1683,7 +1683,7 @@
         <v>0.6082610657672887</v>
       </c>
       <c r="C52" t="n">
-        <v>0.390087567199013</v>
+        <v>0.3900875671990131</v>
       </c>
       <c r="D52" t="n">
         <v>0.4760576784610748</v>
@@ -2009,7 +2009,7 @@
         <v>0.07480202615261078</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1529666798417514</v>
+        <v>0.1529666798417513</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
         <v>0.1253760391814873</v>
       </c>
       <c r="C71" t="n">
-        <v>0.132573833529041</v>
+        <v>0.1325738335290409</v>
       </c>
       <c r="D71" t="n">
         <v>0.02854494377970695</v>
@@ -2163,7 +2163,7 @@
         <v>0.2488343744699408</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1892112707317714</v>
+        <v>0.1892112707317715</v>
       </c>
       <c r="D76" t="n">
         <v>0.03315313532948494</v>
@@ -2283,13 +2283,13 @@
         <v>0.3838290151127853</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3218228931227876</v>
+        <v>0.3218228931227875</v>
       </c>
       <c r="D82" t="n">
         <v>0.5310629606246948</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4122382896200893</v>
+        <v>0.4122382896200892</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
         <v>0.2824306744480671</v>
       </c>
       <c r="C89" t="n">
-        <v>0.1301902088386243</v>
+        <v>0.1301902088386244</v>
       </c>
       <c r="D89" t="n">
         <v>0.06094458699226379</v>
@@ -2583,7 +2583,7 @@
         <v>0.1200011740842674</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1595057475653788</v>
+        <v>0.1595057475653789</v>
       </c>
       <c r="D97" t="n">
         <v>0.04209328442811966</v>
@@ -2703,7 +2703,7 @@
         <v>0.2327777161843984</v>
       </c>
       <c r="C103" t="n">
-        <v>0.1760676424483896</v>
+        <v>0.1760676424483897</v>
       </c>
       <c r="D103" t="n">
         <v>0.06800888478755951</v>
@@ -2823,7 +2823,7 @@
         <v>0.2603288772160174</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2156516811085383</v>
+        <v>0.2156516811085384</v>
       </c>
       <c r="D109" t="n">
         <v>0.06313595920801163</v>
@@ -2943,7 +2943,7 @@
         <v>0.3215744765622564</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2423932088510731</v>
+        <v>0.2423932088510732</v>
       </c>
       <c r="D115" t="n">
         <v>0.09896806627511978</v>
@@ -3143,7 +3143,7 @@
         <v>0.1664674759613062</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1790466394075589</v>
+        <v>0.179046639407559</v>
       </c>
       <c r="D125" t="n">
         <v>0.03753819689154625</v>
@@ -3443,7 +3443,7 @@
         <v>0.2331993948741976</v>
       </c>
       <c r="C140" t="n">
-        <v>0.1673815682125459</v>
+        <v>0.167381568212546</v>
       </c>
       <c r="D140" t="n">
         <v>0.0735790953040123</v>
@@ -3723,7 +3723,7 @@
         <v>0.1783957571550112</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1691316468433854</v>
+        <v>0.1691316468433855</v>
       </c>
       <c r="D154" t="n">
         <v>0.131822258234024</v>
@@ -3749,7 +3749,7 @@
         <v>0.09174433350563049</v>
       </c>
       <c r="E155" t="n">
-        <v>0.166356924284507</v>
+        <v>0.1663569242845071</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0.138518206701358</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1586554795133839</v>
+        <v>0.158655479513384</v>
       </c>
       <c r="D157" t="n">
         <v>0.04647943004965782</v>
@@ -3863,7 +3863,7 @@
         <v>0.5776623423806377</v>
       </c>
       <c r="C161" t="n">
-        <v>0.2929229842412049</v>
+        <v>0.2929229842412048</v>
       </c>
       <c r="D161" t="n">
         <v>0.119443491101265</v>
@@ -3883,13 +3883,13 @@
         <v>0.1699331182172456</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1599006425528003</v>
+        <v>0.1599006425528004</v>
       </c>
       <c r="D162" t="n">
         <v>0.104073166847229</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1446356425390916</v>
+        <v>0.1446356425390917</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
         <v>0.2865348751146375</v>
       </c>
       <c r="C167" t="n">
-        <v>0.2446251107431703</v>
+        <v>0.2446251107431704</v>
       </c>
       <c r="D167" t="n">
         <v>0.1489203125238419</v>
@@ -4023,7 +4023,7 @@
         <v>0.3782075718991662</v>
       </c>
       <c r="C169" t="n">
-        <v>0.291444952216988</v>
+        <v>0.2914449522169881</v>
       </c>
       <c r="D169" t="n">
         <v>0.1138434186577797</v>
@@ -4483,7 +4483,7 @@
         <v>0.1954804148651044</v>
       </c>
       <c r="C192" t="n">
-        <v>0.1688192095890888</v>
+        <v>0.1688192095890889</v>
       </c>
       <c r="D192" t="n">
         <v>0.1357305943965912</v>
@@ -4709,7 +4709,7 @@
         <v>0.167051836848259</v>
       </c>
       <c r="E203" t="n">
-        <v>0.191498972112037</v>
+        <v>0.1914989721120369</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
         <v>0.2809907184533081</v>
       </c>
       <c r="C221" t="n">
-        <v>0.2482800606555355</v>
+        <v>0.2482800606555356</v>
       </c>
       <c r="D221" t="n">
         <v>0.1110203266143799</v>
@@ -5143,7 +5143,7 @@
         <v>0.4137265016073279</v>
       </c>
       <c r="C225" t="n">
-        <v>0.3678176128793121</v>
+        <v>0.3678176128793122</v>
       </c>
       <c r="D225" t="n">
         <v>0.3718783259391785</v>
@@ -5163,7 +5163,7 @@
         <v>0.421681055583582</v>
       </c>
       <c r="C226" t="n">
-        <v>0.3846254505714859</v>
+        <v>0.3846254505714858</v>
       </c>
       <c r="D226" t="n">
         <v>0.5614699125289917</v>
@@ -5363,7 +5363,7 @@
         <v>0.2970185547964772</v>
       </c>
       <c r="C236" t="n">
-        <v>0.1909047351971769</v>
+        <v>0.1909047351971768</v>
       </c>
       <c r="D236" t="n">
         <v>0.162515789270401</v>
@@ -5663,7 +5663,7 @@
         <v>0.2792796919928957</v>
       </c>
       <c r="C251" t="n">
-        <v>0.2611231350126407</v>
+        <v>0.2611231350126408</v>
       </c>
       <c r="D251" t="n">
         <v>0.09601052105426788</v>
@@ -5743,13 +5743,13 @@
         <v>0.2725856581182082</v>
       </c>
       <c r="C255" t="n">
-        <v>0.2502262604231769</v>
+        <v>0.2502262604231768</v>
       </c>
       <c r="D255" t="n">
         <v>0.1455259472131729</v>
       </c>
       <c r="E255" t="n">
-        <v>0.2227792885848527</v>
+        <v>0.2227792885848526</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -5863,13 +5863,13 @@
         <v>0.3890805583312117</v>
       </c>
       <c r="C261" t="n">
-        <v>0.3073905915730032</v>
+        <v>0.3073905915730033</v>
       </c>
       <c r="D261" t="n">
         <v>0.3155582845211029</v>
       </c>
       <c r="E261" t="n">
-        <v>0.3373431448084392</v>
+        <v>0.3373431448084394</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0.2684587172965865</v>
       </c>
       <c r="C265" t="n">
-        <v>0.2451078761413231</v>
+        <v>0.245107876141323</v>
       </c>
       <c r="D265" t="n">
         <v>0.211183100938797</v>
       </c>
       <c r="E265" t="n">
-        <v>0.2415832314589022</v>
+        <v>0.2415832314589021</v>
       </c>
       <c r="F265" t="n">
         <v>0</v>
@@ -6043,7 +6043,7 @@
         <v>0.2955514954491868</v>
       </c>
       <c r="C270" t="n">
-        <v>0.2502690299836345</v>
+        <v>0.2502690299836346</v>
       </c>
       <c r="D270" t="n">
         <v>0.1999837905168533</v>
@@ -6149,7 +6149,7 @@
         <v>0.12990902364254</v>
       </c>
       <c r="E275" t="n">
-        <v>0.1850713120648824</v>
+        <v>0.1850713120648825</v>
       </c>
       <c r="F275" t="n">
         <v>0</v>
@@ -6323,13 +6323,13 @@
         <v>0.7568156864178142</v>
       </c>
       <c r="C284" t="n">
-        <v>0.4490935707747755</v>
+        <v>0.4490935707747756</v>
       </c>
       <c r="D284" t="n">
         <v>0.4620886743068695</v>
       </c>
       <c r="E284" t="n">
-        <v>0.5559993104998197</v>
+        <v>0.5559993104998198</v>
       </c>
       <c r="F284" t="n">
         <v>1</v>
@@ -6343,7 +6343,7 @@
         <v>0.3557972288818013</v>
       </c>
       <c r="C285" t="n">
-        <v>0.2380236721138009</v>
+        <v>0.2380236721138008</v>
       </c>
       <c r="D285" t="n">
         <v>0.1098784953355789</v>
@@ -6383,7 +6383,7 @@
         <v>0.6307942581508617</v>
       </c>
       <c r="C287" t="n">
-        <v>0.4315749329320095</v>
+        <v>0.4315749329320096</v>
       </c>
       <c r="D287" t="n">
         <v>0.6829118728637695</v>
@@ -6629,7 +6629,7 @@
         <v>0.1781473755836487</v>
       </c>
       <c r="E299" t="n">
-        <v>0.1572760647085383</v>
+        <v>0.1572760647085382</v>
       </c>
       <c r="F299" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
         <v>0.6020297703142017</v>
       </c>
       <c r="C301" t="n">
-        <v>0.4459142746254918</v>
+        <v>0.4459142746254919</v>
       </c>
       <c r="D301" t="n">
         <v>0.4878115057945251</v>
@@ -6723,7 +6723,7 @@
         <v>0.5030306303959471</v>
       </c>
       <c r="C304" t="n">
-        <v>0.3875461986572109</v>
+        <v>0.387546198657211</v>
       </c>
       <c r="D304" t="n">
         <v>0.3270591795444489</v>
@@ -6883,7 +6883,7 @@
         <v>0.2956139429909411</v>
       </c>
       <c r="C312" t="n">
-        <v>0.1856010182455337</v>
+        <v>0.1856010182455338</v>
       </c>
       <c r="D312" t="n">
         <v>0.1582192480564117</v>
@@ -6983,7 +6983,7 @@
         <v>0.2097969378868546</v>
       </c>
       <c r="C317" t="n">
-        <v>0.2561149226411029</v>
+        <v>0.256114922641103</v>
       </c>
       <c r="D317" t="n">
         <v>0.3014366626739502</v>
@@ -7023,7 +7023,7 @@
         <v>0.4900897603289248</v>
       </c>
       <c r="C319" t="n">
-        <v>0.3296289512356696</v>
+        <v>0.3296289512356697</v>
       </c>
       <c r="D319" t="n">
         <v>0.5925583243370056</v>
@@ -7063,7 +7063,7 @@
         <v>0.4132458347103894</v>
       </c>
       <c r="C321" t="n">
-        <v>0.2845608243306738</v>
+        <v>0.2845608243306739</v>
       </c>
       <c r="D321" t="n">
         <v>0.2736613154411316</v>
@@ -7089,7 +7089,7 @@
         <v>0.3746398985385895</v>
       </c>
       <c r="E322" t="n">
-        <v>0.3771774660111273</v>
+        <v>0.3771774660111274</v>
       </c>
       <c r="F322" t="n">
         <v>0</v>
@@ -7123,7 +7123,7 @@
         <v>0.3540002714859015</v>
       </c>
       <c r="C324" t="n">
-        <v>0.2274029563986385</v>
+        <v>0.2274029563986384</v>
       </c>
       <c r="D324" t="n">
         <v>0.1844043433666229</v>
@@ -7723,7 +7723,7 @@
         <v>0.2163744083428907</v>
       </c>
       <c r="C354" t="n">
-        <v>0.2440190853233989</v>
+        <v>0.2440190853233988</v>
       </c>
       <c r="D354" t="n">
         <v>0.1729945838451385</v>
@@ -7803,13 +7803,13 @@
         <v>0.5882286934495428</v>
       </c>
       <c r="C358" t="n">
-        <v>0.3595630951327165</v>
+        <v>0.3595630951327164</v>
       </c>
       <c r="D358" t="n">
         <v>0.4411697387695312</v>
       </c>
       <c r="E358" t="n">
-        <v>0.4629871757839302</v>
+        <v>0.4629871757839301</v>
       </c>
       <c r="F358" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
         <v>0.592594630431325</v>
       </c>
       <c r="C359" t="n">
-        <v>0.4263509213265251</v>
+        <v>0.4263509213265252</v>
       </c>
       <c r="D359" t="n">
         <v>0.1660622805356979</v>
@@ -8009,7 +8009,7 @@
         <v>0.1057377681136131</v>
       </c>
       <c r="E368" t="n">
-        <v>0.2730766966585138</v>
+        <v>0.2730766966585137</v>
       </c>
       <c r="F368" t="n">
         <v>0</v>
@@ -8089,7 +8089,7 @@
         <v>0.05858550220727921</v>
       </c>
       <c r="E372" t="n">
-        <v>0.1193574672686906</v>
+        <v>0.1193574672686907</v>
       </c>
       <c r="F372" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
         <v>0.4385193931910839</v>
       </c>
       <c r="C380" t="n">
-        <v>0.3951778616586796</v>
+        <v>0.3951778616586797</v>
       </c>
       <c r="D380" t="n">
         <v>0.5299926400184631</v>
@@ -8263,7 +8263,7 @@
         <v>0.3145057088931605</v>
       </c>
       <c r="C381" t="n">
-        <v>0.3056208754025039</v>
+        <v>0.305620875402504</v>
       </c>
       <c r="D381" t="n">
         <v>0.5034465789794922</v>
@@ -8289,7 +8289,7 @@
         <v>0.1385198980569839</v>
       </c>
       <c r="E382" t="n">
-        <v>0.1939961169609977</v>
+        <v>0.1939961169609978</v>
       </c>
       <c r="F382" t="n">
         <v>0</v>
@@ -8483,13 +8483,13 @@
         <v>0.6932223680809925</v>
       </c>
       <c r="C392" t="n">
-        <v>0.4728141752586971</v>
+        <v>0.472814175258697</v>
       </c>
       <c r="D392" t="n">
         <v>0.7170804738998413</v>
       </c>
       <c r="E392" t="n">
-        <v>0.627705672413177</v>
+        <v>0.6277056724131769</v>
       </c>
       <c r="F392" t="n">
         <v>1</v>
@@ -8563,7 +8563,7 @@
         <v>0.6531456108684935</v>
       </c>
       <c r="C396" t="n">
-        <v>0.5562953687400906</v>
+        <v>0.5562953687400907</v>
       </c>
       <c r="D396" t="n">
         <v>0.5934635996818542</v>
@@ -8603,7 +8603,7 @@
         <v>0.8284934443638365</v>
       </c>
       <c r="C398" t="n">
-        <v>0.7220806178522101</v>
+        <v>0.72208061785221</v>
       </c>
       <c r="D398" t="n">
         <v>0.7797842025756836</v>
@@ -8683,7 +8683,7 @@
         <v>0.7418033458940942</v>
       </c>
       <c r="C402" t="n">
-        <v>0.7574872279660374</v>
+        <v>0.7574872279660375</v>
       </c>
       <c r="D402" t="n">
         <v>0.7469063401222229</v>
@@ -8703,7 +8703,7 @@
         <v>0.7864841878944848</v>
       </c>
       <c r="C403" t="n">
-        <v>0.7936473596863918</v>
+        <v>0.7936473596863917</v>
       </c>
       <c r="D403" t="n">
         <v>0.7636206150054932</v>
@@ -8763,13 +8763,13 @@
         <v>0.7263824412054082</v>
       </c>
       <c r="C406" t="n">
-        <v>0.7479820533627247</v>
+        <v>0.7479820533627248</v>
       </c>
       <c r="D406" t="n">
         <v>0.7600780725479126</v>
       </c>
       <c r="E406" t="n">
-        <v>0.7448141890386818</v>
+        <v>0.7448141890386819</v>
       </c>
       <c r="F406" t="n">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>0.7133755643709148</v>
       </c>
       <c r="C409" t="n">
-        <v>0.6039945885371903</v>
+        <v>0.6039945885371905</v>
       </c>
       <c r="D409" t="n">
         <v>0.7675989866256714</v>
@@ -9003,13 +9003,13 @@
         <v>0.8626745395287253</v>
       </c>
       <c r="C418" t="n">
-        <v>0.8686777703504157</v>
+        <v>0.8686777703504156</v>
       </c>
       <c r="D418" t="n">
         <v>0.7717434763908386</v>
       </c>
       <c r="E418" t="n">
-        <v>0.8343652620899933</v>
+        <v>0.8343652620899932</v>
       </c>
       <c r="F418" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
         <v>0.7791690767823022</v>
       </c>
       <c r="C420" t="n">
-        <v>0.6517866745386142</v>
+        <v>0.6517866745386143</v>
       </c>
       <c r="D420" t="n">
         <v>0.7627346515655518</v>
@@ -9143,13 +9143,13 @@
         <v>0.8482116567794409</v>
       </c>
       <c r="C425" t="n">
-        <v>0.831284053472201</v>
+        <v>0.8312840534722012</v>
       </c>
       <c r="D425" t="n">
         <v>0.8001583814620972</v>
       </c>
       <c r="E425" t="n">
-        <v>0.8265513639045796</v>
+        <v>0.8265513639045797</v>
       </c>
       <c r="F425" t="n">
         <v>1</v>
@@ -9163,7 +9163,7 @@
         <v>0.8413484292096403</v>
       </c>
       <c r="C426" t="n">
-        <v>0.8115896037647705</v>
+        <v>0.8115896037647703</v>
       </c>
       <c r="D426" t="n">
         <v>0.7865818738937378</v>
@@ -9223,7 +9223,7 @@
         <v>0.7409991849871445</v>
       </c>
       <c r="C429" t="n">
-        <v>0.7199336933378517</v>
+        <v>0.7199336933378518</v>
       </c>
       <c r="D429" t="n">
         <v>0.75993812084198</v>
@@ -9263,7 +9263,7 @@
         <v>0.7361939037605112</v>
       </c>
       <c r="C431" t="n">
-        <v>0.7198258502273461</v>
+        <v>0.7198258502273462</v>
       </c>
       <c r="D431" t="n">
         <v>0.7525700330734253</v>
@@ -9323,7 +9323,7 @@
         <v>0.7752135500054844</v>
       </c>
       <c r="C434" t="n">
-        <v>0.7627177089442388</v>
+        <v>0.762717708944239</v>
       </c>
       <c r="D434" t="n">
         <v>0.7499321699142456</v>
@@ -9403,7 +9403,7 @@
         <v>0.8211970199838354</v>
       </c>
       <c r="C438" t="n">
-        <v>0.800931950076599</v>
+        <v>0.8009319500765992</v>
       </c>
       <c r="D438" t="n">
         <v>0.795230507850647</v>
@@ -9423,7 +9423,7 @@
         <v>0.8134696906291824</v>
       </c>
       <c r="C439" t="n">
-        <v>0.7926208262448645</v>
+        <v>0.7926208262448644</v>
       </c>
       <c r="D439" t="n">
         <v>0.7631657123565674</v>
@@ -9443,7 +9443,7 @@
         <v>0.7885729067093337</v>
       </c>
       <c r="C440" t="n">
-        <v>0.7815909786712013</v>
+        <v>0.7815909786712015</v>
       </c>
       <c r="D440" t="n">
         <v>0.7848934531211853</v>
@@ -9503,7 +9503,7 @@
         <v>0.6239040182987818</v>
       </c>
       <c r="C443" t="n">
-        <v>0.6026311141473918</v>
+        <v>0.6026311141473919</v>
       </c>
       <c r="D443" t="n">
         <v>0.7240750193595886</v>
@@ -9523,13 +9523,13 @@
         <v>0.8739041861647179</v>
       </c>
       <c r="C444" t="n">
-        <v>0.9004654559839228</v>
+        <v>0.9004654559839229</v>
       </c>
       <c r="D444" t="n">
         <v>0.8072708249092102</v>
       </c>
       <c r="E444" t="n">
-        <v>0.8605468223526169</v>
+        <v>0.860546822352617</v>
       </c>
       <c r="F444" t="n">
         <v>1</v>
@@ -9583,7 +9583,7 @@
         <v>0.827089953068781</v>
       </c>
       <c r="C447" t="n">
-        <v>0.7806574793310066</v>
+        <v>0.7806574793310067</v>
       </c>
       <c r="D447" t="n">
         <v>0.7780506014823914</v>
@@ -9683,13 +9683,13 @@
         <v>0.7072879051608444</v>
       </c>
       <c r="C452" t="n">
-        <v>0.5581548593975223</v>
+        <v>0.5581548593975224</v>
       </c>
       <c r="D452" t="n">
         <v>0.7851336598396301</v>
       </c>
       <c r="E452" t="n">
-        <v>0.6835254747993322</v>
+        <v>0.6835254747993323</v>
       </c>
       <c r="F452" t="n">
         <v>1</v>
@@ -9783,13 +9783,13 @@
         <v>0.7841315385970687</v>
       </c>
       <c r="C457" t="n">
-        <v>0.7429713629347701</v>
+        <v>0.7429713629347703</v>
       </c>
       <c r="D457" t="n">
         <v>0.7789515852928162</v>
       </c>
       <c r="E457" t="n">
-        <v>0.7686848289415517</v>
+        <v>0.7686848289415518</v>
       </c>
       <c r="F457" t="n">
         <v>1</v>
@@ -9883,13 +9883,13 @@
         <v>0.7909289415046126</v>
       </c>
       <c r="C462" t="n">
-        <v>0.7954073643862392</v>
+        <v>0.7954073643862394</v>
       </c>
       <c r="D462" t="n">
         <v>0.7880520820617676</v>
       </c>
       <c r="E462" t="n">
-        <v>0.7914627959842063</v>
+        <v>0.7914627959842065</v>
       </c>
       <c r="F462" t="n">
         <v>1</v>
